--- a/data/spike.xlsx
+++ b/data/spike.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phbro\Desktop\DOCUMENTS\ActuRank\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC6FA50-B278-46E4-BB28-CE0C6C8B6473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4AC837-1345-4EE9-B6E5-503C67BC7EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="66">
   <si>
     <t>players</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>31/10/2024</t>
+  </si>
+  <si>
+    <t>05/05/2025</t>
   </si>
 </sst>
 </file>
@@ -3367,7 +3370,7 @@
         <v>11</v>
       </c>
       <c r="E68" s="1">
-        <f t="shared" ref="E68:E94" si="2">IF(F68&gt;G68,1,0)</f>
+        <f t="shared" ref="E68:E120" si="2">IF(F68&gt;G68,1,0)</f>
         <v>1</v>
       </c>
       <c r="F68" s="5">
@@ -3384,7 +3387,7 @@
       </c>
       <c r="J68" s="1"/>
       <c r="K68" s="9" t="str">
-        <f t="shared" ref="K68:K94" si="3">IF(OR(OR(AND(OR(A68=B68,A68=C68,A68=D68,B68=C68,B68=D68,C68=D68),OR(A68&lt;&gt;"",D68&lt;&gt;"")),H68&gt;MAX(F68:G68),B68=C68),OR(AND(ISBLANK(A68)=FALSE,ISNA(VLOOKUP(A68,$M$3:$O$27,1,FALSE))),ISNA(VLOOKUP(B68,$M$3:$O$27,1,FALSE)),ISNA(VLOOKUP(C68,$M$3:$O$27,1,FALSE)),AND(ISBLANK(D68)=FALSE,ISNA(VLOOKUP(D68,$M$3:$O$27,1,FALSE))),OR(COUNTBLANK(A68:D68)=1,COUNTBLANK(A68:D68)=3))),"ERREUR","")</f>
+        <f t="shared" ref="K68:K120" si="3">IF(OR(OR(AND(OR(A68=B68,A68=C68,A68=D68,B68=C68,B68=D68,C68=D68),OR(A68&lt;&gt;"",D68&lt;&gt;"")),H68&gt;MAX(F68:G68),B68=C68),OR(AND(ISBLANK(A68)=FALSE,ISNA(VLOOKUP(A68,$M$3:$O$27,1,FALSE))),ISNA(VLOOKUP(B68,$M$3:$O$27,1,FALSE)),ISNA(VLOOKUP(C68,$M$3:$O$27,1,FALSE)),AND(ISBLANK(D68)=FALSE,ISNA(VLOOKUP(D68,$M$3:$O$27,1,FALSE))),OR(COUNTBLANK(A68:D68)=1,COUNTBLANK(A68:D68)=3))),"ERREUR","")</f>
         <v/>
       </c>
       <c r="L68" s="1"/>
@@ -4407,442 +4410,1014 @@
       <c r="O94" s="1"/>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="7"/>
-      <c r="D95" s="7"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="5"/>
-      <c r="G95" s="5"/>
-      <c r="H95" s="1"/>
-      <c r="I95" s="1"/>
+      <c r="A95" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E95" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F95" s="5">
+        <v>8</v>
+      </c>
+      <c r="G95" s="5">
+        <v>6</v>
+      </c>
+      <c r="H95" s="1">
+        <v>7</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J95" s="1"/>
-      <c r="K95" s="9"/>
+      <c r="K95" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L95" s="1"/>
       <c r="M95" s="1"/>
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6"/>
-      <c r="C96" s="7"/>
-      <c r="D96" s="7"/>
-      <c r="E96" s="1"/>
-      <c r="F96" s="5"/>
-      <c r="G96" s="5"/>
-      <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
+      <c r="A96" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E96" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F96" s="5">
+        <v>8</v>
+      </c>
+      <c r="G96" s="5">
+        <v>6</v>
+      </c>
+      <c r="H96" s="1">
+        <v>7</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J96" s="1"/>
-      <c r="K96" s="9"/>
+      <c r="K96" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L96" s="1"/>
       <c r="M96" s="1"/>
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="7"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="1"/>
-      <c r="F97" s="5"/>
-      <c r="G97" s="5"/>
-      <c r="H97" s="1"/>
-      <c r="I97" s="1"/>
+      <c r="A97" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E97" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F97" s="5">
+        <v>7</v>
+      </c>
+      <c r="G97" s="5">
+        <v>5</v>
+      </c>
+      <c r="H97" s="1">
+        <v>7</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J97" s="1"/>
-      <c r="K97" s="9"/>
+      <c r="K97" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L97" s="1"/>
       <c r="M97" s="1"/>
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="7"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="1"/>
-      <c r="F98" s="5"/>
-      <c r="G98" s="5"/>
-      <c r="H98" s="1"/>
-      <c r="I98" s="1"/>
+      <c r="A98" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E98" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F98" s="5">
+        <v>7</v>
+      </c>
+      <c r="G98" s="5">
+        <v>0</v>
+      </c>
+      <c r="H98" s="1">
+        <v>7</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J98" s="1"/>
-      <c r="K98" s="9"/>
+      <c r="K98" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L98" s="1"/>
       <c r="M98" s="1"/>
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A99" s="6"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="7"/>
-      <c r="D99" s="7"/>
-      <c r="E99" s="1"/>
-      <c r="F99" s="5"/>
-      <c r="G99" s="5"/>
-      <c r="H99" s="1"/>
-      <c r="I99" s="1"/>
+      <c r="A99" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E99" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F99" s="5">
+        <v>7</v>
+      </c>
+      <c r="G99" s="5">
+        <v>2</v>
+      </c>
+      <c r="H99" s="1">
+        <v>7</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J99" s="1"/>
-      <c r="K99" s="9"/>
+      <c r="K99" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L99" s="1"/>
       <c r="M99" s="1"/>
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A100" s="6"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="7"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="1"/>
-      <c r="F100" s="5"/>
-      <c r="G100" s="5"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
+      <c r="A100" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F100" s="5">
+        <v>7</v>
+      </c>
+      <c r="G100" s="5">
+        <v>5</v>
+      </c>
+      <c r="H100" s="1">
+        <v>7</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J100" s="1"/>
-      <c r="K100" s="9"/>
+      <c r="K100" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L100" s="1"/>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
       <c r="O100" s="1"/>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A101" s="6"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="7"/>
-      <c r="D101" s="7"/>
-      <c r="E101" s="1"/>
-      <c r="F101" s="5"/>
-      <c r="G101" s="5"/>
-      <c r="H101" s="1"/>
-      <c r="I101" s="1"/>
+      <c r="A101" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E101" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F101" s="5">
+        <v>7</v>
+      </c>
+      <c r="G101" s="5">
+        <v>4</v>
+      </c>
+      <c r="H101" s="1">
+        <v>7</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J101" s="1"/>
-      <c r="K101" s="9"/>
+      <c r="K101" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L101" s="1"/>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A102" s="6"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="7"/>
-      <c r="D102" s="7"/>
-      <c r="E102" s="1"/>
-      <c r="F102" s="5"/>
-      <c r="G102" s="5"/>
-      <c r="H102" s="1"/>
-      <c r="I102" s="1"/>
+      <c r="A102" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F102" s="5">
+        <v>7</v>
+      </c>
+      <c r="G102" s="5">
+        <v>4</v>
+      </c>
+      <c r="H102" s="1">
+        <v>7</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J102" s="1"/>
-      <c r="K102" s="9"/>
+      <c r="K102" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L102" s="1"/>
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
       <c r="O102" s="1"/>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="7"/>
-      <c r="D103" s="7"/>
-      <c r="E103" s="1"/>
-      <c r="F103" s="5"/>
-      <c r="G103" s="5"/>
-      <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
+      <c r="A103" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E103" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F103" s="5">
+        <v>7</v>
+      </c>
+      <c r="G103" s="5">
+        <v>4</v>
+      </c>
+      <c r="H103" s="1">
+        <v>7</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J103" s="1"/>
-      <c r="K103" s="9"/>
+      <c r="K103" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L103" s="1"/>
       <c r="M103" s="1"/>
       <c r="N103" s="1"/>
       <c r="O103" s="1"/>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6"/>
-      <c r="C104" s="7"/>
-      <c r="D104" s="7"/>
-      <c r="E104" s="1"/>
-      <c r="F104" s="5"/>
-      <c r="G104" s="5"/>
-      <c r="H104" s="1"/>
-      <c r="I104" s="1"/>
+      <c r="A104" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E104" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F104" s="5">
+        <v>7</v>
+      </c>
+      <c r="G104" s="5">
+        <v>4</v>
+      </c>
+      <c r="H104" s="1">
+        <v>7</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J104" s="1"/>
-      <c r="K104" s="9"/>
+      <c r="K104" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L104" s="1"/>
       <c r="M104" s="1"/>
       <c r="N104" s="1"/>
       <c r="O104" s="1"/>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="7"/>
-      <c r="D105" s="7"/>
-      <c r="E105" s="1"/>
-      <c r="F105" s="5"/>
-      <c r="G105" s="5"/>
-      <c r="H105" s="1"/>
-      <c r="I105" s="1"/>
+      <c r="A105" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E105" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F105" s="5">
+        <v>7</v>
+      </c>
+      <c r="G105" s="5">
+        <v>0</v>
+      </c>
+      <c r="H105" s="1">
+        <v>7</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J105" s="1"/>
-      <c r="K105" s="9"/>
+      <c r="K105" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L105" s="1"/>
       <c r="M105" s="1"/>
       <c r="N105" s="1"/>
       <c r="O105" s="1"/>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A106" s="6"/>
-      <c r="B106" s="6"/>
-      <c r="C106" s="7"/>
-      <c r="D106" s="7"/>
-      <c r="E106" s="1"/>
-      <c r="F106" s="5"/>
-      <c r="G106" s="5"/>
-      <c r="H106" s="1"/>
-      <c r="I106" s="1"/>
+      <c r="A106" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E106" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F106" s="5">
+        <v>7</v>
+      </c>
+      <c r="G106" s="5">
+        <v>2</v>
+      </c>
+      <c r="H106" s="1">
+        <v>7</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J106" s="1"/>
-      <c r="K106" s="9"/>
+      <c r="K106" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L106" s="1"/>
       <c r="M106" s="1"/>
       <c r="N106" s="1"/>
       <c r="O106" s="1"/>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A107" s="6"/>
-      <c r="B107" s="6"/>
-      <c r="C107" s="7"/>
-      <c r="D107" s="7"/>
-      <c r="E107" s="1"/>
-      <c r="F107" s="5"/>
-      <c r="G107" s="5"/>
-      <c r="H107" s="1"/>
-      <c r="I107" s="1"/>
+      <c r="A107" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C107" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E107" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F107" s="5">
+        <v>7</v>
+      </c>
+      <c r="G107" s="5">
+        <v>3</v>
+      </c>
+      <c r="H107" s="1">
+        <v>7</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J107" s="1"/>
-      <c r="K107" s="9"/>
+      <c r="K107" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L107" s="1"/>
       <c r="M107" s="1"/>
       <c r="N107" s="1"/>
       <c r="O107" s="1"/>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A108" s="6"/>
-      <c r="B108" s="6"/>
-      <c r="C108" s="7"/>
-      <c r="D108" s="7"/>
-      <c r="E108" s="1"/>
-      <c r="F108" s="5"/>
-      <c r="G108" s="5"/>
-      <c r="H108" s="1"/>
-      <c r="I108" s="1"/>
+      <c r="A108" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E108" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F108" s="5">
+        <v>7</v>
+      </c>
+      <c r="G108" s="5">
+        <v>4</v>
+      </c>
+      <c r="H108" s="1">
+        <v>7</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J108" s="1"/>
-      <c r="K108" s="9"/>
+      <c r="K108" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L108" s="1"/>
       <c r="M108" s="1"/>
       <c r="N108" s="1"/>
       <c r="O108" s="1"/>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="7"/>
-      <c r="D109" s="7"/>
-      <c r="E109" s="1"/>
-      <c r="F109" s="5"/>
-      <c r="G109" s="5"/>
-      <c r="H109" s="1"/>
-      <c r="I109" s="1"/>
+      <c r="A109" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E109" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F109" s="5">
+        <v>7</v>
+      </c>
+      <c r="G109" s="5">
+        <v>4</v>
+      </c>
+      <c r="H109" s="1">
+        <v>7</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J109" s="1"/>
-      <c r="K109" s="9"/>
+      <c r="K109" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L109" s="1"/>
       <c r="M109" s="1"/>
       <c r="N109" s="1"/>
       <c r="O109" s="1"/>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A110" s="6"/>
-      <c r="B110" s="6"/>
-      <c r="C110" s="7"/>
-      <c r="D110" s="7"/>
-      <c r="E110" s="1"/>
-      <c r="F110" s="5"/>
-      <c r="G110" s="5"/>
-      <c r="H110" s="1"/>
-      <c r="I110" s="1"/>
+      <c r="A110" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E110" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F110" s="5">
+        <v>7</v>
+      </c>
+      <c r="G110" s="5">
+        <v>2</v>
+      </c>
+      <c r="H110" s="1">
+        <v>7</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J110" s="1"/>
-      <c r="K110" s="9"/>
+      <c r="K110" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L110" s="1"/>
       <c r="M110" s="1"/>
       <c r="N110" s="1"/>
       <c r="O110" s="1"/>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A111" s="6"/>
-      <c r="B111" s="6"/>
-      <c r="C111" s="7"/>
-      <c r="D111" s="7"/>
-      <c r="E111" s="1"/>
-      <c r="F111" s="5"/>
-      <c r="G111" s="5"/>
-      <c r="H111" s="1"/>
-      <c r="I111" s="1"/>
+      <c r="A111" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E111" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F111" s="5">
+        <v>7</v>
+      </c>
+      <c r="G111" s="5">
+        <v>3</v>
+      </c>
+      <c r="H111" s="1">
+        <v>7</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J111" s="1"/>
-      <c r="K111" s="9"/>
+      <c r="K111" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L111" s="1"/>
       <c r="M111" s="1"/>
       <c r="N111" s="1"/>
       <c r="O111" s="1"/>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A112" s="6"/>
-      <c r="B112" s="6"/>
-      <c r="C112" s="7"/>
-      <c r="D112" s="7"/>
-      <c r="E112" s="1"/>
-      <c r="F112" s="5"/>
-      <c r="G112" s="5"/>
-      <c r="H112" s="1"/>
-      <c r="I112" s="1"/>
+      <c r="A112" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E112" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F112" s="5">
+        <v>7</v>
+      </c>
+      <c r="G112" s="5">
+        <v>3</v>
+      </c>
+      <c r="H112" s="1">
+        <v>7</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J112" s="1"/>
-      <c r="K112" s="9"/>
+      <c r="K112" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L112" s="1"/>
       <c r="M112" s="1"/>
       <c r="N112" s="1"/>
       <c r="O112" s="1"/>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A113" s="6"/>
-      <c r="B113" s="6"/>
-      <c r="C113" s="7"/>
-      <c r="D113" s="7"/>
-      <c r="E113" s="1"/>
-      <c r="F113" s="5"/>
-      <c r="G113" s="5"/>
-      <c r="H113" s="1"/>
-      <c r="I113" s="1"/>
+      <c r="A113" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E113" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F113" s="5">
+        <v>7</v>
+      </c>
+      <c r="G113" s="5">
+        <v>5</v>
+      </c>
+      <c r="H113" s="1">
+        <v>7</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J113" s="1"/>
-      <c r="K113" s="9"/>
+      <c r="K113" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L113" s="1"/>
       <c r="M113" s="1"/>
       <c r="N113" s="1"/>
       <c r="O113" s="1"/>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A114" s="6"/>
-      <c r="B114" s="6"/>
-      <c r="C114" s="7"/>
-      <c r="D114" s="7"/>
-      <c r="E114" s="1"/>
-      <c r="F114" s="5"/>
-      <c r="G114" s="5"/>
-      <c r="H114" s="1"/>
-      <c r="I114" s="1"/>
+      <c r="A114" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F114" s="5">
+        <v>7</v>
+      </c>
+      <c r="G114" s="5">
+        <v>3</v>
+      </c>
+      <c r="H114" s="1">
+        <v>7</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J114" s="1"/>
-      <c r="K114" s="9"/>
+      <c r="K114" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L114" s="1"/>
       <c r="M114" s="1"/>
       <c r="N114" s="1"/>
       <c r="O114" s="1"/>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A115" s="6"/>
-      <c r="B115" s="6"/>
-      <c r="C115" s="7"/>
-      <c r="D115" s="7"/>
-      <c r="E115" s="1"/>
-      <c r="F115" s="5"/>
-      <c r="G115" s="5"/>
-      <c r="H115" s="1"/>
-      <c r="I115" s="1"/>
+      <c r="A115" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E115" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F115" s="5">
+        <v>7</v>
+      </c>
+      <c r="G115" s="5">
+        <v>4</v>
+      </c>
+      <c r="H115" s="1">
+        <v>7</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J115" s="1"/>
-      <c r="K115" s="9"/>
+      <c r="K115" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L115" s="1"/>
       <c r="M115" s="1"/>
       <c r="N115" s="1"/>
       <c r="O115" s="1"/>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A116" s="6"/>
-      <c r="B116" s="6"/>
-      <c r="C116" s="7"/>
-      <c r="D116" s="7"/>
-      <c r="E116" s="1"/>
-      <c r="F116" s="5"/>
-      <c r="G116" s="5"/>
-      <c r="H116" s="1"/>
-      <c r="I116" s="1"/>
+      <c r="A116" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E116" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F116" s="5">
+        <v>7</v>
+      </c>
+      <c r="G116" s="5">
+        <v>2</v>
+      </c>
+      <c r="H116" s="1">
+        <v>7</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J116" s="1"/>
-      <c r="K116" s="9"/>
+      <c r="K116" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L116" s="1"/>
       <c r="M116" s="1"/>
       <c r="N116" s="1"/>
       <c r="O116" s="1"/>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
-      <c r="C117" s="7"/>
-      <c r="D117" s="7"/>
-      <c r="E117" s="1"/>
-      <c r="F117" s="5"/>
-      <c r="G117" s="5"/>
-      <c r="H117" s="1"/>
-      <c r="I117" s="1"/>
+      <c r="A117" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F117" s="5">
+        <v>7</v>
+      </c>
+      <c r="G117" s="5">
+        <v>4</v>
+      </c>
+      <c r="H117" s="1">
+        <v>7</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J117" s="1"/>
-      <c r="K117" s="9"/>
+      <c r="K117" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L117" s="1"/>
       <c r="M117" s="1"/>
       <c r="N117" s="1"/>
       <c r="O117" s="1"/>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A118" s="6"/>
-      <c r="B118" s="6"/>
-      <c r="C118" s="7"/>
-      <c r="D118" s="7"/>
-      <c r="E118" s="1"/>
-      <c r="F118" s="5"/>
-      <c r="G118" s="5"/>
-      <c r="H118" s="1"/>
-      <c r="I118" s="1"/>
+      <c r="A118" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E118" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F118" s="5">
+        <v>7</v>
+      </c>
+      <c r="G118" s="5">
+        <v>3</v>
+      </c>
+      <c r="H118" s="1">
+        <v>7</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J118" s="1"/>
-      <c r="K118" s="9"/>
+      <c r="K118" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L118" s="1"/>
       <c r="M118" s="1"/>
       <c r="N118" s="1"/>
       <c r="O118" s="1"/>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A119" s="6"/>
-      <c r="B119" s="6"/>
-      <c r="C119" s="7"/>
-      <c r="D119" s="7"/>
-      <c r="E119" s="1"/>
-      <c r="F119" s="5"/>
-      <c r="G119" s="5"/>
-      <c r="H119" s="1"/>
-      <c r="I119" s="1"/>
+      <c r="A119" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E119" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F119" s="5">
+        <v>7</v>
+      </c>
+      <c r="G119" s="5">
+        <v>2</v>
+      </c>
+      <c r="H119" s="1">
+        <v>7</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J119" s="1"/>
-      <c r="K119" s="9"/>
+      <c r="K119" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L119" s="1"/>
       <c r="M119" s="1"/>
       <c r="N119" s="1"/>
       <c r="O119" s="1"/>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A120" s="6"/>
-      <c r="B120" s="6"/>
-      <c r="C120" s="7"/>
-      <c r="D120" s="7"/>
-      <c r="E120" s="1"/>
-      <c r="F120" s="5"/>
-      <c r="G120" s="5"/>
-      <c r="H120" s="1"/>
-      <c r="I120" s="1"/>
+      <c r="A120" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E120" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F120" s="5">
+        <v>8</v>
+      </c>
+      <c r="G120" s="5">
+        <v>6</v>
+      </c>
+      <c r="H120" s="1">
+        <v>7</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="J120" s="1"/>
-      <c r="K120" s="9"/>
+      <c r="K120" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L120" s="1"/>
       <c r="M120" s="1"/>
       <c r="N120" s="1"/>

--- a/data/spike.xlsx
+++ b/data/spike.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phbro\Desktop\DOCUMENTS\ActuRank\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4AC837-1345-4EE9-B6E5-503C67BC7EEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033B0746-735C-4677-B0EB-05FCB644E80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="67">
   <si>
     <t>players</t>
   </si>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>05/05/2025</t>
+  </si>
+  <si>
+    <t>08/07/2025</t>
   </si>
 </sst>
 </file>
@@ -3370,7 +3373,7 @@
         <v>11</v>
       </c>
       <c r="E68" s="1">
-        <f t="shared" ref="E68:E120" si="2">IF(F68&gt;G68,1,0)</f>
+        <f t="shared" ref="E68:E131" si="2">IF(F68&gt;G68,1,0)</f>
         <v>1</v>
       </c>
       <c r="F68" s="5">
@@ -3387,7 +3390,7 @@
       </c>
       <c r="J68" s="1"/>
       <c r="K68" s="9" t="str">
-        <f t="shared" ref="K68:K120" si="3">IF(OR(OR(AND(OR(A68=B68,A68=C68,A68=D68,B68=C68,B68=D68,C68=D68),OR(A68&lt;&gt;"",D68&lt;&gt;"")),H68&gt;MAX(F68:G68),B68=C68),OR(AND(ISBLANK(A68)=FALSE,ISNA(VLOOKUP(A68,$M$3:$O$27,1,FALSE))),ISNA(VLOOKUP(B68,$M$3:$O$27,1,FALSE)),ISNA(VLOOKUP(C68,$M$3:$O$27,1,FALSE)),AND(ISBLANK(D68)=FALSE,ISNA(VLOOKUP(D68,$M$3:$O$27,1,FALSE))),OR(COUNTBLANK(A68:D68)=1,COUNTBLANK(A68:D68)=3))),"ERREUR","")</f>
+        <f t="shared" ref="K68:K131" si="3">IF(OR(OR(AND(OR(A68=B68,A68=C68,A68=D68,B68=C68,B68=D68,C68=D68),OR(A68&lt;&gt;"",D68&lt;&gt;"")),H68&gt;MAX(F68:G68),B68=C68),OR(AND(ISBLANK(A68)=FALSE,ISNA(VLOOKUP(A68,$M$3:$O$27,1,FALSE))),ISNA(VLOOKUP(B68,$M$3:$O$27,1,FALSE)),ISNA(VLOOKUP(C68,$M$3:$O$27,1,FALSE)),AND(ISBLANK(D68)=FALSE,ISNA(VLOOKUP(D68,$M$3:$O$27,1,FALSE))),OR(COUNTBLANK(A68:D68)=1,COUNTBLANK(A68:D68)=3))),"ERREUR","")</f>
         <v/>
       </c>
       <c r="L68" s="1"/>
@@ -5424,204 +5427,468 @@
       <c r="O120" s="1"/>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A121" s="6"/>
-      <c r="B121" s="6"/>
-      <c r="C121" s="7"/>
-      <c r="D121" s="7"/>
-      <c r="E121" s="1"/>
-      <c r="F121" s="5"/>
-      <c r="G121" s="5"/>
-      <c r="H121" s="1"/>
-      <c r="I121" s="1"/>
+      <c r="A121" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E121" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F121" s="5">
+        <v>11</v>
+      </c>
+      <c r="G121" s="5">
+        <v>9</v>
+      </c>
+      <c r="H121" s="1">
+        <v>11</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="J121" s="1"/>
-      <c r="K121" s="9"/>
+      <c r="K121" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L121" s="1"/>
       <c r="M121" s="1"/>
       <c r="N121" s="1"/>
       <c r="O121" s="1"/>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A122" s="6"/>
-      <c r="B122" s="6"/>
-      <c r="C122" s="7"/>
-      <c r="D122" s="7"/>
-      <c r="E122" s="1"/>
-      <c r="F122" s="5"/>
-      <c r="G122" s="5"/>
-      <c r="H122" s="1"/>
-      <c r="I122" s="1"/>
+      <c r="A122" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E122" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F122" s="5">
+        <v>11</v>
+      </c>
+      <c r="G122" s="5">
+        <v>7</v>
+      </c>
+      <c r="H122" s="1">
+        <v>11</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="J122" s="1"/>
-      <c r="K122" s="9"/>
+      <c r="K122" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L122" s="1"/>
       <c r="M122" s="1"/>
       <c r="N122" s="1"/>
       <c r="O122" s="1"/>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A123" s="6"/>
-      <c r="B123" s="6"/>
-      <c r="C123" s="7"/>
-      <c r="D123" s="7"/>
-      <c r="E123" s="1"/>
-      <c r="F123" s="5"/>
-      <c r="G123" s="5"/>
-      <c r="H123" s="1"/>
-      <c r="I123" s="1"/>
+      <c r="A123" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E123" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F123" s="5">
+        <v>11</v>
+      </c>
+      <c r="G123" s="5">
+        <v>7</v>
+      </c>
+      <c r="H123" s="1">
+        <v>11</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="J123" s="1"/>
-      <c r="K123" s="9"/>
+      <c r="K123" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L123" s="1"/>
       <c r="M123" s="1"/>
       <c r="N123" s="1"/>
       <c r="O123" s="1"/>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A124" s="6"/>
-      <c r="B124" s="6"/>
-      <c r="C124" s="7"/>
-      <c r="D124" s="7"/>
-      <c r="E124" s="1"/>
-      <c r="F124" s="5"/>
-      <c r="G124" s="5"/>
-      <c r="H124" s="1"/>
-      <c r="I124" s="1"/>
+      <c r="A124" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E124" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F124" s="5">
+        <v>11</v>
+      </c>
+      <c r="G124" s="5">
+        <v>4</v>
+      </c>
+      <c r="H124" s="1">
+        <v>11</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="J124" s="1"/>
-      <c r="K124" s="9"/>
+      <c r="K124" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L124" s="1"/>
       <c r="M124" s="1"/>
       <c r="N124" s="1"/>
       <c r="O124" s="1"/>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A125" s="6"/>
-      <c r="B125" s="6"/>
-      <c r="C125" s="7"/>
-      <c r="D125" s="7"/>
-      <c r="E125" s="1"/>
-      <c r="F125" s="5"/>
-      <c r="G125" s="5"/>
-      <c r="H125" s="1"/>
-      <c r="I125" s="1"/>
+      <c r="A125" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E125" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F125" s="5">
+        <v>11</v>
+      </c>
+      <c r="G125" s="5">
+        <v>9</v>
+      </c>
+      <c r="H125" s="1">
+        <v>11</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="J125" s="1"/>
-      <c r="K125" s="9"/>
+      <c r="K125" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L125" s="1"/>
       <c r="M125" s="1"/>
       <c r="N125" s="1"/>
       <c r="O125" s="1"/>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A126" s="6"/>
-      <c r="B126" s="6"/>
-      <c r="C126" s="7"/>
-      <c r="D126" s="7"/>
-      <c r="E126" s="1"/>
-      <c r="F126" s="5"/>
-      <c r="G126" s="5"/>
-      <c r="H126" s="1"/>
-      <c r="I126" s="1"/>
+      <c r="A126" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E126" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F126" s="5">
+        <v>11</v>
+      </c>
+      <c r="G126" s="5">
+        <v>7</v>
+      </c>
+      <c r="H126" s="1">
+        <v>11</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="J126" s="1"/>
-      <c r="K126" s="9"/>
+      <c r="K126" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L126" s="1"/>
       <c r="M126" s="1"/>
       <c r="N126" s="1"/>
       <c r="O126" s="1"/>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A127" s="6"/>
-      <c r="B127" s="6"/>
-      <c r="C127" s="7"/>
-      <c r="D127" s="7"/>
-      <c r="E127" s="1"/>
-      <c r="F127" s="5"/>
-      <c r="G127" s="5"/>
-      <c r="H127" s="1"/>
-      <c r="I127" s="1"/>
+      <c r="A127" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E127" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F127" s="5">
+        <v>11</v>
+      </c>
+      <c r="G127" s="5">
+        <v>7</v>
+      </c>
+      <c r="H127" s="1">
+        <v>11</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="J127" s="1"/>
-      <c r="K127" s="9"/>
+      <c r="K127" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L127" s="1"/>
       <c r="M127" s="1"/>
       <c r="N127" s="1"/>
       <c r="O127" s="1"/>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A128" s="6"/>
-      <c r="B128" s="6"/>
-      <c r="C128" s="7"/>
-      <c r="D128" s="7"/>
-      <c r="E128" s="1"/>
-      <c r="F128" s="5"/>
-      <c r="G128" s="5"/>
-      <c r="H128" s="1"/>
-      <c r="I128" s="1"/>
+      <c r="A128" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E128" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F128" s="5">
+        <v>11</v>
+      </c>
+      <c r="G128" s="5">
+        <v>6</v>
+      </c>
+      <c r="H128" s="1">
+        <v>11</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="J128" s="1"/>
-      <c r="K128" s="9"/>
+      <c r="K128" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L128" s="1"/>
       <c r="M128" s="1"/>
       <c r="N128" s="1"/>
       <c r="O128" s="1"/>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A129" s="6"/>
-      <c r="B129" s="6"/>
-      <c r="C129" s="7"/>
-      <c r="D129" s="7"/>
-      <c r="E129" s="1"/>
-      <c r="F129" s="5"/>
-      <c r="G129" s="5"/>
-      <c r="H129" s="1"/>
-      <c r="I129" s="1"/>
+      <c r="A129" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E129" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F129" s="5">
+        <v>11</v>
+      </c>
+      <c r="G129" s="5">
+        <v>5</v>
+      </c>
+      <c r="H129" s="1">
+        <v>11</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="J129" s="1"/>
-      <c r="K129" s="9"/>
+      <c r="K129" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L129" s="1"/>
       <c r="M129" s="1"/>
       <c r="N129" s="1"/>
       <c r="O129" s="1"/>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A130" s="6"/>
-      <c r="B130" s="6"/>
-      <c r="C130" s="7"/>
-      <c r="D130" s="7"/>
-      <c r="E130" s="1"/>
-      <c r="F130" s="5"/>
-      <c r="G130" s="5"/>
-      <c r="H130" s="1"/>
-      <c r="I130" s="1"/>
+      <c r="A130" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E130" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F130" s="5">
+        <v>11</v>
+      </c>
+      <c r="G130" s="5">
+        <v>4</v>
+      </c>
+      <c r="H130" s="1">
+        <v>11</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="J130" s="1"/>
-      <c r="K130" s="9"/>
+      <c r="K130" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L130" s="1"/>
       <c r="M130" s="1"/>
       <c r="N130" s="1"/>
       <c r="O130" s="1"/>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A131" s="6"/>
-      <c r="B131" s="6"/>
-      <c r="C131" s="7"/>
-      <c r="D131" s="7"/>
-      <c r="E131" s="1"/>
-      <c r="F131" s="5"/>
-      <c r="G131" s="5"/>
-      <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
+      <c r="A131" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E131" s="1">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F131" s="5">
+        <v>11</v>
+      </c>
+      <c r="G131" s="5">
+        <v>8</v>
+      </c>
+      <c r="H131" s="1">
+        <v>11</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="J131" s="1"/>
-      <c r="K131" s="9"/>
+      <c r="K131" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
       <c r="L131" s="1"/>
       <c r="M131" s="1"/>
       <c r="N131" s="1"/>
       <c r="O131" s="1"/>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A132" s="6"/>
-      <c r="B132" s="6"/>
-      <c r="C132" s="7"/>
-      <c r="D132" s="7"/>
-      <c r="E132" s="1"/>
-      <c r="F132" s="5"/>
-      <c r="G132" s="5"/>
-      <c r="H132" s="1"/>
-      <c r="I132" s="1"/>
+      <c r="A132" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E132" s="1">
+        <f t="shared" ref="E132" si="4">IF(F132&gt;G132,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="F132" s="5">
+        <v>11</v>
+      </c>
+      <c r="G132" s="5">
+        <v>6</v>
+      </c>
+      <c r="H132" s="1">
+        <v>11</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="J132" s="1"/>
-      <c r="K132" s="9"/>
+      <c r="K132" s="9" t="str">
+        <f t="shared" ref="K132" si="5">IF(OR(OR(AND(OR(A132=B132,A132=C132,A132=D132,B132=C132,B132=D132,C132=D132),OR(A132&lt;&gt;"",D132&lt;&gt;"")),H132&gt;MAX(F132:G132),B132=C132),OR(AND(ISBLANK(A132)=FALSE,ISNA(VLOOKUP(A132,$M$3:$O$27,1,FALSE))),ISNA(VLOOKUP(B132,$M$3:$O$27,1,FALSE)),ISNA(VLOOKUP(C132,$M$3:$O$27,1,FALSE)),AND(ISBLANK(D132)=FALSE,ISNA(VLOOKUP(D132,$M$3:$O$27,1,FALSE))),OR(COUNTBLANK(A132:D132)=1,COUNTBLANK(A132:D132)=3))),"ERREUR","")</f>
+        <v/>
+      </c>
       <c r="L132" s="1"/>
       <c r="M132" s="1"/>
       <c r="N132" s="1"/>

--- a/data/spike.xlsx
+++ b/data/spike.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phbro\Desktop\DOCUMENTS\ActuRank\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilpe\Documents\DOCUMENTS\ActuRank\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033B0746-735C-4677-B0EB-05FCB644E80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F10DD0-C6A6-4257-A09C-7473587DE9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="68">
   <si>
     <t>players</t>
   </si>
@@ -237,6 +237,9 @@
   </si>
   <si>
     <t>08/07/2025</t>
+  </si>
+  <si>
+    <t>23/07/2025</t>
   </si>
 </sst>
 </file>
@@ -629,12 +632,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O935"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="8.88671875" style="10"/>
+    <col min="11" max="11" width="8.90625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -661,7 +664,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -692,7 +695,7 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -737,7 +740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>11</v>
       </c>
@@ -782,7 +785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
@@ -827,7 +830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -872,7 +875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
@@ -917,7 +920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>12</v>
       </c>
@@ -962,7 +965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
@@ -1007,7 +1010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>17</v>
       </c>
@@ -1052,7 +1055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>13</v>
       </c>
@@ -1097,7 +1100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>12</v>
       </c>
@@ -1142,7 +1145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>17</v>
       </c>
@@ -1187,7 +1190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
@@ -1232,7 +1235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>12</v>
       </c>
@@ -1277,7 +1280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>12</v>
       </c>
@@ -1322,7 +1325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>12</v>
       </c>
@@ -1367,7 +1370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>19</v>
       </c>
@@ -1412,7 +1415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>13</v>
       </c>
@@ -1457,7 +1460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
@@ -1502,7 +1505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>12</v>
       </c>
@@ -1547,7 +1550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>12</v>
       </c>
@@ -1592,7 +1595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>19</v>
       </c>
@@ -1637,7 +1640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>11</v>
       </c>
@@ -1682,7 +1685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>17</v>
       </c>
@@ -1721,7 +1724,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>12</v>
       </c>
@@ -1760,7 +1763,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>12</v>
       </c>
@@ -1799,7 +1802,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>19</v>
       </c>
@@ -1838,7 +1841,7 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>13</v>
       </c>
@@ -1877,7 +1880,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
         <v>13</v>
       </c>
@@ -1916,7 +1919,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>17</v>
       </c>
@@ -1955,7 +1958,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>13</v>
       </c>
@@ -1994,7 +1997,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>19</v>
       </c>
@@ -2033,7 +2036,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>11</v>
       </c>
@@ -2072,7 +2075,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
         <v>17</v>
       </c>
@@ -2111,7 +2114,7 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
         <v>12</v>
       </c>
@@ -2150,7 +2153,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
         <v>13</v>
       </c>
@@ -2189,7 +2192,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
         <v>13</v>
       </c>
@@ -2228,7 +2231,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
         <v>13</v>
       </c>
@@ -2267,7 +2270,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
         <v>19</v>
       </c>
@@ -2306,7 +2309,7 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
         <v>12</v>
       </c>
@@ -2345,7 +2348,7 @@
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
         <v>12</v>
       </c>
@@ -2384,7 +2387,7 @@
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>12</v>
       </c>
@@ -2423,7 +2426,7 @@
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
         <v>13</v>
       </c>
@@ -2462,7 +2465,7 @@
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
         <v>12</v>
       </c>
@@ -2501,7 +2504,7 @@
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
         <v>12</v>
       </c>
@@ -2540,7 +2543,7 @@
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
         <v>13</v>
       </c>
@@ -2579,7 +2582,7 @@
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>13</v>
       </c>
@@ -2618,7 +2621,7 @@
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
         <v>11</v>
       </c>
@@ -2657,7 +2660,7 @@
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
         <v>13</v>
       </c>
@@ -2696,7 +2699,7 @@
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
         <v>12</v>
       </c>
@@ -2735,7 +2738,7 @@
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
         <v>13</v>
       </c>
@@ -2774,7 +2777,7 @@
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
         <v>13</v>
       </c>
@@ -2813,7 +2816,7 @@
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
         <v>12</v>
       </c>
@@ -2852,7 +2855,7 @@
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
         <v>17</v>
       </c>
@@ -2891,7 +2894,7 @@
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>17</v>
       </c>
@@ -2930,7 +2933,7 @@
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
         <v>17</v>
       </c>
@@ -2969,7 +2972,7 @@
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
         <v>12</v>
       </c>
@@ -3008,7 +3011,7 @@
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
         <v>12</v>
       </c>
@@ -3047,7 +3050,7 @@
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
         <v>11</v>
       </c>
@@ -3086,7 +3089,7 @@
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
         <v>12</v>
       </c>
@@ -3125,7 +3128,7 @@
       <c r="N61" s="1"/>
       <c r="O61" s="1"/>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
         <v>13</v>
       </c>
@@ -3164,7 +3167,7 @@
       <c r="N62" s="1"/>
       <c r="O62" s="1"/>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" s="6" t="s">
         <v>13</v>
       </c>
@@ -3203,7 +3206,7 @@
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
         <v>12</v>
       </c>
@@ -3242,7 +3245,7 @@
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
         <v>12</v>
       </c>
@@ -3281,7 +3284,7 @@
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
         <v>12</v>
       </c>
@@ -3320,7 +3323,7 @@
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>12</v>
       </c>
@@ -3359,7 +3362,7 @@
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
         <v>12</v>
       </c>
@@ -3398,7 +3401,7 @@
       <c r="N68" s="1"/>
       <c r="O68" s="1"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
         <v>12</v>
       </c>
@@ -3437,7 +3440,7 @@
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" s="6" t="s">
         <v>13</v>
       </c>
@@ -3476,7 +3479,7 @@
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" s="6" t="s">
         <v>11</v>
       </c>
@@ -3515,7 +3518,7 @@
       <c r="N71" s="1"/>
       <c r="O71" s="1"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" s="6" t="s">
         <v>13</v>
       </c>
@@ -3554,7 +3557,7 @@
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" s="6" t="s">
         <v>12</v>
       </c>
@@ -3593,7 +3596,7 @@
       <c r="N73" s="1"/>
       <c r="O73" s="1"/>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" s="6" t="s">
         <v>39</v>
       </c>
@@ -3632,7 +3635,7 @@
       <c r="N74" s="1"/>
       <c r="O74" s="1"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
         <v>12</v>
       </c>
@@ -3671,7 +3674,7 @@
       <c r="N75" s="1"/>
       <c r="O75" s="1"/>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" s="6" t="s">
         <v>12</v>
       </c>
@@ -3710,7 +3713,7 @@
       <c r="N76" s="1"/>
       <c r="O76" s="1"/>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" s="6" t="s">
         <v>12</v>
       </c>
@@ -3749,7 +3752,7 @@
       <c r="N77" s="1"/>
       <c r="O77" s="1"/>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
         <v>12</v>
       </c>
@@ -3788,7 +3791,7 @@
       <c r="N78" s="1"/>
       <c r="O78" s="1"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" s="6" t="s">
         <v>12</v>
       </c>
@@ -3827,7 +3830,7 @@
       <c r="N79" s="1"/>
       <c r="O79" s="1"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" s="6" t="s">
         <v>12</v>
       </c>
@@ -3866,7 +3869,7 @@
       <c r="N80" s="1"/>
       <c r="O80" s="1"/>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" s="6" t="s">
         <v>11</v>
       </c>
@@ -3905,7 +3908,7 @@
       <c r="N81" s="1"/>
       <c r="O81" s="1"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" s="6" t="s">
         <v>12</v>
       </c>
@@ -3944,7 +3947,7 @@
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" s="6" t="s">
         <v>17</v>
       </c>
@@ -3983,7 +3986,7 @@
       <c r="N83" s="1"/>
       <c r="O83" s="1"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" s="6" t="s">
         <v>12</v>
       </c>
@@ -4022,7 +4025,7 @@
       <c r="N84" s="1"/>
       <c r="O84" s="1"/>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" s="6" t="s">
         <v>12</v>
       </c>
@@ -4061,7 +4064,7 @@
       <c r="N85" s="1"/>
       <c r="O85" s="1"/>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" s="6" t="s">
         <v>21</v>
       </c>
@@ -4100,7 +4103,7 @@
       <c r="N86" s="1"/>
       <c r="O86" s="1"/>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
         <v>11</v>
       </c>
@@ -4139,7 +4142,7 @@
       <c r="N87" s="1"/>
       <c r="O87" s="1"/>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" s="6" t="s">
         <v>13</v>
       </c>
@@ -4178,7 +4181,7 @@
       <c r="N88" s="1"/>
       <c r="O88" s="1"/>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" s="6" t="s">
         <v>13</v>
       </c>
@@ -4217,7 +4220,7 @@
       <c r="N89" s="1"/>
       <c r="O89" s="1"/>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
         <v>13</v>
       </c>
@@ -4256,7 +4259,7 @@
       <c r="N90" s="1"/>
       <c r="O90" s="1"/>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" s="6" t="s">
         <v>13</v>
       </c>
@@ -4295,7 +4298,7 @@
       <c r="N91" s="1"/>
       <c r="O91" s="1"/>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" s="6" t="s">
         <v>13</v>
       </c>
@@ -4334,7 +4337,7 @@
       <c r="N92" s="1"/>
       <c r="O92" s="1"/>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" s="6" t="s">
         <v>12</v>
       </c>
@@ -4373,7 +4376,7 @@
       <c r="N93" s="1"/>
       <c r="O93" s="1"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94" s="6" t="s">
         <v>13</v>
       </c>
@@ -4412,7 +4415,7 @@
       <c r="N94" s="1"/>
       <c r="O94" s="1"/>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" s="6" t="s">
         <v>21</v>
       </c>
@@ -4451,7 +4454,7 @@
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A96" s="6" t="s">
         <v>13</v>
       </c>
@@ -4490,7 +4493,7 @@
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A97" s="6" t="s">
         <v>12</v>
       </c>
@@ -4529,7 +4532,7 @@
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A98" s="6" t="s">
         <v>17</v>
       </c>
@@ -4568,7 +4571,7 @@
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A99" s="6" t="s">
         <v>13</v>
       </c>
@@ -4607,7 +4610,7 @@
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A100" s="6" t="s">
         <v>13</v>
       </c>
@@ -4646,7 +4649,7 @@
       <c r="N100" s="1"/>
       <c r="O100" s="1"/>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A101" s="6" t="s">
         <v>13</v>
       </c>
@@ -4685,7 +4688,7 @@
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A102" s="6" t="s">
         <v>13</v>
       </c>
@@ -4724,7 +4727,7 @@
       <c r="N102" s="1"/>
       <c r="O102" s="1"/>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A103" s="6" t="s">
         <v>13</v>
       </c>
@@ -4763,7 +4766,7 @@
       <c r="N103" s="1"/>
       <c r="O103" s="1"/>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A104" s="6" t="s">
         <v>13</v>
       </c>
@@ -4802,7 +4805,7 @@
       <c r="N104" s="1"/>
       <c r="O104" s="1"/>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A105" s="6" t="s">
         <v>12</v>
       </c>
@@ -4841,7 +4844,7 @@
       <c r="N105" s="1"/>
       <c r="O105" s="1"/>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A106" s="6" t="s">
         <v>12</v>
       </c>
@@ -4880,7 +4883,7 @@
       <c r="N106" s="1"/>
       <c r="O106" s="1"/>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A107" s="6" t="s">
         <v>12</v>
       </c>
@@ -4919,7 +4922,7 @@
       <c r="N107" s="1"/>
       <c r="O107" s="1"/>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A108" s="6" t="s">
         <v>12</v>
       </c>
@@ -4958,7 +4961,7 @@
       <c r="N108" s="1"/>
       <c r="O108" s="1"/>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A109" s="6" t="s">
         <v>12</v>
       </c>
@@ -4997,7 +5000,7 @@
       <c r="N109" s="1"/>
       <c r="O109" s="1"/>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A110" s="6" t="s">
         <v>12</v>
       </c>
@@ -5036,7 +5039,7 @@
       <c r="N110" s="1"/>
       <c r="O110" s="1"/>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A111" s="6" t="s">
         <v>13</v>
       </c>
@@ -5075,7 +5078,7 @@
       <c r="N111" s="1"/>
       <c r="O111" s="1"/>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A112" s="6" t="s">
         <v>12</v>
       </c>
@@ -5114,7 +5117,7 @@
       <c r="N112" s="1"/>
       <c r="O112" s="1"/>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A113" s="6" t="s">
         <v>54</v>
       </c>
@@ -5153,7 +5156,7 @@
       <c r="N113" s="1"/>
       <c r="O113" s="1"/>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A114" s="6" t="s">
         <v>54</v>
       </c>
@@ -5192,7 +5195,7 @@
       <c r="N114" s="1"/>
       <c r="O114" s="1"/>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A115" s="6" t="s">
         <v>12</v>
       </c>
@@ -5231,7 +5234,7 @@
       <c r="N115" s="1"/>
       <c r="O115" s="1"/>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A116" s="6" t="s">
         <v>13</v>
       </c>
@@ -5270,7 +5273,7 @@
       <c r="N116" s="1"/>
       <c r="O116" s="1"/>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A117" s="6" t="s">
         <v>54</v>
       </c>
@@ -5309,7 +5312,7 @@
       <c r="N117" s="1"/>
       <c r="O117" s="1"/>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A118" s="6" t="s">
         <v>17</v>
       </c>
@@ -5348,7 +5351,7 @@
       <c r="N118" s="1"/>
       <c r="O118" s="1"/>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A119" s="6" t="s">
         <v>12</v>
       </c>
@@ -5387,7 +5390,7 @@
       <c r="N119" s="1"/>
       <c r="O119" s="1"/>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A120" s="6" t="s">
         <v>12</v>
       </c>
@@ -5426,7 +5429,7 @@
       <c r="N120" s="1"/>
       <c r="O120" s="1"/>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A121" s="6" t="s">
         <v>54</v>
       </c>
@@ -5465,7 +5468,7 @@
       <c r="N121" s="1"/>
       <c r="O121" s="1"/>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A122" s="6" t="s">
         <v>13</v>
       </c>
@@ -5504,7 +5507,7 @@
       <c r="N122" s="1"/>
       <c r="O122" s="1"/>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A123" s="6" t="s">
         <v>13</v>
       </c>
@@ -5543,7 +5546,7 @@
       <c r="N123" s="1"/>
       <c r="O123" s="1"/>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A124" s="6" t="s">
         <v>54</v>
       </c>
@@ -5582,7 +5585,7 @@
       <c r="N124" s="1"/>
       <c r="O124" s="1"/>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A125" s="6" t="s">
         <v>27</v>
       </c>
@@ -5621,7 +5624,7 @@
       <c r="N125" s="1"/>
       <c r="O125" s="1"/>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A126" s="6" t="s">
         <v>17</v>
       </c>
@@ -5660,7 +5663,7 @@
       <c r="N126" s="1"/>
       <c r="O126" s="1"/>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A127" s="6" t="s">
         <v>17</v>
       </c>
@@ -5699,7 +5702,7 @@
       <c r="N127" s="1"/>
       <c r="O127" s="1"/>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A128" s="6" t="s">
         <v>13</v>
       </c>
@@ -5738,7 +5741,7 @@
       <c r="N128" s="1"/>
       <c r="O128" s="1"/>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A129" s="6" t="s">
         <v>13</v>
       </c>
@@ -5777,7 +5780,7 @@
       <c r="N129" s="1"/>
       <c r="O129" s="1"/>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A130" s="6" t="s">
         <v>13</v>
       </c>
@@ -5816,7 +5819,7 @@
       <c r="N130" s="1"/>
       <c r="O130" s="1"/>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A131" s="6" t="s">
         <v>13</v>
       </c>
@@ -5855,7 +5858,7 @@
       <c r="N131" s="1"/>
       <c r="O131" s="1"/>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A132" s="6" t="s">
         <v>17</v>
       </c>
@@ -5869,7 +5872,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="1">
-        <f t="shared" ref="E132" si="4">IF(F132&gt;G132,1,0)</f>
+        <f t="shared" ref="E132:E156" si="4">IF(F132&gt;G132,1,0)</f>
         <v>1</v>
       </c>
       <c r="F132" s="5">
@@ -5886,7 +5889,7 @@
       </c>
       <c r="J132" s="1"/>
       <c r="K132" s="9" t="str">
-        <f t="shared" ref="K132" si="5">IF(OR(OR(AND(OR(A132=B132,A132=C132,A132=D132,B132=C132,B132=D132,C132=D132),OR(A132&lt;&gt;"",D132&lt;&gt;"")),H132&gt;MAX(F132:G132),B132=C132),OR(AND(ISBLANK(A132)=FALSE,ISNA(VLOOKUP(A132,$M$3:$O$27,1,FALSE))),ISNA(VLOOKUP(B132,$M$3:$O$27,1,FALSE)),ISNA(VLOOKUP(C132,$M$3:$O$27,1,FALSE)),AND(ISBLANK(D132)=FALSE,ISNA(VLOOKUP(D132,$M$3:$O$27,1,FALSE))),OR(COUNTBLANK(A132:D132)=1,COUNTBLANK(A132:D132)=3))),"ERREUR","")</f>
+        <f t="shared" ref="K132:K146" si="5">IF(OR(OR(AND(OR(A132=B132,A132=C132,A132=D132,B132=C132,B132=D132,C132=D132),OR(A132&lt;&gt;"",D132&lt;&gt;"")),H132&gt;MAX(F132:G132),B132=C132),OR(AND(ISBLANK(A132)=FALSE,ISNA(VLOOKUP(A132,$M$3:$O$27,1,FALSE))),ISNA(VLOOKUP(B132,$M$3:$O$27,1,FALSE)),ISNA(VLOOKUP(C132,$M$3:$O$27,1,FALSE)),AND(ISBLANK(D132)=FALSE,ISNA(VLOOKUP(D132,$M$3:$O$27,1,FALSE))),OR(COUNTBLANK(A132:D132)=1,COUNTBLANK(A132:D132)=3))),"ERREUR","")</f>
         <v/>
       </c>
       <c r="L132" s="1"/>
@@ -5894,254 +5897,581 @@
       <c r="N132" s="1"/>
       <c r="O132" s="1"/>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A133" s="6"/>
-      <c r="B133" s="6"/>
-      <c r="C133" s="7"/>
-      <c r="D133" s="7"/>
-      <c r="E133" s="1"/>
-      <c r="F133" s="5"/>
-      <c r="G133" s="5"/>
-      <c r="H133" s="1"/>
-      <c r="I133" s="1"/>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A133" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E133" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F133" s="5">
+        <v>7</v>
+      </c>
+      <c r="G133" s="5">
+        <v>4</v>
+      </c>
+      <c r="H133" s="1">
+        <v>7</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J133" s="1"/>
-      <c r="K133" s="9"/>
+      <c r="K133" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
       <c r="L133" s="1"/>
       <c r="M133" s="1"/>
       <c r="N133" s="1"/>
       <c r="O133" s="1"/>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A134" s="6"/>
-      <c r="B134" s="6"/>
-      <c r="C134" s="7"/>
-      <c r="D134" s="7"/>
-      <c r="E134" s="1"/>
-      <c r="F134" s="5"/>
-      <c r="G134" s="5"/>
-      <c r="H134" s="1"/>
-      <c r="I134" s="1"/>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A134" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E134" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F134" s="5">
+        <v>8</v>
+      </c>
+      <c r="G134" s="5">
+        <v>6</v>
+      </c>
+      <c r="H134" s="1">
+        <v>7</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J134" s="1"/>
-      <c r="K134" s="9"/>
+      <c r="K134" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
       <c r="L134" s="1"/>
       <c r="M134" s="1"/>
       <c r="N134" s="1"/>
       <c r="O134" s="1"/>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A135" s="6"/>
-      <c r="B135" s="6"/>
-      <c r="C135" s="7"/>
-      <c r="D135" s="7"/>
-      <c r="E135" s="1"/>
-      <c r="F135" s="5"/>
-      <c r="G135" s="5"/>
-      <c r="H135" s="1"/>
-      <c r="I135" s="1"/>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A135" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E135" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F135" s="5">
+        <v>7</v>
+      </c>
+      <c r="G135" s="5">
+        <v>2</v>
+      </c>
+      <c r="H135" s="1">
+        <v>7</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J135" s="1"/>
-      <c r="K135" s="9"/>
+      <c r="K135" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
       <c r="L135" s="1"/>
       <c r="M135" s="1"/>
       <c r="N135" s="1"/>
       <c r="O135" s="1"/>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A136" s="6"/>
-      <c r="B136" s="6"/>
-      <c r="C136" s="7"/>
-      <c r="D136" s="7"/>
-      <c r="E136" s="1"/>
-      <c r="F136" s="5"/>
-      <c r="G136" s="5"/>
-      <c r="H136" s="1"/>
-      <c r="I136" s="1"/>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A136" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D136" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E136" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F136" s="5">
+        <v>7</v>
+      </c>
+      <c r="G136" s="5">
+        <v>5</v>
+      </c>
+      <c r="H136" s="1">
+        <v>7</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J136" s="1"/>
-      <c r="K136" s="9"/>
+      <c r="K136" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
       <c r="L136" s="1"/>
       <c r="M136" s="1"/>
       <c r="N136" s="1"/>
       <c r="O136" s="1"/>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A137" s="6"/>
-      <c r="B137" s="6"/>
-      <c r="C137" s="7"/>
-      <c r="D137" s="7"/>
-      <c r="E137" s="1"/>
-      <c r="F137" s="5"/>
-      <c r="G137" s="5"/>
-      <c r="H137" s="1"/>
-      <c r="I137" s="1"/>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A137" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E137" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F137" s="5">
+        <v>7</v>
+      </c>
+      <c r="G137" s="5">
+        <v>4</v>
+      </c>
+      <c r="H137" s="1">
+        <v>7</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J137" s="1"/>
-      <c r="K137" s="9"/>
+      <c r="K137" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
       <c r="L137" s="1"/>
       <c r="M137" s="1"/>
       <c r="N137" s="1"/>
       <c r="O137" s="1"/>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A138" s="6"/>
-      <c r="B138" s="6"/>
-      <c r="C138" s="7"/>
-      <c r="D138" s="7"/>
-      <c r="E138" s="1"/>
-      <c r="F138" s="5"/>
-      <c r="G138" s="5"/>
-      <c r="H138" s="1"/>
-      <c r="I138" s="1"/>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A138" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E138" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F138" s="5">
+        <v>7</v>
+      </c>
+      <c r="G138" s="5">
+        <v>5</v>
+      </c>
+      <c r="H138" s="1">
+        <v>7</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J138" s="1"/>
-      <c r="K138" s="9"/>
+      <c r="K138" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
       <c r="L138" s="1"/>
       <c r="M138" s="1"/>
       <c r="N138" s="1"/>
       <c r="O138" s="1"/>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A139" s="6"/>
-      <c r="B139" s="6"/>
-      <c r="C139" s="7"/>
-      <c r="D139" s="7"/>
-      <c r="E139" s="1"/>
-      <c r="F139" s="5"/>
-      <c r="G139" s="5"/>
-      <c r="H139" s="1"/>
-      <c r="I139" s="1"/>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A139" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E139" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F139" s="5">
+        <v>7</v>
+      </c>
+      <c r="G139" s="5">
+        <v>5</v>
+      </c>
+      <c r="H139" s="1">
+        <v>7</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J139" s="1"/>
-      <c r="K139" s="9"/>
+      <c r="K139" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
       <c r="L139" s="1"/>
       <c r="M139" s="1"/>
       <c r="N139" s="1"/>
       <c r="O139" s="1"/>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A140" s="6"/>
-      <c r="B140" s="6"/>
-      <c r="C140" s="7"/>
-      <c r="D140" s="7"/>
-      <c r="E140" s="1"/>
-      <c r="F140" s="5"/>
-      <c r="G140" s="5"/>
-      <c r="H140" s="1"/>
-      <c r="I140" s="1"/>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A140" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E140" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F140" s="5">
+        <v>8</v>
+      </c>
+      <c r="G140" s="5">
+        <v>6</v>
+      </c>
+      <c r="H140" s="1">
+        <v>7</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J140" s="1"/>
-      <c r="K140" s="9"/>
+      <c r="K140" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
       <c r="L140" s="1"/>
       <c r="M140" s="1"/>
       <c r="N140" s="1"/>
       <c r="O140" s="1"/>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A141" s="6"/>
-      <c r="B141" s="6"/>
-      <c r="C141" s="7"/>
-      <c r="D141" s="7"/>
-      <c r="E141" s="1"/>
-      <c r="F141" s="5"/>
-      <c r="G141" s="5"/>
-      <c r="H141" s="1"/>
-      <c r="I141" s="1"/>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A141" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E141" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F141" s="5">
+        <v>7</v>
+      </c>
+      <c r="G141" s="5">
+        <v>5</v>
+      </c>
+      <c r="H141" s="1">
+        <v>7</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J141" s="1"/>
-      <c r="K141" s="9"/>
+      <c r="K141" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
       <c r="L141" s="1"/>
       <c r="M141" s="1"/>
       <c r="N141" s="1"/>
       <c r="O141" s="1"/>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A142" s="6"/>
-      <c r="B142" s="6"/>
-      <c r="C142" s="7"/>
-      <c r="D142" s="7"/>
-      <c r="E142" s="1"/>
-      <c r="F142" s="5"/>
-      <c r="G142" s="5"/>
-      <c r="H142" s="1"/>
-      <c r="I142" s="1"/>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A142" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E142" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F142" s="5">
+        <v>8</v>
+      </c>
+      <c r="G142" s="5">
+        <v>6</v>
+      </c>
+      <c r="H142" s="1">
+        <v>7</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J142" s="1"/>
-      <c r="K142" s="9"/>
+      <c r="K142" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
       <c r="L142" s="1"/>
       <c r="M142" s="1"/>
       <c r="N142" s="1"/>
       <c r="O142" s="1"/>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A143" s="6"/>
-      <c r="B143" s="6"/>
-      <c r="C143" s="7"/>
-      <c r="D143" s="7"/>
-      <c r="E143" s="1"/>
-      <c r="F143" s="5"/>
-      <c r="G143" s="5"/>
-      <c r="H143" s="1"/>
-      <c r="I143" s="1"/>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A143" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E143" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F143" s="5">
+        <v>7</v>
+      </c>
+      <c r="G143" s="5">
+        <v>4</v>
+      </c>
+      <c r="H143" s="1">
+        <v>7</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J143" s="1"/>
-      <c r="K143" s="9"/>
+      <c r="K143" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
       <c r="L143" s="1"/>
       <c r="M143" s="1"/>
       <c r="N143" s="1"/>
       <c r="O143" s="1"/>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A144" s="6"/>
-      <c r="B144" s="6"/>
-      <c r="C144" s="7"/>
-      <c r="D144" s="7"/>
-      <c r="E144" s="1"/>
-      <c r="F144" s="5"/>
-      <c r="G144" s="5"/>
-      <c r="H144" s="1"/>
-      <c r="I144" s="1"/>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A144" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E144" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F144" s="5">
+        <v>7</v>
+      </c>
+      <c r="G144" s="5">
+        <v>5</v>
+      </c>
+      <c r="H144" s="1">
+        <v>7</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J144" s="1"/>
-      <c r="K144" s="9"/>
+      <c r="K144" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
       <c r="L144" s="1"/>
       <c r="M144" s="1"/>
       <c r="N144" s="1"/>
       <c r="O144" s="1"/>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A145" s="6"/>
-      <c r="B145" s="6"/>
-      <c r="C145" s="7"/>
-      <c r="D145" s="7"/>
-      <c r="E145" s="1"/>
-      <c r="F145" s="5"/>
-      <c r="G145" s="5"/>
-      <c r="H145" s="1"/>
-      <c r="I145" s="1"/>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A145" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E145" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F145" s="5">
+        <v>7</v>
+      </c>
+      <c r="G145" s="5">
+        <v>3</v>
+      </c>
+      <c r="H145" s="1">
+        <v>7</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J145" s="1"/>
-      <c r="K145" s="9"/>
+      <c r="K145" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
       <c r="L145" s="1"/>
       <c r="M145" s="1"/>
       <c r="N145" s="1"/>
       <c r="O145" s="1"/>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A146" s="6"/>
-      <c r="B146" s="6"/>
-      <c r="C146" s="7"/>
-      <c r="D146" s="7"/>
-      <c r="E146" s="1"/>
-      <c r="F146" s="5"/>
-      <c r="G146" s="5"/>
-      <c r="H146" s="1"/>
-      <c r="I146" s="1"/>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A146" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E146" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F146" s="5">
+        <v>7</v>
+      </c>
+      <c r="G146" s="5">
+        <v>3</v>
+      </c>
+      <c r="H146" s="1">
+        <v>7</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J146" s="1"/>
-      <c r="K146" s="9"/>
+      <c r="K146" s="9" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
       <c r="L146" s="1"/>
       <c r="M146" s="1"/>
       <c r="N146" s="1"/>
       <c r="O146" s="1"/>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A147" s="6"/>
-      <c r="B147" s="6"/>
-      <c r="C147" s="7"/>
-      <c r="D147" s="7"/>
-      <c r="E147" s="1"/>
-      <c r="F147" s="5"/>
-      <c r="G147" s="5"/>
-      <c r="H147" s="1"/>
-      <c r="I147" s="1"/>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A147" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E147" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F147" s="5">
+        <v>7</v>
+      </c>
+      <c r="G147" s="5">
+        <v>5</v>
+      </c>
+      <c r="H147" s="1">
+        <v>7</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J147" s="1"/>
       <c r="K147" s="9"/>
       <c r="L147" s="1"/>
@@ -6149,16 +6479,35 @@
       <c r="N147" s="1"/>
       <c r="O147" s="1"/>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A148" s="6"/>
-      <c r="B148" s="6"/>
-      <c r="C148" s="7"/>
-      <c r="D148" s="7"/>
-      <c r="E148" s="1"/>
-      <c r="F148" s="5"/>
-      <c r="G148" s="5"/>
-      <c r="H148" s="1"/>
-      <c r="I148" s="1"/>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A148" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E148" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F148" s="5">
+        <v>7</v>
+      </c>
+      <c r="G148" s="5">
+        <v>5</v>
+      </c>
+      <c r="H148" s="1">
+        <v>7</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J148" s="1"/>
       <c r="K148" s="9"/>
       <c r="L148" s="1"/>
@@ -6166,16 +6515,35 @@
       <c r="N148" s="1"/>
       <c r="O148" s="1"/>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A149" s="6"/>
-      <c r="B149" s="6"/>
-      <c r="C149" s="7"/>
-      <c r="D149" s="7"/>
-      <c r="E149" s="1"/>
-      <c r="F149" s="5"/>
-      <c r="G149" s="5"/>
-      <c r="H149" s="1"/>
-      <c r="I149" s="1"/>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A149" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E149" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F149" s="5">
+        <v>7</v>
+      </c>
+      <c r="G149" s="5">
+        <v>2</v>
+      </c>
+      <c r="H149" s="1">
+        <v>7</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J149" s="1"/>
       <c r="K149" s="9"/>
       <c r="L149" s="1"/>
@@ -6183,16 +6551,35 @@
       <c r="N149" s="1"/>
       <c r="O149" s="1"/>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A150" s="6"/>
-      <c r="B150" s="6"/>
-      <c r="C150" s="7"/>
-      <c r="D150" s="7"/>
-      <c r="E150" s="1"/>
-      <c r="F150" s="5"/>
-      <c r="G150" s="5"/>
-      <c r="H150" s="1"/>
-      <c r="I150" s="1"/>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A150" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E150" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F150" s="5">
+        <v>7</v>
+      </c>
+      <c r="G150" s="5">
+        <v>5</v>
+      </c>
+      <c r="H150" s="1">
+        <v>7</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J150" s="1"/>
       <c r="K150" s="9"/>
       <c r="L150" s="1"/>
@@ -6200,16 +6587,35 @@
       <c r="N150" s="1"/>
       <c r="O150" s="1"/>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A151" s="6"/>
-      <c r="B151" s="6"/>
-      <c r="C151" s="7"/>
-      <c r="D151" s="7"/>
-      <c r="E151" s="1"/>
-      <c r="F151" s="5"/>
-      <c r="G151" s="5"/>
-      <c r="H151" s="1"/>
-      <c r="I151" s="1"/>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A151" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E151" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F151" s="5">
+        <v>9</v>
+      </c>
+      <c r="G151" s="5">
+        <v>7</v>
+      </c>
+      <c r="H151" s="1">
+        <v>7</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J151" s="1"/>
       <c r="K151" s="9"/>
       <c r="L151" s="1"/>
@@ -6217,16 +6623,35 @@
       <c r="N151" s="1"/>
       <c r="O151" s="1"/>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A152" s="6"/>
-      <c r="B152" s="6"/>
-      <c r="C152" s="7"/>
-      <c r="D152" s="7"/>
-      <c r="E152" s="1"/>
-      <c r="F152" s="5"/>
-      <c r="G152" s="5"/>
-      <c r="H152" s="1"/>
-      <c r="I152" s="1"/>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A152" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D152" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E152" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F152" s="5">
+        <v>7</v>
+      </c>
+      <c r="G152" s="5">
+        <v>4</v>
+      </c>
+      <c r="H152" s="1">
+        <v>7</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J152" s="1"/>
       <c r="K152" s="9"/>
       <c r="L152" s="1"/>
@@ -6234,16 +6659,35 @@
       <c r="N152" s="1"/>
       <c r="O152" s="1"/>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A153" s="6"/>
-      <c r="B153" s="6"/>
-      <c r="C153" s="7"/>
-      <c r="D153" s="7"/>
-      <c r="E153" s="1"/>
-      <c r="F153" s="5"/>
-      <c r="G153" s="5"/>
-      <c r="H153" s="1"/>
-      <c r="I153" s="1"/>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A153" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D153" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E153" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F153" s="5">
+        <v>11</v>
+      </c>
+      <c r="G153" s="5">
+        <v>6</v>
+      </c>
+      <c r="H153" s="1">
+        <v>11</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J153" s="1"/>
       <c r="K153" s="9"/>
       <c r="L153" s="1"/>
@@ -6251,16 +6695,35 @@
       <c r="N153" s="1"/>
       <c r="O153" s="1"/>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A154" s="6"/>
-      <c r="B154" s="6"/>
-      <c r="C154" s="7"/>
-      <c r="D154" s="7"/>
-      <c r="E154" s="1"/>
-      <c r="F154" s="5"/>
-      <c r="G154" s="5"/>
-      <c r="H154" s="1"/>
-      <c r="I154" s="1"/>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A154" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E154" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F154" s="5">
+        <v>11</v>
+      </c>
+      <c r="G154" s="5">
+        <v>9</v>
+      </c>
+      <c r="H154" s="1">
+        <v>11</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J154" s="1"/>
       <c r="K154" s="9"/>
       <c r="L154" s="1"/>
@@ -6268,16 +6731,35 @@
       <c r="N154" s="1"/>
       <c r="O154" s="1"/>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A155" s="6"/>
-      <c r="B155" s="6"/>
-      <c r="C155" s="7"/>
-      <c r="D155" s="7"/>
-      <c r="E155" s="1"/>
-      <c r="F155" s="5"/>
-      <c r="G155" s="5"/>
-      <c r="H155" s="1"/>
-      <c r="I155" s="1"/>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A155" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E155" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F155" s="5">
+        <v>11</v>
+      </c>
+      <c r="G155" s="5">
+        <v>8</v>
+      </c>
+      <c r="H155" s="1">
+        <v>11</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J155" s="1"/>
       <c r="K155" s="9"/>
       <c r="L155" s="1"/>
@@ -6285,16 +6767,35 @@
       <c r="N155" s="1"/>
       <c r="O155" s="1"/>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A156" s="6"/>
-      <c r="B156" s="6"/>
-      <c r="C156" s="7"/>
-      <c r="D156" s="7"/>
-      <c r="E156" s="1"/>
-      <c r="F156" s="5"/>
-      <c r="G156" s="5"/>
-      <c r="H156" s="1"/>
-      <c r="I156" s="1"/>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A156" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D156" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E156" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F156" s="5">
+        <v>11</v>
+      </c>
+      <c r="G156" s="5">
+        <v>7</v>
+      </c>
+      <c r="H156" s="1">
+        <v>11</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="J156" s="1"/>
       <c r="K156" s="9"/>
       <c r="L156" s="1"/>
@@ -6302,7 +6803,7 @@
       <c r="N156" s="1"/>
       <c r="O156" s="1"/>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A157" s="6"/>
       <c r="B157" s="6"/>
       <c r="C157" s="7"/>
@@ -6319,7 +6820,7 @@
       <c r="N157" s="1"/>
       <c r="O157" s="1"/>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A158" s="6"/>
       <c r="B158" s="6"/>
       <c r="C158" s="7"/>
@@ -6336,7 +6837,7 @@
       <c r="N158" s="1"/>
       <c r="O158" s="1"/>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A159" s="6"/>
       <c r="B159" s="6"/>
       <c r="C159" s="7"/>
@@ -6353,7 +6854,7 @@
       <c r="N159" s="1"/>
       <c r="O159" s="1"/>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A160" s="6"/>
       <c r="B160" s="6"/>
       <c r="C160" s="7"/>
@@ -6370,7 +6871,7 @@
       <c r="N160" s="1"/>
       <c r="O160" s="1"/>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A161" s="6"/>
       <c r="B161" s="6"/>
       <c r="C161" s="7"/>
@@ -6387,7 +6888,7 @@
       <c r="N161" s="1"/>
       <c r="O161" s="1"/>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A162" s="6"/>
       <c r="B162" s="6"/>
       <c r="C162" s="7"/>
@@ -6404,7 +6905,7 @@
       <c r="N162" s="1"/>
       <c r="O162" s="1"/>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A163" s="6"/>
       <c r="B163" s="6"/>
       <c r="C163" s="7"/>
@@ -6421,7 +6922,7 @@
       <c r="N163" s="1"/>
       <c r="O163" s="1"/>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A164" s="6"/>
       <c r="B164" s="6"/>
       <c r="C164" s="7"/>
@@ -6438,7 +6939,7 @@
       <c r="N164" s="1"/>
       <c r="O164" s="1"/>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A165" s="6"/>
       <c r="B165" s="6"/>
       <c r="C165" s="7"/>
@@ -6455,7 +6956,7 @@
       <c r="N165" s="1"/>
       <c r="O165" s="1"/>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A166" s="6"/>
       <c r="B166" s="6"/>
       <c r="C166" s="7"/>
@@ -6472,7 +6973,7 @@
       <c r="N166" s="1"/>
       <c r="O166" s="1"/>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A167" s="6"/>
       <c r="B167" s="6"/>
       <c r="C167" s="7"/>
@@ -6489,7 +6990,7 @@
       <c r="N167" s="1"/>
       <c r="O167" s="1"/>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A168" s="6"/>
       <c r="B168" s="6"/>
       <c r="C168" s="7"/>
@@ -6506,7 +7007,7 @@
       <c r="N168" s="1"/>
       <c r="O168" s="1"/>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A169" s="6"/>
       <c r="B169" s="6"/>
       <c r="C169" s="7"/>
@@ -6523,7 +7024,7 @@
       <c r="N169" s="1"/>
       <c r="O169" s="1"/>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A170" s="6"/>
       <c r="B170" s="6"/>
       <c r="C170" s="7"/>
@@ -6540,7 +7041,7 @@
       <c r="N170" s="1"/>
       <c r="O170" s="1"/>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A171" s="6"/>
       <c r="B171" s="6"/>
       <c r="C171" s="7"/>
@@ -6557,7 +7058,7 @@
       <c r="N171" s="1"/>
       <c r="O171" s="1"/>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A172" s="6"/>
       <c r="B172" s="6"/>
       <c r="C172" s="7"/>
@@ -6574,7 +7075,7 @@
       <c r="N172" s="1"/>
       <c r="O172" s="1"/>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A173" s="6"/>
       <c r="B173" s="6"/>
       <c r="C173" s="7"/>
@@ -6591,7 +7092,7 @@
       <c r="N173" s="1"/>
       <c r="O173" s="1"/>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A174" s="6"/>
       <c r="B174" s="6"/>
       <c r="C174" s="7"/>
@@ -6608,7 +7109,7 @@
       <c r="N174" s="1"/>
       <c r="O174" s="1"/>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A175" s="6"/>
       <c r="B175" s="6"/>
       <c r="C175" s="7"/>
@@ -6625,7 +7126,7 @@
       <c r="N175" s="1"/>
       <c r="O175" s="1"/>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A176" s="6"/>
       <c r="B176" s="6"/>
       <c r="C176" s="7"/>
@@ -6642,7 +7143,7 @@
       <c r="N176" s="1"/>
       <c r="O176" s="1"/>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A177" s="6"/>
       <c r="B177" s="6"/>
       <c r="C177" s="7"/>
@@ -6659,7 +7160,7 @@
       <c r="N177" s="1"/>
       <c r="O177" s="1"/>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A178" s="6"/>
       <c r="B178" s="6"/>
       <c r="C178" s="7"/>
@@ -6676,7 +7177,7 @@
       <c r="N178" s="1"/>
       <c r="O178" s="1"/>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A179" s="6"/>
       <c r="B179" s="6"/>
       <c r="C179" s="7"/>
@@ -6693,7 +7194,7 @@
       <c r="N179" s="1"/>
       <c r="O179" s="1"/>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A180" s="6"/>
       <c r="B180" s="6"/>
       <c r="C180" s="7"/>
@@ -6710,7 +7211,7 @@
       <c r="N180" s="1"/>
       <c r="O180" s="1"/>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A181" s="6"/>
       <c r="B181" s="6"/>
       <c r="C181" s="7"/>
@@ -6727,7 +7228,7 @@
       <c r="N181" s="1"/>
       <c r="O181" s="1"/>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A182" s="6"/>
       <c r="B182" s="6"/>
       <c r="C182" s="7"/>
@@ -6744,7 +7245,7 @@
       <c r="N182" s="1"/>
       <c r="O182" s="1"/>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A183" s="6"/>
       <c r="B183" s="6"/>
       <c r="C183" s="7"/>
@@ -6761,7 +7262,7 @@
       <c r="N183" s="1"/>
       <c r="O183" s="1"/>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A184" s="6"/>
       <c r="B184" s="6"/>
       <c r="C184" s="7"/>
@@ -6778,7 +7279,7 @@
       <c r="N184" s="1"/>
       <c r="O184" s="1"/>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A185" s="6"/>
       <c r="B185" s="6"/>
       <c r="C185" s="7"/>
@@ -6795,7 +7296,7 @@
       <c r="N185" s="1"/>
       <c r="O185" s="1"/>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A186" s="6"/>
       <c r="B186" s="6"/>
       <c r="C186" s="7"/>
@@ -6812,7 +7313,7 @@
       <c r="N186" s="1"/>
       <c r="O186" s="1"/>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A187" s="6"/>
       <c r="B187" s="6"/>
       <c r="C187" s="7"/>
@@ -6829,7 +7330,7 @@
       <c r="N187" s="1"/>
       <c r="O187" s="1"/>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A188" s="6"/>
       <c r="B188" s="6"/>
       <c r="C188" s="7"/>
@@ -6846,7 +7347,7 @@
       <c r="N188" s="1"/>
       <c r="O188" s="1"/>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A189" s="6"/>
       <c r="B189" s="6"/>
       <c r="C189" s="7"/>
@@ -6863,7 +7364,7 @@
       <c r="N189" s="1"/>
       <c r="O189" s="1"/>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A190" s="6"/>
       <c r="B190" s="6"/>
       <c r="C190" s="7"/>
@@ -6880,7 +7381,7 @@
       <c r="N190" s="1"/>
       <c r="O190" s="1"/>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A191" s="6"/>
       <c r="B191" s="6"/>
       <c r="C191" s="7"/>
@@ -6897,7 +7398,7 @@
       <c r="N191" s="1"/>
       <c r="O191" s="1"/>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A192" s="6"/>
       <c r="B192" s="6"/>
       <c r="C192" s="7"/>
@@ -6914,7 +7415,7 @@
       <c r="N192" s="1"/>
       <c r="O192" s="1"/>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A193" s="6"/>
       <c r="B193" s="6"/>
       <c r="C193" s="7"/>
@@ -6931,7 +7432,7 @@
       <c r="N193" s="1"/>
       <c r="O193" s="1"/>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A194" s="6"/>
       <c r="B194" s="6"/>
       <c r="C194" s="7"/>
@@ -6948,7 +7449,7 @@
       <c r="N194" s="1"/>
       <c r="O194" s="1"/>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A195" s="6"/>
       <c r="B195" s="6"/>
       <c r="C195" s="7"/>
@@ -6965,7 +7466,7 @@
       <c r="N195" s="1"/>
       <c r="O195" s="1"/>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A196" s="6"/>
       <c r="B196" s="6"/>
       <c r="C196" s="7"/>
@@ -6982,7 +7483,7 @@
       <c r="N196" s="1"/>
       <c r="O196" s="1"/>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A197" s="6"/>
       <c r="B197" s="6"/>
       <c r="C197" s="7"/>
@@ -6999,7 +7500,7 @@
       <c r="N197" s="1"/>
       <c r="O197" s="1"/>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A198" s="6"/>
       <c r="B198" s="6"/>
       <c r="C198" s="7"/>
@@ -7016,7 +7517,7 @@
       <c r="N198" s="1"/>
       <c r="O198" s="1"/>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A199" s="6"/>
       <c r="B199" s="6"/>
       <c r="C199" s="7"/>
@@ -7033,7 +7534,7 @@
       <c r="N199" s="1"/>
       <c r="O199" s="1"/>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A200" s="6"/>
       <c r="B200" s="6"/>
       <c r="C200" s="7"/>
@@ -7050,7 +7551,7 @@
       <c r="N200" s="1"/>
       <c r="O200" s="1"/>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A201" s="6"/>
       <c r="B201" s="6"/>
       <c r="C201" s="7"/>
@@ -7067,7 +7568,7 @@
       <c r="N201" s="1"/>
       <c r="O201" s="1"/>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A202" s="6"/>
       <c r="B202" s="6"/>
       <c r="C202" s="7"/>
@@ -7084,7 +7585,7 @@
       <c r="N202" s="1"/>
       <c r="O202" s="1"/>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A203" s="6"/>
       <c r="B203" s="6"/>
       <c r="C203" s="7"/>
@@ -7101,7 +7602,7 @@
       <c r="N203" s="1"/>
       <c r="O203" s="1"/>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A204" s="6"/>
       <c r="B204" s="6"/>
       <c r="C204" s="7"/>
@@ -7118,7 +7619,7 @@
       <c r="N204" s="1"/>
       <c r="O204" s="1"/>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A205" s="6"/>
       <c r="B205" s="6"/>
       <c r="C205" s="7"/>
@@ -7135,7 +7636,7 @@
       <c r="N205" s="1"/>
       <c r="O205" s="1"/>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A206" s="6"/>
       <c r="B206" s="6"/>
       <c r="C206" s="7"/>
@@ -7152,7 +7653,7 @@
       <c r="N206" s="1"/>
       <c r="O206" s="1"/>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A207" s="6"/>
       <c r="B207" s="6"/>
       <c r="C207" s="7"/>
@@ -7169,7 +7670,7 @@
       <c r="N207" s="1"/>
       <c r="O207" s="1"/>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A208" s="6"/>
       <c r="B208" s="6"/>
       <c r="C208" s="7"/>
@@ -7186,7 +7687,7 @@
       <c r="N208" s="1"/>
       <c r="O208" s="1"/>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A209" s="6"/>
       <c r="B209" s="6"/>
       <c r="C209" s="7"/>
@@ -7203,7 +7704,7 @@
       <c r="N209" s="1"/>
       <c r="O209" s="1"/>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A210" s="6"/>
       <c r="B210" s="6"/>
       <c r="C210" s="7"/>
@@ -7220,7 +7721,7 @@
       <c r="N210" s="1"/>
       <c r="O210" s="1"/>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A211" s="6"/>
       <c r="B211" s="6"/>
       <c r="C211" s="7"/>
@@ -7237,7 +7738,7 @@
       <c r="N211" s="1"/>
       <c r="O211" s="1"/>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A212" s="6"/>
       <c r="B212" s="6"/>
       <c r="C212" s="7"/>
@@ -7254,7 +7755,7 @@
       <c r="N212" s="1"/>
       <c r="O212" s="1"/>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A213" s="6"/>
       <c r="B213" s="6"/>
       <c r="C213" s="7"/>
@@ -7271,7 +7772,7 @@
       <c r="N213" s="1"/>
       <c r="O213" s="1"/>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A214" s="6"/>
       <c r="B214" s="6"/>
       <c r="C214" s="7"/>
@@ -7288,7 +7789,7 @@
       <c r="N214" s="1"/>
       <c r="O214" s="1"/>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A215" s="6"/>
       <c r="B215" s="6"/>
       <c r="C215" s="7"/>
@@ -7305,7 +7806,7 @@
       <c r="N215" s="1"/>
       <c r="O215" s="1"/>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A216" s="6"/>
       <c r="B216" s="6"/>
       <c r="C216" s="7"/>
@@ -7322,7 +7823,7 @@
       <c r="N216" s="1"/>
       <c r="O216" s="1"/>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A217" s="6"/>
       <c r="B217" s="6"/>
       <c r="C217" s="7"/>
@@ -7339,7 +7840,7 @@
       <c r="N217" s="1"/>
       <c r="O217" s="1"/>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A218" s="6"/>
       <c r="B218" s="6"/>
       <c r="C218" s="7"/>
@@ -7356,7 +7857,7 @@
       <c r="N218" s="1"/>
       <c r="O218" s="1"/>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A219" s="6"/>
       <c r="B219" s="6"/>
       <c r="C219" s="7"/>
@@ -7373,7 +7874,7 @@
       <c r="N219" s="1"/>
       <c r="O219" s="1"/>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A220" s="6"/>
       <c r="B220" s="6"/>
       <c r="C220" s="7"/>
@@ -7390,7 +7891,7 @@
       <c r="N220" s="1"/>
       <c r="O220" s="1"/>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A221" s="6"/>
       <c r="B221" s="6"/>
       <c r="C221" s="7"/>
@@ -7407,7 +7908,7 @@
       <c r="N221" s="1"/>
       <c r="O221" s="1"/>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A222" s="6"/>
       <c r="B222" s="6"/>
       <c r="C222" s="7"/>
@@ -7424,7 +7925,7 @@
       <c r="N222" s="1"/>
       <c r="O222" s="1"/>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A223" s="6"/>
       <c r="B223" s="6"/>
       <c r="C223" s="7"/>
@@ -7441,7 +7942,7 @@
       <c r="N223" s="1"/>
       <c r="O223" s="1"/>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A224" s="6"/>
       <c r="B224" s="6"/>
       <c r="C224" s="7"/>
@@ -7458,7 +7959,7 @@
       <c r="N224" s="1"/>
       <c r="O224" s="1"/>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A225" s="6"/>
       <c r="B225" s="6"/>
       <c r="C225" s="7"/>
@@ -7475,7 +7976,7 @@
       <c r="N225" s="1"/>
       <c r="O225" s="1"/>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A226" s="6"/>
       <c r="B226" s="6"/>
       <c r="C226" s="7"/>
@@ -7492,7 +7993,7 @@
       <c r="N226" s="1"/>
       <c r="O226" s="1"/>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A227" s="6"/>
       <c r="B227" s="6"/>
       <c r="C227" s="7"/>
@@ -7509,7 +8010,7 @@
       <c r="N227" s="1"/>
       <c r="O227" s="1"/>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A228" s="6"/>
       <c r="B228" s="6"/>
       <c r="C228" s="7"/>
@@ -7526,7 +8027,7 @@
       <c r="N228" s="1"/>
       <c r="O228" s="1"/>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A229" s="6"/>
       <c r="B229" s="6"/>
       <c r="C229" s="7"/>
@@ -7543,7 +8044,7 @@
       <c r="N229" s="1"/>
       <c r="O229" s="1"/>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A230" s="6"/>
       <c r="B230" s="6"/>
       <c r="C230" s="7"/>
@@ -7560,7 +8061,7 @@
       <c r="N230" s="1"/>
       <c r="O230" s="1"/>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A231" s="6"/>
       <c r="B231" s="6"/>
       <c r="C231" s="7"/>
@@ -7577,7 +8078,7 @@
       <c r="N231" s="1"/>
       <c r="O231" s="1"/>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A232" s="6"/>
       <c r="B232" s="6"/>
       <c r="C232" s="7"/>
@@ -7594,7 +8095,7 @@
       <c r="N232" s="1"/>
       <c r="O232" s="1"/>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A233" s="6"/>
       <c r="B233" s="6"/>
       <c r="C233" s="7"/>
@@ -7611,7 +8112,7 @@
       <c r="N233" s="1"/>
       <c r="O233" s="1"/>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A234" s="6"/>
       <c r="B234" s="6"/>
       <c r="C234" s="7"/>
@@ -7628,7 +8129,7 @@
       <c r="N234" s="1"/>
       <c r="O234" s="1"/>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A235" s="6"/>
       <c r="B235" s="6"/>
       <c r="C235" s="7"/>
@@ -7645,7 +8146,7 @@
       <c r="N235" s="1"/>
       <c r="O235" s="1"/>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A236" s="6"/>
       <c r="B236" s="6"/>
       <c r="C236" s="7"/>
@@ -7662,7 +8163,7 @@
       <c r="N236" s="1"/>
       <c r="O236" s="1"/>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A237" s="6"/>
       <c r="B237" s="6"/>
       <c r="C237" s="7"/>
@@ -7679,7 +8180,7 @@
       <c r="N237" s="1"/>
       <c r="O237" s="1"/>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A238" s="6"/>
       <c r="B238" s="6"/>
       <c r="C238" s="7"/>
@@ -7696,7 +8197,7 @@
       <c r="N238" s="1"/>
       <c r="O238" s="1"/>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A239" s="6"/>
       <c r="B239" s="6"/>
       <c r="C239" s="7"/>
@@ -7713,7 +8214,7 @@
       <c r="N239" s="1"/>
       <c r="O239" s="1"/>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A240" s="6"/>
       <c r="B240" s="6"/>
       <c r="C240" s="7"/>
@@ -7730,7 +8231,7 @@
       <c r="N240" s="1"/>
       <c r="O240" s="1"/>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A241" s="6"/>
       <c r="B241" s="6"/>
       <c r="C241" s="7"/>
@@ -7747,7 +8248,7 @@
       <c r="N241" s="1"/>
       <c r="O241" s="1"/>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A242" s="6"/>
       <c r="B242" s="6"/>
       <c r="C242" s="7"/>
@@ -7764,7 +8265,7 @@
       <c r="N242" s="1"/>
       <c r="O242" s="1"/>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A243" s="6"/>
       <c r="B243" s="6"/>
       <c r="C243" s="7"/>
@@ -7781,7 +8282,7 @@
       <c r="N243" s="1"/>
       <c r="O243" s="1"/>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A244" s="6"/>
       <c r="B244" s="6"/>
       <c r="C244" s="7"/>
@@ -7798,7 +8299,7 @@
       <c r="N244" s="1"/>
       <c r="O244" s="1"/>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A245" s="6"/>
       <c r="B245" s="6"/>
       <c r="C245" s="7"/>
@@ -7815,7 +8316,7 @@
       <c r="N245" s="1"/>
       <c r="O245" s="1"/>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A246" s="6"/>
       <c r="B246" s="6"/>
       <c r="C246" s="7"/>
@@ -7832,7 +8333,7 @@
       <c r="N246" s="1"/>
       <c r="O246" s="1"/>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A247" s="6"/>
       <c r="B247" s="6"/>
       <c r="C247" s="7"/>
@@ -7849,7 +8350,7 @@
       <c r="N247" s="1"/>
       <c r="O247" s="1"/>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A248" s="6"/>
       <c r="B248" s="6"/>
       <c r="C248" s="7"/>
@@ -7866,7 +8367,7 @@
       <c r="N248" s="1"/>
       <c r="O248" s="1"/>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A249" s="6"/>
       <c r="B249" s="6"/>
       <c r="C249" s="7"/>
@@ -7883,7 +8384,7 @@
       <c r="N249" s="1"/>
       <c r="O249" s="1"/>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A250" s="6"/>
       <c r="B250" s="6"/>
       <c r="C250" s="7"/>
@@ -7900,7 +8401,7 @@
       <c r="N250" s="1"/>
       <c r="O250" s="1"/>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A251" s="6"/>
       <c r="B251" s="6"/>
       <c r="C251" s="7"/>
@@ -7917,7 +8418,7 @@
       <c r="N251" s="1"/>
       <c r="O251" s="1"/>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A252" s="6"/>
       <c r="B252" s="6"/>
       <c r="C252" s="7"/>
@@ -7934,7 +8435,7 @@
       <c r="N252" s="1"/>
       <c r="O252" s="1"/>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A253" s="6"/>
       <c r="B253" s="6"/>
       <c r="C253" s="7"/>
@@ -7951,7 +8452,7 @@
       <c r="N253" s="1"/>
       <c r="O253" s="1"/>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A254" s="6"/>
       <c r="B254" s="6"/>
       <c r="C254" s="7"/>
@@ -7968,7 +8469,7 @@
       <c r="N254" s="1"/>
       <c r="O254" s="1"/>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A255" s="6"/>
       <c r="B255" s="6"/>
       <c r="C255" s="7"/>
@@ -7985,7 +8486,7 @@
       <c r="N255" s="1"/>
       <c r="O255" s="1"/>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A256" s="6"/>
       <c r="B256" s="6"/>
       <c r="C256" s="7"/>
@@ -8002,7 +8503,7 @@
       <c r="N256" s="1"/>
       <c r="O256" s="1"/>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A257" s="6"/>
       <c r="B257" s="6"/>
       <c r="C257" s="7"/>
@@ -8019,7 +8520,7 @@
       <c r="N257" s="1"/>
       <c r="O257" s="1"/>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A258" s="6"/>
       <c r="B258" s="6"/>
       <c r="C258" s="7"/>
@@ -8036,7 +8537,7 @@
       <c r="N258" s="1"/>
       <c r="O258" s="1"/>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A259" s="6"/>
       <c r="B259" s="6"/>
       <c r="C259" s="7"/>
@@ -8053,7 +8554,7 @@
       <c r="N259" s="1"/>
       <c r="O259" s="1"/>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A260" s="6"/>
       <c r="B260" s="6"/>
       <c r="C260" s="7"/>
@@ -8070,7 +8571,7 @@
       <c r="N260" s="1"/>
       <c r="O260" s="1"/>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A261" s="6"/>
       <c r="B261" s="6"/>
       <c r="C261" s="7"/>
@@ -8087,7 +8588,7 @@
       <c r="N261" s="1"/>
       <c r="O261" s="1"/>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A262" s="6"/>
       <c r="B262" s="6"/>
       <c r="C262" s="7"/>
@@ -8104,7 +8605,7 @@
       <c r="N262" s="1"/>
       <c r="O262" s="1"/>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A263" s="6"/>
       <c r="B263" s="6"/>
       <c r="C263" s="7"/>
@@ -8121,7 +8622,7 @@
       <c r="N263" s="1"/>
       <c r="O263" s="1"/>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A264" s="6"/>
       <c r="B264" s="6"/>
       <c r="C264" s="7"/>
@@ -8138,7 +8639,7 @@
       <c r="N264" s="1"/>
       <c r="O264" s="1"/>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A265" s="6"/>
       <c r="B265" s="6"/>
       <c r="C265" s="7"/>
@@ -8155,7 +8656,7 @@
       <c r="N265" s="1"/>
       <c r="O265" s="1"/>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A266" s="6"/>
       <c r="B266" s="6"/>
       <c r="C266" s="7"/>
@@ -8172,7 +8673,7 @@
       <c r="N266" s="1"/>
       <c r="O266" s="1"/>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A267" s="6"/>
       <c r="B267" s="6"/>
       <c r="C267" s="7"/>
@@ -8189,7 +8690,7 @@
       <c r="N267" s="1"/>
       <c r="O267" s="1"/>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A268" s="6"/>
       <c r="B268" s="6"/>
       <c r="C268" s="7"/>
@@ -8206,7 +8707,7 @@
       <c r="N268" s="1"/>
       <c r="O268" s="1"/>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A269" s="6"/>
       <c r="B269" s="6"/>
       <c r="C269" s="7"/>
@@ -8223,7 +8724,7 @@
       <c r="N269" s="1"/>
       <c r="O269" s="1"/>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A270" s="6"/>
       <c r="B270" s="6"/>
       <c r="C270" s="7"/>
@@ -8240,7 +8741,7 @@
       <c r="N270" s="1"/>
       <c r="O270" s="1"/>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A271" s="6"/>
       <c r="B271" s="6"/>
       <c r="C271" s="7"/>
@@ -8257,7 +8758,7 @@
       <c r="N271" s="1"/>
       <c r="O271" s="1"/>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A272" s="6"/>
       <c r="B272" s="6"/>
       <c r="C272" s="7"/>
@@ -8274,7 +8775,7 @@
       <c r="N272" s="1"/>
       <c r="O272" s="1"/>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A273" s="6"/>
       <c r="B273" s="6"/>
       <c r="C273" s="7"/>
@@ -8291,7 +8792,7 @@
       <c r="N273" s="1"/>
       <c r="O273" s="1"/>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A274" s="6"/>
       <c r="B274" s="6"/>
       <c r="C274" s="7"/>
@@ -8308,7 +8809,7 @@
       <c r="N274" s="1"/>
       <c r="O274" s="1"/>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A275" s="6"/>
       <c r="B275" s="6"/>
       <c r="C275" s="7"/>
@@ -8325,7 +8826,7 @@
       <c r="N275" s="1"/>
       <c r="O275" s="1"/>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A276" s="6"/>
       <c r="B276" s="6"/>
       <c r="C276" s="7"/>
@@ -8342,7 +8843,7 @@
       <c r="N276" s="1"/>
       <c r="O276" s="1"/>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A277" s="6"/>
       <c r="B277" s="6"/>
       <c r="C277" s="7"/>
@@ -8359,7 +8860,7 @@
       <c r="N277" s="1"/>
       <c r="O277" s="1"/>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A278" s="6"/>
       <c r="B278" s="6"/>
       <c r="C278" s="7"/>
@@ -8376,7 +8877,7 @@
       <c r="N278" s="1"/>
       <c r="O278" s="1"/>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A279" s="6"/>
       <c r="B279" s="6"/>
       <c r="C279" s="7"/>
@@ -8393,7 +8894,7 @@
       <c r="N279" s="1"/>
       <c r="O279" s="1"/>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A280" s="6"/>
       <c r="B280" s="6"/>
       <c r="C280" s="7"/>
@@ -8410,7 +8911,7 @@
       <c r="N280" s="1"/>
       <c r="O280" s="1"/>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A281" s="6"/>
       <c r="B281" s="6"/>
       <c r="C281" s="7"/>
@@ -8427,7 +8928,7 @@
       <c r="N281" s="1"/>
       <c r="O281" s="1"/>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A282" s="6"/>
       <c r="B282" s="6"/>
       <c r="C282" s="7"/>
@@ -8444,7 +8945,7 @@
       <c r="N282" s="1"/>
       <c r="O282" s="1"/>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A283" s="6"/>
       <c r="B283" s="6"/>
       <c r="C283" s="7"/>
@@ -8461,7 +8962,7 @@
       <c r="N283" s="1"/>
       <c r="O283" s="1"/>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A284" s="6"/>
       <c r="B284" s="6"/>
       <c r="C284" s="7"/>
@@ -8478,7 +8979,7 @@
       <c r="N284" s="1"/>
       <c r="O284" s="1"/>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A285" s="6"/>
       <c r="B285" s="6"/>
       <c r="C285" s="7"/>
@@ -8495,7 +8996,7 @@
       <c r="N285" s="1"/>
       <c r="O285" s="1"/>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A286" s="6"/>
       <c r="B286" s="6"/>
       <c r="C286" s="7"/>
@@ -8512,7 +9013,7 @@
       <c r="N286" s="1"/>
       <c r="O286" s="1"/>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A287" s="6"/>
       <c r="B287" s="6"/>
       <c r="C287" s="7"/>
@@ -8529,7 +9030,7 @@
       <c r="N287" s="1"/>
       <c r="O287" s="1"/>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A288" s="6"/>
       <c r="B288" s="6"/>
       <c r="C288" s="7"/>
@@ -8546,7 +9047,7 @@
       <c r="N288" s="1"/>
       <c r="O288" s="1"/>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A289" s="6"/>
       <c r="B289" s="6"/>
       <c r="C289" s="7"/>
@@ -8563,7 +9064,7 @@
       <c r="N289" s="1"/>
       <c r="O289" s="1"/>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A290" s="6"/>
       <c r="B290" s="6"/>
       <c r="C290" s="7"/>
@@ -8580,7 +9081,7 @@
       <c r="N290" s="1"/>
       <c r="O290" s="1"/>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A291" s="6"/>
       <c r="B291" s="6"/>
       <c r="C291" s="7"/>
@@ -8597,7 +9098,7 @@
       <c r="N291" s="1"/>
       <c r="O291" s="1"/>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A292" s="6"/>
       <c r="B292" s="6"/>
       <c r="C292" s="7"/>
@@ -8614,7 +9115,7 @@
       <c r="N292" s="1"/>
       <c r="O292" s="1"/>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A293" s="6"/>
       <c r="B293" s="6"/>
       <c r="C293" s="7"/>
@@ -8631,7 +9132,7 @@
       <c r="N293" s="1"/>
       <c r="O293" s="1"/>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A294" s="6"/>
       <c r="B294" s="6"/>
       <c r="C294" s="7"/>
@@ -8648,7 +9149,7 @@
       <c r="N294" s="1"/>
       <c r="O294" s="1"/>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A295" s="6"/>
       <c r="B295" s="6"/>
       <c r="C295" s="7"/>
@@ -8665,7 +9166,7 @@
       <c r="N295" s="1"/>
       <c r="O295" s="1"/>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A296" s="6"/>
       <c r="B296" s="6"/>
       <c r="C296" s="7"/>
@@ -8682,7 +9183,7 @@
       <c r="N296" s="1"/>
       <c r="O296" s="1"/>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A297" s="6"/>
       <c r="B297" s="6"/>
       <c r="C297" s="7"/>
@@ -8699,7 +9200,7 @@
       <c r="N297" s="1"/>
       <c r="O297" s="1"/>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A298" s="6"/>
       <c r="B298" s="6"/>
       <c r="C298" s="7"/>
@@ -8716,7 +9217,7 @@
       <c r="N298" s="1"/>
       <c r="O298" s="1"/>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A299" s="6"/>
       <c r="B299" s="6"/>
       <c r="C299" s="7"/>
@@ -8733,7 +9234,7 @@
       <c r="N299" s="1"/>
       <c r="O299" s="1"/>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A300" s="6"/>
       <c r="B300" s="6"/>
       <c r="C300" s="7"/>
@@ -8750,7 +9251,7 @@
       <c r="N300" s="1"/>
       <c r="O300" s="1"/>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A301" s="6"/>
       <c r="B301" s="6"/>
       <c r="C301" s="7"/>
@@ -8767,7 +9268,7 @@
       <c r="N301" s="1"/>
       <c r="O301" s="1"/>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A302" s="6"/>
       <c r="B302" s="6"/>
       <c r="C302" s="7"/>
@@ -8784,7 +9285,7 @@
       <c r="N302" s="1"/>
       <c r="O302" s="1"/>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A303" s="6"/>
       <c r="B303" s="6"/>
       <c r="C303" s="7"/>
@@ -8801,7 +9302,7 @@
       <c r="N303" s="1"/>
       <c r="O303" s="1"/>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A304" s="6"/>
       <c r="B304" s="6"/>
       <c r="C304" s="7"/>
@@ -8818,7 +9319,7 @@
       <c r="N304" s="1"/>
       <c r="O304" s="1"/>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A305" s="6"/>
       <c r="B305" s="6"/>
       <c r="C305" s="7"/>
@@ -8835,7 +9336,7 @@
       <c r="N305" s="1"/>
       <c r="O305" s="1"/>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A306" s="6"/>
       <c r="B306" s="6"/>
       <c r="C306" s="7"/>
@@ -8852,7 +9353,7 @@
       <c r="N306" s="1"/>
       <c r="O306" s="1"/>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A307" s="6"/>
       <c r="B307" s="6"/>
       <c r="C307" s="7"/>
@@ -8869,7 +9370,7 @@
       <c r="N307" s="1"/>
       <c r="O307" s="1"/>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A308" s="6"/>
       <c r="B308" s="6"/>
       <c r="C308" s="7"/>
@@ -8886,7 +9387,7 @@
       <c r="N308" s="1"/>
       <c r="O308" s="1"/>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A309" s="6"/>
       <c r="B309" s="6"/>
       <c r="C309" s="7"/>
@@ -8903,7 +9404,7 @@
       <c r="N309" s="1"/>
       <c r="O309" s="1"/>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A310" s="6"/>
       <c r="B310" s="6"/>
       <c r="C310" s="7"/>
@@ -8920,7 +9421,7 @@
       <c r="N310" s="1"/>
       <c r="O310" s="1"/>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A311" s="6"/>
       <c r="B311" s="6"/>
       <c r="C311" s="7"/>
@@ -8937,7 +9438,7 @@
       <c r="N311" s="1"/>
       <c r="O311" s="1"/>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A312" s="6"/>
       <c r="B312" s="6"/>
       <c r="C312" s="7"/>
@@ -8954,7 +9455,7 @@
       <c r="N312" s="1"/>
       <c r="O312" s="1"/>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A313" s="6"/>
       <c r="B313" s="6"/>
       <c r="C313" s="7"/>
@@ -8971,7 +9472,7 @@
       <c r="N313" s="1"/>
       <c r="O313" s="1"/>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A314" s="6"/>
       <c r="B314" s="6"/>
       <c r="C314" s="7"/>
@@ -8988,7 +9489,7 @@
       <c r="N314" s="1"/>
       <c r="O314" s="1"/>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A315" s="6"/>
       <c r="B315" s="6"/>
       <c r="C315" s="7"/>
@@ -9005,7 +9506,7 @@
       <c r="N315" s="1"/>
       <c r="O315" s="1"/>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A316" s="6"/>
       <c r="B316" s="6"/>
       <c r="C316" s="7"/>
@@ -9022,7 +9523,7 @@
       <c r="N316" s="1"/>
       <c r="O316" s="1"/>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A317" s="6"/>
       <c r="B317" s="6"/>
       <c r="C317" s="7"/>
@@ -9039,7 +9540,7 @@
       <c r="N317" s="1"/>
       <c r="O317" s="1"/>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A318" s="6"/>
       <c r="B318" s="6"/>
       <c r="C318" s="7"/>
@@ -9056,7 +9557,7 @@
       <c r="N318" s="1"/>
       <c r="O318" s="1"/>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A319" s="6"/>
       <c r="B319" s="6"/>
       <c r="C319" s="7"/>
@@ -9073,7 +9574,7 @@
       <c r="N319" s="1"/>
       <c r="O319" s="1"/>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A320" s="6"/>
       <c r="B320" s="6"/>
       <c r="C320" s="7"/>
@@ -9090,7 +9591,7 @@
       <c r="N320" s="1"/>
       <c r="O320" s="1"/>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A321" s="6"/>
       <c r="B321" s="6"/>
       <c r="C321" s="7"/>
@@ -9107,7 +9608,7 @@
       <c r="N321" s="1"/>
       <c r="O321" s="1"/>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A322" s="6"/>
       <c r="B322" s="6"/>
       <c r="C322" s="7"/>
@@ -9124,7 +9625,7 @@
       <c r="N322" s="1"/>
       <c r="O322" s="1"/>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A323" s="6"/>
       <c r="B323" s="6"/>
       <c r="C323" s="7"/>
@@ -9141,7 +9642,7 @@
       <c r="N323" s="1"/>
       <c r="O323" s="1"/>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A324" s="6"/>
       <c r="B324" s="6"/>
       <c r="C324" s="7"/>
@@ -9158,7 +9659,7 @@
       <c r="N324" s="1"/>
       <c r="O324" s="1"/>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A325" s="6"/>
       <c r="B325" s="6"/>
       <c r="C325" s="7"/>
@@ -9175,7 +9676,7 @@
       <c r="N325" s="1"/>
       <c r="O325" s="1"/>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A326" s="6"/>
       <c r="B326" s="6"/>
       <c r="C326" s="7"/>
@@ -9192,7 +9693,7 @@
       <c r="N326" s="1"/>
       <c r="O326" s="1"/>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A327" s="6"/>
       <c r="B327" s="6"/>
       <c r="C327" s="7"/>
@@ -9209,7 +9710,7 @@
       <c r="N327" s="1"/>
       <c r="O327" s="1"/>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A328" s="6"/>
       <c r="B328" s="6"/>
       <c r="C328" s="7"/>
@@ -9226,7 +9727,7 @@
       <c r="N328" s="1"/>
       <c r="O328" s="1"/>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A329" s="6"/>
       <c r="B329" s="6"/>
       <c r="C329" s="7"/>
@@ -9243,7 +9744,7 @@
       <c r="N329" s="1"/>
       <c r="O329" s="1"/>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A330" s="6"/>
       <c r="B330" s="6"/>
       <c r="C330" s="7"/>
@@ -9260,7 +9761,7 @@
       <c r="N330" s="1"/>
       <c r="O330" s="1"/>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A331" s="6"/>
       <c r="B331" s="6"/>
       <c r="C331" s="7"/>
@@ -9277,7 +9778,7 @@
       <c r="N331" s="1"/>
       <c r="O331" s="1"/>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A332" s="6"/>
       <c r="B332" s="6"/>
       <c r="C332" s="7"/>
@@ -9294,7 +9795,7 @@
       <c r="N332" s="1"/>
       <c r="O332" s="1"/>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A333" s="6"/>
       <c r="B333" s="6"/>
       <c r="C333" s="7"/>
@@ -9311,7 +9812,7 @@
       <c r="N333" s="1"/>
       <c r="O333" s="1"/>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A334" s="6"/>
       <c r="B334" s="6"/>
       <c r="C334" s="7"/>
@@ -9328,7 +9829,7 @@
       <c r="N334" s="1"/>
       <c r="O334" s="1"/>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A335" s="6"/>
       <c r="B335" s="6"/>
       <c r="C335" s="7"/>
@@ -9345,7 +9846,7 @@
       <c r="N335" s="1"/>
       <c r="O335" s="1"/>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A336" s="6"/>
       <c r="B336" s="6"/>
       <c r="C336" s="7"/>
@@ -9362,7 +9863,7 @@
       <c r="N336" s="1"/>
       <c r="O336" s="1"/>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A337" s="6"/>
       <c r="B337" s="6"/>
       <c r="C337" s="7"/>
@@ -9379,7 +9880,7 @@
       <c r="N337" s="1"/>
       <c r="O337" s="1"/>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A338" s="6"/>
       <c r="B338" s="6"/>
       <c r="C338" s="7"/>
@@ -9396,7 +9897,7 @@
       <c r="N338" s="1"/>
       <c r="O338" s="1"/>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A339" s="6"/>
       <c r="B339" s="6"/>
       <c r="C339" s="7"/>
@@ -9413,7 +9914,7 @@
       <c r="N339" s="1"/>
       <c r="O339" s="1"/>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A340" s="6"/>
       <c r="B340" s="6"/>
       <c r="C340" s="7"/>
@@ -9430,7 +9931,7 @@
       <c r="N340" s="1"/>
       <c r="O340" s="1"/>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A341" s="6"/>
       <c r="B341" s="6"/>
       <c r="C341" s="7"/>
@@ -9447,7 +9948,7 @@
       <c r="N341" s="1"/>
       <c r="O341" s="1"/>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A342" s="6"/>
       <c r="B342" s="6"/>
       <c r="C342" s="7"/>
@@ -9464,7 +9965,7 @@
       <c r="N342" s="1"/>
       <c r="O342" s="1"/>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A343" s="6"/>
       <c r="B343" s="6"/>
       <c r="C343" s="7"/>
@@ -9481,7 +9982,7 @@
       <c r="N343" s="1"/>
       <c r="O343" s="1"/>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A344" s="6"/>
       <c r="B344" s="6"/>
       <c r="C344" s="7"/>
@@ -9498,7 +9999,7 @@
       <c r="N344" s="1"/>
       <c r="O344" s="1"/>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A345" s="6"/>
       <c r="B345" s="6"/>
       <c r="C345" s="7"/>
@@ -9515,7 +10016,7 @@
       <c r="N345" s="1"/>
       <c r="O345" s="1"/>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A346" s="6"/>
       <c r="B346" s="6"/>
       <c r="C346" s="7"/>
@@ -9532,7 +10033,7 @@
       <c r="N346" s="1"/>
       <c r="O346" s="1"/>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A347" s="6"/>
       <c r="B347" s="6"/>
       <c r="C347" s="7"/>
@@ -9549,7 +10050,7 @@
       <c r="N347" s="1"/>
       <c r="O347" s="1"/>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A348" s="6"/>
       <c r="B348" s="6"/>
       <c r="C348" s="7"/>
@@ -9566,7 +10067,7 @@
       <c r="N348" s="1"/>
       <c r="O348" s="1"/>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A349" s="6"/>
       <c r="B349" s="6"/>
       <c r="C349" s="7"/>
@@ -9583,7 +10084,7 @@
       <c r="N349" s="1"/>
       <c r="O349" s="1"/>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A350" s="6"/>
       <c r="B350" s="6"/>
       <c r="C350" s="7"/>
@@ -9600,7 +10101,7 @@
       <c r="N350" s="1"/>
       <c r="O350" s="1"/>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A351" s="6"/>
       <c r="B351" s="6"/>
       <c r="C351" s="7"/>
@@ -9617,7 +10118,7 @@
       <c r="N351" s="1"/>
       <c r="O351" s="1"/>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A352" s="6"/>
       <c r="B352" s="6"/>
       <c r="C352" s="7"/>
@@ -9634,7 +10135,7 @@
       <c r="N352" s="1"/>
       <c r="O352" s="1"/>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A353" s="6"/>
       <c r="B353" s="6"/>
       <c r="C353" s="7"/>
@@ -9651,7 +10152,7 @@
       <c r="N353" s="1"/>
       <c r="O353" s="1"/>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A354" s="6"/>
       <c r="B354" s="6"/>
       <c r="C354" s="7"/>
@@ -9668,7 +10169,7 @@
       <c r="N354" s="1"/>
       <c r="O354" s="1"/>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A355" s="6"/>
       <c r="B355" s="6"/>
       <c r="C355" s="7"/>
@@ -9685,7 +10186,7 @@
       <c r="N355" s="1"/>
       <c r="O355" s="1"/>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A356" s="6"/>
       <c r="B356" s="6"/>
       <c r="C356" s="7"/>
@@ -9702,7 +10203,7 @@
       <c r="N356" s="1"/>
       <c r="O356" s="1"/>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A357" s="6"/>
       <c r="B357" s="6"/>
       <c r="C357" s="7"/>
@@ -9719,7 +10220,7 @@
       <c r="N357" s="1"/>
       <c r="O357" s="1"/>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A358" s="6"/>
       <c r="B358" s="6"/>
       <c r="C358" s="7"/>
@@ -9736,7 +10237,7 @@
       <c r="N358" s="1"/>
       <c r="O358" s="1"/>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A359" s="6"/>
       <c r="B359" s="6"/>
       <c r="C359" s="7"/>
@@ -9753,7 +10254,7 @@
       <c r="N359" s="1"/>
       <c r="O359" s="1"/>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A360" s="6"/>
       <c r="B360" s="6"/>
       <c r="C360" s="7"/>
@@ -9770,7 +10271,7 @@
       <c r="N360" s="1"/>
       <c r="O360" s="1"/>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A361" s="6"/>
       <c r="B361" s="6"/>
       <c r="C361" s="7"/>
@@ -9787,7 +10288,7 @@
       <c r="N361" s="1"/>
       <c r="O361" s="1"/>
     </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A362" s="6"/>
       <c r="B362" s="6"/>
       <c r="C362" s="7"/>
@@ -9804,7 +10305,7 @@
       <c r="N362" s="1"/>
       <c r="O362" s="1"/>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A363" s="6"/>
       <c r="B363" s="6"/>
       <c r="C363" s="7"/>
@@ -9821,7 +10322,7 @@
       <c r="N363" s="1"/>
       <c r="O363" s="1"/>
     </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A364" s="6"/>
       <c r="B364" s="6"/>
       <c r="C364" s="7"/>
@@ -9838,7 +10339,7 @@
       <c r="N364" s="1"/>
       <c r="O364" s="1"/>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A365" s="6"/>
       <c r="B365" s="6"/>
       <c r="C365" s="7"/>
@@ -9855,7 +10356,7 @@
       <c r="N365" s="1"/>
       <c r="O365" s="1"/>
     </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A366" s="6"/>
       <c r="B366" s="6"/>
       <c r="C366" s="7"/>
@@ -9872,7 +10373,7 @@
       <c r="N366" s="1"/>
       <c r="O366" s="1"/>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A367" s="6"/>
       <c r="B367" s="6"/>
       <c r="C367" s="7"/>
@@ -9889,7 +10390,7 @@
       <c r="N367" s="1"/>
       <c r="O367" s="1"/>
     </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A368" s="6"/>
       <c r="B368" s="6"/>
       <c r="C368" s="7"/>
@@ -9906,7 +10407,7 @@
       <c r="N368" s="1"/>
       <c r="O368" s="1"/>
     </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A369" s="6"/>
       <c r="B369" s="6"/>
       <c r="C369" s="7"/>
@@ -9923,7 +10424,7 @@
       <c r="N369" s="1"/>
       <c r="O369" s="1"/>
     </row>
-    <row r="370" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A370" s="6"/>
       <c r="B370" s="6"/>
       <c r="C370" s="7"/>
@@ -9940,7 +10441,7 @@
       <c r="N370" s="1"/>
       <c r="O370" s="1"/>
     </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A371" s="6"/>
       <c r="B371" s="6"/>
       <c r="C371" s="7"/>
@@ -9957,7 +10458,7 @@
       <c r="N371" s="1"/>
       <c r="O371" s="1"/>
     </row>
-    <row r="372" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A372" s="6"/>
       <c r="B372" s="6"/>
       <c r="C372" s="7"/>
@@ -9974,7 +10475,7 @@
       <c r="N372" s="1"/>
       <c r="O372" s="1"/>
     </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A373" s="6"/>
       <c r="B373" s="6"/>
       <c r="C373" s="7"/>
@@ -9991,7 +10492,7 @@
       <c r="N373" s="1"/>
       <c r="O373" s="1"/>
     </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A374" s="6"/>
       <c r="B374" s="6"/>
       <c r="C374" s="7"/>
@@ -10008,7 +10509,7 @@
       <c r="N374" s="1"/>
       <c r="O374" s="1"/>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A375" s="6"/>
       <c r="B375" s="6"/>
       <c r="C375" s="7"/>
@@ -10025,7 +10526,7 @@
       <c r="N375" s="1"/>
       <c r="O375" s="1"/>
     </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A376" s="6"/>
       <c r="B376" s="6"/>
       <c r="C376" s="7"/>
@@ -10042,7 +10543,7 @@
       <c r="N376" s="1"/>
       <c r="O376" s="1"/>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A377" s="6"/>
       <c r="B377" s="6"/>
       <c r="C377" s="7"/>
@@ -10059,7 +10560,7 @@
       <c r="N377" s="1"/>
       <c r="O377" s="1"/>
     </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A378" s="6"/>
       <c r="B378" s="6"/>
       <c r="C378" s="7"/>
@@ -10076,7 +10577,7 @@
       <c r="N378" s="1"/>
       <c r="O378" s="1"/>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A379" s="6"/>
       <c r="B379" s="6"/>
       <c r="C379" s="7"/>
@@ -10093,7 +10594,7 @@
       <c r="N379" s="1"/>
       <c r="O379" s="1"/>
     </row>
-    <row r="380" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A380" s="6"/>
       <c r="B380" s="6"/>
       <c r="C380" s="7"/>
@@ -10110,7 +10611,7 @@
       <c r="N380" s="1"/>
       <c r="O380" s="1"/>
     </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A381" s="6"/>
       <c r="B381" s="6"/>
       <c r="C381" s="7"/>
@@ -10127,7 +10628,7 @@
       <c r="N381" s="1"/>
       <c r="O381" s="1"/>
     </row>
-    <row r="382" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A382" s="6"/>
       <c r="B382" s="6"/>
       <c r="C382" s="7"/>
@@ -10144,7 +10645,7 @@
       <c r="N382" s="1"/>
       <c r="O382" s="1"/>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A383" s="6"/>
       <c r="B383" s="6"/>
       <c r="C383" s="7"/>
@@ -10161,7 +10662,7 @@
       <c r="N383" s="1"/>
       <c r="O383" s="1"/>
     </row>
-    <row r="384" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A384" s="6"/>
       <c r="B384" s="6"/>
       <c r="C384" s="7"/>
@@ -10178,7 +10679,7 @@
       <c r="N384" s="1"/>
       <c r="O384" s="1"/>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A385" s="6"/>
       <c r="B385" s="6"/>
       <c r="C385" s="7"/>
@@ -10195,7 +10696,7 @@
       <c r="N385" s="1"/>
       <c r="O385" s="1"/>
     </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A386" s="6"/>
       <c r="B386" s="6"/>
       <c r="C386" s="7"/>
@@ -10212,7 +10713,7 @@
       <c r="N386" s="1"/>
       <c r="O386" s="1"/>
     </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A387" s="6"/>
       <c r="B387" s="6"/>
       <c r="C387" s="7"/>
@@ -10229,7 +10730,7 @@
       <c r="N387" s="1"/>
       <c r="O387" s="1"/>
     </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A388" s="6"/>
       <c r="B388" s="6"/>
       <c r="C388" s="7"/>
@@ -10246,7 +10747,7 @@
       <c r="N388" s="1"/>
       <c r="O388" s="1"/>
     </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A389" s="6"/>
       <c r="B389" s="6"/>
       <c r="C389" s="7"/>
@@ -10263,7 +10764,7 @@
       <c r="N389" s="1"/>
       <c r="O389" s="1"/>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A390" s="6"/>
       <c r="B390" s="6"/>
       <c r="C390" s="7"/>
@@ -10280,7 +10781,7 @@
       <c r="N390" s="1"/>
       <c r="O390" s="1"/>
     </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A391" s="6"/>
       <c r="B391" s="6"/>
       <c r="C391" s="7"/>
@@ -10297,7 +10798,7 @@
       <c r="N391" s="1"/>
       <c r="O391" s="1"/>
     </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A392" s="6"/>
       <c r="B392" s="6"/>
       <c r="C392" s="7"/>
@@ -10314,7 +10815,7 @@
       <c r="N392" s="1"/>
       <c r="O392" s="1"/>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A393" s="6"/>
       <c r="B393" s="6"/>
       <c r="C393" s="7"/>
@@ -10331,7 +10832,7 @@
       <c r="N393" s="1"/>
       <c r="O393" s="1"/>
     </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A394" s="6"/>
       <c r="B394" s="6"/>
       <c r="C394" s="7"/>
@@ -10348,7 +10849,7 @@
       <c r="N394" s="1"/>
       <c r="O394" s="1"/>
     </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A395" s="6"/>
       <c r="B395" s="6"/>
       <c r="C395" s="7"/>
@@ -10365,7 +10866,7 @@
       <c r="N395" s="1"/>
       <c r="O395" s="1"/>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A396" s="6"/>
       <c r="B396" s="6"/>
       <c r="C396" s="7"/>
@@ -10382,7 +10883,7 @@
       <c r="N396" s="1"/>
       <c r="O396" s="1"/>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A397" s="6"/>
       <c r="B397" s="6"/>
       <c r="C397" s="7"/>
@@ -10399,7 +10900,7 @@
       <c r="N397" s="1"/>
       <c r="O397" s="1"/>
     </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A398" s="6"/>
       <c r="B398" s="6"/>
       <c r="C398" s="7"/>
@@ -10416,7 +10917,7 @@
       <c r="N398" s="1"/>
       <c r="O398" s="1"/>
     </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A399" s="6"/>
       <c r="B399" s="6"/>
       <c r="C399" s="7"/>
@@ -10433,7 +10934,7 @@
       <c r="N399" s="1"/>
       <c r="O399" s="1"/>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A400" s="6"/>
       <c r="B400" s="6"/>
       <c r="C400" s="7"/>
@@ -10450,7 +10951,7 @@
       <c r="N400" s="1"/>
       <c r="O400" s="1"/>
     </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A401" s="6"/>
       <c r="B401" s="6"/>
       <c r="C401" s="7"/>
@@ -10467,7 +10968,7 @@
       <c r="N401" s="1"/>
       <c r="O401" s="1"/>
     </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A402" s="6"/>
       <c r="B402" s="6"/>
       <c r="C402" s="7"/>
@@ -10484,7 +10985,7 @@
       <c r="N402" s="1"/>
       <c r="O402" s="1"/>
     </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A403" s="6"/>
       <c r="B403" s="6"/>
       <c r="C403" s="7"/>
@@ -10501,7 +11002,7 @@
       <c r="N403" s="1"/>
       <c r="O403" s="1"/>
     </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A404" s="6"/>
       <c r="B404" s="6"/>
       <c r="C404" s="7"/>
@@ -10518,7 +11019,7 @@
       <c r="N404" s="1"/>
       <c r="O404" s="1"/>
     </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A405" s="6"/>
       <c r="B405" s="6"/>
       <c r="C405" s="7"/>
@@ -10535,7 +11036,7 @@
       <c r="N405" s="1"/>
       <c r="O405" s="1"/>
     </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A406" s="6"/>
       <c r="B406" s="6"/>
       <c r="C406" s="7"/>
@@ -10552,7 +11053,7 @@
       <c r="N406" s="1"/>
       <c r="O406" s="1"/>
     </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A407" s="6"/>
       <c r="B407" s="6"/>
       <c r="C407" s="7"/>
@@ -10569,7 +11070,7 @@
       <c r="N407" s="1"/>
       <c r="O407" s="1"/>
     </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A408" s="6"/>
       <c r="B408" s="6"/>
       <c r="C408" s="7"/>
@@ -10586,7 +11087,7 @@
       <c r="N408" s="1"/>
       <c r="O408" s="1"/>
     </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A409" s="6"/>
       <c r="B409" s="6"/>
       <c r="C409" s="7"/>
@@ -10603,7 +11104,7 @@
       <c r="N409" s="1"/>
       <c r="O409" s="1"/>
     </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A410" s="6"/>
       <c r="B410" s="6"/>
       <c r="C410" s="7"/>
@@ -10620,7 +11121,7 @@
       <c r="N410" s="1"/>
       <c r="O410" s="1"/>
     </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A411" s="6"/>
       <c r="B411" s="6"/>
       <c r="C411" s="7"/>
@@ -10637,7 +11138,7 @@
       <c r="N411" s="1"/>
       <c r="O411" s="1"/>
     </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A412" s="6"/>
       <c r="B412" s="6"/>
       <c r="C412" s="7"/>
@@ -10654,7 +11155,7 @@
       <c r="N412" s="1"/>
       <c r="O412" s="1"/>
     </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A413" s="6"/>
       <c r="B413" s="6"/>
       <c r="C413" s="7"/>
@@ -10671,7 +11172,7 @@
       <c r="N413" s="1"/>
       <c r="O413" s="1"/>
     </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A414" s="6"/>
       <c r="B414" s="6"/>
       <c r="C414" s="7"/>
@@ -10688,7 +11189,7 @@
       <c r="N414" s="1"/>
       <c r="O414" s="1"/>
     </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A415" s="6"/>
       <c r="B415" s="6"/>
       <c r="C415" s="7"/>
@@ -10705,7 +11206,7 @@
       <c r="N415" s="1"/>
       <c r="O415" s="1"/>
     </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A416" s="6"/>
       <c r="B416" s="6"/>
       <c r="C416" s="7"/>
@@ -10722,7 +11223,7 @@
       <c r="N416" s="1"/>
       <c r="O416" s="1"/>
     </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A417" s="6"/>
       <c r="B417" s="6"/>
       <c r="C417" s="7"/>
@@ -10739,7 +11240,7 @@
       <c r="N417" s="1"/>
       <c r="O417" s="1"/>
     </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A418" s="6"/>
       <c r="B418" s="6"/>
       <c r="C418" s="7"/>
@@ -10756,7 +11257,7 @@
       <c r="N418" s="1"/>
       <c r="O418" s="1"/>
     </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A419" s="6"/>
       <c r="B419" s="6"/>
       <c r="C419" s="7"/>
@@ -10773,7 +11274,7 @@
       <c r="N419" s="1"/>
       <c r="O419" s="1"/>
     </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A420" s="6"/>
       <c r="B420" s="6"/>
       <c r="C420" s="7"/>
@@ -10790,7 +11291,7 @@
       <c r="N420" s="1"/>
       <c r="O420" s="1"/>
     </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A421" s="6"/>
       <c r="B421" s="6"/>
       <c r="C421" s="7"/>
@@ -10807,7 +11308,7 @@
       <c r="N421" s="1"/>
       <c r="O421" s="1"/>
     </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A422" s="6"/>
       <c r="B422" s="6"/>
       <c r="C422" s="7"/>
@@ -10824,7 +11325,7 @@
       <c r="N422" s="1"/>
       <c r="O422" s="1"/>
     </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A423" s="6"/>
       <c r="B423" s="6"/>
       <c r="C423" s="7"/>
@@ -10841,7 +11342,7 @@
       <c r="N423" s="1"/>
       <c r="O423" s="1"/>
     </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A424" s="6"/>
       <c r="B424" s="6"/>
       <c r="C424" s="7"/>
@@ -10858,7 +11359,7 @@
       <c r="N424" s="1"/>
       <c r="O424" s="1"/>
     </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A425" s="6"/>
       <c r="B425" s="6"/>
       <c r="C425" s="7"/>
@@ -10875,7 +11376,7 @@
       <c r="N425" s="1"/>
       <c r="O425" s="1"/>
     </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A426" s="6"/>
       <c r="B426" s="6"/>
       <c r="C426" s="7"/>
@@ -10892,7 +11393,7 @@
       <c r="N426" s="1"/>
       <c r="O426" s="1"/>
     </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A427" s="6"/>
       <c r="B427" s="6"/>
       <c r="C427" s="7"/>
@@ -10909,7 +11410,7 @@
       <c r="N427" s="1"/>
       <c r="O427" s="1"/>
     </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A428" s="6"/>
       <c r="B428" s="6"/>
       <c r="C428" s="7"/>
@@ -10926,7 +11427,7 @@
       <c r="N428" s="1"/>
       <c r="O428" s="1"/>
     </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A429" s="6"/>
       <c r="B429" s="6"/>
       <c r="C429" s="7"/>
@@ -10943,7 +11444,7 @@
       <c r="N429" s="1"/>
       <c r="O429" s="1"/>
     </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A430" s="6"/>
       <c r="B430" s="6"/>
       <c r="C430" s="7"/>
@@ -10960,7 +11461,7 @@
       <c r="N430" s="1"/>
       <c r="O430" s="1"/>
     </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A431" s="6"/>
       <c r="B431" s="6"/>
       <c r="C431" s="7"/>
@@ -10977,7 +11478,7 @@
       <c r="N431" s="1"/>
       <c r="O431" s="1"/>
     </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A432" s="6"/>
       <c r="B432" s="6"/>
       <c r="C432" s="7"/>
@@ -10994,7 +11495,7 @@
       <c r="N432" s="1"/>
       <c r="O432" s="1"/>
     </row>
-    <row r="433" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A433" s="6"/>
       <c r="B433" s="6"/>
       <c r="C433" s="7"/>
@@ -11011,7 +11512,7 @@
       <c r="N433" s="1"/>
       <c r="O433" s="1"/>
     </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A434" s="6"/>
       <c r="B434" s="6"/>
       <c r="C434" s="7"/>
@@ -11028,7 +11529,7 @@
       <c r="N434" s="1"/>
       <c r="O434" s="1"/>
     </row>
-    <row r="435" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A435" s="6"/>
       <c r="B435" s="6"/>
       <c r="C435" s="7"/>
@@ -11045,7 +11546,7 @@
       <c r="N435" s="1"/>
       <c r="O435" s="1"/>
     </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A436" s="6"/>
       <c r="B436" s="6"/>
       <c r="C436" s="7"/>
@@ -11062,7 +11563,7 @@
       <c r="N436" s="1"/>
       <c r="O436" s="1"/>
     </row>
-    <row r="437" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A437" s="6"/>
       <c r="B437" s="6"/>
       <c r="C437" s="7"/>
@@ -11079,7 +11580,7 @@
       <c r="N437" s="1"/>
       <c r="O437" s="1"/>
     </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A438" s="6"/>
       <c r="B438" s="6"/>
       <c r="C438" s="7"/>
@@ -11096,7 +11597,7 @@
       <c r="N438" s="1"/>
       <c r="O438" s="1"/>
     </row>
-    <row r="439" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A439" s="6"/>
       <c r="B439" s="6"/>
       <c r="C439" s="7"/>
@@ -11113,7 +11614,7 @@
       <c r="N439" s="1"/>
       <c r="O439" s="1"/>
     </row>
-    <row r="440" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A440" s="6"/>
       <c r="B440" s="6"/>
       <c r="C440" s="7"/>
@@ -11130,7 +11631,7 @@
       <c r="N440" s="1"/>
       <c r="O440" s="1"/>
     </row>
-    <row r="441" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A441" s="6"/>
       <c r="B441" s="6"/>
       <c r="C441" s="7"/>
@@ -11147,7 +11648,7 @@
       <c r="N441" s="1"/>
       <c r="O441" s="1"/>
     </row>
-    <row r="442" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A442" s="6"/>
       <c r="B442" s="6"/>
       <c r="C442" s="7"/>
@@ -11164,7 +11665,7 @@
       <c r="N442" s="1"/>
       <c r="O442" s="1"/>
     </row>
-    <row r="443" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A443" s="6"/>
       <c r="B443" s="6"/>
       <c r="C443" s="7"/>
@@ -11181,7 +11682,7 @@
       <c r="N443" s="1"/>
       <c r="O443" s="1"/>
     </row>
-    <row r="444" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A444" s="6"/>
       <c r="B444" s="6"/>
       <c r="C444" s="7"/>
@@ -11198,7 +11699,7 @@
       <c r="N444" s="1"/>
       <c r="O444" s="1"/>
     </row>
-    <row r="445" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A445" s="6"/>
       <c r="B445" s="6"/>
       <c r="C445" s="7"/>
@@ -11215,7 +11716,7 @@
       <c r="N445" s="1"/>
       <c r="O445" s="1"/>
     </row>
-    <row r="446" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A446" s="6"/>
       <c r="B446" s="6"/>
       <c r="C446" s="7"/>
@@ -11232,7 +11733,7 @@
       <c r="N446" s="1"/>
       <c r="O446" s="1"/>
     </row>
-    <row r="447" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A447" s="6"/>
       <c r="B447" s="6"/>
       <c r="C447" s="7"/>
@@ -11249,7 +11750,7 @@
       <c r="N447" s="1"/>
       <c r="O447" s="1"/>
     </row>
-    <row r="448" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A448" s="6"/>
       <c r="B448" s="6"/>
       <c r="C448" s="7"/>
@@ -11266,7 +11767,7 @@
       <c r="N448" s="1"/>
       <c r="O448" s="1"/>
     </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A449" s="6"/>
       <c r="B449" s="6"/>
       <c r="C449" s="7"/>
@@ -11283,7 +11784,7 @@
       <c r="N449" s="1"/>
       <c r="O449" s="1"/>
     </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A450" s="6"/>
       <c r="B450" s="6"/>
       <c r="C450" s="7"/>
@@ -11300,7 +11801,7 @@
       <c r="N450" s="1"/>
       <c r="O450" s="1"/>
     </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A451" s="6"/>
       <c r="B451" s="6"/>
       <c r="C451" s="7"/>
@@ -11317,7 +11818,7 @@
       <c r="N451" s="1"/>
       <c r="O451" s="1"/>
     </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A452" s="6"/>
       <c r="B452" s="6"/>
       <c r="C452" s="7"/>
@@ -11334,7 +11835,7 @@
       <c r="N452" s="1"/>
       <c r="O452" s="1"/>
     </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A453" s="6"/>
       <c r="B453" s="6"/>
       <c r="C453" s="7"/>
@@ -11351,7 +11852,7 @@
       <c r="N453" s="1"/>
       <c r="O453" s="1"/>
     </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A454" s="6"/>
       <c r="B454" s="6"/>
       <c r="C454" s="7"/>
@@ -11368,7 +11869,7 @@
       <c r="N454" s="1"/>
       <c r="O454" s="1"/>
     </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A455" s="6"/>
       <c r="B455" s="6"/>
       <c r="C455" s="7"/>
@@ -11385,7 +11886,7 @@
       <c r="N455" s="1"/>
       <c r="O455" s="1"/>
     </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A456" s="6"/>
       <c r="B456" s="6"/>
       <c r="C456" s="7"/>
@@ -11402,7 +11903,7 @@
       <c r="N456" s="1"/>
       <c r="O456" s="1"/>
     </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A457" s="6"/>
       <c r="B457" s="6"/>
       <c r="C457" s="7"/>
@@ -11419,7 +11920,7 @@
       <c r="N457" s="1"/>
       <c r="O457" s="1"/>
     </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A458" s="6"/>
       <c r="B458" s="6"/>
       <c r="C458" s="7"/>
@@ -11436,7 +11937,7 @@
       <c r="N458" s="1"/>
       <c r="O458" s="1"/>
     </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A459" s="6"/>
       <c r="B459" s="6"/>
       <c r="C459" s="7"/>
@@ -11453,7 +11954,7 @@
       <c r="N459" s="1"/>
       <c r="O459" s="1"/>
     </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A460" s="6"/>
       <c r="B460" s="6"/>
       <c r="C460" s="7"/>
@@ -11470,7 +11971,7 @@
       <c r="N460" s="1"/>
       <c r="O460" s="1"/>
     </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A461" s="6"/>
       <c r="B461" s="6"/>
       <c r="C461" s="7"/>
@@ -11487,7 +11988,7 @@
       <c r="N461" s="1"/>
       <c r="O461" s="1"/>
     </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A462" s="6"/>
       <c r="B462" s="6"/>
       <c r="C462" s="7"/>
@@ -11504,7 +12005,7 @@
       <c r="N462" s="1"/>
       <c r="O462" s="1"/>
     </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A463" s="6"/>
       <c r="B463" s="6"/>
       <c r="C463" s="7"/>
@@ -11521,7 +12022,7 @@
       <c r="N463" s="1"/>
       <c r="O463" s="1"/>
     </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A464" s="6"/>
       <c r="B464" s="6"/>
       <c r="C464" s="7"/>
@@ -11538,7 +12039,7 @@
       <c r="N464" s="1"/>
       <c r="O464" s="1"/>
     </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A465" s="6"/>
       <c r="B465" s="6"/>
       <c r="C465" s="7"/>
@@ -11555,7 +12056,7 @@
       <c r="N465" s="1"/>
       <c r="O465" s="1"/>
     </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A466" s="6"/>
       <c r="B466" s="6"/>
       <c r="C466" s="7"/>
@@ -11572,7 +12073,7 @@
       <c r="N466" s="1"/>
       <c r="O466" s="1"/>
     </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A467" s="6"/>
       <c r="B467" s="6"/>
       <c r="C467" s="7"/>
@@ -11589,7 +12090,7 @@
       <c r="N467" s="1"/>
       <c r="O467" s="1"/>
     </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A468" s="6"/>
       <c r="B468" s="6"/>
       <c r="C468" s="7"/>
@@ -11606,7 +12107,7 @@
       <c r="N468" s="1"/>
       <c r="O468" s="1"/>
     </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A469" s="6"/>
       <c r="B469" s="6"/>
       <c r="C469" s="7"/>
@@ -11623,7 +12124,7 @@
       <c r="N469" s="1"/>
       <c r="O469" s="1"/>
     </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A470" s="6"/>
       <c r="B470" s="6"/>
       <c r="C470" s="7"/>
@@ -11640,7 +12141,7 @@
       <c r="N470" s="1"/>
       <c r="O470" s="1"/>
     </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A471" s="6"/>
       <c r="B471" s="6"/>
       <c r="C471" s="7"/>
@@ -11657,7 +12158,7 @@
       <c r="N471" s="1"/>
       <c r="O471" s="1"/>
     </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A472" s="6"/>
       <c r="B472" s="6"/>
       <c r="C472" s="7"/>
@@ -11674,7 +12175,7 @@
       <c r="N472" s="1"/>
       <c r="O472" s="1"/>
     </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A473" s="6"/>
       <c r="B473" s="6"/>
       <c r="C473" s="7"/>
@@ -11691,7 +12192,7 @@
       <c r="N473" s="1"/>
       <c r="O473" s="1"/>
     </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A474" s="6"/>
       <c r="B474" s="6"/>
       <c r="C474" s="7"/>
@@ -11708,7 +12209,7 @@
       <c r="N474" s="1"/>
       <c r="O474" s="1"/>
     </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A475" s="6"/>
       <c r="B475" s="6"/>
       <c r="C475" s="7"/>
@@ -11725,7 +12226,7 @@
       <c r="N475" s="1"/>
       <c r="O475" s="1"/>
     </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A476" s="6"/>
       <c r="B476" s="6"/>
       <c r="C476" s="7"/>
@@ -11742,7 +12243,7 @@
       <c r="N476" s="1"/>
       <c r="O476" s="1"/>
     </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A477" s="6"/>
       <c r="B477" s="6"/>
       <c r="C477" s="7"/>
@@ -11759,7 +12260,7 @@
       <c r="N477" s="1"/>
       <c r="O477" s="1"/>
     </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A478" s="6"/>
       <c r="B478" s="6"/>
       <c r="C478" s="7"/>
@@ -11776,7 +12277,7 @@
       <c r="N478" s="1"/>
       <c r="O478" s="1"/>
     </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A479" s="6"/>
       <c r="B479" s="6"/>
       <c r="C479" s="7"/>
@@ -11793,7 +12294,7 @@
       <c r="N479" s="1"/>
       <c r="O479" s="1"/>
     </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A480" s="6"/>
       <c r="B480" s="6"/>
       <c r="C480" s="7"/>
@@ -11810,7 +12311,7 @@
       <c r="N480" s="1"/>
       <c r="O480" s="1"/>
     </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A481" s="6"/>
       <c r="B481" s="6"/>
       <c r="C481" s="7"/>
@@ -11827,7 +12328,7 @@
       <c r="N481" s="1"/>
       <c r="O481" s="1"/>
     </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A482" s="6"/>
       <c r="B482" s="6"/>
       <c r="C482" s="7"/>
@@ -11844,7 +12345,7 @@
       <c r="N482" s="1"/>
       <c r="O482" s="1"/>
     </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A483" s="6"/>
       <c r="B483" s="6"/>
       <c r="C483" s="7"/>
@@ -11861,7 +12362,7 @@
       <c r="N483" s="1"/>
       <c r="O483" s="1"/>
     </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A484" s="6"/>
       <c r="B484" s="6"/>
       <c r="C484" s="7"/>
@@ -11878,7 +12379,7 @@
       <c r="N484" s="1"/>
       <c r="O484" s="1"/>
     </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A485" s="6"/>
       <c r="B485" s="6"/>
       <c r="C485" s="7"/>
@@ -11895,7 +12396,7 @@
       <c r="N485" s="1"/>
       <c r="O485" s="1"/>
     </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A486" s="6"/>
       <c r="B486" s="6"/>
       <c r="C486" s="7"/>
@@ -11912,7 +12413,7 @@
       <c r="N486" s="1"/>
       <c r="O486" s="1"/>
     </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A487" s="6"/>
       <c r="B487" s="6"/>
       <c r="C487" s="7"/>
@@ -11929,7 +12430,7 @@
       <c r="N487" s="1"/>
       <c r="O487" s="1"/>
     </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A488" s="6"/>
       <c r="B488" s="6"/>
       <c r="C488" s="7"/>
@@ -11946,7 +12447,7 @@
       <c r="N488" s="1"/>
       <c r="O488" s="1"/>
     </row>
-    <row r="489" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A489" s="6"/>
       <c r="B489" s="6"/>
       <c r="C489" s="7"/>
@@ -11963,7 +12464,7 @@
       <c r="N489" s="1"/>
       <c r="O489" s="1"/>
     </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A490" s="6"/>
       <c r="B490" s="6"/>
       <c r="C490" s="7"/>
@@ -11980,7 +12481,7 @@
       <c r="N490" s="1"/>
       <c r="O490" s="1"/>
     </row>
-    <row r="491" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A491" s="6"/>
       <c r="B491" s="6"/>
       <c r="C491" s="7"/>
@@ -11997,7 +12498,7 @@
       <c r="N491" s="1"/>
       <c r="O491" s="1"/>
     </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A492" s="6"/>
       <c r="B492" s="6"/>
       <c r="C492" s="7"/>
@@ -12014,7 +12515,7 @@
       <c r="N492" s="1"/>
       <c r="O492" s="1"/>
     </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A493" s="6"/>
       <c r="B493" s="6"/>
       <c r="C493" s="7"/>
@@ -12031,7 +12532,7 @@
       <c r="N493" s="1"/>
       <c r="O493" s="1"/>
     </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A494" s="6"/>
       <c r="B494" s="6"/>
       <c r="C494" s="7"/>
@@ -12048,7 +12549,7 @@
       <c r="N494" s="1"/>
       <c r="O494" s="1"/>
     </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A495" s="6"/>
       <c r="B495" s="6"/>
       <c r="C495" s="7"/>
@@ -12065,7 +12566,7 @@
       <c r="N495" s="1"/>
       <c r="O495" s="1"/>
     </row>
-    <row r="496" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A496" s="6"/>
       <c r="B496" s="6"/>
       <c r="C496" s="7"/>
@@ -12082,7 +12583,7 @@
       <c r="N496" s="1"/>
       <c r="O496" s="1"/>
     </row>
-    <row r="497" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A497" s="6"/>
       <c r="B497" s="6"/>
       <c r="C497" s="7"/>
@@ -12099,7 +12600,7 @@
       <c r="N497" s="1"/>
       <c r="O497" s="1"/>
     </row>
-    <row r="498" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A498" s="6"/>
       <c r="B498" s="6"/>
       <c r="C498" s="7"/>
@@ -12116,7 +12617,7 @@
       <c r="N498" s="1"/>
       <c r="O498" s="1"/>
     </row>
-    <row r="499" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A499" s="6"/>
       <c r="B499" s="6"/>
       <c r="C499" s="7"/>
@@ -12133,7 +12634,7 @@
       <c r="N499" s="1"/>
       <c r="O499" s="1"/>
     </row>
-    <row r="500" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A500" s="6"/>
       <c r="B500" s="6"/>
       <c r="C500" s="7"/>
@@ -12150,7 +12651,7 @@
       <c r="N500" s="1"/>
       <c r="O500" s="1"/>
     </row>
-    <row r="501" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A501" s="6"/>
       <c r="B501" s="6"/>
       <c r="C501" s="7"/>
@@ -12167,7 +12668,7 @@
       <c r="N501" s="1"/>
       <c r="O501" s="1"/>
     </row>
-    <row r="502" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A502" s="6"/>
       <c r="B502" s="6"/>
       <c r="C502" s="7"/>
@@ -12184,7 +12685,7 @@
       <c r="N502" s="1"/>
       <c r="O502" s="1"/>
     </row>
-    <row r="503" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A503" s="6"/>
       <c r="B503" s="6"/>
       <c r="C503" s="7"/>
@@ -12201,7 +12702,7 @@
       <c r="N503" s="1"/>
       <c r="O503" s="1"/>
     </row>
-    <row r="504" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A504" s="6"/>
       <c r="B504" s="6"/>
       <c r="C504" s="7"/>
@@ -12218,7 +12719,7 @@
       <c r="N504" s="1"/>
       <c r="O504" s="1"/>
     </row>
-    <row r="505" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A505" s="6"/>
       <c r="B505" s="6"/>
       <c r="C505" s="7"/>
@@ -12235,7 +12736,7 @@
       <c r="N505" s="1"/>
       <c r="O505" s="1"/>
     </row>
-    <row r="506" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A506" s="6"/>
       <c r="B506" s="6"/>
       <c r="C506" s="7"/>
@@ -12252,7 +12753,7 @@
       <c r="N506" s="1"/>
       <c r="O506" s="1"/>
     </row>
-    <row r="507" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A507" s="6"/>
       <c r="B507" s="6"/>
       <c r="C507" s="7"/>
@@ -12269,7 +12770,7 @@
       <c r="N507" s="1"/>
       <c r="O507" s="1"/>
     </row>
-    <row r="508" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A508" s="6"/>
       <c r="B508" s="6"/>
       <c r="C508" s="7"/>
@@ -12286,7 +12787,7 @@
       <c r="N508" s="1"/>
       <c r="O508" s="1"/>
     </row>
-    <row r="509" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A509" s="6"/>
       <c r="B509" s="6"/>
       <c r="C509" s="7"/>
@@ -12303,7 +12804,7 @@
       <c r="N509" s="1"/>
       <c r="O509" s="1"/>
     </row>
-    <row r="510" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A510" s="6"/>
       <c r="B510" s="6"/>
       <c r="C510" s="7"/>
@@ -12320,7 +12821,7 @@
       <c r="N510" s="1"/>
       <c r="O510" s="1"/>
     </row>
-    <row r="511" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A511" s="6"/>
       <c r="B511" s="6"/>
       <c r="C511" s="7"/>
@@ -12337,7 +12838,7 @@
       <c r="N511" s="1"/>
       <c r="O511" s="1"/>
     </row>
-    <row r="512" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A512" s="6"/>
       <c r="B512" s="6"/>
       <c r="C512" s="7"/>
@@ -12354,7 +12855,7 @@
       <c r="N512" s="1"/>
       <c r="O512" s="1"/>
     </row>
-    <row r="513" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A513" s="6"/>
       <c r="B513" s="6"/>
       <c r="C513" s="7"/>
@@ -12371,7 +12872,7 @@
       <c r="N513" s="1"/>
       <c r="O513" s="1"/>
     </row>
-    <row r="514" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A514" s="6"/>
       <c r="B514" s="6"/>
       <c r="C514" s="7"/>
@@ -12388,7 +12889,7 @@
       <c r="N514" s="1"/>
       <c r="O514" s="1"/>
     </row>
-    <row r="515" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A515" s="6"/>
       <c r="B515" s="6"/>
       <c r="C515" s="7"/>
@@ -12405,7 +12906,7 @@
       <c r="N515" s="1"/>
       <c r="O515" s="1"/>
     </row>
-    <row r="516" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A516" s="6"/>
       <c r="B516" s="6"/>
       <c r="C516" s="7"/>
@@ -12422,7 +12923,7 @@
       <c r="N516" s="1"/>
       <c r="O516" s="1"/>
     </row>
-    <row r="517" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A517" s="6"/>
       <c r="B517" s="6"/>
       <c r="C517" s="7"/>
@@ -12439,7 +12940,7 @@
       <c r="N517" s="1"/>
       <c r="O517" s="1"/>
     </row>
-    <row r="518" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A518" s="6"/>
       <c r="B518" s="6"/>
       <c r="C518" s="7"/>
@@ -12456,7 +12957,7 @@
       <c r="N518" s="1"/>
       <c r="O518" s="1"/>
     </row>
-    <row r="519" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A519" s="6"/>
       <c r="B519" s="6"/>
       <c r="C519" s="7"/>
@@ -12473,7 +12974,7 @@
       <c r="N519" s="1"/>
       <c r="O519" s="1"/>
     </row>
-    <row r="520" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A520" s="6"/>
       <c r="B520" s="6"/>
       <c r="C520" s="7"/>
@@ -12490,7 +12991,7 @@
       <c r="N520" s="1"/>
       <c r="O520" s="1"/>
     </row>
-    <row r="521" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A521" s="6"/>
       <c r="B521" s="6"/>
       <c r="C521" s="7"/>
@@ -12507,7 +13008,7 @@
       <c r="N521" s="1"/>
       <c r="O521" s="1"/>
     </row>
-    <row r="522" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A522" s="6"/>
       <c r="B522" s="6"/>
       <c r="C522" s="7"/>
@@ -12524,7 +13025,7 @@
       <c r="N522" s="1"/>
       <c r="O522" s="1"/>
     </row>
-    <row r="523" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A523" s="6"/>
       <c r="B523" s="6"/>
       <c r="C523" s="7"/>
@@ -12541,7 +13042,7 @@
       <c r="N523" s="1"/>
       <c r="O523" s="1"/>
     </row>
-    <row r="524" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A524" s="6"/>
       <c r="B524" s="6"/>
       <c r="C524" s="7"/>
@@ -12558,7 +13059,7 @@
       <c r="N524" s="1"/>
       <c r="O524" s="1"/>
     </row>
-    <row r="525" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A525" s="6"/>
       <c r="B525" s="6"/>
       <c r="C525" s="7"/>
@@ -12575,7 +13076,7 @@
       <c r="N525" s="1"/>
       <c r="O525" s="1"/>
     </row>
-    <row r="526" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A526" s="6"/>
       <c r="B526" s="6"/>
       <c r="C526" s="7"/>
@@ -12592,7 +13093,7 @@
       <c r="N526" s="1"/>
       <c r="O526" s="1"/>
     </row>
-    <row r="527" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A527" s="6"/>
       <c r="B527" s="6"/>
       <c r="C527" s="7"/>
@@ -12609,7 +13110,7 @@
       <c r="N527" s="1"/>
       <c r="O527" s="1"/>
     </row>
-    <row r="528" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A528" s="6"/>
       <c r="B528" s="6"/>
       <c r="C528" s="7"/>
@@ -12626,7 +13127,7 @@
       <c r="N528" s="1"/>
       <c r="O528" s="1"/>
     </row>
-    <row r="529" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A529" s="6"/>
       <c r="B529" s="6"/>
       <c r="C529" s="7"/>
@@ -12643,7 +13144,7 @@
       <c r="N529" s="1"/>
       <c r="O529" s="1"/>
     </row>
-    <row r="530" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A530" s="6"/>
       <c r="B530" s="6"/>
       <c r="C530" s="7"/>
@@ -12660,7 +13161,7 @@
       <c r="N530" s="1"/>
       <c r="O530" s="1"/>
     </row>
-    <row r="531" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A531" s="6"/>
       <c r="B531" s="6"/>
       <c r="C531" s="7"/>
@@ -12677,7 +13178,7 @@
       <c r="N531" s="1"/>
       <c r="O531" s="1"/>
     </row>
-    <row r="532" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A532" s="6"/>
       <c r="B532" s="6"/>
       <c r="C532" s="7"/>
@@ -12694,7 +13195,7 @@
       <c r="N532" s="1"/>
       <c r="O532" s="1"/>
     </row>
-    <row r="533" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A533" s="6"/>
       <c r="B533" s="6"/>
       <c r="C533" s="7"/>
@@ -12711,7 +13212,7 @@
       <c r="N533" s="1"/>
       <c r="O533" s="1"/>
     </row>
-    <row r="534" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A534" s="6"/>
       <c r="B534" s="6"/>
       <c r="C534" s="7"/>
@@ -12728,7 +13229,7 @@
       <c r="N534" s="1"/>
       <c r="O534" s="1"/>
     </row>
-    <row r="535" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A535" s="6"/>
       <c r="B535" s="6"/>
       <c r="C535" s="7"/>
@@ -12745,7 +13246,7 @@
       <c r="N535" s="1"/>
       <c r="O535" s="1"/>
     </row>
-    <row r="536" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A536" s="6"/>
       <c r="B536" s="6"/>
       <c r="C536" s="7"/>
@@ -12762,7 +13263,7 @@
       <c r="N536" s="1"/>
       <c r="O536" s="1"/>
     </row>
-    <row r="537" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A537" s="6"/>
       <c r="B537" s="6"/>
       <c r="C537" s="7"/>
@@ -12779,7 +13280,7 @@
       <c r="N537" s="1"/>
       <c r="O537" s="1"/>
     </row>
-    <row r="538" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A538" s="6"/>
       <c r="B538" s="6"/>
       <c r="C538" s="7"/>
@@ -12796,7 +13297,7 @@
       <c r="N538" s="1"/>
       <c r="O538" s="1"/>
     </row>
-    <row r="539" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A539" s="6"/>
       <c r="B539" s="6"/>
       <c r="C539" s="7"/>
@@ -12813,7 +13314,7 @@
       <c r="N539" s="1"/>
       <c r="O539" s="1"/>
     </row>
-    <row r="540" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A540" s="6"/>
       <c r="B540" s="6"/>
       <c r="C540" s="7"/>
@@ -12830,7 +13331,7 @@
       <c r="N540" s="1"/>
       <c r="O540" s="1"/>
     </row>
-    <row r="541" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A541" s="6"/>
       <c r="B541" s="6"/>
       <c r="C541" s="7"/>
@@ -12847,7 +13348,7 @@
       <c r="N541" s="1"/>
       <c r="O541" s="1"/>
     </row>
-    <row r="542" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A542" s="6"/>
       <c r="B542" s="6"/>
       <c r="C542" s="7"/>
@@ -12864,7 +13365,7 @@
       <c r="N542" s="1"/>
       <c r="O542" s="1"/>
     </row>
-    <row r="543" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A543" s="6"/>
       <c r="B543" s="6"/>
       <c r="C543" s="7"/>
@@ -12881,7 +13382,7 @@
       <c r="N543" s="1"/>
       <c r="O543" s="1"/>
     </row>
-    <row r="544" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A544" s="6"/>
       <c r="B544" s="6"/>
       <c r="C544" s="7"/>
@@ -12898,7 +13399,7 @@
       <c r="N544" s="1"/>
       <c r="O544" s="1"/>
     </row>
-    <row r="545" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A545" s="6"/>
       <c r="B545" s="6"/>
       <c r="C545" s="7"/>
@@ -12915,7 +13416,7 @@
       <c r="N545" s="1"/>
       <c r="O545" s="1"/>
     </row>
-    <row r="546" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A546" s="6"/>
       <c r="B546" s="6"/>
       <c r="C546" s="7"/>
@@ -12932,7 +13433,7 @@
       <c r="N546" s="1"/>
       <c r="O546" s="1"/>
     </row>
-    <row r="547" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A547" s="6"/>
       <c r="B547" s="6"/>
       <c r="C547" s="7"/>
@@ -12949,7 +13450,7 @@
       <c r="N547" s="1"/>
       <c r="O547" s="1"/>
     </row>
-    <row r="548" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A548" s="6"/>
       <c r="B548" s="6"/>
       <c r="C548" s="7"/>
@@ -12966,7 +13467,7 @@
       <c r="N548" s="1"/>
       <c r="O548" s="1"/>
     </row>
-    <row r="549" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A549" s="6"/>
       <c r="B549" s="6"/>
       <c r="C549" s="7"/>
@@ -12983,7 +13484,7 @@
       <c r="N549" s="1"/>
       <c r="O549" s="1"/>
     </row>
-    <row r="550" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A550" s="6"/>
       <c r="B550" s="6"/>
       <c r="C550" s="7"/>
@@ -13000,7 +13501,7 @@
       <c r="N550" s="1"/>
       <c r="O550" s="1"/>
     </row>
-    <row r="551" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A551" s="6"/>
       <c r="B551" s="6"/>
       <c r="C551" s="7"/>
@@ -13017,7 +13518,7 @@
       <c r="N551" s="1"/>
       <c r="O551" s="1"/>
     </row>
-    <row r="552" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A552" s="6"/>
       <c r="B552" s="6"/>
       <c r="C552" s="7"/>
@@ -13034,7 +13535,7 @@
       <c r="N552" s="1"/>
       <c r="O552" s="1"/>
     </row>
-    <row r="553" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A553" s="6"/>
       <c r="B553" s="6"/>
       <c r="C553" s="7"/>
@@ -13051,7 +13552,7 @@
       <c r="N553" s="1"/>
       <c r="O553" s="1"/>
     </row>
-    <row r="554" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A554" s="6"/>
       <c r="B554" s="6"/>
       <c r="C554" s="7"/>
@@ -13068,7 +13569,7 @@
       <c r="N554" s="1"/>
       <c r="O554" s="1"/>
     </row>
-    <row r="555" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A555" s="6"/>
       <c r="B555" s="6"/>
       <c r="C555" s="7"/>
@@ -13085,7 +13586,7 @@
       <c r="N555" s="1"/>
       <c r="O555" s="1"/>
     </row>
-    <row r="556" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A556" s="6"/>
       <c r="B556" s="6"/>
       <c r="C556" s="7"/>
@@ -13102,7 +13603,7 @@
       <c r="N556" s="1"/>
       <c r="O556" s="1"/>
     </row>
-    <row r="557" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A557" s="6"/>
       <c r="B557" s="6"/>
       <c r="C557" s="7"/>
@@ -13119,7 +13620,7 @@
       <c r="N557" s="1"/>
       <c r="O557" s="1"/>
     </row>
-    <row r="558" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A558" s="6"/>
       <c r="B558" s="6"/>
       <c r="C558" s="7"/>
@@ -13136,7 +13637,7 @@
       <c r="N558" s="1"/>
       <c r="O558" s="1"/>
     </row>
-    <row r="559" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A559" s="6"/>
       <c r="B559" s="6"/>
       <c r="C559" s="7"/>
@@ -13153,7 +13654,7 @@
       <c r="N559" s="1"/>
       <c r="O559" s="1"/>
     </row>
-    <row r="560" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A560" s="6"/>
       <c r="B560" s="6"/>
       <c r="C560" s="7"/>
@@ -13170,7 +13671,7 @@
       <c r="N560" s="1"/>
       <c r="O560" s="1"/>
     </row>
-    <row r="561" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A561" s="6"/>
       <c r="B561" s="6"/>
       <c r="C561" s="7"/>
@@ -13187,7 +13688,7 @@
       <c r="N561" s="1"/>
       <c r="O561" s="1"/>
     </row>
-    <row r="562" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A562" s="6"/>
       <c r="B562" s="6"/>
       <c r="C562" s="7"/>
@@ -13204,7 +13705,7 @@
       <c r="N562" s="1"/>
       <c r="O562" s="1"/>
     </row>
-    <row r="563" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A563" s="6"/>
       <c r="B563" s="6"/>
       <c r="C563" s="7"/>
@@ -13221,7 +13722,7 @@
       <c r="N563" s="1"/>
       <c r="O563" s="1"/>
     </row>
-    <row r="564" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A564" s="6"/>
       <c r="B564" s="6"/>
       <c r="C564" s="7"/>
@@ -13238,7 +13739,7 @@
       <c r="N564" s="1"/>
       <c r="O564" s="1"/>
     </row>
-    <row r="565" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A565" s="6"/>
       <c r="B565" s="6"/>
       <c r="C565" s="7"/>
@@ -13255,7 +13756,7 @@
       <c r="N565" s="1"/>
       <c r="O565" s="1"/>
     </row>
-    <row r="566" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A566" s="6"/>
       <c r="B566" s="6"/>
       <c r="C566" s="7"/>
@@ -13272,7 +13773,7 @@
       <c r="N566" s="1"/>
       <c r="O566" s="1"/>
     </row>
-    <row r="567" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A567" s="6"/>
       <c r="B567" s="6"/>
       <c r="C567" s="7"/>
@@ -13289,7 +13790,7 @@
       <c r="N567" s="1"/>
       <c r="O567" s="1"/>
     </row>
-    <row r="568" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A568" s="6"/>
       <c r="B568" s="6"/>
       <c r="C568" s="7"/>
@@ -13306,7 +13807,7 @@
       <c r="N568" s="1"/>
       <c r="O568" s="1"/>
     </row>
-    <row r="569" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A569" s="6"/>
       <c r="B569" s="6"/>
       <c r="C569" s="7"/>
@@ -13323,7 +13824,7 @@
       <c r="N569" s="1"/>
       <c r="O569" s="1"/>
     </row>
-    <row r="570" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A570" s="6"/>
       <c r="B570" s="6"/>
       <c r="C570" s="7"/>
@@ -13340,7 +13841,7 @@
       <c r="N570" s="1"/>
       <c r="O570" s="1"/>
     </row>
-    <row r="571" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A571" s="6"/>
       <c r="B571" s="6"/>
       <c r="C571" s="7"/>
@@ -13357,7 +13858,7 @@
       <c r="N571" s="1"/>
       <c r="O571" s="1"/>
     </row>
-    <row r="572" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A572" s="6"/>
       <c r="B572" s="6"/>
       <c r="C572" s="7"/>
@@ -13374,7 +13875,7 @@
       <c r="N572" s="1"/>
       <c r="O572" s="1"/>
     </row>
-    <row r="573" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A573" s="6"/>
       <c r="B573" s="6"/>
       <c r="C573" s="7"/>
@@ -13391,7 +13892,7 @@
       <c r="N573" s="1"/>
       <c r="O573" s="1"/>
     </row>
-    <row r="574" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A574" s="6"/>
       <c r="B574" s="6"/>
       <c r="C574" s="7"/>
@@ -13408,7 +13909,7 @@
       <c r="N574" s="1"/>
       <c r="O574" s="1"/>
     </row>
-    <row r="575" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A575" s="6"/>
       <c r="B575" s="6"/>
       <c r="C575" s="7"/>
@@ -13425,7 +13926,7 @@
       <c r="N575" s="1"/>
       <c r="O575" s="1"/>
     </row>
-    <row r="576" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A576" s="6"/>
       <c r="B576" s="6"/>
       <c r="C576" s="7"/>
@@ -13442,7 +13943,7 @@
       <c r="N576" s="1"/>
       <c r="O576" s="1"/>
     </row>
-    <row r="577" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A577" s="6"/>
       <c r="B577" s="6"/>
       <c r="C577" s="7"/>
@@ -13459,7 +13960,7 @@
       <c r="N577" s="1"/>
       <c r="O577" s="1"/>
     </row>
-    <row r="578" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A578" s="6"/>
       <c r="B578" s="6"/>
       <c r="C578" s="7"/>
@@ -13476,7 +13977,7 @@
       <c r="N578" s="1"/>
       <c r="O578" s="1"/>
     </row>
-    <row r="579" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A579" s="6"/>
       <c r="B579" s="6"/>
       <c r="C579" s="7"/>
@@ -13493,7 +13994,7 @@
       <c r="N579" s="1"/>
       <c r="O579" s="1"/>
     </row>
-    <row r="580" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A580" s="6"/>
       <c r="B580" s="6"/>
       <c r="C580" s="7"/>
@@ -13510,7 +14011,7 @@
       <c r="N580" s="1"/>
       <c r="O580" s="1"/>
     </row>
-    <row r="581" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A581" s="6"/>
       <c r="B581" s="6"/>
       <c r="C581" s="7"/>
@@ -13527,7 +14028,7 @@
       <c r="N581" s="1"/>
       <c r="O581" s="1"/>
     </row>
-    <row r="582" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A582" s="6"/>
       <c r="B582" s="6"/>
       <c r="C582" s="7"/>
@@ -13544,7 +14045,7 @@
       <c r="N582" s="1"/>
       <c r="O582" s="1"/>
     </row>
-    <row r="583" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A583" s="6"/>
       <c r="B583" s="6"/>
       <c r="C583" s="7"/>
@@ -13561,7 +14062,7 @@
       <c r="N583" s="1"/>
       <c r="O583" s="1"/>
     </row>
-    <row r="584" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A584" s="6"/>
       <c r="B584" s="6"/>
       <c r="C584" s="7"/>
@@ -13578,7 +14079,7 @@
       <c r="N584" s="1"/>
       <c r="O584" s="1"/>
     </row>
-    <row r="585" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A585" s="6"/>
       <c r="B585" s="6"/>
       <c r="C585" s="7"/>
@@ -13595,7 +14096,7 @@
       <c r="N585" s="1"/>
       <c r="O585" s="1"/>
     </row>
-    <row r="586" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A586" s="6"/>
       <c r="B586" s="6"/>
       <c r="C586" s="7"/>
@@ -13612,7 +14113,7 @@
       <c r="N586" s="1"/>
       <c r="O586" s="1"/>
     </row>
-    <row r="587" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A587" s="6"/>
       <c r="B587" s="6"/>
       <c r="C587" s="7"/>
@@ -13629,7 +14130,7 @@
       <c r="N587" s="1"/>
       <c r="O587" s="1"/>
     </row>
-    <row r="588" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A588" s="6"/>
       <c r="B588" s="6"/>
       <c r="C588" s="7"/>
@@ -13646,7 +14147,7 @@
       <c r="N588" s="1"/>
       <c r="O588" s="1"/>
     </row>
-    <row r="589" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A589" s="6"/>
       <c r="B589" s="6"/>
       <c r="C589" s="7"/>
@@ -13663,7 +14164,7 @@
       <c r="N589" s="1"/>
       <c r="O589" s="1"/>
     </row>
-    <row r="590" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A590" s="6"/>
       <c r="B590" s="6"/>
       <c r="C590" s="7"/>
@@ -13680,7 +14181,7 @@
       <c r="N590" s="1"/>
       <c r="O590" s="1"/>
     </row>
-    <row r="591" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A591" s="6"/>
       <c r="B591" s="6"/>
       <c r="C591" s="7"/>
@@ -13697,7 +14198,7 @@
       <c r="N591" s="1"/>
       <c r="O591" s="1"/>
     </row>
-    <row r="592" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A592" s="6"/>
       <c r="B592" s="6"/>
       <c r="C592" s="7"/>
@@ -13714,7 +14215,7 @@
       <c r="N592" s="1"/>
       <c r="O592" s="1"/>
     </row>
-    <row r="593" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A593" s="6"/>
       <c r="B593" s="6"/>
       <c r="C593" s="7"/>
@@ -13731,7 +14232,7 @@
       <c r="N593" s="1"/>
       <c r="O593" s="1"/>
     </row>
-    <row r="594" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A594" s="6"/>
       <c r="B594" s="6"/>
       <c r="C594" s="7"/>
@@ -13748,7 +14249,7 @@
       <c r="N594" s="1"/>
       <c r="O594" s="1"/>
     </row>
-    <row r="595" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A595" s="6"/>
       <c r="B595" s="6"/>
       <c r="C595" s="7"/>
@@ -13765,7 +14266,7 @@
       <c r="N595" s="1"/>
       <c r="O595" s="1"/>
     </row>
-    <row r="596" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A596" s="6"/>
       <c r="B596" s="6"/>
       <c r="C596" s="7"/>
@@ -13782,7 +14283,7 @@
       <c r="N596" s="1"/>
       <c r="O596" s="1"/>
     </row>
-    <row r="597" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A597" s="6"/>
       <c r="B597" s="6"/>
       <c r="C597" s="7"/>
@@ -13799,7 +14300,7 @@
       <c r="N597" s="1"/>
       <c r="O597" s="1"/>
     </row>
-    <row r="598" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A598" s="6"/>
       <c r="B598" s="6"/>
       <c r="C598" s="7"/>
@@ -13816,7 +14317,7 @@
       <c r="N598" s="1"/>
       <c r="O598" s="1"/>
     </row>
-    <row r="599" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A599" s="6"/>
       <c r="B599" s="6"/>
       <c r="C599" s="7"/>
@@ -13833,7 +14334,7 @@
       <c r="N599" s="1"/>
       <c r="O599" s="1"/>
     </row>
-    <row r="600" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A600" s="6"/>
       <c r="B600" s="6"/>
       <c r="C600" s="7"/>
@@ -13850,7 +14351,7 @@
       <c r="N600" s="1"/>
       <c r="O600" s="1"/>
     </row>
-    <row r="601" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A601" s="6"/>
       <c r="B601" s="6"/>
       <c r="C601" s="7"/>
@@ -13867,7 +14368,7 @@
       <c r="N601" s="1"/>
       <c r="O601" s="1"/>
     </row>
-    <row r="602" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A602" s="6"/>
       <c r="B602" s="6"/>
       <c r="C602" s="7"/>
@@ -13879,7 +14380,7 @@
       <c r="I602" s="1"/>
       <c r="K602" s="9"/>
     </row>
-    <row r="603" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A603" s="6"/>
       <c r="B603" s="6"/>
       <c r="C603" s="7"/>
@@ -13891,7 +14392,7 @@
       <c r="I603" s="1"/>
       <c r="K603" s="9"/>
     </row>
-    <row r="604" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A604" s="6"/>
       <c r="B604" s="6"/>
       <c r="C604" s="7"/>
@@ -13903,7 +14404,7 @@
       <c r="I604" s="1"/>
       <c r="K604" s="9"/>
     </row>
-    <row r="605" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A605" s="6"/>
       <c r="B605" s="6"/>
       <c r="C605" s="7"/>
@@ -13915,7 +14416,7 @@
       <c r="I605" s="1"/>
       <c r="K605" s="9"/>
     </row>
-    <row r="606" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A606" s="6"/>
       <c r="B606" s="6"/>
       <c r="C606" s="7"/>
@@ -13927,7 +14428,7 @@
       <c r="I606" s="1"/>
       <c r="K606" s="9"/>
     </row>
-    <row r="607" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A607" s="6"/>
       <c r="B607" s="6"/>
       <c r="C607" s="7"/>
@@ -13939,7 +14440,7 @@
       <c r="I607" s="1"/>
       <c r="K607" s="9"/>
     </row>
-    <row r="608" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A608" s="6"/>
       <c r="B608" s="6"/>
       <c r="C608" s="7"/>
@@ -13951,7 +14452,7 @@
       <c r="I608" s="1"/>
       <c r="K608" s="9"/>
     </row>
-    <row r="609" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A609" s="6"/>
       <c r="B609" s="6"/>
       <c r="C609" s="7"/>
@@ -13963,7 +14464,7 @@
       <c r="I609" s="1"/>
       <c r="K609" s="9"/>
     </row>
-    <row r="610" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A610" s="6"/>
       <c r="B610" s="6"/>
       <c r="C610" s="7"/>
@@ -13975,7 +14476,7 @@
       <c r="I610" s="1"/>
       <c r="K610" s="9"/>
     </row>
-    <row r="611" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A611" s="6"/>
       <c r="B611" s="6"/>
       <c r="C611" s="7"/>
@@ -13987,7 +14488,7 @@
       <c r="I611" s="1"/>
       <c r="K611" s="9"/>
     </row>
-    <row r="612" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A612" s="6"/>
       <c r="B612" s="6"/>
       <c r="C612" s="7"/>
@@ -13999,7 +14500,7 @@
       <c r="I612" s="1"/>
       <c r="K612" s="9"/>
     </row>
-    <row r="613" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A613" s="6"/>
       <c r="B613" s="6"/>
       <c r="C613" s="7"/>
@@ -14011,7 +14512,7 @@
       <c r="I613" s="1"/>
       <c r="K613" s="9"/>
     </row>
-    <row r="614" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A614" s="6"/>
       <c r="B614" s="6"/>
       <c r="C614" s="7"/>
@@ -14023,7 +14524,7 @@
       <c r="I614" s="1"/>
       <c r="K614" s="9"/>
     </row>
-    <row r="615" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A615" s="6"/>
       <c r="B615" s="6"/>
       <c r="C615" s="7"/>
@@ -14035,7 +14536,7 @@
       <c r="I615" s="1"/>
       <c r="K615" s="9"/>
     </row>
-    <row r="616" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A616" s="6"/>
       <c r="B616" s="6"/>
       <c r="C616" s="7"/>
@@ -14047,7 +14548,7 @@
       <c r="I616" s="1"/>
       <c r="K616" s="9"/>
     </row>
-    <row r="617" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A617" s="6"/>
       <c r="B617" s="6"/>
       <c r="C617" s="7"/>
@@ -14059,7 +14560,7 @@
       <c r="I617" s="1"/>
       <c r="K617" s="9"/>
     </row>
-    <row r="618" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A618" s="6"/>
       <c r="B618" s="6"/>
       <c r="C618" s="7"/>
@@ -14071,7 +14572,7 @@
       <c r="I618" s="1"/>
       <c r="K618" s="9"/>
     </row>
-    <row r="619" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A619" s="6"/>
       <c r="B619" s="6"/>
       <c r="C619" s="7"/>
@@ -14083,7 +14584,7 @@
       <c r="I619" s="1"/>
       <c r="K619" s="9"/>
     </row>
-    <row r="620" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A620" s="6"/>
       <c r="B620" s="6"/>
       <c r="C620" s="7"/>
@@ -14095,7 +14596,7 @@
       <c r="I620" s="1"/>
       <c r="K620" s="9"/>
     </row>
-    <row r="621" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A621" s="6"/>
       <c r="B621" s="6"/>
       <c r="C621" s="7"/>
@@ -14107,7 +14608,7 @@
       <c r="I621" s="1"/>
       <c r="K621" s="9"/>
     </row>
-    <row r="622" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A622" s="6"/>
       <c r="B622" s="6"/>
       <c r="C622" s="7"/>
@@ -14119,7 +14620,7 @@
       <c r="I622" s="1"/>
       <c r="K622" s="9"/>
     </row>
-    <row r="623" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A623" s="6"/>
       <c r="B623" s="6"/>
       <c r="C623" s="7"/>
@@ -14131,7 +14632,7 @@
       <c r="I623" s="1"/>
       <c r="K623" s="9"/>
     </row>
-    <row r="624" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A624" s="6"/>
       <c r="B624" s="6"/>
       <c r="C624" s="7"/>
@@ -14143,7 +14644,7 @@
       <c r="I624" s="1"/>
       <c r="K624" s="9"/>
     </row>
-    <row r="625" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A625" s="6"/>
       <c r="B625" s="6"/>
       <c r="C625" s="7"/>
@@ -14155,7 +14656,7 @@
       <c r="I625" s="1"/>
       <c r="K625" s="9"/>
     </row>
-    <row r="626" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A626" s="6"/>
       <c r="B626" s="6"/>
       <c r="C626" s="7"/>
@@ -14167,7 +14668,7 @@
       <c r="I626" s="1"/>
       <c r="K626" s="9"/>
     </row>
-    <row r="627" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A627" s="6"/>
       <c r="B627" s="6"/>
       <c r="C627" s="7"/>
@@ -14179,7 +14680,7 @@
       <c r="I627" s="1"/>
       <c r="K627" s="9"/>
     </row>
-    <row r="628" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A628" s="6"/>
       <c r="B628" s="6"/>
       <c r="C628" s="7"/>
@@ -14191,7 +14692,7 @@
       <c r="I628" s="1"/>
       <c r="K628" s="9"/>
     </row>
-    <row r="629" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A629" s="6"/>
       <c r="B629" s="6"/>
       <c r="C629" s="7"/>
@@ -14203,7 +14704,7 @@
       <c r="I629" s="1"/>
       <c r="K629" s="9"/>
     </row>
-    <row r="630" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A630" s="6"/>
       <c r="B630" s="6"/>
       <c r="C630" s="7"/>
@@ -14215,7 +14716,7 @@
       <c r="I630" s="1"/>
       <c r="K630" s="9"/>
     </row>
-    <row r="631" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A631" s="6"/>
       <c r="B631" s="6"/>
       <c r="C631" s="7"/>
@@ -14227,7 +14728,7 @@
       <c r="I631" s="1"/>
       <c r="K631" s="9"/>
     </row>
-    <row r="632" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A632" s="6"/>
       <c r="B632" s="6"/>
       <c r="C632" s="7"/>
@@ -14239,7 +14740,7 @@
       <c r="I632" s="1"/>
       <c r="K632" s="9"/>
     </row>
-    <row r="633" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A633" s="6"/>
       <c r="B633" s="6"/>
       <c r="C633" s="7"/>
@@ -14251,7 +14752,7 @@
       <c r="I633" s="1"/>
       <c r="K633" s="9"/>
     </row>
-    <row r="634" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A634" s="6"/>
       <c r="B634" s="6"/>
       <c r="C634" s="7"/>
@@ -14263,7 +14764,7 @@
       <c r="I634" s="1"/>
       <c r="K634" s="9"/>
     </row>
-    <row r="635" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A635" s="6"/>
       <c r="B635" s="6"/>
       <c r="C635" s="7"/>
@@ -14275,7 +14776,7 @@
       <c r="I635" s="1"/>
       <c r="K635" s="9"/>
     </row>
-    <row r="636" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A636" s="6"/>
       <c r="B636" s="6"/>
       <c r="C636" s="7"/>
@@ -14287,7 +14788,7 @@
       <c r="I636" s="1"/>
       <c r="K636" s="9"/>
     </row>
-    <row r="637" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A637" s="6"/>
       <c r="B637" s="6"/>
       <c r="C637" s="7"/>
@@ -14299,7 +14800,7 @@
       <c r="I637" s="1"/>
       <c r="K637" s="9"/>
     </row>
-    <row r="638" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A638" s="6"/>
       <c r="B638" s="6"/>
       <c r="C638" s="7"/>
@@ -14311,7 +14812,7 @@
       <c r="I638" s="1"/>
       <c r="K638" s="9"/>
     </row>
-    <row r="639" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A639" s="6"/>
       <c r="B639" s="6"/>
       <c r="C639" s="7"/>
@@ -14323,7 +14824,7 @@
       <c r="I639" s="1"/>
       <c r="K639" s="9"/>
     </row>
-    <row r="640" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A640" s="6"/>
       <c r="B640" s="6"/>
       <c r="C640" s="7"/>
@@ -14335,7 +14836,7 @@
       <c r="I640" s="1"/>
       <c r="K640" s="9"/>
     </row>
-    <row r="641" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A641" s="6"/>
       <c r="B641" s="6"/>
       <c r="C641" s="7"/>
@@ -14347,7 +14848,7 @@
       <c r="I641" s="1"/>
       <c r="K641" s="9"/>
     </row>
-    <row r="642" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A642" s="6"/>
       <c r="B642" s="6"/>
       <c r="C642" s="7"/>
@@ -14359,7 +14860,7 @@
       <c r="I642" s="1"/>
       <c r="K642" s="9"/>
     </row>
-    <row r="643" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A643" s="6"/>
       <c r="B643" s="6"/>
       <c r="C643" s="7"/>
@@ -14371,7 +14872,7 @@
       <c r="I643" s="1"/>
       <c r="K643" s="9"/>
     </row>
-    <row r="644" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A644" s="6"/>
       <c r="B644" s="6"/>
       <c r="C644" s="7"/>
@@ -14383,7 +14884,7 @@
       <c r="I644" s="1"/>
       <c r="K644" s="9"/>
     </row>
-    <row r="645" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A645" s="6"/>
       <c r="B645" s="6"/>
       <c r="C645" s="7"/>
@@ -14395,7 +14896,7 @@
       <c r="I645" s="1"/>
       <c r="K645" s="9"/>
     </row>
-    <row r="646" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A646" s="6"/>
       <c r="B646" s="6"/>
       <c r="C646" s="7"/>
@@ -14407,7 +14908,7 @@
       <c r="I646" s="1"/>
       <c r="K646" s="9"/>
     </row>
-    <row r="647" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A647" s="6"/>
       <c r="B647" s="6"/>
       <c r="C647" s="7"/>
@@ -14419,7 +14920,7 @@
       <c r="I647" s="1"/>
       <c r="K647" s="9"/>
     </row>
-    <row r="648" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A648" s="6"/>
       <c r="B648" s="6"/>
       <c r="C648" s="7"/>
@@ -14431,7 +14932,7 @@
       <c r="I648" s="1"/>
       <c r="K648" s="9"/>
     </row>
-    <row r="649" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A649" s="6"/>
       <c r="B649" s="6"/>
       <c r="C649" s="7"/>
@@ -14443,7 +14944,7 @@
       <c r="I649" s="1"/>
       <c r="K649" s="9"/>
     </row>
-    <row r="650" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A650" s="6"/>
       <c r="B650" s="6"/>
       <c r="C650" s="7"/>
@@ -14455,7 +14956,7 @@
       <c r="I650" s="1"/>
       <c r="K650" s="9"/>
     </row>
-    <row r="651" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A651" s="6"/>
       <c r="B651" s="6"/>
       <c r="C651" s="7"/>
@@ -14467,7 +14968,7 @@
       <c r="I651" s="1"/>
       <c r="K651" s="9"/>
     </row>
-    <row r="652" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A652" s="6"/>
       <c r="B652" s="6"/>
       <c r="C652" s="7"/>
@@ -14479,7 +14980,7 @@
       <c r="I652" s="1"/>
       <c r="K652" s="9"/>
     </row>
-    <row r="653" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A653" s="6"/>
       <c r="B653" s="6"/>
       <c r="C653" s="7"/>
@@ -14491,7 +14992,7 @@
       <c r="I653" s="1"/>
       <c r="K653" s="9"/>
     </row>
-    <row r="654" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A654" s="6"/>
       <c r="B654" s="6"/>
       <c r="C654" s="7"/>
@@ -14503,7 +15004,7 @@
       <c r="I654" s="1"/>
       <c r="K654" s="9"/>
     </row>
-    <row r="655" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A655" s="6"/>
       <c r="B655" s="6"/>
       <c r="C655" s="7"/>
@@ -14515,7 +15016,7 @@
       <c r="I655" s="1"/>
       <c r="K655" s="9"/>
     </row>
-    <row r="656" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A656" s="6"/>
       <c r="B656" s="6"/>
       <c r="C656" s="7"/>
@@ -14527,7 +15028,7 @@
       <c r="I656" s="1"/>
       <c r="K656" s="9"/>
     </row>
-    <row r="657" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A657" s="6"/>
       <c r="B657" s="6"/>
       <c r="C657" s="7"/>
@@ -14539,7 +15040,7 @@
       <c r="I657" s="1"/>
       <c r="K657" s="9"/>
     </row>
-    <row r="658" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A658" s="6"/>
       <c r="B658" s="6"/>
       <c r="C658" s="7"/>
@@ -14551,7 +15052,7 @@
       <c r="I658" s="1"/>
       <c r="K658" s="9"/>
     </row>
-    <row r="659" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A659" s="6"/>
       <c r="B659" s="6"/>
       <c r="C659" s="7"/>
@@ -14563,7 +15064,7 @@
       <c r="I659" s="1"/>
       <c r="K659" s="9"/>
     </row>
-    <row r="660" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A660" s="6"/>
       <c r="B660" s="6"/>
       <c r="C660" s="7"/>
@@ -14575,7 +15076,7 @@
       <c r="I660" s="1"/>
       <c r="K660" s="9"/>
     </row>
-    <row r="661" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A661" s="6"/>
       <c r="B661" s="6"/>
       <c r="C661" s="7"/>
@@ -14587,7 +15088,7 @@
       <c r="I661" s="1"/>
       <c r="K661" s="9"/>
     </row>
-    <row r="662" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A662" s="6"/>
       <c r="B662" s="6"/>
       <c r="C662" s="7"/>
@@ -14599,7 +15100,7 @@
       <c r="I662" s="1"/>
       <c r="K662" s="9"/>
     </row>
-    <row r="663" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A663" s="6"/>
       <c r="B663" s="6"/>
       <c r="C663" s="7"/>
@@ -14611,7 +15112,7 @@
       <c r="I663" s="1"/>
       <c r="K663" s="9"/>
     </row>
-    <row r="664" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A664" s="6"/>
       <c r="B664" s="6"/>
       <c r="C664" s="7"/>
@@ -14623,7 +15124,7 @@
       <c r="I664" s="1"/>
       <c r="K664" s="9"/>
     </row>
-    <row r="665" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A665" s="6"/>
       <c r="B665" s="6"/>
       <c r="C665" s="7"/>
@@ -14635,7 +15136,7 @@
       <c r="I665" s="1"/>
       <c r="K665" s="9"/>
     </row>
-    <row r="666" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A666" s="6"/>
       <c r="B666" s="6"/>
       <c r="C666" s="7"/>
@@ -14647,7 +15148,7 @@
       <c r="I666" s="1"/>
       <c r="K666" s="9"/>
     </row>
-    <row r="667" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A667" s="6"/>
       <c r="B667" s="6"/>
       <c r="C667" s="7"/>
@@ -14659,7 +15160,7 @@
       <c r="I667" s="1"/>
       <c r="K667" s="9"/>
     </row>
-    <row r="668" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A668" s="6"/>
       <c r="B668" s="6"/>
       <c r="C668" s="7"/>
@@ -14671,7 +15172,7 @@
       <c r="I668" s="1"/>
       <c r="K668" s="9"/>
     </row>
-    <row r="669" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A669" s="6"/>
       <c r="B669" s="6"/>
       <c r="C669" s="7"/>
@@ -14683,7 +15184,7 @@
       <c r="I669" s="1"/>
       <c r="K669" s="9"/>
     </row>
-    <row r="670" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A670" s="6"/>
       <c r="B670" s="6"/>
       <c r="C670" s="7"/>
@@ -14695,7 +15196,7 @@
       <c r="I670" s="1"/>
       <c r="K670" s="9"/>
     </row>
-    <row r="671" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A671" s="6"/>
       <c r="B671" s="6"/>
       <c r="C671" s="7"/>
@@ -14707,7 +15208,7 @@
       <c r="I671" s="1"/>
       <c r="K671" s="9"/>
     </row>
-    <row r="672" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A672" s="6"/>
       <c r="B672" s="6"/>
       <c r="C672" s="7"/>
@@ -14719,7 +15220,7 @@
       <c r="I672" s="1"/>
       <c r="K672" s="9"/>
     </row>
-    <row r="673" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A673" s="6"/>
       <c r="B673" s="6"/>
       <c r="C673" s="7"/>
@@ -14731,7 +15232,7 @@
       <c r="I673" s="1"/>
       <c r="K673" s="9"/>
     </row>
-    <row r="674" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A674" s="6"/>
       <c r="B674" s="6"/>
       <c r="C674" s="7"/>
@@ -14743,7 +15244,7 @@
       <c r="I674" s="1"/>
       <c r="K674" s="9"/>
     </row>
-    <row r="675" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A675" s="6"/>
       <c r="B675" s="6"/>
       <c r="C675" s="7"/>
@@ -14755,7 +15256,7 @@
       <c r="I675" s="1"/>
       <c r="K675" s="9"/>
     </row>
-    <row r="676" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A676" s="6"/>
       <c r="B676" s="6"/>
       <c r="C676" s="7"/>
@@ -14767,7 +15268,7 @@
       <c r="I676" s="1"/>
       <c r="K676" s="9"/>
     </row>
-    <row r="677" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A677" s="6"/>
       <c r="B677" s="6"/>
       <c r="C677" s="7"/>
@@ -14779,7 +15280,7 @@
       <c r="I677" s="1"/>
       <c r="K677" s="9"/>
     </row>
-    <row r="678" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A678" s="6"/>
       <c r="B678" s="6"/>
       <c r="C678" s="7"/>
@@ -14791,7 +15292,7 @@
       <c r="I678" s="1"/>
       <c r="K678" s="9"/>
     </row>
-    <row r="679" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A679" s="6"/>
       <c r="B679" s="6"/>
       <c r="C679" s="7"/>
@@ -14803,7 +15304,7 @@
       <c r="I679" s="1"/>
       <c r="K679" s="9"/>
     </row>
-    <row r="680" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A680" s="6"/>
       <c r="B680" s="6"/>
       <c r="C680" s="7"/>
@@ -14815,7 +15316,7 @@
       <c r="I680" s="1"/>
       <c r="K680" s="9"/>
     </row>
-    <row r="681" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A681" s="6"/>
       <c r="B681" s="6"/>
       <c r="C681" s="7"/>
@@ -14827,7 +15328,7 @@
       <c r="I681" s="1"/>
       <c r="K681" s="9"/>
     </row>
-    <row r="682" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A682" s="6"/>
       <c r="B682" s="6"/>
       <c r="C682" s="7"/>
@@ -14839,7 +15340,7 @@
       <c r="I682" s="1"/>
       <c r="K682" s="9"/>
     </row>
-    <row r="683" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A683" s="6"/>
       <c r="B683" s="6"/>
       <c r="C683" s="7"/>
@@ -14851,7 +15352,7 @@
       <c r="I683" s="1"/>
       <c r="K683" s="9"/>
     </row>
-    <row r="684" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A684" s="6"/>
       <c r="B684" s="6"/>
       <c r="C684" s="7"/>
@@ -14863,7 +15364,7 @@
       <c r="I684" s="1"/>
       <c r="K684" s="9"/>
     </row>
-    <row r="685" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A685" s="6"/>
       <c r="B685" s="6"/>
       <c r="C685" s="7"/>
@@ -14875,7 +15376,7 @@
       <c r="I685" s="1"/>
       <c r="K685" s="9"/>
     </row>
-    <row r="686" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A686" s="6"/>
       <c r="B686" s="6"/>
       <c r="C686" s="7"/>
@@ -14887,7 +15388,7 @@
       <c r="I686" s="1"/>
       <c r="K686" s="9"/>
     </row>
-    <row r="687" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A687" s="6"/>
       <c r="B687" s="6"/>
       <c r="C687" s="7"/>
@@ -14899,7 +15400,7 @@
       <c r="I687" s="1"/>
       <c r="K687" s="9"/>
     </row>
-    <row r="688" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A688" s="6"/>
       <c r="B688" s="6"/>
       <c r="C688" s="7"/>
@@ -14911,7 +15412,7 @@
       <c r="I688" s="1"/>
       <c r="K688" s="9"/>
     </row>
-    <row r="689" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A689" s="6"/>
       <c r="B689" s="6"/>
       <c r="C689" s="7"/>
@@ -14923,7 +15424,7 @@
       <c r="I689" s="1"/>
       <c r="K689" s="9"/>
     </row>
-    <row r="690" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A690" s="6"/>
       <c r="B690" s="6"/>
       <c r="C690" s="7"/>
@@ -14935,7 +15436,7 @@
       <c r="I690" s="1"/>
       <c r="K690" s="9"/>
     </row>
-    <row r="691" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A691" s="6"/>
       <c r="B691" s="6"/>
       <c r="C691" s="7"/>
@@ -14947,7 +15448,7 @@
       <c r="I691" s="1"/>
       <c r="K691" s="9"/>
     </row>
-    <row r="692" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A692" s="6"/>
       <c r="B692" s="6"/>
       <c r="C692" s="7"/>
@@ -14959,7 +15460,7 @@
       <c r="I692" s="1"/>
       <c r="K692" s="9"/>
     </row>
-    <row r="693" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A693" s="6"/>
       <c r="B693" s="6"/>
       <c r="C693" s="7"/>
@@ -14971,7 +15472,7 @@
       <c r="I693" s="1"/>
       <c r="K693" s="9"/>
     </row>
-    <row r="694" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A694" s="6"/>
       <c r="B694" s="6"/>
       <c r="C694" s="7"/>
@@ -14983,7 +15484,7 @@
       <c r="I694" s="1"/>
       <c r="K694" s="9"/>
     </row>
-    <row r="695" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A695" s="6"/>
       <c r="B695" s="6"/>
       <c r="C695" s="7"/>
@@ -14995,7 +15496,7 @@
       <c r="I695" s="1"/>
       <c r="K695" s="9"/>
     </row>
-    <row r="696" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A696" s="6"/>
       <c r="B696" s="6"/>
       <c r="C696" s="7"/>
@@ -15007,7 +15508,7 @@
       <c r="I696" s="1"/>
       <c r="K696" s="9"/>
     </row>
-    <row r="697" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A697" s="6"/>
       <c r="B697" s="6"/>
       <c r="C697" s="7"/>
@@ -15019,7 +15520,7 @@
       <c r="I697" s="1"/>
       <c r="K697" s="9"/>
     </row>
-    <row r="698" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A698" s="6"/>
       <c r="B698" s="6"/>
       <c r="C698" s="7"/>
@@ -15031,7 +15532,7 @@
       <c r="I698" s="1"/>
       <c r="K698" s="9"/>
     </row>
-    <row r="699" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A699" s="6"/>
       <c r="B699" s="6"/>
       <c r="C699" s="7"/>
@@ -15043,7 +15544,7 @@
       <c r="I699" s="1"/>
       <c r="K699" s="9"/>
     </row>
-    <row r="700" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A700" s="6"/>
       <c r="B700" s="6"/>
       <c r="C700" s="7"/>
@@ -15055,7 +15556,7 @@
       <c r="I700" s="1"/>
       <c r="K700" s="9"/>
     </row>
-    <row r="701" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A701" s="6"/>
       <c r="B701" s="6"/>
       <c r="C701" s="7"/>
@@ -15067,7 +15568,7 @@
       <c r="I701" s="1"/>
       <c r="K701" s="9"/>
     </row>
-    <row r="702" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A702" s="6"/>
       <c r="B702" s="6"/>
       <c r="C702" s="7"/>
@@ -15079,7 +15580,7 @@
       <c r="I702" s="1"/>
       <c r="K702" s="9"/>
     </row>
-    <row r="703" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A703" s="6"/>
       <c r="B703" s="6"/>
       <c r="C703" s="7"/>
@@ -15091,7 +15592,7 @@
       <c r="I703" s="1"/>
       <c r="K703" s="9"/>
     </row>
-    <row r="704" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A704" s="6"/>
       <c r="B704" s="6"/>
       <c r="C704" s="7"/>
@@ -15103,7 +15604,7 @@
       <c r="I704" s="1"/>
       <c r="K704" s="9"/>
     </row>
-    <row r="705" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A705" s="6"/>
       <c r="B705" s="6"/>
       <c r="C705" s="7"/>
@@ -15115,7 +15616,7 @@
       <c r="I705" s="1"/>
       <c r="K705" s="9"/>
     </row>
-    <row r="706" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A706" s="6"/>
       <c r="B706" s="6"/>
       <c r="C706" s="7"/>
@@ -15127,7 +15628,7 @@
       <c r="I706" s="1"/>
       <c r="K706" s="9"/>
     </row>
-    <row r="707" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A707" s="6"/>
       <c r="B707" s="6"/>
       <c r="C707" s="7"/>
@@ -15139,7 +15640,7 @@
       <c r="I707" s="1"/>
       <c r="K707" s="9"/>
     </row>
-    <row r="708" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A708" s="6"/>
       <c r="B708" s="6"/>
       <c r="C708" s="7"/>
@@ -15151,7 +15652,7 @@
       <c r="I708" s="1"/>
       <c r="K708" s="9"/>
     </row>
-    <row r="709" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A709" s="6"/>
       <c r="B709" s="6"/>
       <c r="C709" s="7"/>
@@ -15163,7 +15664,7 @@
       <c r="I709" s="1"/>
       <c r="K709" s="9"/>
     </row>
-    <row r="710" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A710" s="6"/>
       <c r="B710" s="6"/>
       <c r="C710" s="7"/>
@@ -15175,7 +15676,7 @@
       <c r="I710" s="1"/>
       <c r="K710" s="9"/>
     </row>
-    <row r="711" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A711" s="6"/>
       <c r="B711" s="6"/>
       <c r="C711" s="7"/>
@@ -15187,7 +15688,7 @@
       <c r="I711" s="1"/>
       <c r="K711" s="9"/>
     </row>
-    <row r="712" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A712" s="6"/>
       <c r="B712" s="6"/>
       <c r="C712" s="7"/>
@@ -15199,7 +15700,7 @@
       <c r="I712" s="1"/>
       <c r="K712" s="9"/>
     </row>
-    <row r="713" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A713" s="6"/>
       <c r="B713" s="6"/>
       <c r="C713" s="7"/>
@@ -15211,7 +15712,7 @@
       <c r="I713" s="1"/>
       <c r="K713" s="9"/>
     </row>
-    <row r="714" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A714" s="6"/>
       <c r="B714" s="6"/>
       <c r="C714" s="7"/>
@@ -15223,7 +15724,7 @@
       <c r="I714" s="1"/>
       <c r="K714" s="9"/>
     </row>
-    <row r="715" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A715" s="6"/>
       <c r="B715" s="6"/>
       <c r="C715" s="7"/>
@@ -15235,7 +15736,7 @@
       <c r="I715" s="1"/>
       <c r="K715" s="9"/>
     </row>
-    <row r="716" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A716" s="6"/>
       <c r="B716" s="6"/>
       <c r="C716" s="7"/>
@@ -15247,7 +15748,7 @@
       <c r="I716" s="1"/>
       <c r="K716" s="9"/>
     </row>
-    <row r="717" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A717" s="6"/>
       <c r="B717" s="6"/>
       <c r="C717" s="7"/>
@@ -15259,7 +15760,7 @@
       <c r="I717" s="1"/>
       <c r="K717" s="9"/>
     </row>
-    <row r="718" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A718" s="6"/>
       <c r="B718" s="6"/>
       <c r="C718" s="7"/>
@@ -15271,7 +15772,7 @@
       <c r="I718" s="1"/>
       <c r="K718" s="9"/>
     </row>
-    <row r="719" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A719" s="6"/>
       <c r="B719" s="6"/>
       <c r="C719" s="7"/>
@@ -15283,7 +15784,7 @@
       <c r="I719" s="1"/>
       <c r="K719" s="9"/>
     </row>
-    <row r="720" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A720" s="6"/>
       <c r="B720" s="6"/>
       <c r="C720" s="7"/>
@@ -15295,7 +15796,7 @@
       <c r="I720" s="1"/>
       <c r="K720" s="9"/>
     </row>
-    <row r="721" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A721" s="6"/>
       <c r="B721" s="6"/>
       <c r="C721" s="7"/>
@@ -15307,7 +15808,7 @@
       <c r="I721" s="1"/>
       <c r="K721" s="9"/>
     </row>
-    <row r="722" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A722" s="6"/>
       <c r="B722" s="6"/>
       <c r="C722" s="7"/>
@@ -15319,7 +15820,7 @@
       <c r="I722" s="1"/>
       <c r="K722" s="9"/>
     </row>
-    <row r="723" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A723" s="6"/>
       <c r="B723" s="6"/>
       <c r="C723" s="7"/>
@@ -15331,7 +15832,7 @@
       <c r="I723" s="1"/>
       <c r="K723" s="9"/>
     </row>
-    <row r="724" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A724" s="6"/>
       <c r="B724" s="6"/>
       <c r="C724" s="7"/>
@@ -15343,7 +15844,7 @@
       <c r="I724" s="1"/>
       <c r="K724" s="9"/>
     </row>
-    <row r="725" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A725" s="6"/>
       <c r="B725" s="6"/>
       <c r="C725" s="7"/>
@@ -15355,7 +15856,7 @@
       <c r="I725" s="1"/>
       <c r="K725" s="9"/>
     </row>
-    <row r="726" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A726" s="6"/>
       <c r="B726" s="6"/>
       <c r="C726" s="7"/>
@@ -15367,7 +15868,7 @@
       <c r="I726" s="1"/>
       <c r="K726" s="9"/>
     </row>
-    <row r="727" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A727" s="6"/>
       <c r="B727" s="6"/>
       <c r="C727" s="7"/>
@@ -15379,7 +15880,7 @@
       <c r="I727" s="1"/>
       <c r="K727" s="9"/>
     </row>
-    <row r="728" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A728" s="6"/>
       <c r="B728" s="6"/>
       <c r="C728" s="7"/>
@@ -15391,7 +15892,7 @@
       <c r="I728" s="1"/>
       <c r="K728" s="9"/>
     </row>
-    <row r="729" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A729" s="6"/>
       <c r="B729" s="6"/>
       <c r="C729" s="7"/>
@@ -15403,7 +15904,7 @@
       <c r="I729" s="1"/>
       <c r="K729" s="9"/>
     </row>
-    <row r="730" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A730" s="6"/>
       <c r="B730" s="6"/>
       <c r="C730" s="7"/>
@@ -15415,7 +15916,7 @@
       <c r="I730" s="1"/>
       <c r="K730" s="9"/>
     </row>
-    <row r="731" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A731" s="6"/>
       <c r="B731" s="6"/>
       <c r="C731" s="7"/>
@@ -15427,7 +15928,7 @@
       <c r="I731" s="1"/>
       <c r="K731" s="9"/>
     </row>
-    <row r="732" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A732" s="6"/>
       <c r="B732" s="6"/>
       <c r="C732" s="7"/>
@@ -15439,7 +15940,7 @@
       <c r="I732" s="1"/>
       <c r="K732" s="9"/>
     </row>
-    <row r="733" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A733" s="6"/>
       <c r="B733" s="6"/>
       <c r="C733" s="7"/>
@@ -15451,7 +15952,7 @@
       <c r="I733" s="1"/>
       <c r="K733" s="9"/>
     </row>
-    <row r="734" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A734" s="6"/>
       <c r="B734" s="6"/>
       <c r="C734" s="7"/>
@@ -15463,7 +15964,7 @@
       <c r="I734" s="1"/>
       <c r="K734" s="9"/>
     </row>
-    <row r="735" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A735" s="6"/>
       <c r="B735" s="6"/>
       <c r="C735" s="7"/>
@@ -15475,7 +15976,7 @@
       <c r="I735" s="1"/>
       <c r="K735" s="9"/>
     </row>
-    <row r="736" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A736" s="6"/>
       <c r="B736" s="6"/>
       <c r="C736" s="7"/>
@@ -15487,7 +15988,7 @@
       <c r="I736" s="1"/>
       <c r="K736" s="9"/>
     </row>
-    <row r="737" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A737" s="6"/>
       <c r="B737" s="6"/>
       <c r="C737" s="7"/>
@@ -15499,7 +16000,7 @@
       <c r="I737" s="1"/>
       <c r="K737" s="9"/>
     </row>
-    <row r="738" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A738" s="6"/>
       <c r="B738" s="6"/>
       <c r="C738" s="7"/>
@@ -15511,7 +16012,7 @@
       <c r="I738" s="1"/>
       <c r="K738" s="9"/>
     </row>
-    <row r="739" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A739" s="6"/>
       <c r="B739" s="6"/>
       <c r="C739" s="7"/>
@@ -15523,7 +16024,7 @@
       <c r="I739" s="1"/>
       <c r="K739" s="9"/>
     </row>
-    <row r="740" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A740" s="6"/>
       <c r="B740" s="6"/>
       <c r="C740" s="7"/>
@@ -15535,7 +16036,7 @@
       <c r="I740" s="1"/>
       <c r="K740" s="9"/>
     </row>
-    <row r="741" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A741" s="6"/>
       <c r="B741" s="6"/>
       <c r="C741" s="7"/>
@@ -15547,7 +16048,7 @@
       <c r="I741" s="1"/>
       <c r="K741" s="9"/>
     </row>
-    <row r="742" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A742" s="6"/>
       <c r="B742" s="6"/>
       <c r="C742" s="7"/>
@@ -15559,7 +16060,7 @@
       <c r="I742" s="1"/>
       <c r="K742" s="9"/>
     </row>
-    <row r="743" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A743" s="6"/>
       <c r="B743" s="6"/>
       <c r="C743" s="7"/>
@@ -15571,7 +16072,7 @@
       <c r="I743" s="1"/>
       <c r="K743" s="9"/>
     </row>
-    <row r="744" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A744" s="6"/>
       <c r="B744" s="6"/>
       <c r="C744" s="7"/>
@@ -15583,7 +16084,7 @@
       <c r="I744" s="1"/>
       <c r="K744" s="9"/>
     </row>
-    <row r="745" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A745" s="6"/>
       <c r="B745" s="6"/>
       <c r="C745" s="7"/>
@@ -15595,7 +16096,7 @@
       <c r="I745" s="1"/>
       <c r="K745" s="9"/>
     </row>
-    <row r="746" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A746" s="6"/>
       <c r="B746" s="6"/>
       <c r="C746" s="7"/>
@@ -15607,7 +16108,7 @@
       <c r="I746" s="1"/>
       <c r="K746" s="9"/>
     </row>
-    <row r="747" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A747" s="6"/>
       <c r="B747" s="6"/>
       <c r="C747" s="7"/>
@@ -15619,7 +16120,7 @@
       <c r="I747" s="1"/>
       <c r="K747" s="9"/>
     </row>
-    <row r="748" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A748" s="6"/>
       <c r="B748" s="6"/>
       <c r="C748" s="7"/>
@@ -15631,7 +16132,7 @@
       <c r="I748" s="1"/>
       <c r="K748" s="9"/>
     </row>
-    <row r="749" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A749" s="6"/>
       <c r="B749" s="6"/>
       <c r="C749" s="7"/>
@@ -15643,7 +16144,7 @@
       <c r="I749" s="1"/>
       <c r="K749" s="9"/>
     </row>
-    <row r="750" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A750" s="6"/>
       <c r="B750" s="6"/>
       <c r="C750" s="7"/>
@@ -15655,7 +16156,7 @@
       <c r="I750" s="1"/>
       <c r="K750" s="9"/>
     </row>
-    <row r="751" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A751" s="6"/>
       <c r="B751" s="6"/>
       <c r="C751" s="7"/>
@@ -15667,7 +16168,7 @@
       <c r="I751" s="1"/>
       <c r="K751" s="9"/>
     </row>
-    <row r="752" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A752" s="6"/>
       <c r="B752" s="6"/>
       <c r="C752" s="7"/>
@@ -15679,7 +16180,7 @@
       <c r="I752" s="1"/>
       <c r="K752" s="9"/>
     </row>
-    <row r="753" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A753" s="6"/>
       <c r="B753" s="6"/>
       <c r="C753" s="7"/>
@@ -15691,7 +16192,7 @@
       <c r="I753" s="1"/>
       <c r="K753" s="9"/>
     </row>
-    <row r="754" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A754" s="6"/>
       <c r="B754" s="6"/>
       <c r="C754" s="7"/>
@@ -15703,7 +16204,7 @@
       <c r="I754" s="1"/>
       <c r="K754" s="9"/>
     </row>
-    <row r="755" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A755" s="6"/>
       <c r="B755" s="6"/>
       <c r="C755" s="7"/>
@@ -15715,7 +16216,7 @@
       <c r="I755" s="1"/>
       <c r="K755" s="9"/>
     </row>
-    <row r="756" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A756" s="6"/>
       <c r="B756" s="6"/>
       <c r="C756" s="7"/>
@@ -15727,7 +16228,7 @@
       <c r="I756" s="1"/>
       <c r="K756" s="9"/>
     </row>
-    <row r="757" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A757" s="6"/>
       <c r="B757" s="6"/>
       <c r="C757" s="7"/>
@@ -15738,7 +16239,7 @@
       <c r="H757" s="1"/>
       <c r="I757" s="1"/>
     </row>
-    <row r="758" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A758" s="6"/>
       <c r="B758" s="6"/>
       <c r="C758" s="7"/>
@@ -15749,7 +16250,7 @@
       <c r="H758" s="1"/>
       <c r="I758" s="1"/>
     </row>
-    <row r="759" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A759" s="6"/>
       <c r="B759" s="6"/>
       <c r="C759" s="7"/>
@@ -15760,7 +16261,7 @@
       <c r="H759" s="1"/>
       <c r="I759" s="1"/>
     </row>
-    <row r="760" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A760" s="6"/>
       <c r="B760" s="6"/>
       <c r="C760" s="7"/>
@@ -15771,7 +16272,7 @@
       <c r="H760" s="1"/>
       <c r="I760" s="1"/>
     </row>
-    <row r="761" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A761" s="6"/>
       <c r="B761" s="6"/>
       <c r="C761" s="7"/>
@@ -15782,7 +16283,7 @@
       <c r="H761" s="1"/>
       <c r="I761" s="1"/>
     </row>
-    <row r="762" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A762" s="6"/>
       <c r="B762" s="6"/>
       <c r="C762" s="7"/>
@@ -15793,7 +16294,7 @@
       <c r="H762" s="1"/>
       <c r="I762" s="1"/>
     </row>
-    <row r="763" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A763" s="6"/>
       <c r="B763" s="6"/>
       <c r="C763" s="7"/>
@@ -15804,7 +16305,7 @@
       <c r="H763" s="1"/>
       <c r="I763" s="1"/>
     </row>
-    <row r="764" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A764" s="6"/>
       <c r="B764" s="6"/>
       <c r="C764" s="7"/>
@@ -15815,7 +16316,7 @@
       <c r="H764" s="1"/>
       <c r="I764" s="1"/>
     </row>
-    <row r="765" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A765" s="6"/>
       <c r="B765" s="6"/>
       <c r="C765" s="7"/>
@@ -15826,7 +16327,7 @@
       <c r="H765" s="1"/>
       <c r="I765" s="1"/>
     </row>
-    <row r="766" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A766" s="6"/>
       <c r="B766" s="6"/>
       <c r="C766" s="7"/>
@@ -15837,7 +16338,7 @@
       <c r="H766" s="1"/>
       <c r="I766" s="1"/>
     </row>
-    <row r="767" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A767" s="6"/>
       <c r="B767" s="6"/>
       <c r="C767" s="7"/>
@@ -15848,7 +16349,7 @@
       <c r="H767" s="1"/>
       <c r="I767" s="1"/>
     </row>
-    <row r="768" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A768" s="6"/>
       <c r="B768" s="6"/>
       <c r="C768" s="7"/>
@@ -15859,7 +16360,7 @@
       <c r="H768" s="1"/>
       <c r="I768" s="1"/>
     </row>
-    <row r="769" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A769" s="6"/>
       <c r="B769" s="6"/>
       <c r="C769" s="7"/>
@@ -15870,7 +16371,7 @@
       <c r="H769" s="1"/>
       <c r="I769" s="1"/>
     </row>
-    <row r="770" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A770" s="6"/>
       <c r="B770" s="6"/>
       <c r="C770" s="7"/>
@@ -15881,7 +16382,7 @@
       <c r="H770" s="1"/>
       <c r="I770" s="1"/>
     </row>
-    <row r="771" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A771" s="6"/>
       <c r="B771" s="6"/>
       <c r="C771" s="7"/>
@@ -15892,7 +16393,7 @@
       <c r="H771" s="1"/>
       <c r="I771" s="1"/>
     </row>
-    <row r="772" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A772" s="6"/>
       <c r="B772" s="6"/>
       <c r="C772" s="7"/>
@@ -15903,7 +16404,7 @@
       <c r="H772" s="1"/>
       <c r="I772" s="1"/>
     </row>
-    <row r="773" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A773" s="6"/>
       <c r="B773" s="6"/>
       <c r="C773" s="7"/>
@@ -15914,7 +16415,7 @@
       <c r="H773" s="1"/>
       <c r="I773" s="1"/>
     </row>
-    <row r="774" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A774" s="6"/>
       <c r="B774" s="6"/>
       <c r="C774" s="7"/>
@@ -15925,7 +16426,7 @@
       <c r="H774" s="1"/>
       <c r="I774" s="1"/>
     </row>
-    <row r="775" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A775" s="6"/>
       <c r="B775" s="6"/>
       <c r="C775" s="7"/>
@@ -15936,7 +16437,7 @@
       <c r="H775" s="1"/>
       <c r="I775" s="1"/>
     </row>
-    <row r="776" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A776" s="6"/>
       <c r="B776" s="6"/>
       <c r="C776" s="7"/>
@@ -15947,7 +16448,7 @@
       <c r="H776" s="1"/>
       <c r="I776" s="1"/>
     </row>
-    <row r="777" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A777" s="6"/>
       <c r="B777" s="6"/>
       <c r="C777" s="7"/>
@@ -15958,7 +16459,7 @@
       <c r="H777" s="1"/>
       <c r="I777" s="1"/>
     </row>
-    <row r="778" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A778" s="6"/>
       <c r="B778" s="6"/>
       <c r="C778" s="7"/>
@@ -15969,7 +16470,7 @@
       <c r="H778" s="1"/>
       <c r="I778" s="1"/>
     </row>
-    <row r="779" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A779" s="6"/>
       <c r="B779" s="6"/>
       <c r="C779" s="7"/>
@@ -15980,7 +16481,7 @@
       <c r="H779" s="1"/>
       <c r="I779" s="1"/>
     </row>
-    <row r="780" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A780" s="6"/>
       <c r="B780" s="6"/>
       <c r="C780" s="7"/>
@@ -15991,7 +16492,7 @@
       <c r="H780" s="1"/>
       <c r="I780" s="1"/>
     </row>
-    <row r="781" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A781" s="6"/>
       <c r="B781" s="6"/>
       <c r="C781" s="7"/>
@@ -16002,7 +16503,7 @@
       <c r="H781" s="1"/>
       <c r="I781" s="1"/>
     </row>
-    <row r="782" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A782" s="6"/>
       <c r="B782" s="6"/>
       <c r="C782" s="7"/>
@@ -16013,7 +16514,7 @@
       <c r="H782" s="1"/>
       <c r="I782" s="1"/>
     </row>
-    <row r="783" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A783" s="6"/>
       <c r="B783" s="6"/>
       <c r="C783" s="7"/>
@@ -16024,7 +16525,7 @@
       <c r="H783" s="1"/>
       <c r="I783" s="1"/>
     </row>
-    <row r="784" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A784" s="6"/>
       <c r="B784" s="6"/>
       <c r="C784" s="7"/>
@@ -16035,7 +16536,7 @@
       <c r="H784" s="1"/>
       <c r="I784" s="1"/>
     </row>
-    <row r="785" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A785" s="6"/>
       <c r="B785" s="6"/>
       <c r="C785" s="7"/>
@@ -16046,7 +16547,7 @@
       <c r="H785" s="1"/>
       <c r="I785" s="1"/>
     </row>
-    <row r="786" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A786" s="6"/>
       <c r="B786" s="6"/>
       <c r="C786" s="7"/>
@@ -16057,7 +16558,7 @@
       <c r="H786" s="1"/>
       <c r="I786" s="1"/>
     </row>
-    <row r="787" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A787" s="6"/>
       <c r="B787" s="6"/>
       <c r="C787" s="7"/>
@@ -16068,7 +16569,7 @@
       <c r="H787" s="1"/>
       <c r="I787" s="1"/>
     </row>
-    <row r="788" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A788" s="6"/>
       <c r="B788" s="6"/>
       <c r="C788" s="7"/>
@@ -16079,7 +16580,7 @@
       <c r="H788" s="1"/>
       <c r="I788" s="1"/>
     </row>
-    <row r="789" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A789" s="6"/>
       <c r="B789" s="6"/>
       <c r="C789" s="7"/>
@@ -16090,7 +16591,7 @@
       <c r="H789" s="1"/>
       <c r="I789" s="1"/>
     </row>
-    <row r="790" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A790" s="6"/>
       <c r="B790" s="6"/>
       <c r="C790" s="7"/>
@@ -16101,7 +16602,7 @@
       <c r="H790" s="1"/>
       <c r="I790" s="1"/>
     </row>
-    <row r="791" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A791" s="6"/>
       <c r="B791" s="6"/>
       <c r="C791" s="7"/>
@@ -16112,7 +16613,7 @@
       <c r="H791" s="1"/>
       <c r="I791" s="1"/>
     </row>
-    <row r="792" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A792" s="6"/>
       <c r="B792" s="6"/>
       <c r="C792" s="7"/>
@@ -16123,7 +16624,7 @@
       <c r="H792" s="1"/>
       <c r="I792" s="1"/>
     </row>
-    <row r="793" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A793" s="6"/>
       <c r="B793" s="6"/>
       <c r="C793" s="7"/>
@@ -16134,7 +16635,7 @@
       <c r="H793" s="1"/>
       <c r="I793" s="1"/>
     </row>
-    <row r="794" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A794" s="6"/>
       <c r="B794" s="6"/>
       <c r="C794" s="7"/>
@@ -16145,7 +16646,7 @@
       <c r="H794" s="1"/>
       <c r="I794" s="1"/>
     </row>
-    <row r="795" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A795" s="6"/>
       <c r="B795" s="6"/>
       <c r="C795" s="7"/>
@@ -16156,7 +16657,7 @@
       <c r="H795" s="1"/>
       <c r="I795" s="1"/>
     </row>
-    <row r="796" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A796" s="6"/>
       <c r="B796" s="6"/>
       <c r="C796" s="7"/>
@@ -16167,7 +16668,7 @@
       <c r="H796" s="1"/>
       <c r="I796" s="1"/>
     </row>
-    <row r="797" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A797" s="6"/>
       <c r="B797" s="6"/>
       <c r="C797" s="7"/>
@@ -16178,7 +16679,7 @@
       <c r="H797" s="1"/>
       <c r="I797" s="1"/>
     </row>
-    <row r="798" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A798" s="6"/>
       <c r="B798" s="6"/>
       <c r="C798" s="7"/>
@@ -16189,7 +16690,7 @@
       <c r="H798" s="1"/>
       <c r="I798" s="1"/>
     </row>
-    <row r="799" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A799" s="6"/>
       <c r="B799" s="6"/>
       <c r="C799" s="7"/>
@@ -16200,7 +16701,7 @@
       <c r="H799" s="1"/>
       <c r="I799" s="1"/>
     </row>
-    <row r="800" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A800" s="6"/>
       <c r="B800" s="6"/>
       <c r="C800" s="7"/>
@@ -16211,7 +16712,7 @@
       <c r="H800" s="1"/>
       <c r="I800" s="1"/>
     </row>
-    <row r="801" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A801" s="6"/>
       <c r="B801" s="6"/>
       <c r="C801" s="7"/>
@@ -16222,7 +16723,7 @@
       <c r="H801" s="1"/>
       <c r="I801" s="1"/>
     </row>
-    <row r="802" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A802" s="6"/>
       <c r="B802" s="6"/>
       <c r="C802" s="7"/>
@@ -16233,7 +16734,7 @@
       <c r="H802" s="1"/>
       <c r="I802" s="1"/>
     </row>
-    <row r="803" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A803" s="6"/>
       <c r="B803" s="6"/>
       <c r="C803" s="7"/>
@@ -16244,7 +16745,7 @@
       <c r="H803" s="1"/>
       <c r="I803" s="1"/>
     </row>
-    <row r="804" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A804" s="6"/>
       <c r="B804" s="6"/>
       <c r="C804" s="7"/>
@@ -16255,7 +16756,7 @@
       <c r="H804" s="1"/>
       <c r="I804" s="1"/>
     </row>
-    <row r="805" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A805" s="6"/>
       <c r="B805" s="6"/>
       <c r="C805" s="7"/>
@@ -16266,7 +16767,7 @@
       <c r="H805" s="1"/>
       <c r="I805" s="1"/>
     </row>
-    <row r="806" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A806" s="6"/>
       <c r="B806" s="6"/>
       <c r="C806" s="7"/>
@@ -16277,7 +16778,7 @@
       <c r="H806" s="1"/>
       <c r="I806" s="1"/>
     </row>
-    <row r="807" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A807" s="6"/>
       <c r="B807" s="6"/>
       <c r="C807" s="7"/>
@@ -16288,7 +16789,7 @@
       <c r="H807" s="1"/>
       <c r="I807" s="1"/>
     </row>
-    <row r="808" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A808" s="6"/>
       <c r="B808" s="6"/>
       <c r="C808" s="7"/>
@@ -16299,7 +16800,7 @@
       <c r="H808" s="1"/>
       <c r="I808" s="1"/>
     </row>
-    <row r="809" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A809" s="6"/>
       <c r="B809" s="6"/>
       <c r="C809" s="7"/>
@@ -16310,7 +16811,7 @@
       <c r="H809" s="1"/>
       <c r="I809" s="1"/>
     </row>
-    <row r="810" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A810" s="6"/>
       <c r="B810" s="6"/>
       <c r="C810" s="7"/>
@@ -16321,7 +16822,7 @@
       <c r="H810" s="1"/>
       <c r="I810" s="1"/>
     </row>
-    <row r="811" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A811" s="6"/>
       <c r="B811" s="6"/>
       <c r="C811" s="7"/>
@@ -16332,7 +16833,7 @@
       <c r="H811" s="1"/>
       <c r="I811" s="1"/>
     </row>
-    <row r="812" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A812" s="6"/>
       <c r="B812" s="6"/>
       <c r="C812" s="7"/>
@@ -16343,7 +16844,7 @@
       <c r="H812" s="1"/>
       <c r="I812" s="1"/>
     </row>
-    <row r="813" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A813" s="6"/>
       <c r="B813" s="6"/>
       <c r="C813" s="7"/>
@@ -16354,7 +16855,7 @@
       <c r="H813" s="1"/>
       <c r="I813" s="1"/>
     </row>
-    <row r="814" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A814" s="6"/>
       <c r="B814" s="6"/>
       <c r="C814" s="7"/>
@@ -16365,7 +16866,7 @@
       <c r="H814" s="1"/>
       <c r="I814" s="1"/>
     </row>
-    <row r="815" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A815" s="6"/>
       <c r="B815" s="6"/>
       <c r="C815" s="7"/>
@@ -16376,7 +16877,7 @@
       <c r="H815" s="1"/>
       <c r="I815" s="1"/>
     </row>
-    <row r="816" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A816" s="6"/>
       <c r="B816" s="6"/>
       <c r="C816" s="7"/>
@@ -16387,7 +16888,7 @@
       <c r="H816" s="1"/>
       <c r="I816" s="1"/>
     </row>
-    <row r="817" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A817" s="6"/>
       <c r="B817" s="6"/>
       <c r="C817" s="7"/>
@@ -16398,7 +16899,7 @@
       <c r="H817" s="1"/>
       <c r="I817" s="1"/>
     </row>
-    <row r="818" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A818" s="6"/>
       <c r="B818" s="6"/>
       <c r="C818" s="7"/>
@@ -16409,7 +16910,7 @@
       <c r="H818" s="1"/>
       <c r="I818" s="1"/>
     </row>
-    <row r="819" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A819" s="6"/>
       <c r="B819" s="6"/>
       <c r="C819" s="7"/>
@@ -16420,7 +16921,7 @@
       <c r="H819" s="1"/>
       <c r="I819" s="1"/>
     </row>
-    <row r="820" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A820" s="6"/>
       <c r="B820" s="6"/>
       <c r="C820" s="7"/>
@@ -16431,7 +16932,7 @@
       <c r="H820" s="1"/>
       <c r="I820" s="1"/>
     </row>
-    <row r="821" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A821" s="6"/>
       <c r="B821" s="6"/>
       <c r="C821" s="7"/>
@@ -16442,7 +16943,7 @@
       <c r="H821" s="1"/>
       <c r="I821" s="1"/>
     </row>
-    <row r="822" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A822" s="6"/>
       <c r="B822" s="6"/>
       <c r="C822" s="7"/>
@@ -16453,7 +16954,7 @@
       <c r="H822" s="1"/>
       <c r="I822" s="1"/>
     </row>
-    <row r="823" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A823" s="6"/>
       <c r="B823" s="6"/>
       <c r="C823" s="7"/>
@@ -16464,7 +16965,7 @@
       <c r="H823" s="1"/>
       <c r="I823" s="1"/>
     </row>
-    <row r="824" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A824" s="6"/>
       <c r="B824" s="6"/>
       <c r="C824" s="7"/>
@@ -16475,7 +16976,7 @@
       <c r="H824" s="1"/>
       <c r="I824" s="1"/>
     </row>
-    <row r="825" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A825" s="6"/>
       <c r="B825" s="6"/>
       <c r="C825" s="7"/>
@@ -16486,7 +16987,7 @@
       <c r="H825" s="1"/>
       <c r="I825" s="1"/>
     </row>
-    <row r="826" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A826" s="6"/>
       <c r="B826" s="6"/>
       <c r="C826" s="7"/>
@@ -16497,7 +16998,7 @@
       <c r="H826" s="1"/>
       <c r="I826" s="1"/>
     </row>
-    <row r="827" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A827" s="6"/>
       <c r="B827" s="6"/>
       <c r="C827" s="7"/>
@@ -16508,7 +17009,7 @@
       <c r="H827" s="1"/>
       <c r="I827" s="1"/>
     </row>
-    <row r="828" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A828" s="6"/>
       <c r="B828" s="6"/>
       <c r="C828" s="7"/>
@@ -16519,7 +17020,7 @@
       <c r="H828" s="1"/>
       <c r="I828" s="1"/>
     </row>
-    <row r="829" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A829" s="6"/>
       <c r="B829" s="6"/>
       <c r="C829" s="7"/>
@@ -16530,7 +17031,7 @@
       <c r="H829" s="1"/>
       <c r="I829" s="1"/>
     </row>
-    <row r="830" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A830" s="6"/>
       <c r="B830" s="6"/>
       <c r="C830" s="7"/>
@@ -16541,7 +17042,7 @@
       <c r="H830" s="1"/>
       <c r="I830" s="1"/>
     </row>
-    <row r="831" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A831" s="6"/>
       <c r="B831" s="6"/>
       <c r="C831" s="7"/>
@@ -16552,7 +17053,7 @@
       <c r="H831" s="1"/>
       <c r="I831" s="1"/>
     </row>
-    <row r="832" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A832" s="6"/>
       <c r="B832" s="6"/>
       <c r="C832" s="7"/>
@@ -16563,7 +17064,7 @@
       <c r="H832" s="1"/>
       <c r="I832" s="1"/>
     </row>
-    <row r="833" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A833" s="6"/>
       <c r="B833" s="6"/>
       <c r="C833" s="7"/>
@@ -16574,7 +17075,7 @@
       <c r="H833" s="1"/>
       <c r="I833" s="1"/>
     </row>
-    <row r="834" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A834" s="6"/>
       <c r="B834" s="6"/>
       <c r="C834" s="7"/>
@@ -16585,7 +17086,7 @@
       <c r="H834" s="1"/>
       <c r="I834" s="1"/>
     </row>
-    <row r="835" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A835" s="6"/>
       <c r="B835" s="6"/>
       <c r="C835" s="7"/>
@@ -16596,7 +17097,7 @@
       <c r="H835" s="1"/>
       <c r="I835" s="1"/>
     </row>
-    <row r="836" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A836" s="6"/>
       <c r="B836" s="6"/>
       <c r="C836" s="7"/>
@@ -16607,7 +17108,7 @@
       <c r="H836" s="1"/>
       <c r="I836" s="1"/>
     </row>
-    <row r="837" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A837" s="6"/>
       <c r="B837" s="6"/>
       <c r="C837" s="7"/>
@@ -16618,7 +17119,7 @@
       <c r="H837" s="1"/>
       <c r="I837" s="1"/>
     </row>
-    <row r="838" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A838" s="6"/>
       <c r="B838" s="6"/>
       <c r="C838" s="7"/>
@@ -16629,7 +17130,7 @@
       <c r="H838" s="1"/>
       <c r="I838" s="1"/>
     </row>
-    <row r="839" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A839" s="6"/>
       <c r="B839" s="6"/>
       <c r="C839" s="7"/>
@@ -16640,7 +17141,7 @@
       <c r="H839" s="1"/>
       <c r="I839" s="1"/>
     </row>
-    <row r="840" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A840" s="6"/>
       <c r="B840" s="6"/>
       <c r="C840" s="7"/>
@@ -16651,7 +17152,7 @@
       <c r="H840" s="1"/>
       <c r="I840" s="1"/>
     </row>
-    <row r="841" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B841" s="6"/>
       <c r="C841" s="7"/>
       <c r="E841" s="1"/>
@@ -16660,7 +17161,7 @@
       <c r="H841" s="1"/>
       <c r="I841" s="1"/>
     </row>
-    <row r="842" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B842" s="6"/>
       <c r="C842" s="7"/>
       <c r="E842" s="1"/>
@@ -16669,7 +17170,7 @@
       <c r="H842" s="1"/>
       <c r="I842" s="1"/>
     </row>
-    <row r="843" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B843" s="6"/>
       <c r="C843" s="7"/>
       <c r="E843" s="1"/>
@@ -16678,7 +17179,7 @@
       <c r="H843" s="1"/>
       <c r="I843" s="1"/>
     </row>
-    <row r="844" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B844" s="6"/>
       <c r="C844" s="7"/>
       <c r="E844" s="1"/>
@@ -16687,7 +17188,7 @@
       <c r="H844" s="1"/>
       <c r="I844" s="1"/>
     </row>
-    <row r="845" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B845" s="6"/>
       <c r="C845" s="7"/>
       <c r="E845" s="1"/>
@@ -16696,7 +17197,7 @@
       <c r="H845" s="1"/>
       <c r="I845" s="1"/>
     </row>
-    <row r="846" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B846" s="6"/>
       <c r="C846" s="7"/>
       <c r="E846" s="1"/>
@@ -16705,7 +17206,7 @@
       <c r="H846" s="1"/>
       <c r="I846" s="1"/>
     </row>
-    <row r="847" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B847" s="6"/>
       <c r="C847" s="7"/>
       <c r="E847" s="1"/>
@@ -16714,7 +17215,7 @@
       <c r="H847" s="1"/>
       <c r="I847" s="1"/>
     </row>
-    <row r="848" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B848" s="6"/>
       <c r="C848" s="7"/>
       <c r="E848" s="1"/>
@@ -16723,7 +17224,7 @@
       <c r="H848" s="1"/>
       <c r="I848" s="1"/>
     </row>
-    <row r="849" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="849" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B849" s="6"/>
       <c r="C849" s="7"/>
       <c r="E849" s="1"/>
@@ -16732,7 +17233,7 @@
       <c r="H849" s="1"/>
       <c r="I849" s="1"/>
     </row>
-    <row r="850" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="850" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B850" s="6"/>
       <c r="C850" s="7"/>
       <c r="E850" s="1"/>
@@ -16741,7 +17242,7 @@
       <c r="H850" s="1"/>
       <c r="I850" s="1"/>
     </row>
-    <row r="851" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="851" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B851" s="6"/>
       <c r="C851" s="7"/>
       <c r="E851" s="1"/>
@@ -16750,7 +17251,7 @@
       <c r="H851" s="1"/>
       <c r="I851" s="1"/>
     </row>
-    <row r="852" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="852" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B852" s="6"/>
       <c r="C852" s="7"/>
       <c r="E852" s="1"/>
@@ -16759,7 +17260,7 @@
       <c r="H852" s="1"/>
       <c r="I852" s="1"/>
     </row>
-    <row r="853" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="853" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B853" s="6"/>
       <c r="C853" s="7"/>
       <c r="E853" s="1"/>
@@ -16768,7 +17269,7 @@
       <c r="H853" s="1"/>
       <c r="I853" s="1"/>
     </row>
-    <row r="854" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="854" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B854" s="6"/>
       <c r="C854" s="7"/>
       <c r="E854" s="1"/>
@@ -16777,7 +17278,7 @@
       <c r="H854" s="1"/>
       <c r="I854" s="1"/>
     </row>
-    <row r="855" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="855" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B855" s="6"/>
       <c r="C855" s="7"/>
       <c r="E855" s="1"/>
@@ -16786,7 +17287,7 @@
       <c r="H855" s="1"/>
       <c r="I855" s="1"/>
     </row>
-    <row r="856" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="856" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B856" s="6"/>
       <c r="C856" s="7"/>
       <c r="E856" s="1"/>
@@ -16795,7 +17296,7 @@
       <c r="H856" s="1"/>
       <c r="I856" s="1"/>
     </row>
-    <row r="857" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="857" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B857" s="6"/>
       <c r="C857" s="7"/>
       <c r="E857" s="1"/>
@@ -16804,7 +17305,7 @@
       <c r="H857" s="1"/>
       <c r="I857" s="1"/>
     </row>
-    <row r="858" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="858" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B858" s="6"/>
       <c r="C858" s="7"/>
       <c r="E858" s="1"/>
@@ -16813,7 +17314,7 @@
       <c r="H858" s="1"/>
       <c r="I858" s="1"/>
     </row>
-    <row r="859" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="859" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B859" s="6"/>
       <c r="C859" s="7"/>
       <c r="E859" s="1"/>
@@ -16822,7 +17323,7 @@
       <c r="H859" s="1"/>
       <c r="I859" s="1"/>
     </row>
-    <row r="860" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="860" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B860" s="6"/>
       <c r="C860" s="7"/>
       <c r="E860" s="1"/>
@@ -16831,7 +17332,7 @@
       <c r="H860" s="1"/>
       <c r="I860" s="1"/>
     </row>
-    <row r="861" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="861" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B861" s="6"/>
       <c r="C861" s="7"/>
       <c r="E861" s="1"/>
@@ -16840,7 +17341,7 @@
       <c r="H861" s="1"/>
       <c r="I861" s="1"/>
     </row>
-    <row r="862" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="862" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B862" s="6"/>
       <c r="C862" s="7"/>
       <c r="E862" s="1"/>
@@ -16849,7 +17350,7 @@
       <c r="H862" s="1"/>
       <c r="I862" s="1"/>
     </row>
-    <row r="863" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="863" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B863" s="6"/>
       <c r="C863" s="7"/>
       <c r="E863" s="1"/>
@@ -16858,7 +17359,7 @@
       <c r="H863" s="1"/>
       <c r="I863" s="1"/>
     </row>
-    <row r="864" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="864" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B864" s="6"/>
       <c r="C864" s="7"/>
       <c r="E864" s="1"/>
@@ -16867,7 +17368,7 @@
       <c r="H864" s="1"/>
       <c r="I864" s="1"/>
     </row>
-    <row r="865" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="865" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B865" s="6"/>
       <c r="C865" s="7"/>
       <c r="E865" s="1"/>
@@ -16876,7 +17377,7 @@
       <c r="H865" s="1"/>
       <c r="I865" s="1"/>
     </row>
-    <row r="866" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="866" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B866" s="6"/>
       <c r="C866" s="7"/>
       <c r="E866" s="1"/>
@@ -16885,7 +17386,7 @@
       <c r="H866" s="1"/>
       <c r="I866" s="1"/>
     </row>
-    <row r="867" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="867" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B867" s="6"/>
       <c r="C867" s="7"/>
       <c r="E867" s="1"/>
@@ -16894,7 +17395,7 @@
       <c r="H867" s="1"/>
       <c r="I867" s="1"/>
     </row>
-    <row r="868" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="868" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B868" s="6"/>
       <c r="C868" s="7"/>
       <c r="E868" s="1"/>
@@ -16903,7 +17404,7 @@
       <c r="H868" s="1"/>
       <c r="I868" s="1"/>
     </row>
-    <row r="869" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="869" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B869" s="6"/>
       <c r="C869" s="7"/>
       <c r="E869" s="1"/>
@@ -16912,7 +17413,7 @@
       <c r="H869" s="1"/>
       <c r="I869" s="1"/>
     </row>
-    <row r="870" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="870" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B870" s="6"/>
       <c r="C870" s="7"/>
       <c r="E870" s="1"/>
@@ -16921,7 +17422,7 @@
       <c r="H870" s="1"/>
       <c r="I870" s="1"/>
     </row>
-    <row r="871" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="871" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B871" s="6"/>
       <c r="C871" s="7"/>
       <c r="E871" s="1"/>
@@ -16930,7 +17431,7 @@
       <c r="H871" s="1"/>
       <c r="I871" s="1"/>
     </row>
-    <row r="872" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="872" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B872" s="6"/>
       <c r="C872" s="7"/>
       <c r="E872" s="1"/>
@@ -16939,7 +17440,7 @@
       <c r="H872" s="1"/>
       <c r="I872" s="1"/>
     </row>
-    <row r="873" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="873" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B873" s="6"/>
       <c r="C873" s="7"/>
       <c r="E873" s="1"/>
@@ -16948,7 +17449,7 @@
       <c r="H873" s="1"/>
       <c r="I873" s="1"/>
     </row>
-    <row r="874" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="874" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B874" s="6"/>
       <c r="C874" s="7"/>
       <c r="E874" s="1"/>
@@ -16957,7 +17458,7 @@
       <c r="H874" s="1"/>
       <c r="I874" s="1"/>
     </row>
-    <row r="875" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="875" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B875" s="6"/>
       <c r="C875" s="7"/>
       <c r="E875" s="1"/>
@@ -16966,7 +17467,7 @@
       <c r="H875" s="1"/>
       <c r="I875" s="1"/>
     </row>
-    <row r="876" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="876" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B876" s="6"/>
       <c r="C876" s="7"/>
       <c r="E876" s="1"/>
@@ -16975,7 +17476,7 @@
       <c r="H876" s="1"/>
       <c r="I876" s="1"/>
     </row>
-    <row r="877" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="877" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B877" s="6"/>
       <c r="C877" s="7"/>
       <c r="E877" s="1"/>
@@ -16984,7 +17485,7 @@
       <c r="H877" s="1"/>
       <c r="I877" s="1"/>
     </row>
-    <row r="878" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="878" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B878" s="6"/>
       <c r="C878" s="7"/>
       <c r="E878" s="1"/>
@@ -16993,7 +17494,7 @@
       <c r="H878" s="1"/>
       <c r="I878" s="1"/>
     </row>
-    <row r="879" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="879" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B879" s="6"/>
       <c r="C879" s="7"/>
       <c r="E879" s="1"/>
@@ -17002,7 +17503,7 @@
       <c r="H879" s="1"/>
       <c r="I879" s="1"/>
     </row>
-    <row r="880" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="880" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B880" s="6"/>
       <c r="C880" s="7"/>
       <c r="E880" s="1"/>
@@ -17011,7 +17512,7 @@
       <c r="H880" s="1"/>
       <c r="I880" s="1"/>
     </row>
-    <row r="881" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="881" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B881" s="6"/>
       <c r="C881" s="7"/>
       <c r="E881" s="1"/>
@@ -17020,7 +17521,7 @@
       <c r="H881" s="1"/>
       <c r="I881" s="1"/>
     </row>
-    <row r="882" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="882" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B882" s="6"/>
       <c r="C882" s="7"/>
       <c r="E882" s="1"/>
@@ -17029,7 +17530,7 @@
       <c r="H882" s="1"/>
       <c r="I882" s="1"/>
     </row>
-    <row r="883" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="883" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B883" s="6"/>
       <c r="C883" s="7"/>
       <c r="E883" s="1"/>
@@ -17038,7 +17539,7 @@
       <c r="H883" s="1"/>
       <c r="I883" s="1"/>
     </row>
-    <row r="884" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="884" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B884" s="6"/>
       <c r="C884" s="7"/>
       <c r="E884" s="1"/>
@@ -17047,7 +17548,7 @@
       <c r="H884" s="1"/>
       <c r="I884" s="1"/>
     </row>
-    <row r="885" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="885" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B885" s="6"/>
       <c r="C885" s="7"/>
       <c r="E885" s="1"/>
@@ -17056,7 +17557,7 @@
       <c r="H885" s="1"/>
       <c r="I885" s="1"/>
     </row>
-    <row r="886" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="886" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B886" s="6"/>
       <c r="C886" s="7"/>
       <c r="E886" s="1"/>
@@ -17065,7 +17566,7 @@
       <c r="H886" s="1"/>
       <c r="I886" s="1"/>
     </row>
-    <row r="887" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="887" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B887" s="6"/>
       <c r="C887" s="7"/>
       <c r="E887" s="1"/>
@@ -17074,7 +17575,7 @@
       <c r="H887" s="1"/>
       <c r="I887" s="1"/>
     </row>
-    <row r="888" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="888" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B888" s="6"/>
       <c r="C888" s="7"/>
       <c r="E888" s="1"/>
@@ -17083,7 +17584,7 @@
       <c r="H888" s="1"/>
       <c r="I888" s="1"/>
     </row>
-    <row r="889" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="889" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B889" s="6"/>
       <c r="C889" s="7"/>
       <c r="E889" s="1"/>
@@ -17092,7 +17593,7 @@
       <c r="H889" s="1"/>
       <c r="I889" s="1"/>
     </row>
-    <row r="890" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="890" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B890" s="6"/>
       <c r="C890" s="7"/>
       <c r="E890" s="1"/>
@@ -17101,7 +17602,7 @@
       <c r="H890" s="1"/>
       <c r="I890" s="1"/>
     </row>
-    <row r="891" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="891" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B891" s="6"/>
       <c r="C891" s="7"/>
       <c r="E891" s="1"/>
@@ -17110,7 +17611,7 @@
       <c r="H891" s="1"/>
       <c r="I891" s="1"/>
     </row>
-    <row r="892" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="892" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B892" s="6"/>
       <c r="C892" s="7"/>
       <c r="E892" s="1"/>
@@ -17119,7 +17620,7 @@
       <c r="H892" s="1"/>
       <c r="I892" s="1"/>
     </row>
-    <row r="893" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="893" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B893" s="6"/>
       <c r="C893" s="7"/>
       <c r="E893" s="1"/>
@@ -17128,7 +17629,7 @@
       <c r="H893" s="1"/>
       <c r="I893" s="1"/>
     </row>
-    <row r="894" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="894" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B894" s="6"/>
       <c r="C894" s="7"/>
       <c r="E894" s="1"/>
@@ -17137,7 +17638,7 @@
       <c r="H894" s="1"/>
       <c r="I894" s="1"/>
     </row>
-    <row r="895" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="895" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B895" s="6"/>
       <c r="C895" s="7"/>
       <c r="E895" s="1"/>
@@ -17146,7 +17647,7 @@
       <c r="H895" s="1"/>
       <c r="I895" s="1"/>
     </row>
-    <row r="896" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="896" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B896" s="6"/>
       <c r="C896" s="7"/>
       <c r="E896" s="1"/>
@@ -17155,7 +17656,7 @@
       <c r="H896" s="1"/>
       <c r="I896" s="1"/>
     </row>
-    <row r="897" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="897" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B897" s="6"/>
       <c r="C897" s="7"/>
       <c r="E897" s="1"/>
@@ -17164,7 +17665,7 @@
       <c r="H897" s="1"/>
       <c r="I897" s="1"/>
     </row>
-    <row r="898" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="898" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B898" s="6"/>
       <c r="C898" s="7"/>
       <c r="E898" s="1"/>
@@ -17173,7 +17674,7 @@
       <c r="H898" s="1"/>
       <c r="I898" s="1"/>
     </row>
-    <row r="899" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="899" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B899" s="6"/>
       <c r="C899" s="7"/>
       <c r="E899" s="1"/>
@@ -17182,7 +17683,7 @@
       <c r="H899" s="1"/>
       <c r="I899" s="1"/>
     </row>
-    <row r="900" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="900" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B900" s="6"/>
       <c r="C900" s="7"/>
       <c r="E900" s="1"/>
@@ -17191,7 +17692,7 @@
       <c r="H900" s="1"/>
       <c r="I900" s="1"/>
     </row>
-    <row r="901" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="901" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B901" s="6"/>
       <c r="C901" s="7"/>
       <c r="E901" s="1"/>
@@ -17200,7 +17701,7 @@
       <c r="H901" s="1"/>
       <c r="I901" s="1"/>
     </row>
-    <row r="902" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="902" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B902" s="6"/>
       <c r="C902" s="7"/>
       <c r="E902" s="1"/>
@@ -17209,7 +17710,7 @@
       <c r="H902" s="1"/>
       <c r="I902" s="1"/>
     </row>
-    <row r="903" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="903" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B903" s="6"/>
       <c r="C903" s="7"/>
       <c r="E903" s="1"/>
@@ -17218,7 +17719,7 @@
       <c r="H903" s="1"/>
       <c r="I903" s="1"/>
     </row>
-    <row r="904" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="904" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B904" s="6"/>
       <c r="C904" s="7"/>
       <c r="E904" s="1"/>
@@ -17227,7 +17728,7 @@
       <c r="H904" s="1"/>
       <c r="I904" s="1"/>
     </row>
-    <row r="905" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="905" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B905" s="6"/>
       <c r="C905" s="7"/>
       <c r="E905" s="1"/>
@@ -17236,7 +17737,7 @@
       <c r="H905" s="1"/>
       <c r="I905" s="1"/>
     </row>
-    <row r="906" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="906" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B906" s="6"/>
       <c r="C906" s="7"/>
       <c r="E906" s="1"/>
@@ -17245,7 +17746,7 @@
       <c r="H906" s="1"/>
       <c r="I906" s="1"/>
     </row>
-    <row r="907" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="907" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B907" s="6"/>
       <c r="C907" s="7"/>
       <c r="E907" s="1"/>
@@ -17254,7 +17755,7 @@
       <c r="H907" s="1"/>
       <c r="I907" s="1"/>
     </row>
-    <row r="908" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="908" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B908" s="6"/>
       <c r="C908" s="7"/>
       <c r="E908" s="1"/>
@@ -17263,7 +17764,7 @@
       <c r="H908" s="1"/>
       <c r="I908" s="1"/>
     </row>
-    <row r="909" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="909" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B909" s="6"/>
       <c r="C909" s="7"/>
       <c r="E909" s="1"/>
@@ -17272,7 +17773,7 @@
       <c r="H909" s="1"/>
       <c r="I909" s="1"/>
     </row>
-    <row r="910" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="910" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B910" s="6"/>
       <c r="C910" s="7"/>
       <c r="E910" s="1"/>
@@ -17281,7 +17782,7 @@
       <c r="H910" s="1"/>
       <c r="I910" s="1"/>
     </row>
-    <row r="911" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="911" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B911" s="6"/>
       <c r="C911" s="7"/>
       <c r="E911" s="1"/>
@@ -17290,7 +17791,7 @@
       <c r="H911" s="1"/>
       <c r="I911" s="1"/>
     </row>
-    <row r="912" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="912" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B912" s="6"/>
       <c r="C912" s="7"/>
       <c r="E912" s="1"/>
@@ -17299,7 +17800,7 @@
       <c r="H912" s="1"/>
       <c r="I912" s="1"/>
     </row>
-    <row r="913" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="913" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B913" s="6"/>
       <c r="C913" s="7"/>
       <c r="E913" s="1"/>
@@ -17308,7 +17809,7 @@
       <c r="H913" s="1"/>
       <c r="I913" s="1"/>
     </row>
-    <row r="914" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="914" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B914" s="6"/>
       <c r="C914" s="7"/>
       <c r="E914" s="1"/>
@@ -17317,7 +17818,7 @@
       <c r="H914" s="1"/>
       <c r="I914" s="1"/>
     </row>
-    <row r="915" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="915" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B915" s="6"/>
       <c r="C915" s="7"/>
       <c r="E915" s="1"/>
@@ -17326,7 +17827,7 @@
       <c r="H915" s="1"/>
       <c r="I915" s="1"/>
     </row>
-    <row r="916" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="916" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B916" s="6"/>
       <c r="C916" s="7"/>
       <c r="E916" s="1"/>
@@ -17335,7 +17836,7 @@
       <c r="H916" s="1"/>
       <c r="I916" s="1"/>
     </row>
-    <row r="917" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="917" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B917" s="6"/>
       <c r="C917" s="7"/>
       <c r="E917" s="1"/>
@@ -17344,7 +17845,7 @@
       <c r="H917" s="1"/>
       <c r="I917" s="1"/>
     </row>
-    <row r="918" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="918" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B918" s="6"/>
       <c r="C918" s="7"/>
       <c r="E918" s="1"/>
@@ -17353,7 +17854,7 @@
       <c r="H918" s="1"/>
       <c r="I918" s="1"/>
     </row>
-    <row r="919" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="919" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B919" s="6"/>
       <c r="C919" s="7"/>
       <c r="E919" s="1"/>
@@ -17362,7 +17863,7 @@
       <c r="H919" s="1"/>
       <c r="I919" s="1"/>
     </row>
-    <row r="920" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="920" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B920" s="6"/>
       <c r="C920" s="7"/>
       <c r="E920" s="1"/>
@@ -17371,7 +17872,7 @@
       <c r="H920" s="1"/>
       <c r="I920" s="1"/>
     </row>
-    <row r="921" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="921" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B921" s="6"/>
       <c r="C921" s="7"/>
       <c r="E921" s="1"/>
@@ -17380,7 +17881,7 @@
       <c r="H921" s="1"/>
       <c r="I921" s="1"/>
     </row>
-    <row r="922" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="922" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B922" s="6"/>
       <c r="C922" s="7"/>
       <c r="E922" s="1"/>
@@ -17389,7 +17890,7 @@
       <c r="H922" s="1"/>
       <c r="I922" s="1"/>
     </row>
-    <row r="923" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="923" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B923" s="6"/>
       <c r="C923" s="7"/>
       <c r="E923" s="1"/>
@@ -17398,7 +17899,7 @@
       <c r="H923" s="1"/>
       <c r="I923" s="1"/>
     </row>
-    <row r="924" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="924" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B924" s="6"/>
       <c r="C924" s="7"/>
       <c r="E924" s="1"/>
@@ -17407,7 +17908,7 @@
       <c r="H924" s="1"/>
       <c r="I924" s="1"/>
     </row>
-    <row r="925" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="925" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B925" s="6"/>
       <c r="C925" s="7"/>
       <c r="E925" s="1"/>
@@ -17416,7 +17917,7 @@
       <c r="H925" s="1"/>
       <c r="I925" s="1"/>
     </row>
-    <row r="926" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="926" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B926" s="6"/>
       <c r="C926" s="7"/>
       <c r="E926" s="1"/>
@@ -17425,7 +17926,7 @@
       <c r="H926" s="1"/>
       <c r="I926" s="1"/>
     </row>
-    <row r="927" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="927" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B927" s="6"/>
       <c r="C927" s="7"/>
       <c r="E927" s="1"/>
@@ -17434,7 +17935,7 @@
       <c r="H927" s="1"/>
       <c r="I927" s="1"/>
     </row>
-    <row r="928" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="928" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B928" s="6"/>
       <c r="C928" s="7"/>
       <c r="E928" s="1"/>
@@ -17443,7 +17944,7 @@
       <c r="H928" s="1"/>
       <c r="I928" s="1"/>
     </row>
-    <row r="929" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="929" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B929" s="6"/>
       <c r="C929" s="7"/>
       <c r="E929" s="1"/>
@@ -17452,7 +17953,7 @@
       <c r="H929" s="1"/>
       <c r="I929" s="1"/>
     </row>
-    <row r="930" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="930" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B930" s="6"/>
       <c r="C930" s="7"/>
       <c r="E930" s="1"/>
@@ -17461,7 +17962,7 @@
       <c r="H930" s="1"/>
       <c r="I930" s="1"/>
     </row>
-    <row r="931" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="931" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B931" s="6"/>
       <c r="C931" s="7"/>
       <c r="E931" s="1"/>
@@ -17470,7 +17971,7 @@
       <c r="H931" s="1"/>
       <c r="I931" s="1"/>
     </row>
-    <row r="932" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="932" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B932" s="6"/>
       <c r="C932" s="7"/>
       <c r="E932" s="1"/>
@@ -17479,7 +17980,7 @@
       <c r="H932" s="1"/>
       <c r="I932" s="1"/>
     </row>
-    <row r="933" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="933" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B933" s="6"/>
       <c r="C933" s="7"/>
       <c r="E933" s="1"/>
@@ -17488,7 +17989,7 @@
       <c r="H933" s="1"/>
       <c r="I933" s="1"/>
     </row>
-    <row r="934" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="934" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B934" s="6"/>
       <c r="C934" s="7"/>
       <c r="E934" s="1"/>
@@ -17497,7 +17998,7 @@
       <c r="H934" s="1"/>
       <c r="I934" s="1"/>
     </row>
-    <row r="935" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="935" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B935" s="6"/>
       <c r="C935" s="7"/>
       <c r="E935" s="1"/>

--- a/data/spike.xlsx
+++ b/data/spike.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilpe\Documents\DOCUMENTS\ActuRank\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F537C6-17CC-4637-BBAA-F7288B1B81D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D492EA0-E77A-4675-93C3-73CE7F6A4828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1260" yWindow="13120" windowWidth="21600" windowHeight="11270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="72">
   <si>
     <t>players</t>
   </si>
@@ -249,6 +249,9 @@
   </si>
   <si>
     <t>18/09/2025</t>
+  </si>
+  <si>
+    <t>23/09/2025</t>
   </si>
 </sst>
 </file>
@@ -5881,7 +5884,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="1">
-        <f t="shared" ref="E132:E218" si="4">IF(F132&gt;G132,1,0)</f>
+        <f t="shared" ref="E132:E230" si="4">IF(F132&gt;G132,1,0)</f>
         <v>1</v>
       </c>
       <c r="F132" s="5">
@@ -5898,7 +5901,7 @@
       </c>
       <c r="J132" s="1"/>
       <c r="K132" s="9" t="str">
-        <f t="shared" ref="K132:K195" si="5">IF(OR(OR(AND(OR(A132=B132,A132=C132,A132=D132,B132=C132,B132=D132,C132=D132),OR(A132&lt;&gt;"",D132&lt;&gt;"")),H132&gt;MAX(F132:G132),B132=C132),OR(AND(ISBLANK(A132)=FALSE,ISNA(VLOOKUP(A132,$M$3:$O$27,1,FALSE))),ISNA(VLOOKUP(B132,$M$3:$O$27,1,FALSE)),ISNA(VLOOKUP(C132,$M$3:$O$27,1,FALSE)),AND(ISBLANK(D132)=FALSE,ISNA(VLOOKUP(D132,$M$3:$O$27,1,FALSE))),OR(COUNTBLANK(A132:D132)=1,COUNTBLANK(A132:D132)=3))),"ERREUR","")</f>
+        <f t="shared" ref="K132:K193" si="5">IF(OR(OR(AND(OR(A132=B132,A132=C132,A132=D132,B132=C132,B132=D132,C132=D132),OR(A132&lt;&gt;"",D132&lt;&gt;"")),H132&gt;MAX(F132:G132),B132=C132),OR(AND(ISBLANK(A132)=FALSE,ISNA(VLOOKUP(A132,$M$3:$O$27,1,FALSE))),ISNA(VLOOKUP(B132,$M$3:$O$27,1,FALSE)),ISNA(VLOOKUP(C132,$M$3:$O$27,1,FALSE)),AND(ISBLANK(D132)=FALSE,ISNA(VLOOKUP(D132,$M$3:$O$27,1,FALSE))),OR(COUNTBLANK(A132:D132)=1,COUNTBLANK(A132:D132)=3))),"ERREUR","")</f>
         <v/>
       </c>
       <c r="L132" s="1"/>
@@ -9213,7 +9216,7 @@
       </c>
       <c r="J217" s="1"/>
       <c r="K217" s="9" t="str">
-        <f t="shared" ref="K217:K218" si="8">IF(OR(OR(AND(OR(A217=B217,A217=C217,A217=D217,B217=C217,B217=D217,C217=D217),OR(A217&lt;&gt;"",D217&lt;&gt;"")),H217&gt;MAX(F217:G217),B217=C217),OR(AND(ISBLANK(A217)=FALSE,ISNA(VLOOKUP(A217,$M$3:$O$27,1,FALSE))),ISNA(VLOOKUP(B217,$M$3:$O$27,1,FALSE)),ISNA(VLOOKUP(C217,$M$3:$O$27,1,FALSE)),AND(ISBLANK(D217)=FALSE,ISNA(VLOOKUP(D217,$M$3:$O$27,1,FALSE))),OR(COUNTBLANK(A217:D217)=1,COUNTBLANK(A217:D217)=3))),"ERREUR","")</f>
+        <f t="shared" ref="K217:K222" si="8">IF(OR(OR(AND(OR(A217=B217,A217=C217,A217=D217,B217=C217,B217=D217,C217=D217),OR(A217&lt;&gt;"",D217&lt;&gt;"")),H217&gt;MAX(F217:G217),B217=C217),OR(AND(ISBLANK(A217)=FALSE,ISNA(VLOOKUP(A217,$M$3:$O$27,1,FALSE))),ISNA(VLOOKUP(B217,$M$3:$O$27,1,FALSE)),ISNA(VLOOKUP(C217,$M$3:$O$27,1,FALSE)),AND(ISBLANK(D217)=FALSE,ISNA(VLOOKUP(D217,$M$3:$O$27,1,FALSE))),OR(COUNTBLANK(A217:D217)=1,COUNTBLANK(A217:D217)=3))),"ERREUR","")</f>
         <v/>
       </c>
       <c r="L217" s="1"/>
@@ -9261,83 +9264,190 @@
       <c r="O218" s="1"/>
     </row>
     <row r="219" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A219" s="6"/>
-      <c r="B219" s="6"/>
-      <c r="C219" s="7"/>
-      <c r="D219" s="7"/>
-      <c r="E219" s="1"/>
-      <c r="F219" s="5"/>
-      <c r="G219" s="5"/>
-      <c r="H219" s="1"/>
-      <c r="I219" s="1"/>
+      <c r="A219" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C219" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D219" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E219" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F219" s="5">
+        <v>11</v>
+      </c>
+      <c r="G219" s="5">
+        <v>5</v>
+      </c>
+      <c r="H219" s="1">
+        <v>11</v>
+      </c>
+      <c r="I219" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="J219" s="1"/>
-      <c r="K219" s="9"/>
+      <c r="K219" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L219" s="1"/>
       <c r="M219" s="1"/>
       <c r="N219" s="1"/>
       <c r="O219" s="1"/>
     </row>
     <row r="220" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A220" s="6"/>
-      <c r="B220" s="6"/>
-      <c r="C220" s="7"/>
-      <c r="D220" s="7"/>
-      <c r="E220" s="1"/>
-      <c r="F220" s="5"/>
-      <c r="G220" s="5"/>
-      <c r="H220" s="1"/>
-      <c r="I220" s="1"/>
+      <c r="A220" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C220" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D220" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E220" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F220" s="5">
+        <v>11</v>
+      </c>
+      <c r="G220" s="5">
+        <v>7</v>
+      </c>
+      <c r="H220" s="1">
+        <v>11</v>
+      </c>
+      <c r="I220" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="J220" s="1"/>
-      <c r="K220" s="9"/>
+      <c r="K220" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L220" s="1"/>
       <c r="M220" s="1"/>
       <c r="N220" s="1"/>
       <c r="O220" s="1"/>
     </row>
     <row r="221" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A221" s="6"/>
-      <c r="B221" s="6"/>
-      <c r="C221" s="7"/>
-      <c r="D221" s="7"/>
-      <c r="E221" s="1"/>
-      <c r="F221" s="5"/>
-      <c r="G221" s="5"/>
-      <c r="H221" s="1"/>
-      <c r="I221" s="1"/>
+      <c r="A221" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C221" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D221" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E221" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F221" s="5">
+        <v>11</v>
+      </c>
+      <c r="G221" s="5">
+        <v>2</v>
+      </c>
+      <c r="H221" s="1">
+        <v>11</v>
+      </c>
+      <c r="I221" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="J221" s="1"/>
-      <c r="K221" s="9"/>
+      <c r="K221" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L221" s="1"/>
       <c r="M221" s="1"/>
       <c r="N221" s="1"/>
       <c r="O221" s="1"/>
     </row>
     <row r="222" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A222" s="6"/>
-      <c r="B222" s="6"/>
-      <c r="C222" s="7"/>
-      <c r="D222" s="7"/>
-      <c r="E222" s="1"/>
-      <c r="F222" s="5"/>
-      <c r="G222" s="5"/>
-      <c r="H222" s="1"/>
-      <c r="I222" s="1"/>
+      <c r="A222" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C222" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D222" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E222" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F222" s="5">
+        <v>7</v>
+      </c>
+      <c r="G222" s="5">
+        <v>5</v>
+      </c>
+      <c r="H222" s="1">
+        <v>7</v>
+      </c>
+      <c r="I222" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="J222" s="1"/>
-      <c r="K222" s="9"/>
+      <c r="K222" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L222" s="1"/>
       <c r="M222" s="1"/>
       <c r="N222" s="1"/>
       <c r="O222" s="1"/>
     </row>
     <row r="223" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A223" s="6"/>
-      <c r="B223" s="6"/>
-      <c r="C223" s="7"/>
-      <c r="D223" s="7"/>
-      <c r="E223" s="1"/>
-      <c r="F223" s="5"/>
-      <c r="G223" s="5"/>
-      <c r="H223" s="1"/>
-      <c r="I223" s="1"/>
+      <c r="A223" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C223" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D223" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E223" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F223" s="5">
+        <v>7</v>
+      </c>
+      <c r="G223" s="5">
+        <v>2</v>
+      </c>
+      <c r="H223" s="1">
+        <v>7</v>
+      </c>
+      <c r="I223" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="J223" s="1"/>
       <c r="K223" s="9"/>
       <c r="L223" s="1"/>
@@ -9346,15 +9456,34 @@
       <c r="O223" s="1"/>
     </row>
     <row r="224" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A224" s="6"/>
-      <c r="B224" s="6"/>
-      <c r="C224" s="7"/>
-      <c r="D224" s="7"/>
-      <c r="E224" s="1"/>
-      <c r="F224" s="5"/>
-      <c r="G224" s="5"/>
-      <c r="H224" s="1"/>
-      <c r="I224" s="1"/>
+      <c r="A224" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C224" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D224" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E224" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F224" s="5">
+        <v>8</v>
+      </c>
+      <c r="G224" s="5">
+        <v>6</v>
+      </c>
+      <c r="H224" s="1">
+        <v>7</v>
+      </c>
+      <c r="I224" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="J224" s="1"/>
       <c r="K224" s="9"/>
       <c r="L224" s="1"/>
@@ -9363,15 +9492,34 @@
       <c r="O224" s="1"/>
     </row>
     <row r="225" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A225" s="6"/>
-      <c r="B225" s="6"/>
-      <c r="C225" s="7"/>
-      <c r="D225" s="7"/>
-      <c r="E225" s="1"/>
-      <c r="F225" s="5"/>
-      <c r="G225" s="5"/>
-      <c r="H225" s="1"/>
-      <c r="I225" s="1"/>
+      <c r="A225" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C225" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D225" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E225" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F225" s="5">
+        <v>7</v>
+      </c>
+      <c r="G225" s="5">
+        <v>4</v>
+      </c>
+      <c r="H225" s="1">
+        <v>7</v>
+      </c>
+      <c r="I225" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="J225" s="1"/>
       <c r="K225" s="9"/>
       <c r="L225" s="1"/>
@@ -9380,15 +9528,34 @@
       <c r="O225" s="1"/>
     </row>
     <row r="226" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A226" s="6"/>
-      <c r="B226" s="6"/>
-      <c r="C226" s="7"/>
-      <c r="D226" s="7"/>
-      <c r="E226" s="1"/>
-      <c r="F226" s="5"/>
-      <c r="G226" s="5"/>
-      <c r="H226" s="1"/>
-      <c r="I226" s="1"/>
+      <c r="A226" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B226" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C226" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D226" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E226" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F226" s="5">
+        <v>7</v>
+      </c>
+      <c r="G226" s="5">
+        <v>5</v>
+      </c>
+      <c r="H226" s="1">
+        <v>7</v>
+      </c>
+      <c r="I226" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="J226" s="1"/>
       <c r="K226" s="9"/>
       <c r="L226" s="1"/>
@@ -9397,15 +9564,34 @@
       <c r="O226" s="1"/>
     </row>
     <row r="227" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A227" s="6"/>
-      <c r="B227" s="6"/>
-      <c r="C227" s="7"/>
-      <c r="D227" s="7"/>
-      <c r="E227" s="1"/>
-      <c r="F227" s="5"/>
-      <c r="G227" s="5"/>
-      <c r="H227" s="1"/>
-      <c r="I227" s="1"/>
+      <c r="A227" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B227" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C227" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D227" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E227" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F227" s="5">
+        <v>7</v>
+      </c>
+      <c r="G227" s="5">
+        <v>1</v>
+      </c>
+      <c r="H227" s="1">
+        <v>7</v>
+      </c>
+      <c r="I227" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="J227" s="1"/>
       <c r="K227" s="9"/>
       <c r="L227" s="1"/>
@@ -9414,15 +9600,34 @@
       <c r="O227" s="1"/>
     </row>
     <row r="228" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A228" s="6"/>
-      <c r="B228" s="6"/>
-      <c r="C228" s="7"/>
-      <c r="D228" s="7"/>
-      <c r="E228" s="1"/>
-      <c r="F228" s="5"/>
-      <c r="G228" s="5"/>
-      <c r="H228" s="1"/>
-      <c r="I228" s="1"/>
+      <c r="A228" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B228" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C228" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D228" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E228" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F228" s="5">
+        <v>7</v>
+      </c>
+      <c r="G228" s="5">
+        <v>2</v>
+      </c>
+      <c r="H228" s="1">
+        <v>7</v>
+      </c>
+      <c r="I228" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="J228" s="1"/>
       <c r="K228" s="9"/>
       <c r="L228" s="1"/>
@@ -9431,15 +9636,34 @@
       <c r="O228" s="1"/>
     </row>
     <row r="229" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A229" s="6"/>
-      <c r="B229" s="6"/>
-      <c r="C229" s="7"/>
-      <c r="D229" s="7"/>
-      <c r="E229" s="1"/>
-      <c r="F229" s="5"/>
-      <c r="G229" s="5"/>
-      <c r="H229" s="1"/>
-      <c r="I229" s="1"/>
+      <c r="A229" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B229" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C229" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D229" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E229" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F229" s="5">
+        <v>8</v>
+      </c>
+      <c r="G229" s="5">
+        <v>6</v>
+      </c>
+      <c r="H229" s="1">
+        <v>7</v>
+      </c>
+      <c r="I229" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="J229" s="1"/>
       <c r="K229" s="9"/>
       <c r="L229" s="1"/>
@@ -9448,15 +9672,34 @@
       <c r="O229" s="1"/>
     </row>
     <row r="230" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A230" s="6"/>
-      <c r="B230" s="6"/>
-      <c r="C230" s="7"/>
-      <c r="D230" s="7"/>
-      <c r="E230" s="1"/>
-      <c r="F230" s="5"/>
-      <c r="G230" s="5"/>
-      <c r="H230" s="1"/>
-      <c r="I230" s="1"/>
+      <c r="A230" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B230" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C230" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D230" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E230" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F230" s="5">
+        <v>7</v>
+      </c>
+      <c r="G230" s="5">
+        <v>3</v>
+      </c>
+      <c r="H230" s="1">
+        <v>7</v>
+      </c>
+      <c r="I230" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="J230" s="1"/>
       <c r="K230" s="9"/>
       <c r="L230" s="1"/>

--- a/data/spike.xlsx
+++ b/data/spike.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilpe\Documents\DOCUMENTS\ActuRank\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D492EA0-E77A-4675-93C3-73CE7F6A4828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BBA88F-1864-4B79-BE2E-2080DD63BADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1260" yWindow="13120" windowWidth="21600" windowHeight="11270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9120" yWindow="10800" windowWidth="12980" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1196" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="74">
   <si>
     <t>players</t>
   </si>
@@ -252,6 +252,12 @@
   </si>
   <si>
     <t>23/09/2025</t>
+  </si>
+  <si>
+    <t>14/10/2025</t>
+  </si>
+  <si>
+    <t>15/10/2025</t>
   </si>
 </sst>
 </file>
@@ -5884,7 +5890,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="1">
-        <f t="shared" ref="E132:E230" si="4">IF(F132&gt;G132,1,0)</f>
+        <f t="shared" ref="E132:E255" si="4">IF(F132&gt;G132,1,0)</f>
         <v>1</v>
       </c>
       <c r="F132" s="5">
@@ -8709,7 +8715,7 @@
       </c>
       <c r="J204" s="1"/>
       <c r="K204" s="9" t="str">
-        <f t="shared" ref="K204:K216" si="7">IF(OR(OR(AND(OR(A204=B204,A204=C204,A204=D204,B204=C204,B204=D204,C204=D204),OR(A204&lt;&gt;"",D204&lt;&gt;"")),H204&gt;MAX(F204:G204),B204=C204),OR(AND(ISBLANK(A204)=FALSE,ISNA(VLOOKUP(A204,$M$3:$O$27,1,FALSE))),ISNA(VLOOKUP(B204,$M$3:$O$27,1,FALSE)),ISNA(VLOOKUP(C204,$M$3:$O$27,1,FALSE)),AND(ISBLANK(D204)=FALSE,ISNA(VLOOKUP(D204,$M$3:$O$27,1,FALSE))),OR(COUNTBLANK(A204:D204)=1,COUNTBLANK(A204:D204)=3))),"ERREUR","")</f>
+        <f t="shared" ref="K204:K255" si="7">IF(OR(OR(AND(OR(A204=B204,A204=C204,A204=D204,B204=C204,B204=D204,C204=D204),OR(A204&lt;&gt;"",D204&lt;&gt;"")),H204&gt;MAX(F204:G204),B204=C204),OR(AND(ISBLANK(A204)=FALSE,ISNA(VLOOKUP(A204,$M$3:$O$27,1,FALSE))),ISNA(VLOOKUP(B204,$M$3:$O$27,1,FALSE)),ISNA(VLOOKUP(C204,$M$3:$O$27,1,FALSE)),AND(ISBLANK(D204)=FALSE,ISNA(VLOOKUP(D204,$M$3:$O$27,1,FALSE))),OR(COUNTBLANK(A204:D204)=1,COUNTBLANK(A204:D204)=3))),"ERREUR","")</f>
         <v/>
       </c>
       <c r="L204" s="1"/>
@@ -9216,7 +9222,7 @@
       </c>
       <c r="J217" s="1"/>
       <c r="K217" s="9" t="str">
-        <f t="shared" ref="K217:K222" si="8">IF(OR(OR(AND(OR(A217=B217,A217=C217,A217=D217,B217=C217,B217=D217,C217=D217),OR(A217&lt;&gt;"",D217&lt;&gt;"")),H217&gt;MAX(F217:G217),B217=C217),OR(AND(ISBLANK(A217)=FALSE,ISNA(VLOOKUP(A217,$M$3:$O$27,1,FALSE))),ISNA(VLOOKUP(B217,$M$3:$O$27,1,FALSE)),ISNA(VLOOKUP(C217,$M$3:$O$27,1,FALSE)),AND(ISBLANK(D217)=FALSE,ISNA(VLOOKUP(D217,$M$3:$O$27,1,FALSE))),OR(COUNTBLANK(A217:D217)=1,COUNTBLANK(A217:D217)=3))),"ERREUR","")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L217" s="1"/>
@@ -9255,7 +9261,7 @@
       </c>
       <c r="J218" s="1"/>
       <c r="K218" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L218" s="1"/>
@@ -9294,7 +9300,7 @@
       </c>
       <c r="J219" s="1"/>
       <c r="K219" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L219" s="1"/>
@@ -9333,7 +9339,7 @@
       </c>
       <c r="J220" s="1"/>
       <c r="K220" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L220" s="1"/>
@@ -9372,7 +9378,7 @@
       </c>
       <c r="J221" s="1"/>
       <c r="K221" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L221" s="1"/>
@@ -9411,7 +9417,7 @@
       </c>
       <c r="J222" s="1"/>
       <c r="K222" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="L222" s="1"/>
@@ -9449,7 +9455,10 @@
         <v>71</v>
       </c>
       <c r="J223" s="1"/>
-      <c r="K223" s="9"/>
+      <c r="K223" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L223" s="1"/>
       <c r="M223" s="1"/>
       <c r="N223" s="1"/>
@@ -9485,7 +9494,10 @@
         <v>71</v>
       </c>
       <c r="J224" s="1"/>
-      <c r="K224" s="9"/>
+      <c r="K224" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L224" s="1"/>
       <c r="M224" s="1"/>
       <c r="N224" s="1"/>
@@ -9521,7 +9533,10 @@
         <v>71</v>
       </c>
       <c r="J225" s="1"/>
-      <c r="K225" s="9"/>
+      <c r="K225" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L225" s="1"/>
       <c r="M225" s="1"/>
       <c r="N225" s="1"/>
@@ -9557,7 +9572,10 @@
         <v>71</v>
       </c>
       <c r="J226" s="1"/>
-      <c r="K226" s="9"/>
+      <c r="K226" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L226" s="1"/>
       <c r="M226" s="1"/>
       <c r="N226" s="1"/>
@@ -9593,7 +9611,10 @@
         <v>71</v>
       </c>
       <c r="J227" s="1"/>
-      <c r="K227" s="9"/>
+      <c r="K227" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L227" s="1"/>
       <c r="M227" s="1"/>
       <c r="N227" s="1"/>
@@ -9629,7 +9650,10 @@
         <v>71</v>
       </c>
       <c r="J228" s="1"/>
-      <c r="K228" s="9"/>
+      <c r="K228" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L228" s="1"/>
       <c r="M228" s="1"/>
       <c r="N228" s="1"/>
@@ -9665,7 +9689,10 @@
         <v>71</v>
       </c>
       <c r="J229" s="1"/>
-      <c r="K229" s="9"/>
+      <c r="K229" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L229" s="1"/>
       <c r="M229" s="1"/>
       <c r="N229" s="1"/>
@@ -9701,432 +9728,985 @@
         <v>71</v>
       </c>
       <c r="J230" s="1"/>
-      <c r="K230" s="9"/>
+      <c r="K230" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L230" s="1"/>
       <c r="M230" s="1"/>
       <c r="N230" s="1"/>
       <c r="O230" s="1"/>
     </row>
     <row r="231" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A231" s="6"/>
-      <c r="B231" s="6"/>
-      <c r="C231" s="7"/>
-      <c r="D231" s="7"/>
-      <c r="E231" s="1"/>
-      <c r="F231" s="5"/>
-      <c r="G231" s="5"/>
-      <c r="H231" s="1"/>
-      <c r="I231" s="1"/>
+      <c r="A231" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C231" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D231" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E231" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F231" s="5">
+        <v>10</v>
+      </c>
+      <c r="G231" s="5">
+        <v>8</v>
+      </c>
+      <c r="H231" s="1">
+        <v>7</v>
+      </c>
+      <c r="I231" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J231" s="1"/>
-      <c r="K231" s="9"/>
+      <c r="K231" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L231" s="1"/>
       <c r="M231" s="1"/>
       <c r="N231" s="1"/>
       <c r="O231" s="1"/>
     </row>
     <row r="232" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A232" s="6"/>
-      <c r="B232" s="6"/>
-      <c r="C232" s="7"/>
-      <c r="D232" s="7"/>
-      <c r="E232" s="1"/>
-      <c r="F232" s="5"/>
-      <c r="G232" s="5"/>
-      <c r="H232" s="1"/>
-      <c r="I232" s="1"/>
+      <c r="A232" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B232" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C232" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D232" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E232" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F232" s="5">
+        <v>7</v>
+      </c>
+      <c r="G232" s="5">
+        <v>3</v>
+      </c>
+      <c r="H232" s="1">
+        <v>7</v>
+      </c>
+      <c r="I232" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J232" s="1"/>
-      <c r="K232" s="9"/>
+      <c r="K232" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L232" s="1"/>
       <c r="M232" s="1"/>
       <c r="N232" s="1"/>
       <c r="O232" s="1"/>
     </row>
     <row r="233" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A233" s="6"/>
-      <c r="B233" s="6"/>
-      <c r="C233" s="7"/>
-      <c r="D233" s="7"/>
-      <c r="E233" s="1"/>
-      <c r="F233" s="5"/>
-      <c r="G233" s="5"/>
-      <c r="H233" s="1"/>
-      <c r="I233" s="1"/>
+      <c r="A233" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B233" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C233" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D233" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E233" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F233" s="5">
+        <v>7</v>
+      </c>
+      <c r="G233" s="5">
+        <v>3</v>
+      </c>
+      <c r="H233" s="1">
+        <v>7</v>
+      </c>
+      <c r="I233" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J233" s="1"/>
-      <c r="K233" s="9"/>
+      <c r="K233" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L233" s="1"/>
       <c r="M233" s="1"/>
       <c r="N233" s="1"/>
       <c r="O233" s="1"/>
     </row>
     <row r="234" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A234" s="6"/>
-      <c r="B234" s="6"/>
-      <c r="C234" s="7"/>
-      <c r="D234" s="7"/>
-      <c r="E234" s="1"/>
-      <c r="F234" s="5"/>
-      <c r="G234" s="5"/>
-      <c r="H234" s="1"/>
-      <c r="I234" s="1"/>
+      <c r="A234" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B234" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C234" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D234" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E234" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F234" s="5">
+        <v>8</v>
+      </c>
+      <c r="G234" s="5">
+        <v>6</v>
+      </c>
+      <c r="H234" s="1">
+        <v>7</v>
+      </c>
+      <c r="I234" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J234" s="1"/>
-      <c r="K234" s="9"/>
+      <c r="K234" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L234" s="1"/>
       <c r="M234" s="1"/>
       <c r="N234" s="1"/>
       <c r="O234" s="1"/>
     </row>
     <row r="235" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A235" s="6"/>
-      <c r="B235" s="6"/>
-      <c r="C235" s="7"/>
-      <c r="D235" s="7"/>
-      <c r="E235" s="1"/>
-      <c r="F235" s="5"/>
-      <c r="G235" s="5"/>
-      <c r="H235" s="1"/>
-      <c r="I235" s="1"/>
+      <c r="A235" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B235" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C235" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D235" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E235" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F235" s="5">
+        <v>8</v>
+      </c>
+      <c r="G235" s="5">
+        <v>6</v>
+      </c>
+      <c r="H235" s="1">
+        <v>7</v>
+      </c>
+      <c r="I235" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J235" s="1"/>
-      <c r="K235" s="9"/>
+      <c r="K235" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L235" s="1"/>
       <c r="M235" s="1"/>
       <c r="N235" s="1"/>
       <c r="O235" s="1"/>
     </row>
     <row r="236" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A236" s="6"/>
-      <c r="B236" s="6"/>
-      <c r="C236" s="7"/>
-      <c r="D236" s="7"/>
-      <c r="E236" s="1"/>
-      <c r="F236" s="5"/>
-      <c r="G236" s="5"/>
-      <c r="H236" s="1"/>
-      <c r="I236" s="1"/>
+      <c r="A236" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B236" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C236" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D236" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E236" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F236" s="5">
+        <v>7</v>
+      </c>
+      <c r="G236" s="5">
+        <v>5</v>
+      </c>
+      <c r="H236" s="1">
+        <v>7</v>
+      </c>
+      <c r="I236" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J236" s="1"/>
-      <c r="K236" s="9"/>
+      <c r="K236" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L236" s="1"/>
       <c r="M236" s="1"/>
       <c r="N236" s="1"/>
       <c r="O236" s="1"/>
     </row>
     <row r="237" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A237" s="6"/>
-      <c r="B237" s="6"/>
-      <c r="C237" s="7"/>
-      <c r="D237" s="7"/>
-      <c r="E237" s="1"/>
-      <c r="F237" s="5"/>
-      <c r="G237" s="5"/>
-      <c r="H237" s="1"/>
-      <c r="I237" s="1"/>
+      <c r="A237" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B237" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C237" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D237" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E237" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F237" s="5">
+        <v>7</v>
+      </c>
+      <c r="G237" s="5">
+        <v>5</v>
+      </c>
+      <c r="H237" s="1">
+        <v>7</v>
+      </c>
+      <c r="I237" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J237" s="1"/>
-      <c r="K237" s="9"/>
+      <c r="K237" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L237" s="1"/>
       <c r="M237" s="1"/>
       <c r="N237" s="1"/>
       <c r="O237" s="1"/>
     </row>
     <row r="238" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A238" s="6"/>
-      <c r="B238" s="6"/>
-      <c r="C238" s="7"/>
-      <c r="D238" s="7"/>
-      <c r="E238" s="1"/>
-      <c r="F238" s="5"/>
-      <c r="G238" s="5"/>
-      <c r="H238" s="1"/>
-      <c r="I238" s="1"/>
+      <c r="A238" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B238" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C238" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D238" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E238" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F238" s="5">
+        <v>11</v>
+      </c>
+      <c r="G238" s="5">
+        <v>8</v>
+      </c>
+      <c r="H238" s="1">
+        <v>11</v>
+      </c>
+      <c r="I238" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J238" s="1"/>
-      <c r="K238" s="9"/>
+      <c r="K238" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L238" s="1"/>
       <c r="M238" s="1"/>
       <c r="N238" s="1"/>
       <c r="O238" s="1"/>
     </row>
     <row r="239" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A239" s="6"/>
-      <c r="B239" s="6"/>
-      <c r="C239" s="7"/>
-      <c r="D239" s="7"/>
-      <c r="E239" s="1"/>
-      <c r="F239" s="5"/>
-      <c r="G239" s="5"/>
-      <c r="H239" s="1"/>
-      <c r="I239" s="1"/>
+      <c r="A239" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B239" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C239" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D239" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E239" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F239" s="5">
+        <v>7</v>
+      </c>
+      <c r="G239" s="5">
+        <v>4</v>
+      </c>
+      <c r="H239" s="1">
+        <v>7</v>
+      </c>
+      <c r="I239" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J239" s="1"/>
-      <c r="K239" s="9"/>
+      <c r="K239" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L239" s="1"/>
       <c r="M239" s="1"/>
       <c r="N239" s="1"/>
       <c r="O239" s="1"/>
     </row>
     <row r="240" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A240" s="6"/>
-      <c r="B240" s="6"/>
-      <c r="C240" s="7"/>
-      <c r="D240" s="7"/>
-      <c r="E240" s="1"/>
-      <c r="F240" s="5"/>
-      <c r="G240" s="5"/>
-      <c r="H240" s="1"/>
-      <c r="I240" s="1"/>
+      <c r="A240" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B240" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C240" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D240" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E240" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F240" s="5">
+        <v>9</v>
+      </c>
+      <c r="G240" s="5">
+        <v>7</v>
+      </c>
+      <c r="H240" s="1">
+        <v>7</v>
+      </c>
+      <c r="I240" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J240" s="1"/>
-      <c r="K240" s="9"/>
+      <c r="K240" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L240" s="1"/>
       <c r="M240" s="1"/>
       <c r="N240" s="1"/>
       <c r="O240" s="1"/>
     </row>
     <row r="241" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A241" s="6"/>
-      <c r="B241" s="6"/>
-      <c r="C241" s="7"/>
-      <c r="D241" s="7"/>
-      <c r="E241" s="1"/>
-      <c r="F241" s="5"/>
-      <c r="G241" s="5"/>
-      <c r="H241" s="1"/>
-      <c r="I241" s="1"/>
+      <c r="A241" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B241" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C241" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D241" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E241" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F241" s="5">
+        <v>13</v>
+      </c>
+      <c r="G241" s="5">
+        <v>8</v>
+      </c>
+      <c r="H241" s="1">
+        <v>13</v>
+      </c>
+      <c r="I241" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J241" s="1"/>
-      <c r="K241" s="9"/>
+      <c r="K241" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L241" s="1"/>
       <c r="M241" s="1"/>
       <c r="N241" s="1"/>
       <c r="O241" s="1"/>
     </row>
     <row r="242" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A242" s="6"/>
-      <c r="B242" s="6"/>
-      <c r="C242" s="7"/>
-      <c r="D242" s="7"/>
-      <c r="E242" s="1"/>
-      <c r="F242" s="5"/>
-      <c r="G242" s="5"/>
-      <c r="H242" s="1"/>
-      <c r="I242" s="1"/>
+      <c r="A242" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B242" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C242" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D242" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E242" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F242" s="5">
+        <v>7</v>
+      </c>
+      <c r="G242" s="5">
+        <v>5</v>
+      </c>
+      <c r="H242" s="1">
+        <v>7</v>
+      </c>
+      <c r="I242" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J242" s="1"/>
-      <c r="K242" s="9"/>
+      <c r="K242" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L242" s="1"/>
       <c r="M242" s="1"/>
       <c r="N242" s="1"/>
       <c r="O242" s="1"/>
     </row>
     <row r="243" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A243" s="6"/>
-      <c r="B243" s="6"/>
-      <c r="C243" s="7"/>
-      <c r="D243" s="7"/>
-      <c r="E243" s="1"/>
-      <c r="F243" s="5"/>
-      <c r="G243" s="5"/>
-      <c r="H243" s="1"/>
-      <c r="I243" s="1"/>
+      <c r="A243" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B243" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C243" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D243" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E243" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F243" s="5">
+        <v>8</v>
+      </c>
+      <c r="G243" s="5">
+        <v>6</v>
+      </c>
+      <c r="H243" s="1">
+        <v>7</v>
+      </c>
+      <c r="I243" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J243" s="1"/>
-      <c r="K243" s="9"/>
+      <c r="K243" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L243" s="1"/>
       <c r="M243" s="1"/>
       <c r="N243" s="1"/>
       <c r="O243" s="1"/>
     </row>
     <row r="244" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A244" s="6"/>
-      <c r="B244" s="6"/>
-      <c r="C244" s="7"/>
-      <c r="D244" s="7"/>
-      <c r="E244" s="1"/>
-      <c r="F244" s="5"/>
-      <c r="G244" s="5"/>
-      <c r="H244" s="1"/>
-      <c r="I244" s="1"/>
+      <c r="A244" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B244" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C244" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D244" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E244" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F244" s="5">
+        <v>7</v>
+      </c>
+      <c r="G244" s="5">
+        <v>4</v>
+      </c>
+      <c r="H244" s="1">
+        <v>7</v>
+      </c>
+      <c r="I244" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J244" s="1"/>
-      <c r="K244" s="9"/>
+      <c r="K244" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L244" s="1"/>
       <c r="M244" s="1"/>
       <c r="N244" s="1"/>
       <c r="O244" s="1"/>
     </row>
     <row r="245" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A245" s="6"/>
-      <c r="B245" s="6"/>
-      <c r="C245" s="7"/>
-      <c r="D245" s="7"/>
-      <c r="E245" s="1"/>
-      <c r="F245" s="5"/>
-      <c r="G245" s="5"/>
-      <c r="H245" s="1"/>
-      <c r="I245" s="1"/>
+      <c r="A245" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B245" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C245" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D245" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E245" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F245" s="5">
+        <v>10</v>
+      </c>
+      <c r="G245" s="5">
+        <v>8</v>
+      </c>
+      <c r="H245" s="1">
+        <v>7</v>
+      </c>
+      <c r="I245" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J245" s="1"/>
-      <c r="K245" s="9"/>
+      <c r="K245" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L245" s="1"/>
       <c r="M245" s="1"/>
       <c r="N245" s="1"/>
       <c r="O245" s="1"/>
     </row>
     <row r="246" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A246" s="6"/>
-      <c r="B246" s="6"/>
-      <c r="C246" s="7"/>
-      <c r="D246" s="7"/>
-      <c r="E246" s="1"/>
-      <c r="F246" s="5"/>
-      <c r="G246" s="5"/>
-      <c r="H246" s="1"/>
-      <c r="I246" s="1"/>
+      <c r="A246" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B246" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C246" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D246" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E246" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F246" s="5">
+        <v>8</v>
+      </c>
+      <c r="G246" s="5">
+        <v>6</v>
+      </c>
+      <c r="H246" s="1">
+        <v>7</v>
+      </c>
+      <c r="I246" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="J246" s="1"/>
-      <c r="K246" s="9"/>
+      <c r="K246" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L246" s="1"/>
       <c r="M246" s="1"/>
       <c r="N246" s="1"/>
       <c r="O246" s="1"/>
     </row>
     <row r="247" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A247" s="6"/>
-      <c r="B247" s="6"/>
-      <c r="C247" s="7"/>
-      <c r="D247" s="7"/>
-      <c r="E247" s="1"/>
-      <c r="F247" s="5"/>
-      <c r="G247" s="5"/>
-      <c r="H247" s="1"/>
-      <c r="I247" s="1"/>
+      <c r="A247" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B247" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C247" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D247" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E247" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F247" s="5">
+        <v>11</v>
+      </c>
+      <c r="G247" s="5">
+        <v>8</v>
+      </c>
+      <c r="H247" s="1">
+        <v>11</v>
+      </c>
+      <c r="I247" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="J247" s="1"/>
-      <c r="K247" s="9"/>
+      <c r="K247" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L247" s="1"/>
       <c r="M247" s="1"/>
       <c r="N247" s="1"/>
       <c r="O247" s="1"/>
     </row>
     <row r="248" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A248" s="6"/>
-      <c r="B248" s="6"/>
-      <c r="C248" s="7"/>
-      <c r="D248" s="7"/>
-      <c r="E248" s="1"/>
-      <c r="F248" s="5"/>
-      <c r="G248" s="5"/>
-      <c r="H248" s="1"/>
-      <c r="I248" s="1"/>
+      <c r="A248" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B248" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C248" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D248" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E248" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F248" s="5">
+        <v>11</v>
+      </c>
+      <c r="G248" s="5">
+        <v>6</v>
+      </c>
+      <c r="H248" s="1">
+        <v>11</v>
+      </c>
+      <c r="I248" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="J248" s="1"/>
-      <c r="K248" s="9"/>
+      <c r="K248" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L248" s="1"/>
       <c r="M248" s="1"/>
       <c r="N248" s="1"/>
       <c r="O248" s="1"/>
     </row>
     <row r="249" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A249" s="6"/>
-      <c r="B249" s="6"/>
-      <c r="C249" s="7"/>
-      <c r="D249" s="7"/>
-      <c r="E249" s="1"/>
-      <c r="F249" s="5"/>
-      <c r="G249" s="5"/>
-      <c r="H249" s="1"/>
-      <c r="I249" s="1"/>
+      <c r="A249" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B249" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C249" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D249" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E249" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F249" s="5">
+        <v>11</v>
+      </c>
+      <c r="G249" s="5">
+        <v>8</v>
+      </c>
+      <c r="H249" s="1">
+        <v>11</v>
+      </c>
+      <c r="I249" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="J249" s="1"/>
-      <c r="K249" s="9"/>
+      <c r="K249" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L249" s="1"/>
       <c r="M249" s="1"/>
       <c r="N249" s="1"/>
       <c r="O249" s="1"/>
     </row>
     <row r="250" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A250" s="6"/>
-      <c r="B250" s="6"/>
-      <c r="C250" s="7"/>
-      <c r="D250" s="7"/>
-      <c r="E250" s="1"/>
-      <c r="F250" s="5"/>
-      <c r="G250" s="5"/>
-      <c r="H250" s="1"/>
-      <c r="I250" s="1"/>
+      <c r="A250" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B250" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C250" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D250" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E250" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F250" s="5">
+        <v>11</v>
+      </c>
+      <c r="G250" s="5">
+        <v>9</v>
+      </c>
+      <c r="H250" s="1">
+        <v>11</v>
+      </c>
+      <c r="I250" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="J250" s="1"/>
-      <c r="K250" s="9"/>
+      <c r="K250" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L250" s="1"/>
       <c r="M250" s="1"/>
       <c r="N250" s="1"/>
       <c r="O250" s="1"/>
     </row>
     <row r="251" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A251" s="6"/>
-      <c r="B251" s="6"/>
-      <c r="C251" s="7"/>
-      <c r="D251" s="7"/>
-      <c r="E251" s="1"/>
-      <c r="F251" s="5"/>
-      <c r="G251" s="5"/>
-      <c r="H251" s="1"/>
-      <c r="I251" s="1"/>
+      <c r="A251" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B251" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C251" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D251" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E251" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F251" s="5">
+        <v>11</v>
+      </c>
+      <c r="G251" s="5">
+        <v>9</v>
+      </c>
+      <c r="H251" s="1">
+        <v>11</v>
+      </c>
+      <c r="I251" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="J251" s="1"/>
-      <c r="K251" s="9"/>
+      <c r="K251" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L251" s="1"/>
       <c r="M251" s="1"/>
       <c r="N251" s="1"/>
       <c r="O251" s="1"/>
     </row>
     <row r="252" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A252" s="6"/>
-      <c r="B252" s="6"/>
-      <c r="C252" s="7"/>
-      <c r="D252" s="7"/>
-      <c r="E252" s="1"/>
-      <c r="F252" s="5"/>
-      <c r="G252" s="5"/>
-      <c r="H252" s="1"/>
-      <c r="I252" s="1"/>
+      <c r="A252" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B252" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C252" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D252" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E252" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F252" s="5">
+        <v>11</v>
+      </c>
+      <c r="G252" s="5">
+        <v>5</v>
+      </c>
+      <c r="H252" s="1">
+        <v>11</v>
+      </c>
+      <c r="I252" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="J252" s="1"/>
-      <c r="K252" s="9"/>
+      <c r="K252" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L252" s="1"/>
       <c r="M252" s="1"/>
       <c r="N252" s="1"/>
       <c r="O252" s="1"/>
     </row>
     <row r="253" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A253" s="6"/>
-      <c r="B253" s="6"/>
-      <c r="C253" s="7"/>
-      <c r="D253" s="7"/>
-      <c r="E253" s="1"/>
-      <c r="F253" s="5"/>
-      <c r="G253" s="5"/>
-      <c r="H253" s="1"/>
-      <c r="I253" s="1"/>
+      <c r="A253" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C253" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D253" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E253" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F253" s="5">
+        <v>11</v>
+      </c>
+      <c r="G253" s="5">
+        <v>9</v>
+      </c>
+      <c r="H253" s="1">
+        <v>11</v>
+      </c>
+      <c r="I253" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="J253" s="1"/>
-      <c r="K253" s="9"/>
+      <c r="K253" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L253" s="1"/>
       <c r="M253" s="1"/>
       <c r="N253" s="1"/>
       <c r="O253" s="1"/>
     </row>
     <row r="254" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A254" s="6"/>
-      <c r="B254" s="6"/>
-      <c r="C254" s="7"/>
-      <c r="D254" s="7"/>
-      <c r="E254" s="1"/>
-      <c r="F254" s="5"/>
-      <c r="G254" s="5"/>
-      <c r="H254" s="1"/>
-      <c r="I254" s="1"/>
+      <c r="A254" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C254" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D254" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E254" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F254" s="5">
+        <v>11</v>
+      </c>
+      <c r="G254" s="5">
+        <v>7</v>
+      </c>
+      <c r="H254" s="1">
+        <v>11</v>
+      </c>
+      <c r="I254" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="J254" s="1"/>
-      <c r="K254" s="9"/>
+      <c r="K254" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L254" s="1"/>
       <c r="M254" s="1"/>
       <c r="N254" s="1"/>
       <c r="O254" s="1"/>
     </row>
     <row r="255" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A255" s="6"/>
-      <c r="B255" s="6"/>
-      <c r="C255" s="7"/>
-      <c r="D255" s="7"/>
-      <c r="E255" s="1"/>
-      <c r="F255" s="5"/>
-      <c r="G255" s="5"/>
-      <c r="H255" s="1"/>
-      <c r="I255" s="1"/>
+      <c r="A255" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B255" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C255" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D255" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E255" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F255" s="5">
+        <v>13</v>
+      </c>
+      <c r="G255" s="5">
+        <v>11</v>
+      </c>
+      <c r="H255" s="1">
+        <v>13</v>
+      </c>
+      <c r="I255" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="J255" s="1"/>
-      <c r="K255" s="9"/>
+      <c r="K255" s="9" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
       <c r="L255" s="1"/>
       <c r="M255" s="1"/>
       <c r="N255" s="1"/>

--- a/data/spike.xlsx
+++ b/data/spike.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilpe\Documents\DOCUMENTS\ActuRank\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75BBA88F-1864-4B79-BE2E-2080DD63BADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417063C9-46D9-49B5-B5B5-CB9B31D0F0C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9120" yWindow="10800" windowWidth="12980" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="77">
   <si>
     <t>players</t>
   </si>
@@ -258,6 +258,15 @@
   </si>
   <si>
     <t>15/10/2025</t>
+  </si>
+  <si>
+    <t>16/06/2026</t>
+  </si>
+  <si>
+    <t>20/05/2026</t>
+  </si>
+  <si>
+    <t>25/06/2026</t>
   </si>
 </sst>
 </file>
@@ -649,13 +658,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O935"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O928"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="11" max="11" width="8.85546875" style="10"/>
+    <col min="11" max="11" width="8.81640625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -682,7 +691,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>5</v>
@@ -713,7 +722,7 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
@@ -758,7 +767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>11</v>
       </c>
@@ -803,7 +812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
@@ -848,7 +857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>17</v>
       </c>
@@ -893,7 +902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
@@ -938,7 +947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>12</v>
       </c>
@@ -983,7 +992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
@@ -1028,7 +1037,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>17</v>
       </c>
@@ -1073,7 +1082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>13</v>
       </c>
@@ -1118,7 +1127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>12</v>
       </c>
@@ -1163,7 +1172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>17</v>
       </c>
@@ -1208,7 +1217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>13</v>
       </c>
@@ -1253,7 +1262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>12</v>
       </c>
@@ -1298,7 +1307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>12</v>
       </c>
@@ -1343,7 +1352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>12</v>
       </c>
@@ -1388,7 +1397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>19</v>
       </c>
@@ -1433,7 +1442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>13</v>
       </c>
@@ -1478,7 +1487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>19</v>
       </c>
@@ -1523,7 +1532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>12</v>
       </c>
@@ -1568,7 +1577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>12</v>
       </c>
@@ -1613,7 +1622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>19</v>
       </c>
@@ -1658,7 +1667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>11</v>
       </c>
@@ -1703,7 +1712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>17</v>
       </c>
@@ -1742,7 +1751,7 @@
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>12</v>
       </c>
@@ -1781,7 +1790,7 @@
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>12</v>
       </c>
@@ -1820,7 +1829,7 @@
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>19</v>
       </c>
@@ -1859,7 +1868,7 @@
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>13</v>
       </c>
@@ -1898,7 +1907,7 @@
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
         <v>13</v>
       </c>
@@ -1937,7 +1946,7 @@
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>17</v>
       </c>
@@ -1976,7 +1985,7 @@
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>13</v>
       </c>
@@ -2015,7 +2024,7 @@
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>19</v>
       </c>
@@ -2054,7 +2063,7 @@
       <c r="N33" s="1"/>
       <c r="O33" s="1"/>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="6" t="s">
         <v>11</v>
       </c>
@@ -2093,7 +2102,7 @@
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="6" t="s">
         <v>17</v>
       </c>
@@ -2132,7 +2141,7 @@
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" s="6" t="s">
         <v>12</v>
       </c>
@@ -2171,7 +2180,7 @@
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
         <v>13</v>
       </c>
@@ -2210,7 +2219,7 @@
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
         <v>13</v>
       </c>
@@ -2249,7 +2258,7 @@
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" s="6" t="s">
         <v>13</v>
       </c>
@@ -2288,7 +2297,7 @@
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="6" t="s">
         <v>19</v>
       </c>
@@ -2327,7 +2336,7 @@
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="6" t="s">
         <v>12</v>
       </c>
@@ -2366,7 +2375,7 @@
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="6" t="s">
         <v>12</v>
       </c>
@@ -2405,7 +2414,7 @@
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
         <v>12</v>
       </c>
@@ -2444,7 +2453,7 @@
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" s="6" t="s">
         <v>13</v>
       </c>
@@ -2483,7 +2492,7 @@
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
         <v>12</v>
       </c>
@@ -2522,7 +2531,7 @@
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="6" t="s">
         <v>12</v>
       </c>
@@ -2561,7 +2570,7 @@
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
         <v>13</v>
       </c>
@@ -2600,7 +2609,7 @@
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
         <v>13</v>
       </c>
@@ -2639,7 +2648,7 @@
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="6" t="s">
         <v>11</v>
       </c>
@@ -2678,7 +2687,7 @@
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" s="6" t="s">
         <v>13</v>
       </c>
@@ -2717,7 +2726,7 @@
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
         <v>12</v>
       </c>
@@ -2756,7 +2765,7 @@
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
         <v>13</v>
       </c>
@@ -2795,7 +2804,7 @@
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" s="6" t="s">
         <v>13</v>
       </c>
@@ -2834,7 +2843,7 @@
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" s="6" t="s">
         <v>12</v>
       </c>
@@ -2873,7 +2882,7 @@
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" s="6" t="s">
         <v>17</v>
       </c>
@@ -2912,7 +2921,7 @@
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>17</v>
       </c>
@@ -2951,7 +2960,7 @@
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" s="6" t="s">
         <v>17</v>
       </c>
@@ -2990,7 +2999,7 @@
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" s="6" t="s">
         <v>12</v>
       </c>
@@ -3029,7 +3038,7 @@
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
         <v>12</v>
       </c>
@@ -3068,7 +3077,7 @@
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
         <v>11</v>
       </c>
@@ -3107,7 +3116,7 @@
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
         <v>12</v>
       </c>
@@ -3146,7 +3155,7 @@
       <c r="N61" s="1"/>
       <c r="O61" s="1"/>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" s="6" t="s">
         <v>13</v>
       </c>
@@ -3185,7 +3194,7 @@
       <c r="N62" s="1"/>
       <c r="O62" s="1"/>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" s="6" t="s">
         <v>13</v>
       </c>
@@ -3224,7 +3233,7 @@
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" s="6" t="s">
         <v>12</v>
       </c>
@@ -3263,7 +3272,7 @@
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
         <v>12</v>
       </c>
@@ -3302,7 +3311,7 @@
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
         <v>12</v>
       </c>
@@ -3341,7 +3350,7 @@
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
         <v>12</v>
       </c>
@@ -3380,7 +3389,7 @@
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" s="6" t="s">
         <v>12</v>
       </c>
@@ -3419,7 +3428,7 @@
       <c r="N68" s="1"/>
       <c r="O68" s="1"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" s="6" t="s">
         <v>12</v>
       </c>
@@ -3458,7 +3467,7 @@
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" s="6" t="s">
         <v>13</v>
       </c>
@@ -3497,7 +3506,7 @@
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" s="6" t="s">
         <v>11</v>
       </c>
@@ -3536,7 +3545,7 @@
       <c r="N71" s="1"/>
       <c r="O71" s="1"/>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" s="6" t="s">
         <v>13</v>
       </c>
@@ -3575,7 +3584,7 @@
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" s="6" t="s">
         <v>12</v>
       </c>
@@ -3614,7 +3623,7 @@
       <c r="N73" s="1"/>
       <c r="O73" s="1"/>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" s="6" t="s">
         <v>39</v>
       </c>
@@ -3653,7 +3662,7 @@
       <c r="N74" s="1"/>
       <c r="O74" s="1"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" s="6" t="s">
         <v>12</v>
       </c>
@@ -3692,7 +3701,7 @@
       <c r="N75" s="1"/>
       <c r="O75" s="1"/>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" s="6" t="s">
         <v>12</v>
       </c>
@@ -3731,7 +3740,7 @@
       <c r="N76" s="1"/>
       <c r="O76" s="1"/>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" s="6" t="s">
         <v>12</v>
       </c>
@@ -3770,7 +3779,7 @@
       <c r="N77" s="1"/>
       <c r="O77" s="1"/>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" s="6" t="s">
         <v>12</v>
       </c>
@@ -3809,7 +3818,7 @@
       <c r="N78" s="1"/>
       <c r="O78" s="1"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" s="6" t="s">
         <v>12</v>
       </c>
@@ -3848,7 +3857,7 @@
       <c r="N79" s="1"/>
       <c r="O79" s="1"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" s="6" t="s">
         <v>12</v>
       </c>
@@ -3887,7 +3896,7 @@
       <c r="N80" s="1"/>
       <c r="O80" s="1"/>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" s="6" t="s">
         <v>11</v>
       </c>
@@ -3926,7 +3935,7 @@
       <c r="N81" s="1"/>
       <c r="O81" s="1"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" s="6" t="s">
         <v>12</v>
       </c>
@@ -3965,7 +3974,7 @@
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" s="6" t="s">
         <v>17</v>
       </c>
@@ -4004,7 +4013,7 @@
       <c r="N83" s="1"/>
       <c r="O83" s="1"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" s="6" t="s">
         <v>12</v>
       </c>
@@ -4043,7 +4052,7 @@
       <c r="N84" s="1"/>
       <c r="O84" s="1"/>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" s="6" t="s">
         <v>12</v>
       </c>
@@ -4082,7 +4091,7 @@
       <c r="N85" s="1"/>
       <c r="O85" s="1"/>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" s="6" t="s">
         <v>21</v>
       </c>
@@ -4121,7 +4130,7 @@
       <c r="N86" s="1"/>
       <c r="O86" s="1"/>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87" s="6" t="s">
         <v>11</v>
       </c>
@@ -4160,7 +4169,7 @@
       <c r="N87" s="1"/>
       <c r="O87" s="1"/>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" s="6" t="s">
         <v>13</v>
       </c>
@@ -4199,7 +4208,7 @@
       <c r="N88" s="1"/>
       <c r="O88" s="1"/>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" s="6" t="s">
         <v>13</v>
       </c>
@@ -4238,7 +4247,7 @@
       <c r="N89" s="1"/>
       <c r="O89" s="1"/>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" s="6" t="s">
         <v>13</v>
       </c>
@@ -4277,7 +4286,7 @@
       <c r="N90" s="1"/>
       <c r="O90" s="1"/>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" s="6" t="s">
         <v>13</v>
       </c>
@@ -4316,7 +4325,7 @@
       <c r="N91" s="1"/>
       <c r="O91" s="1"/>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" s="6" t="s">
         <v>13</v>
       </c>
@@ -4355,7 +4364,7 @@
       <c r="N92" s="1"/>
       <c r="O92" s="1"/>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" s="6" t="s">
         <v>12</v>
       </c>
@@ -4394,7 +4403,7 @@
       <c r="N93" s="1"/>
       <c r="O93" s="1"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94" s="6" t="s">
         <v>13</v>
       </c>
@@ -4433,7 +4442,7 @@
       <c r="N94" s="1"/>
       <c r="O94" s="1"/>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" s="6" t="s">
         <v>21</v>
       </c>
@@ -4472,7 +4481,7 @@
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A96" s="6" t="s">
         <v>13</v>
       </c>
@@ -4511,7 +4520,7 @@
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A97" s="6" t="s">
         <v>12</v>
       </c>
@@ -4550,7 +4559,7 @@
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A98" s="6" t="s">
         <v>17</v>
       </c>
@@ -4589,7 +4598,7 @@
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A99" s="6" t="s">
         <v>13</v>
       </c>
@@ -4628,7 +4637,7 @@
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A100" s="6" t="s">
         <v>13</v>
       </c>
@@ -4667,7 +4676,7 @@
       <c r="N100" s="1"/>
       <c r="O100" s="1"/>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A101" s="6" t="s">
         <v>13</v>
       </c>
@@ -4706,7 +4715,7 @@
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A102" s="6" t="s">
         <v>13</v>
       </c>
@@ -4745,7 +4754,7 @@
       <c r="N102" s="1"/>
       <c r="O102" s="1"/>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A103" s="6" t="s">
         <v>13</v>
       </c>
@@ -4784,7 +4793,7 @@
       <c r="N103" s="1"/>
       <c r="O103" s="1"/>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A104" s="6" t="s">
         <v>13</v>
       </c>
@@ -4823,7 +4832,7 @@
       <c r="N104" s="1"/>
       <c r="O104" s="1"/>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A105" s="6" t="s">
         <v>12</v>
       </c>
@@ -4862,7 +4871,7 @@
       <c r="N105" s="1"/>
       <c r="O105" s="1"/>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A106" s="6" t="s">
         <v>12</v>
       </c>
@@ -4901,7 +4910,7 @@
       <c r="N106" s="1"/>
       <c r="O106" s="1"/>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A107" s="6" t="s">
         <v>12</v>
       </c>
@@ -4940,7 +4949,7 @@
       <c r="N107" s="1"/>
       <c r="O107" s="1"/>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A108" s="6" t="s">
         <v>12</v>
       </c>
@@ -4979,7 +4988,7 @@
       <c r="N108" s="1"/>
       <c r="O108" s="1"/>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A109" s="6" t="s">
         <v>12</v>
       </c>
@@ -5018,7 +5027,7 @@
       <c r="N109" s="1"/>
       <c r="O109" s="1"/>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A110" s="6" t="s">
         <v>12</v>
       </c>
@@ -5057,7 +5066,7 @@
       <c r="N110" s="1"/>
       <c r="O110" s="1"/>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A111" s="6" t="s">
         <v>13</v>
       </c>
@@ -5096,7 +5105,7 @@
       <c r="N111" s="1"/>
       <c r="O111" s="1"/>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A112" s="6" t="s">
         <v>12</v>
       </c>
@@ -5135,7 +5144,7 @@
       <c r="N112" s="1"/>
       <c r="O112" s="1"/>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A113" s="6" t="s">
         <v>54</v>
       </c>
@@ -5174,7 +5183,7 @@
       <c r="N113" s="1"/>
       <c r="O113" s="1"/>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A114" s="6" t="s">
         <v>54</v>
       </c>
@@ -5213,7 +5222,7 @@
       <c r="N114" s="1"/>
       <c r="O114" s="1"/>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A115" s="6" t="s">
         <v>12</v>
       </c>
@@ -5252,7 +5261,7 @@
       <c r="N115" s="1"/>
       <c r="O115" s="1"/>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A116" s="6" t="s">
         <v>13</v>
       </c>
@@ -5291,7 +5300,7 @@
       <c r="N116" s="1"/>
       <c r="O116" s="1"/>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A117" s="6" t="s">
         <v>54</v>
       </c>
@@ -5330,7 +5339,7 @@
       <c r="N117" s="1"/>
       <c r="O117" s="1"/>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A118" s="6" t="s">
         <v>17</v>
       </c>
@@ -5369,7 +5378,7 @@
       <c r="N118" s="1"/>
       <c r="O118" s="1"/>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A119" s="6" t="s">
         <v>12</v>
       </c>
@@ -5408,7 +5417,7 @@
       <c r="N119" s="1"/>
       <c r="O119" s="1"/>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A120" s="6" t="s">
         <v>12</v>
       </c>
@@ -5447,7 +5456,7 @@
       <c r="N120" s="1"/>
       <c r="O120" s="1"/>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A121" s="6" t="s">
         <v>54</v>
       </c>
@@ -5486,7 +5495,7 @@
       <c r="N121" s="1"/>
       <c r="O121" s="1"/>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A122" s="6" t="s">
         <v>13</v>
       </c>
@@ -5525,7 +5534,7 @@
       <c r="N122" s="1"/>
       <c r="O122" s="1"/>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A123" s="6" t="s">
         <v>13</v>
       </c>
@@ -5564,7 +5573,7 @@
       <c r="N123" s="1"/>
       <c r="O123" s="1"/>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A124" s="6" t="s">
         <v>54</v>
       </c>
@@ -5603,7 +5612,7 @@
       <c r="N124" s="1"/>
       <c r="O124" s="1"/>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A125" s="6" t="s">
         <v>27</v>
       </c>
@@ -5642,7 +5651,7 @@
       <c r="N125" s="1"/>
       <c r="O125" s="1"/>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A126" s="6" t="s">
         <v>17</v>
       </c>
@@ -5681,7 +5690,7 @@
       <c r="N126" s="1"/>
       <c r="O126" s="1"/>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A127" s="6" t="s">
         <v>17</v>
       </c>
@@ -5720,7 +5729,7 @@
       <c r="N127" s="1"/>
       <c r="O127" s="1"/>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A128" s="6" t="s">
         <v>13</v>
       </c>
@@ -5759,7 +5768,7 @@
       <c r="N128" s="1"/>
       <c r="O128" s="1"/>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A129" s="6" t="s">
         <v>13</v>
       </c>
@@ -5798,7 +5807,7 @@
       <c r="N129" s="1"/>
       <c r="O129" s="1"/>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A130" s="6" t="s">
         <v>13</v>
       </c>
@@ -5837,7 +5846,7 @@
       <c r="N130" s="1"/>
       <c r="O130" s="1"/>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A131" s="6" t="s">
         <v>13</v>
       </c>
@@ -5876,7 +5885,7 @@
       <c r="N131" s="1"/>
       <c r="O131" s="1"/>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A132" s="6" t="s">
         <v>17</v>
       </c>
@@ -5890,7 +5899,7 @@
         <v>27</v>
       </c>
       <c r="E132" s="1">
-        <f t="shared" ref="E132:E255" si="4">IF(F132&gt;G132,1,0)</f>
+        <f t="shared" ref="E132:E265" si="4">IF(F132&gt;G132,1,0)</f>
         <v>1</v>
       </c>
       <c r="F132" s="5">
@@ -5915,7 +5924,7 @@
       <c r="N132" s="1"/>
       <c r="O132" s="1"/>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A133" s="6" t="s">
         <v>13</v>
       </c>
@@ -5954,7 +5963,7 @@
       <c r="N133" s="1"/>
       <c r="O133" s="1"/>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A134" s="6" t="s">
         <v>12</v>
       </c>
@@ -5993,7 +6002,7 @@
       <c r="N134" s="1"/>
       <c r="O134" s="1"/>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A135" s="6" t="s">
         <v>12</v>
       </c>
@@ -6032,7 +6041,7 @@
       <c r="N135" s="1"/>
       <c r="O135" s="1"/>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A136" s="6" t="s">
         <v>12</v>
       </c>
@@ -6071,7 +6080,7 @@
       <c r="N136" s="1"/>
       <c r="O136" s="1"/>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A137" s="6" t="s">
         <v>12</v>
       </c>
@@ -6110,7 +6119,7 @@
       <c r="N137" s="1"/>
       <c r="O137" s="1"/>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A138" s="6" t="s">
         <v>21</v>
       </c>
@@ -6149,7 +6158,7 @@
       <c r="N138" s="1"/>
       <c r="O138" s="1"/>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A139" s="6" t="s">
         <v>12</v>
       </c>
@@ -6188,7 +6197,7 @@
       <c r="N139" s="1"/>
       <c r="O139" s="1"/>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A140" s="6" t="s">
         <v>12</v>
       </c>
@@ -6227,7 +6236,7 @@
       <c r="N140" s="1"/>
       <c r="O140" s="1"/>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A141" s="6" t="s">
         <v>13</v>
       </c>
@@ -6266,7 +6275,7 @@
       <c r="N141" s="1"/>
       <c r="O141" s="1"/>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A142" s="6" t="s">
         <v>12</v>
       </c>
@@ -6305,7 +6314,7 @@
       <c r="N142" s="1"/>
       <c r="O142" s="1"/>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A143" s="6" t="s">
         <v>54</v>
       </c>
@@ -6344,7 +6353,7 @@
       <c r="N143" s="1"/>
       <c r="O143" s="1"/>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A144" s="6" t="s">
         <v>54</v>
       </c>
@@ -6383,7 +6392,7 @@
       <c r="N144" s="1"/>
       <c r="O144" s="1"/>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A145" s="6" t="s">
         <v>12</v>
       </c>
@@ -6422,7 +6431,7 @@
       <c r="N145" s="1"/>
       <c r="O145" s="1"/>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A146" s="6" t="s">
         <v>13</v>
       </c>
@@ -6461,7 +6470,7 @@
       <c r="N146" s="1"/>
       <c r="O146" s="1"/>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A147" s="6" t="s">
         <v>21</v>
       </c>
@@ -6500,7 +6509,7 @@
       <c r="N147" s="1"/>
       <c r="O147" s="1"/>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A148" s="6" t="s">
         <v>13</v>
       </c>
@@ -6539,7 +6548,7 @@
       <c r="N148" s="1"/>
       <c r="O148" s="1"/>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A149" s="6" t="s">
         <v>12</v>
       </c>
@@ -6578,7 +6587,7 @@
       <c r="N149" s="1"/>
       <c r="O149" s="1"/>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A150" s="6" t="s">
         <v>12</v>
       </c>
@@ -6617,7 +6626,7 @@
       <c r="N150" s="1"/>
       <c r="O150" s="1"/>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A151" s="6" t="s">
         <v>13</v>
       </c>
@@ -6656,7 +6665,7 @@
       <c r="N151" s="1"/>
       <c r="O151" s="1"/>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A152" s="6" t="s">
         <v>12</v>
       </c>
@@ -6695,7 +6704,7 @@
       <c r="N152" s="1"/>
       <c r="O152" s="1"/>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A153" s="6" t="s">
         <v>54</v>
       </c>
@@ -6734,7 +6743,7 @@
       <c r="N153" s="1"/>
       <c r="O153" s="1"/>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A154" s="6" t="s">
         <v>13</v>
       </c>
@@ -6773,7 +6782,7 @@
       <c r="N154" s="1"/>
       <c r="O154" s="1"/>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A155" s="6" t="s">
         <v>13</v>
       </c>
@@ -6812,7 +6821,7 @@
       <c r="N155" s="1"/>
       <c r="O155" s="1"/>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A156" s="6" t="s">
         <v>13</v>
       </c>
@@ -6851,7 +6860,7 @@
       <c r="N156" s="1"/>
       <c r="O156" s="1"/>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A157" s="6" t="s">
         <v>13</v>
       </c>
@@ -6890,7 +6899,7 @@
       <c r="N157" s="1"/>
       <c r="O157" s="1"/>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A158" s="6" t="s">
         <v>13</v>
       </c>
@@ -6929,7 +6938,7 @@
       <c r="N158" s="1"/>
       <c r="O158" s="1"/>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A159" s="6" t="s">
         <v>13</v>
       </c>
@@ -6968,7 +6977,7 @@
       <c r="N159" s="1"/>
       <c r="O159" s="1"/>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A160" s="6" t="s">
         <v>13</v>
       </c>
@@ -7007,7 +7016,7 @@
       <c r="N160" s="1"/>
       <c r="O160" s="1"/>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A161" s="6" t="s">
         <v>12</v>
       </c>
@@ -7046,7 +7055,7 @@
       <c r="N161" s="1"/>
       <c r="O161" s="1"/>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A162" s="6" t="s">
         <v>13</v>
       </c>
@@ -7085,7 +7094,7 @@
       <c r="N162" s="1"/>
       <c r="O162" s="1"/>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A163" s="6" t="s">
         <v>17</v>
       </c>
@@ -7124,7 +7133,7 @@
       <c r="N163" s="1"/>
       <c r="O163" s="1"/>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A164" s="6" t="s">
         <v>13</v>
       </c>
@@ -7163,7 +7172,7 @@
       <c r="N164" s="1"/>
       <c r="O164" s="1"/>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A165" s="6" t="s">
         <v>12</v>
       </c>
@@ -7202,7 +7211,7 @@
       <c r="N165" s="1"/>
       <c r="O165" s="1"/>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A166" s="6" t="s">
         <v>12</v>
       </c>
@@ -7241,7 +7250,7 @@
       <c r="N166" s="1"/>
       <c r="O166" s="1"/>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A167" s="6" t="s">
         <v>13</v>
       </c>
@@ -7280,7 +7289,7 @@
       <c r="N167" s="1"/>
       <c r="O167" s="1"/>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A168" s="6" t="s">
         <v>11</v>
       </c>
@@ -7319,7 +7328,7 @@
       <c r="N168" s="1"/>
       <c r="O168" s="1"/>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A169" s="6" t="s">
         <v>13</v>
       </c>
@@ -7358,7 +7367,7 @@
       <c r="N169" s="1"/>
       <c r="O169" s="1"/>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A170" s="6" t="s">
         <v>13</v>
       </c>
@@ -7397,7 +7406,7 @@
       <c r="N170" s="1"/>
       <c r="O170" s="1"/>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A171" s="6" t="s">
         <v>12</v>
       </c>
@@ -7436,7 +7445,7 @@
       <c r="N171" s="1"/>
       <c r="O171" s="1"/>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A172" s="6" t="s">
         <v>13</v>
       </c>
@@ -7475,7 +7484,7 @@
       <c r="N172" s="1"/>
       <c r="O172" s="1"/>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A173" s="6" t="s">
         <v>17</v>
       </c>
@@ -7514,7 +7523,7 @@
       <c r="N173" s="1"/>
       <c r="O173" s="1"/>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A174" s="6" t="s">
         <v>17</v>
       </c>
@@ -7553,7 +7562,7 @@
       <c r="N174" s="1"/>
       <c r="O174" s="1"/>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A175" s="6" t="s">
         <v>12</v>
       </c>
@@ -7592,7 +7601,7 @@
       <c r="N175" s="1"/>
       <c r="O175" s="1"/>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A176" s="6" t="s">
         <v>21</v>
       </c>
@@ -7631,7 +7640,7 @@
       <c r="N176" s="1"/>
       <c r="O176" s="1"/>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A177" s="6" t="s">
         <v>11</v>
       </c>
@@ -7670,7 +7679,7 @@
       <c r="N177" s="1"/>
       <c r="O177" s="1"/>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A178" s="6" t="s">
         <v>12</v>
       </c>
@@ -7709,7 +7718,7 @@
       <c r="N178" s="1"/>
       <c r="O178" s="1"/>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A179" s="6" t="s">
         <v>13</v>
       </c>
@@ -7748,7 +7757,7 @@
       <c r="N179" s="1"/>
       <c r="O179" s="1"/>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A180" s="6" t="s">
         <v>25</v>
       </c>
@@ -7787,7 +7796,7 @@
       <c r="N180" s="1"/>
       <c r="O180" s="1"/>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A181" s="6" t="s">
         <v>12</v>
       </c>
@@ -7826,7 +7835,7 @@
       <c r="N181" s="1"/>
       <c r="O181" s="1"/>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A182" s="6" t="s">
         <v>11</v>
       </c>
@@ -7865,7 +7874,7 @@
       <c r="N182" s="1"/>
       <c r="O182" s="1"/>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A183" s="6" t="s">
         <v>17</v>
       </c>
@@ -7904,7 +7913,7 @@
       <c r="N183" s="1"/>
       <c r="O183" s="1"/>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A184" s="6" t="s">
         <v>11</v>
       </c>
@@ -7943,7 +7952,7 @@
       <c r="N184" s="1"/>
       <c r="O184" s="1"/>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A185" s="6" t="s">
         <v>13</v>
       </c>
@@ -7982,7 +7991,7 @@
       <c r="N185" s="1"/>
       <c r="O185" s="1"/>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A186" s="6" t="s">
         <v>13</v>
       </c>
@@ -8021,7 +8030,7 @@
       <c r="N186" s="1"/>
       <c r="O186" s="1"/>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A187" s="6" t="s">
         <v>13</v>
       </c>
@@ -8060,7 +8069,7 @@
       <c r="N187" s="1"/>
       <c r="O187" s="1"/>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A188" s="6" t="s">
         <v>13</v>
       </c>
@@ -8099,7 +8108,7 @@
       <c r="N188" s="1"/>
       <c r="O188" s="1"/>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A189" s="6" t="s">
         <v>17</v>
       </c>
@@ -8138,7 +8147,7 @@
       <c r="N189" s="1"/>
       <c r="O189" s="1"/>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A190" s="6" t="s">
         <v>12</v>
       </c>
@@ -8177,7 +8186,7 @@
       <c r="N190" s="1"/>
       <c r="O190" s="1"/>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A191" s="6" t="s">
         <v>13</v>
       </c>
@@ -8216,7 +8225,7 @@
       <c r="N191" s="1"/>
       <c r="O191" s="1"/>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A192" s="6" t="s">
         <v>11</v>
       </c>
@@ -8255,7 +8264,7 @@
       <c r="N192" s="1"/>
       <c r="O192" s="1"/>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A193" s="6" t="s">
         <v>17</v>
       </c>
@@ -8294,7 +8303,7 @@
       <c r="N193" s="1"/>
       <c r="O193" s="1"/>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A194" s="6" t="s">
         <v>21</v>
       </c>
@@ -8333,7 +8342,7 @@
       <c r="N194" s="1"/>
       <c r="O194" s="1"/>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A195" s="6" t="s">
         <v>21</v>
       </c>
@@ -8372,7 +8381,7 @@
       <c r="N195" s="1"/>
       <c r="O195" s="1"/>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A196" s="6" t="s">
         <v>13</v>
       </c>
@@ -8411,7 +8420,7 @@
       <c r="N196" s="1"/>
       <c r="O196" s="1"/>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A197" s="6" t="s">
         <v>13</v>
       </c>
@@ -8450,7 +8459,7 @@
       <c r="N197" s="1"/>
       <c r="O197" s="1"/>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A198" s="6" t="s">
         <v>17</v>
       </c>
@@ -8489,7 +8498,7 @@
       <c r="N198" s="1"/>
       <c r="O198" s="1"/>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A199" s="6" t="s">
         <v>17</v>
       </c>
@@ -8528,7 +8537,7 @@
       <c r="N199" s="1"/>
       <c r="O199" s="1"/>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A200" s="6" t="s">
         <v>11</v>
       </c>
@@ -8567,7 +8576,7 @@
       <c r="N200" s="1"/>
       <c r="O200" s="1"/>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A201" s="6" t="s">
         <v>13</v>
       </c>
@@ -8606,7 +8615,7 @@
       <c r="N201" s="1"/>
       <c r="O201" s="1"/>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A202" s="6" t="s">
         <v>13</v>
       </c>
@@ -8645,7 +8654,7 @@
       <c r="N202" s="1"/>
       <c r="O202" s="1"/>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A203" s="6" t="s">
         <v>11</v>
       </c>
@@ -8684,7 +8693,7 @@
       <c r="N203" s="1"/>
       <c r="O203" s="1"/>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A204" s="6" t="s">
         <v>11</v>
       </c>
@@ -8723,7 +8732,7 @@
       <c r="N204" s="1"/>
       <c r="O204" s="1"/>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A205" s="6" t="s">
         <v>21</v>
       </c>
@@ -8762,7 +8771,7 @@
       <c r="N205" s="1"/>
       <c r="O205" s="1"/>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A206" s="6" t="s">
         <v>17</v>
       </c>
@@ -8801,7 +8810,7 @@
       <c r="N206" s="1"/>
       <c r="O206" s="1"/>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A207" s="6" t="s">
         <v>13</v>
       </c>
@@ -8840,7 +8849,7 @@
       <c r="N207" s="1"/>
       <c r="O207" s="1"/>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A208" s="6" t="s">
         <v>13</v>
       </c>
@@ -8879,7 +8888,7 @@
       <c r="N208" s="1"/>
       <c r="O208" s="1"/>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A209" s="6" t="s">
         <v>17</v>
       </c>
@@ -8918,7 +8927,7 @@
       <c r="N209" s="1"/>
       <c r="O209" s="1"/>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A210" s="6" t="s">
         <v>17</v>
       </c>
@@ -8957,7 +8966,7 @@
       <c r="N210" s="1"/>
       <c r="O210" s="1"/>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A211" s="6" t="s">
         <v>54</v>
       </c>
@@ -8996,7 +9005,7 @@
       <c r="N211" s="1"/>
       <c r="O211" s="1"/>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A212" s="6" t="s">
         <v>21</v>
       </c>
@@ -9035,7 +9044,7 @@
       <c r="N212" s="1"/>
       <c r="O212" s="1"/>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A213" s="6" t="s">
         <v>11</v>
       </c>
@@ -9074,7 +9083,7 @@
       <c r="N213" s="1"/>
       <c r="O213" s="1"/>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A214" s="6" t="s">
         <v>54</v>
       </c>
@@ -9113,7 +9122,7 @@
       <c r="N214" s="1"/>
       <c r="O214" s="1"/>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A215" s="6" t="s">
         <v>13</v>
       </c>
@@ -9152,7 +9161,7 @@
       <c r="N215" s="1"/>
       <c r="O215" s="1"/>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A216" s="6" t="s">
         <v>13</v>
       </c>
@@ -9191,7 +9200,7 @@
       <c r="N216" s="1"/>
       <c r="O216" s="1"/>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A217" s="6" t="s">
         <v>13</v>
       </c>
@@ -9230,7 +9239,7 @@
       <c r="N217" s="1"/>
       <c r="O217" s="1"/>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A218" s="6" t="s">
         <v>13</v>
       </c>
@@ -9269,7 +9278,7 @@
       <c r="N218" s="1"/>
       <c r="O218" s="1"/>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A219" s="6" t="s">
         <v>21</v>
       </c>
@@ -9308,7 +9317,7 @@
       <c r="N219" s="1"/>
       <c r="O219" s="1"/>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A220" s="6" t="s">
         <v>13</v>
       </c>
@@ -9347,7 +9356,7 @@
       <c r="N220" s="1"/>
       <c r="O220" s="1"/>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A221" s="6" t="s">
         <v>13</v>
       </c>
@@ -9386,7 +9395,7 @@
       <c r="N221" s="1"/>
       <c r="O221" s="1"/>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A222" s="6" t="s">
         <v>21</v>
       </c>
@@ -9425,7 +9434,7 @@
       <c r="N222" s="1"/>
       <c r="O222" s="1"/>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A223" s="6" t="s">
         <v>11</v>
       </c>
@@ -9464,7 +9473,7 @@
       <c r="N223" s="1"/>
       <c r="O223" s="1"/>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A224" s="6" t="s">
         <v>21</v>
       </c>
@@ -9503,7 +9512,7 @@
       <c r="N224" s="1"/>
       <c r="O224" s="1"/>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A225" s="6" t="s">
         <v>21</v>
       </c>
@@ -9542,7 +9551,7 @@
       <c r="N225" s="1"/>
       <c r="O225" s="1"/>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A226" s="6" t="s">
         <v>13</v>
       </c>
@@ -9581,7 +9590,7 @@
       <c r="N226" s="1"/>
       <c r="O226" s="1"/>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A227" s="6" t="s">
         <v>12</v>
       </c>
@@ -9620,7 +9629,7 @@
       <c r="N227" s="1"/>
       <c r="O227" s="1"/>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A228" s="6" t="s">
         <v>12</v>
       </c>
@@ -9659,7 +9668,7 @@
       <c r="N228" s="1"/>
       <c r="O228" s="1"/>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A229" s="6" t="s">
         <v>11</v>
       </c>
@@ -9698,7 +9707,7 @@
       <c r="N229" s="1"/>
       <c r="O229" s="1"/>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A230" s="6" t="s">
         <v>54</v>
       </c>
@@ -9737,7 +9746,7 @@
       <c r="N230" s="1"/>
       <c r="O230" s="1"/>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A231" s="6" t="s">
         <v>12</v>
       </c>
@@ -9776,7 +9785,7 @@
       <c r="N231" s="1"/>
       <c r="O231" s="1"/>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A232" s="6" t="s">
         <v>12</v>
       </c>
@@ -9815,7 +9824,7 @@
       <c r="N232" s="1"/>
       <c r="O232" s="1"/>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A233" s="6" t="s">
         <v>12</v>
       </c>
@@ -9854,7 +9863,7 @@
       <c r="N233" s="1"/>
       <c r="O233" s="1"/>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A234" s="6" t="s">
         <v>13</v>
       </c>
@@ -9893,7 +9902,7 @@
       <c r="N234" s="1"/>
       <c r="O234" s="1"/>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A235" s="6" t="s">
         <v>21</v>
       </c>
@@ -9932,7 +9941,7 @@
       <c r="N235" s="1"/>
       <c r="O235" s="1"/>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A236" s="6" t="s">
         <v>12</v>
       </c>
@@ -9971,7 +9980,7 @@
       <c r="N236" s="1"/>
       <c r="O236" s="1"/>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A237" s="6" t="s">
         <v>13</v>
       </c>
@@ -10010,7 +10019,7 @@
       <c r="N237" s="1"/>
       <c r="O237" s="1"/>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A238" s="6" t="s">
         <v>12</v>
       </c>
@@ -10049,7 +10058,7 @@
       <c r="N238" s="1"/>
       <c r="O238" s="1"/>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A239" s="6" t="s">
         <v>12</v>
       </c>
@@ -10088,7 +10097,7 @@
       <c r="N239" s="1"/>
       <c r="O239" s="1"/>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A240" s="6" t="s">
         <v>13</v>
       </c>
@@ -10127,7 +10136,7 @@
       <c r="N240" s="1"/>
       <c r="O240" s="1"/>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A241" s="6" t="s">
         <v>13</v>
       </c>
@@ -10166,7 +10175,7 @@
       <c r="N241" s="1"/>
       <c r="O241" s="1"/>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A242" s="6" t="s">
         <v>21</v>
       </c>
@@ -10205,7 +10214,7 @@
       <c r="N242" s="1"/>
       <c r="O242" s="1"/>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A243" s="6" t="s">
         <v>54</v>
       </c>
@@ -10244,7 +10253,7 @@
       <c r="N243" s="1"/>
       <c r="O243" s="1"/>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A244" s="6" t="s">
         <v>21</v>
       </c>
@@ -10283,7 +10292,7 @@
       <c r="N244" s="1"/>
       <c r="O244" s="1"/>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A245" s="6" t="s">
         <v>17</v>
       </c>
@@ -10322,7 +10331,7 @@
       <c r="N245" s="1"/>
       <c r="O245" s="1"/>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A246" s="6" t="s">
         <v>54</v>
       </c>
@@ -10361,7 +10370,7 @@
       <c r="N246" s="1"/>
       <c r="O246" s="1"/>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A247" s="6" t="s">
         <v>12</v>
       </c>
@@ -10400,7 +10409,7 @@
       <c r="N247" s="1"/>
       <c r="O247" s="1"/>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A248" s="6" t="s">
         <v>12</v>
       </c>
@@ -10439,7 +10448,7 @@
       <c r="N248" s="1"/>
       <c r="O248" s="1"/>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A249" s="6" t="s">
         <v>13</v>
       </c>
@@ -10478,7 +10487,7 @@
       <c r="N249" s="1"/>
       <c r="O249" s="1"/>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A250" s="6" t="s">
         <v>13</v>
       </c>
@@ -10517,7 +10526,7 @@
       <c r="N250" s="1"/>
       <c r="O250" s="1"/>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A251" s="6" t="s">
         <v>21</v>
       </c>
@@ -10556,7 +10565,7 @@
       <c r="N251" s="1"/>
       <c r="O251" s="1"/>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A252" s="6" t="s">
         <v>21</v>
       </c>
@@ -10595,7 +10604,7 @@
       <c r="N252" s="1"/>
       <c r="O252" s="1"/>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A253" s="6" t="s">
         <v>12</v>
       </c>
@@ -10634,7 +10643,7 @@
       <c r="N253" s="1"/>
       <c r="O253" s="1"/>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A254" s="6" t="s">
         <v>12</v>
       </c>
@@ -10673,7 +10682,7 @@
       <c r="N254" s="1"/>
       <c r="O254" s="1"/>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A255" s="6" t="s">
         <v>12</v>
       </c>
@@ -10712,500 +10721,1119 @@
       <c r="N255" s="1"/>
       <c r="O255" s="1"/>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A256" s="6"/>
-      <c r="B256" s="6"/>
-      <c r="C256" s="7"/>
-      <c r="D256" s="7"/>
-      <c r="E256" s="1"/>
-      <c r="F256" s="5"/>
-      <c r="G256" s="5"/>
-      <c r="H256" s="1"/>
-      <c r="I256" s="1"/>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A256" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B256" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C256" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D256" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E256" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F256" s="5">
+        <v>7</v>
+      </c>
+      <c r="G256" s="5">
+        <v>5</v>
+      </c>
+      <c r="H256" s="1">
+        <v>7</v>
+      </c>
+      <c r="I256" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="J256" s="1"/>
-      <c r="K256" s="9"/>
+      <c r="K256" s="9" t="str">
+        <f t="shared" ref="K256:K284" si="8">IF(OR(OR(AND(OR(A256=B256,A256=C256,A256=D256,B256=C256,B256=D256,C256=D256),OR(A256&lt;&gt;"",D256&lt;&gt;"")),H256&gt;MAX(F256:G256),B256=C256),OR(AND(ISBLANK(A256)=FALSE,ISNA(VLOOKUP(A256,$M$3:$O$27,1,FALSE))),ISNA(VLOOKUP(B256,$M$3:$O$27,1,FALSE)),ISNA(VLOOKUP(C256,$M$3:$O$27,1,FALSE)),AND(ISBLANK(D256)=FALSE,ISNA(VLOOKUP(D256,$M$3:$O$27,1,FALSE))),OR(COUNTBLANK(A256:D256)=1,COUNTBLANK(A256:D256)=3))),"ERREUR","")</f>
+        <v/>
+      </c>
       <c r="L256" s="1"/>
       <c r="M256" s="1"/>
       <c r="N256" s="1"/>
       <c r="O256" s="1"/>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A257" s="6"/>
-      <c r="B257" s="6"/>
-      <c r="C257" s="7"/>
-      <c r="D257" s="7"/>
-      <c r="E257" s="1"/>
-      <c r="F257" s="5"/>
-      <c r="G257" s="5"/>
-      <c r="H257" s="1"/>
-      <c r="I257" s="1"/>
+    <row r="257" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A257" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B257" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C257" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D257" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E257" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F257" s="5">
+        <v>8</v>
+      </c>
+      <c r="G257" s="5">
+        <v>6</v>
+      </c>
+      <c r="H257" s="1">
+        <v>7</v>
+      </c>
+      <c r="I257" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="J257" s="1"/>
-      <c r="K257" s="9"/>
+      <c r="K257" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L257" s="1"/>
       <c r="M257" s="1"/>
       <c r="N257" s="1"/>
       <c r="O257" s="1"/>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A258" s="6"/>
-      <c r="B258" s="6"/>
-      <c r="C258" s="7"/>
-      <c r="D258" s="7"/>
-      <c r="E258" s="1"/>
-      <c r="F258" s="5"/>
-      <c r="G258" s="5"/>
-      <c r="H258" s="1"/>
-      <c r="I258" s="1"/>
+    <row r="258" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A258" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B258" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C258" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D258" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E258" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F258" s="5">
+        <v>7</v>
+      </c>
+      <c r="G258" s="5">
+        <v>4</v>
+      </c>
+      <c r="H258" s="1">
+        <v>7</v>
+      </c>
+      <c r="I258" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="J258" s="1"/>
-      <c r="K258" s="9"/>
+      <c r="K258" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L258" s="1"/>
       <c r="M258" s="1"/>
       <c r="N258" s="1"/>
       <c r="O258" s="1"/>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A259" s="6"/>
-      <c r="B259" s="6"/>
-      <c r="C259" s="7"/>
-      <c r="D259" s="7"/>
-      <c r="E259" s="1"/>
-      <c r="F259" s="5"/>
-      <c r="G259" s="5"/>
-      <c r="H259" s="1"/>
-      <c r="I259" s="1"/>
+    <row r="259" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A259" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B259" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C259" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D259" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E259" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F259" s="5">
+        <v>13</v>
+      </c>
+      <c r="G259" s="5">
+        <v>10</v>
+      </c>
+      <c r="H259" s="1">
+        <v>7</v>
+      </c>
+      <c r="I259" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="J259" s="1"/>
-      <c r="K259" s="9"/>
+      <c r="K259" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L259" s="1"/>
       <c r="M259" s="1"/>
       <c r="N259" s="1"/>
       <c r="O259" s="1"/>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A260" s="6"/>
-      <c r="B260" s="6"/>
-      <c r="C260" s="7"/>
-      <c r="D260" s="7"/>
-      <c r="E260" s="1"/>
-      <c r="F260" s="5"/>
-      <c r="G260" s="5"/>
-      <c r="H260" s="1"/>
-      <c r="I260" s="1"/>
+    <row r="260" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A260" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B260" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C260" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D260" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E260" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F260" s="5">
+        <v>7</v>
+      </c>
+      <c r="G260" s="5">
+        <v>5</v>
+      </c>
+      <c r="H260" s="1">
+        <v>7</v>
+      </c>
+      <c r="I260" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="J260" s="1"/>
-      <c r="K260" s="9"/>
+      <c r="K260" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L260" s="1"/>
       <c r="M260" s="1"/>
       <c r="N260" s="1"/>
       <c r="O260" s="1"/>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A261" s="6"/>
-      <c r="B261" s="6"/>
-      <c r="C261" s="7"/>
-      <c r="D261" s="7"/>
-      <c r="E261" s="1"/>
-      <c r="F261" s="5"/>
-      <c r="G261" s="5"/>
-      <c r="H261" s="1"/>
-      <c r="I261" s="1"/>
+    <row r="261" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A261" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B261" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C261" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D261" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E261" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F261" s="5">
+        <v>7</v>
+      </c>
+      <c r="G261" s="5">
+        <v>5</v>
+      </c>
+      <c r="H261" s="1">
+        <v>7</v>
+      </c>
+      <c r="I261" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="J261" s="1"/>
-      <c r="K261" s="9"/>
+      <c r="K261" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L261" s="1"/>
       <c r="M261" s="1"/>
       <c r="N261" s="1"/>
       <c r="O261" s="1"/>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A262" s="6"/>
-      <c r="B262" s="6"/>
-      <c r="C262" s="7"/>
-      <c r="D262" s="7"/>
-      <c r="E262" s="1"/>
-      <c r="F262" s="5"/>
-      <c r="G262" s="5"/>
-      <c r="H262" s="1"/>
-      <c r="I262" s="1"/>
+    <row r="262" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A262" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B262" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C262" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D262" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E262" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F262" s="5">
+        <v>7</v>
+      </c>
+      <c r="G262" s="5">
+        <v>2</v>
+      </c>
+      <c r="H262" s="1">
+        <v>7</v>
+      </c>
+      <c r="I262" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="J262" s="1"/>
-      <c r="K262" s="9"/>
+      <c r="K262" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L262" s="1"/>
       <c r="M262" s="1"/>
       <c r="N262" s="1"/>
       <c r="O262" s="1"/>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A263" s="6"/>
-      <c r="B263" s="6"/>
-      <c r="C263" s="7"/>
-      <c r="D263" s="7"/>
-      <c r="E263" s="1"/>
-      <c r="F263" s="5"/>
-      <c r="G263" s="5"/>
-      <c r="H263" s="1"/>
-      <c r="I263" s="1"/>
+    <row r="263" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A263" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B263" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C263" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D263" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E263" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F263" s="5">
+        <v>7</v>
+      </c>
+      <c r="G263" s="5">
+        <v>4</v>
+      </c>
+      <c r="H263" s="1">
+        <v>7</v>
+      </c>
+      <c r="I263" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="J263" s="1"/>
-      <c r="K263" s="9"/>
+      <c r="K263" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L263" s="1"/>
       <c r="M263" s="1"/>
       <c r="N263" s="1"/>
       <c r="O263" s="1"/>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A264" s="6"/>
-      <c r="B264" s="6"/>
-      <c r="C264" s="7"/>
-      <c r="D264" s="7"/>
-      <c r="E264" s="1"/>
-      <c r="F264" s="5"/>
-      <c r="G264" s="5"/>
-      <c r="H264" s="1"/>
-      <c r="I264" s="1"/>
+    <row r="264" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A264" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B264" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C264" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D264" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E264" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F264" s="5">
+        <v>7</v>
+      </c>
+      <c r="G264" s="5">
+        <v>3</v>
+      </c>
+      <c r="H264" s="1">
+        <v>7</v>
+      </c>
+      <c r="I264" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="J264" s="1"/>
-      <c r="K264" s="9"/>
+      <c r="K264" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L264" s="1"/>
       <c r="M264" s="1"/>
       <c r="N264" s="1"/>
       <c r="O264" s="1"/>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A265" s="6"/>
-      <c r="B265" s="6"/>
-      <c r="C265" s="7"/>
-      <c r="D265" s="7"/>
-      <c r="E265" s="1"/>
-      <c r="F265" s="5"/>
-      <c r="G265" s="5"/>
-      <c r="H265" s="1"/>
-      <c r="I265" s="1"/>
+    <row r="265" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A265" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B265" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C265" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D265" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E265" s="1">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F265" s="5">
+        <v>7</v>
+      </c>
+      <c r="G265" s="5">
+        <v>2</v>
+      </c>
+      <c r="H265" s="1">
+        <v>7</v>
+      </c>
+      <c r="I265" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="J265" s="1"/>
-      <c r="K265" s="9"/>
+      <c r="K265" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L265" s="1"/>
       <c r="M265" s="1"/>
       <c r="N265" s="1"/>
       <c r="O265" s="1"/>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A266" s="6"/>
-      <c r="B266" s="6"/>
-      <c r="C266" s="7"/>
-      <c r="D266" s="7"/>
-      <c r="E266" s="1"/>
-      <c r="F266" s="5"/>
-      <c r="G266" s="5"/>
-      <c r="H266" s="1"/>
-      <c r="I266" s="1"/>
+    <row r="266" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A266" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B266" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C266" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D266" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E266" s="1">
+        <v>1</v>
+      </c>
+      <c r="F266" s="5">
+        <v>12</v>
+      </c>
+      <c r="G266" s="5">
+        <v>10</v>
+      </c>
+      <c r="H266" s="1">
+        <v>11</v>
+      </c>
+      <c r="I266" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="J266" s="1"/>
-      <c r="K266" s="9"/>
+      <c r="K266" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L266" s="1"/>
       <c r="M266" s="1"/>
       <c r="N266" s="1"/>
       <c r="O266" s="1"/>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A267" s="6"/>
-      <c r="B267" s="6"/>
-      <c r="C267" s="7"/>
-      <c r="D267" s="7"/>
-      <c r="E267" s="1"/>
-      <c r="F267" s="5"/>
-      <c r="G267" s="5"/>
-      <c r="H267" s="1"/>
-      <c r="I267" s="1"/>
+    <row r="267" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A267" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B267" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C267" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D267" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E267" s="1">
+        <v>1</v>
+      </c>
+      <c r="F267" s="5">
+        <v>11</v>
+      </c>
+      <c r="G267" s="5">
+        <v>4</v>
+      </c>
+      <c r="H267" s="1">
+        <v>11</v>
+      </c>
+      <c r="I267" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="J267" s="1"/>
-      <c r="K267" s="9"/>
+      <c r="K267" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L267" s="1"/>
       <c r="M267" s="1"/>
       <c r="N267" s="1"/>
       <c r="O267" s="1"/>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A268" s="6"/>
-      <c r="B268" s="6"/>
-      <c r="C268" s="7"/>
-      <c r="D268" s="7"/>
-      <c r="E268" s="1"/>
-      <c r="F268" s="5"/>
-      <c r="G268" s="5"/>
-      <c r="H268" s="1"/>
-      <c r="I268" s="1"/>
+    <row r="268" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A268" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B268" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C268" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D268" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E268" s="1">
+        <v>1</v>
+      </c>
+      <c r="F268" s="5">
+        <v>11</v>
+      </c>
+      <c r="G268" s="5">
+        <v>3</v>
+      </c>
+      <c r="H268" s="1">
+        <v>11</v>
+      </c>
+      <c r="I268" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="J268" s="1"/>
-      <c r="K268" s="9"/>
+      <c r="K268" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L268" s="1"/>
       <c r="M268" s="1"/>
       <c r="N268" s="1"/>
       <c r="O268" s="1"/>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A269" s="6"/>
-      <c r="B269" s="6"/>
-      <c r="C269" s="7"/>
-      <c r="D269" s="7"/>
-      <c r="E269" s="1"/>
-      <c r="F269" s="5"/>
-      <c r="G269" s="5"/>
-      <c r="H269" s="1"/>
-      <c r="I269" s="1"/>
+    <row r="269" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A269" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B269" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C269" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D269" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E269" s="1">
+        <v>1</v>
+      </c>
+      <c r="F269" s="5">
+        <v>11</v>
+      </c>
+      <c r="G269" s="5">
+        <v>5</v>
+      </c>
+      <c r="H269" s="1">
+        <v>11</v>
+      </c>
+      <c r="I269" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="J269" s="1"/>
-      <c r="K269" s="9"/>
+      <c r="K269" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L269" s="1"/>
       <c r="M269" s="1"/>
       <c r="N269" s="1"/>
       <c r="O269" s="1"/>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A270" s="6"/>
-      <c r="B270" s="6"/>
-      <c r="C270" s="7"/>
-      <c r="D270" s="7"/>
-      <c r="E270" s="1"/>
-      <c r="F270" s="5"/>
-      <c r="G270" s="5"/>
-      <c r="H270" s="1"/>
-      <c r="I270" s="1"/>
+    <row r="270" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A270" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B270" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C270" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D270" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E270" s="1">
+        <v>1</v>
+      </c>
+      <c r="F270" s="5">
+        <v>11</v>
+      </c>
+      <c r="G270" s="5">
+        <v>9</v>
+      </c>
+      <c r="H270" s="1">
+        <v>11</v>
+      </c>
+      <c r="I270" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="J270" s="1"/>
-      <c r="K270" s="9"/>
+      <c r="K270" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L270" s="1"/>
       <c r="M270" s="1"/>
       <c r="N270" s="1"/>
       <c r="O270" s="1"/>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A271" s="6"/>
-      <c r="B271" s="6"/>
-      <c r="C271" s="7"/>
-      <c r="D271" s="7"/>
-      <c r="E271" s="1"/>
-      <c r="F271" s="5"/>
-      <c r="G271" s="5"/>
-      <c r="H271" s="1"/>
-      <c r="I271" s="1"/>
+    <row r="271" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A271" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B271" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C271" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D271" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E271" s="1">
+        <v>1</v>
+      </c>
+      <c r="F271" s="5">
+        <v>13</v>
+      </c>
+      <c r="G271" s="5">
+        <v>11</v>
+      </c>
+      <c r="H271" s="1">
+        <v>11</v>
+      </c>
+      <c r="I271" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="J271" s="1"/>
-      <c r="K271" s="9"/>
+      <c r="K271" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L271" s="1"/>
       <c r="M271" s="1"/>
       <c r="N271" s="1"/>
       <c r="O271" s="1"/>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A272" s="6"/>
-      <c r="B272" s="6"/>
-      <c r="C272" s="7"/>
-      <c r="D272" s="7"/>
-      <c r="E272" s="1"/>
-      <c r="F272" s="5"/>
-      <c r="G272" s="5"/>
-      <c r="H272" s="1"/>
-      <c r="I272" s="1"/>
+    <row r="272" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A272" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B272" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C272" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D272" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E272" s="1">
+        <v>1</v>
+      </c>
+      <c r="F272" s="5">
+        <v>11</v>
+      </c>
+      <c r="G272" s="5">
+        <v>7</v>
+      </c>
+      <c r="H272" s="1">
+        <v>11</v>
+      </c>
+      <c r="I272" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="J272" s="1"/>
-      <c r="K272" s="9"/>
+      <c r="K272" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L272" s="1"/>
       <c r="M272" s="1"/>
       <c r="N272" s="1"/>
       <c r="O272" s="1"/>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A273" s="6"/>
-      <c r="B273" s="6"/>
-      <c r="C273" s="7"/>
-      <c r="D273" s="7"/>
-      <c r="E273" s="1"/>
-      <c r="F273" s="5"/>
-      <c r="G273" s="5"/>
-      <c r="H273" s="1"/>
-      <c r="I273" s="1"/>
+    <row r="273" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A273" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B273" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C273" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D273" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E273" s="1">
+        <v>1</v>
+      </c>
+      <c r="F273" s="5">
+        <v>11</v>
+      </c>
+      <c r="G273" s="5">
+        <v>7</v>
+      </c>
+      <c r="H273" s="1">
+        <v>11</v>
+      </c>
+      <c r="I273" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="J273" s="1"/>
-      <c r="K273" s="9"/>
+      <c r="K273" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L273" s="1"/>
       <c r="M273" s="1"/>
       <c r="N273" s="1"/>
       <c r="O273" s="1"/>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A274" s="6"/>
-      <c r="B274" s="6"/>
-      <c r="C274" s="7"/>
-      <c r="D274" s="7"/>
-      <c r="E274" s="1"/>
-      <c r="F274" s="5"/>
-      <c r="G274" s="5"/>
-      <c r="H274" s="1"/>
-      <c r="I274" s="1"/>
+    <row r="274" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A274" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B274" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C274" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D274" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E274" s="1">
+        <v>1</v>
+      </c>
+      <c r="F274" s="5">
+        <v>11</v>
+      </c>
+      <c r="G274" s="5">
+        <v>8</v>
+      </c>
+      <c r="H274" s="1">
+        <v>11</v>
+      </c>
+      <c r="I274" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="J274" s="1"/>
-      <c r="K274" s="9"/>
+      <c r="K274" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L274" s="1"/>
       <c r="M274" s="1"/>
       <c r="N274" s="1"/>
       <c r="O274" s="1"/>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A275" s="6"/>
-      <c r="B275" s="6"/>
-      <c r="C275" s="7"/>
-      <c r="D275" s="7"/>
-      <c r="E275" s="1"/>
-      <c r="F275" s="5"/>
-      <c r="G275" s="5"/>
-      <c r="H275" s="1"/>
-      <c r="I275" s="1"/>
+    <row r="275" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A275" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B275" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C275" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D275" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E275" s="1">
+        <v>1</v>
+      </c>
+      <c r="F275" s="5">
+        <v>11</v>
+      </c>
+      <c r="G275" s="5">
+        <v>9</v>
+      </c>
+      <c r="H275" s="1">
+        <v>11</v>
+      </c>
+      <c r="I275" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="J275" s="1"/>
-      <c r="K275" s="9"/>
+      <c r="K275" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L275" s="1"/>
       <c r="M275" s="1"/>
       <c r="N275" s="1"/>
       <c r="O275" s="1"/>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A276" s="6"/>
-      <c r="B276" s="6"/>
-      <c r="C276" s="7"/>
-      <c r="D276" s="7"/>
-      <c r="E276" s="1"/>
-      <c r="F276" s="5"/>
-      <c r="G276" s="5"/>
-      <c r="H276" s="1"/>
-      <c r="I276" s="1"/>
+    <row r="276" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A276" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B276" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C276" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D276" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E276" s="1">
+        <v>1</v>
+      </c>
+      <c r="F276" s="5">
+        <v>11</v>
+      </c>
+      <c r="G276" s="5">
+        <v>7</v>
+      </c>
+      <c r="H276" s="1">
+        <v>11</v>
+      </c>
+      <c r="I276" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="J276" s="1"/>
-      <c r="K276" s="9"/>
+      <c r="K276" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L276" s="1"/>
       <c r="M276" s="1"/>
       <c r="N276" s="1"/>
       <c r="O276" s="1"/>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A277" s="6"/>
-      <c r="B277" s="6"/>
-      <c r="C277" s="7"/>
-      <c r="D277" s="7"/>
-      <c r="E277" s="1"/>
-      <c r="F277" s="5"/>
-      <c r="G277" s="5"/>
-      <c r="H277" s="1"/>
-      <c r="I277" s="1"/>
+    <row r="277" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A277" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B277" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C277" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D277" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E277" s="1">
+        <v>1</v>
+      </c>
+      <c r="F277" s="5">
+        <v>11</v>
+      </c>
+      <c r="G277" s="5">
+        <v>5</v>
+      </c>
+      <c r="H277" s="1">
+        <v>11</v>
+      </c>
+      <c r="I277" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="J277" s="1"/>
-      <c r="K277" s="9"/>
+      <c r="K277" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L277" s="1"/>
       <c r="M277" s="1"/>
       <c r="N277" s="1"/>
       <c r="O277" s="1"/>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A278" s="6"/>
-      <c r="B278" s="6"/>
-      <c r="C278" s="7"/>
-      <c r="D278" s="7"/>
-      <c r="E278" s="1"/>
-      <c r="F278" s="5"/>
-      <c r="G278" s="5"/>
-      <c r="H278" s="1"/>
-      <c r="I278" s="1"/>
+    <row r="278" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A278" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B278" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C278" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D278" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E278" s="1">
+        <v>1</v>
+      </c>
+      <c r="F278" s="5">
+        <v>11</v>
+      </c>
+      <c r="G278" s="5">
+        <v>9</v>
+      </c>
+      <c r="H278" s="1">
+        <v>11</v>
+      </c>
+      <c r="I278" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="J278" s="1"/>
-      <c r="K278" s="9"/>
+      <c r="K278" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L278" s="1"/>
       <c r="M278" s="1"/>
       <c r="N278" s="1"/>
       <c r="O278" s="1"/>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A279" s="6"/>
-      <c r="B279" s="6"/>
-      <c r="C279" s="7"/>
-      <c r="D279" s="7"/>
-      <c r="E279" s="1"/>
-      <c r="F279" s="5"/>
-      <c r="G279" s="5"/>
-      <c r="H279" s="1"/>
-      <c r="I279" s="1"/>
+    <row r="279" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A279" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B279" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C279" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D279" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E279" s="1">
+        <v>1</v>
+      </c>
+      <c r="F279" s="5">
+        <v>11</v>
+      </c>
+      <c r="G279" s="5">
+        <v>5</v>
+      </c>
+      <c r="H279" s="1">
+        <v>11</v>
+      </c>
+      <c r="I279" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="J279" s="1"/>
-      <c r="K279" s="9"/>
+      <c r="K279" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L279" s="1"/>
       <c r="M279" s="1"/>
       <c r="N279" s="1"/>
       <c r="O279" s="1"/>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A280" s="6"/>
-      <c r="B280" s="6"/>
-      <c r="C280" s="7"/>
-      <c r="D280" s="7"/>
-      <c r="E280" s="1"/>
-      <c r="F280" s="5"/>
-      <c r="G280" s="5"/>
-      <c r="H280" s="1"/>
-      <c r="I280" s="1"/>
+    <row r="280" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A280" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B280" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C280" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D280" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E280" s="1">
+        <v>1</v>
+      </c>
+      <c r="F280" s="5">
+        <v>11</v>
+      </c>
+      <c r="G280" s="5">
+        <v>3</v>
+      </c>
+      <c r="H280" s="1">
+        <v>11</v>
+      </c>
+      <c r="I280" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="J280" s="1"/>
-      <c r="K280" s="9"/>
+      <c r="K280" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L280" s="1"/>
       <c r="M280" s="1"/>
       <c r="N280" s="1"/>
       <c r="O280" s="1"/>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A281" s="6"/>
-      <c r="B281" s="6"/>
-      <c r="C281" s="7"/>
-      <c r="D281" s="7"/>
-      <c r="E281" s="1"/>
-      <c r="F281" s="5"/>
-      <c r="G281" s="5"/>
-      <c r="H281" s="1"/>
-      <c r="I281" s="1"/>
+    <row r="281" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A281" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B281" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C281" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D281" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E281" s="1">
+        <v>1</v>
+      </c>
+      <c r="F281" s="5">
+        <v>11</v>
+      </c>
+      <c r="G281" s="5">
+        <v>9</v>
+      </c>
+      <c r="H281" s="1">
+        <v>11</v>
+      </c>
+      <c r="I281" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="J281" s="1"/>
-      <c r="K281" s="9"/>
+      <c r="K281" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L281" s="1"/>
       <c r="M281" s="1"/>
       <c r="N281" s="1"/>
       <c r="O281" s="1"/>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A282" s="6"/>
-      <c r="B282" s="6"/>
-      <c r="C282" s="7"/>
-      <c r="D282" s="7"/>
-      <c r="E282" s="1"/>
-      <c r="F282" s="5"/>
-      <c r="G282" s="5"/>
-      <c r="H282" s="1"/>
-      <c r="I282" s="1"/>
+    <row r="282" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A282" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C282" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D282" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E282" s="1">
+        <v>1</v>
+      </c>
+      <c r="F282" s="5">
+        <v>11</v>
+      </c>
+      <c r="G282" s="5">
+        <v>8</v>
+      </c>
+      <c r="H282" s="1">
+        <v>11</v>
+      </c>
+      <c r="I282" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="J282" s="1"/>
-      <c r="K282" s="9"/>
+      <c r="K282" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L282" s="1"/>
       <c r="M282" s="1"/>
       <c r="N282" s="1"/>
       <c r="O282" s="1"/>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A283" s="6"/>
-      <c r="B283" s="6"/>
-      <c r="C283" s="7"/>
-      <c r="D283" s="7"/>
-      <c r="E283" s="1"/>
-      <c r="F283" s="5"/>
-      <c r="G283" s="5"/>
-      <c r="H283" s="1"/>
-      <c r="I283" s="1"/>
+    <row r="283" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A283" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C283" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D283" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E283" s="1">
+        <v>1</v>
+      </c>
+      <c r="F283" s="5">
+        <v>11</v>
+      </c>
+      <c r="G283" s="5">
+        <v>8</v>
+      </c>
+      <c r="H283" s="1">
+        <v>11</v>
+      </c>
+      <c r="I283" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="J283" s="1"/>
-      <c r="K283" s="9"/>
+      <c r="K283" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L283" s="1"/>
       <c r="M283" s="1"/>
       <c r="N283" s="1"/>
       <c r="O283" s="1"/>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A284" s="6"/>
-      <c r="B284" s="6"/>
-      <c r="C284" s="7"/>
-      <c r="D284" s="7"/>
-      <c r="E284" s="1"/>
-      <c r="F284" s="5"/>
-      <c r="G284" s="5"/>
-      <c r="H284" s="1"/>
-      <c r="I284" s="1"/>
+    <row r="284" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A284" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C284" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D284" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E284" s="1">
+        <v>1</v>
+      </c>
+      <c r="F284" s="5">
+        <v>11</v>
+      </c>
+      <c r="G284" s="5">
+        <v>7</v>
+      </c>
+      <c r="H284" s="1">
+        <v>11</v>
+      </c>
+      <c r="I284" s="1" t="s">
+        <v>76</v>
+      </c>
       <c r="J284" s="1"/>
-      <c r="K284" s="9"/>
+      <c r="K284" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
       <c r="L284" s="1"/>
       <c r="M284" s="1"/>
       <c r="N284" s="1"/>
       <c r="O284" s="1"/>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A285" s="6"/>
       <c r="B285" s="6"/>
       <c r="C285" s="7"/>
@@ -11222,7 +11850,7 @@
       <c r="N285" s="1"/>
       <c r="O285" s="1"/>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A286" s="6"/>
       <c r="B286" s="6"/>
       <c r="C286" s="7"/>
@@ -11239,7 +11867,7 @@
       <c r="N286" s="1"/>
       <c r="O286" s="1"/>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A287" s="6"/>
       <c r="B287" s="6"/>
       <c r="C287" s="7"/>
@@ -11256,7 +11884,7 @@
       <c r="N287" s="1"/>
       <c r="O287" s="1"/>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A288" s="6"/>
       <c r="B288" s="6"/>
       <c r="C288" s="7"/>
@@ -11273,7 +11901,7 @@
       <c r="N288" s="1"/>
       <c r="O288" s="1"/>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A289" s="6"/>
       <c r="B289" s="6"/>
       <c r="C289" s="7"/>
@@ -11290,7 +11918,7 @@
       <c r="N289" s="1"/>
       <c r="O289" s="1"/>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A290" s="6"/>
       <c r="B290" s="6"/>
       <c r="C290" s="7"/>
@@ -11307,7 +11935,7 @@
       <c r="N290" s="1"/>
       <c r="O290" s="1"/>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A291" s="6"/>
       <c r="B291" s="6"/>
       <c r="C291" s="7"/>
@@ -11324,7 +11952,7 @@
       <c r="N291" s="1"/>
       <c r="O291" s="1"/>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A292" s="6"/>
       <c r="B292" s="6"/>
       <c r="C292" s="7"/>
@@ -11341,7 +11969,7 @@
       <c r="N292" s="1"/>
       <c r="O292" s="1"/>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A293" s="6"/>
       <c r="B293" s="6"/>
       <c r="C293" s="7"/>
@@ -11358,7 +11986,7 @@
       <c r="N293" s="1"/>
       <c r="O293" s="1"/>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A294" s="6"/>
       <c r="B294" s="6"/>
       <c r="C294" s="7"/>
@@ -11375,7 +12003,7 @@
       <c r="N294" s="1"/>
       <c r="O294" s="1"/>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A295" s="6"/>
       <c r="B295" s="6"/>
       <c r="C295" s="7"/>
@@ -11392,7 +12020,7 @@
       <c r="N295" s="1"/>
       <c r="O295" s="1"/>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A296" s="6"/>
       <c r="B296" s="6"/>
       <c r="C296" s="7"/>
@@ -11409,7 +12037,7 @@
       <c r="N296" s="1"/>
       <c r="O296" s="1"/>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A297" s="6"/>
       <c r="B297" s="6"/>
       <c r="C297" s="7"/>
@@ -11426,7 +12054,7 @@
       <c r="N297" s="1"/>
       <c r="O297" s="1"/>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A298" s="6"/>
       <c r="B298" s="6"/>
       <c r="C298" s="7"/>
@@ -11443,7 +12071,7 @@
       <c r="N298" s="1"/>
       <c r="O298" s="1"/>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A299" s="6"/>
       <c r="B299" s="6"/>
       <c r="C299" s="7"/>
@@ -11460,7 +12088,7 @@
       <c r="N299" s="1"/>
       <c r="O299" s="1"/>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A300" s="6"/>
       <c r="B300" s="6"/>
       <c r="C300" s="7"/>
@@ -11477,7 +12105,7 @@
       <c r="N300" s="1"/>
       <c r="O300" s="1"/>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A301" s="6"/>
       <c r="B301" s="6"/>
       <c r="C301" s="7"/>
@@ -11494,7 +12122,7 @@
       <c r="N301" s="1"/>
       <c r="O301" s="1"/>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A302" s="6"/>
       <c r="B302" s="6"/>
       <c r="C302" s="7"/>
@@ -11511,7 +12139,7 @@
       <c r="N302" s="1"/>
       <c r="O302" s="1"/>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A303" s="6"/>
       <c r="B303" s="6"/>
       <c r="C303" s="7"/>
@@ -11528,7 +12156,7 @@
       <c r="N303" s="1"/>
       <c r="O303" s="1"/>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A304" s="6"/>
       <c r="B304" s="6"/>
       <c r="C304" s="7"/>
@@ -11545,7 +12173,7 @@
       <c r="N304" s="1"/>
       <c r="O304" s="1"/>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A305" s="6"/>
       <c r="B305" s="6"/>
       <c r="C305" s="7"/>
@@ -11562,7 +12190,7 @@
       <c r="N305" s="1"/>
       <c r="O305" s="1"/>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A306" s="6"/>
       <c r="B306" s="6"/>
       <c r="C306" s="7"/>
@@ -11579,7 +12207,7 @@
       <c r="N306" s="1"/>
       <c r="O306" s="1"/>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A307" s="6"/>
       <c r="B307" s="6"/>
       <c r="C307" s="7"/>
@@ -11596,7 +12224,7 @@
       <c r="N307" s="1"/>
       <c r="O307" s="1"/>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A308" s="6"/>
       <c r="B308" s="6"/>
       <c r="C308" s="7"/>
@@ -11613,7 +12241,7 @@
       <c r="N308" s="1"/>
       <c r="O308" s="1"/>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A309" s="6"/>
       <c r="B309" s="6"/>
       <c r="C309" s="7"/>
@@ -11630,7 +12258,7 @@
       <c r="N309" s="1"/>
       <c r="O309" s="1"/>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A310" s="6"/>
       <c r="B310" s="6"/>
       <c r="C310" s="7"/>
@@ -11647,7 +12275,7 @@
       <c r="N310" s="1"/>
       <c r="O310" s="1"/>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A311" s="6"/>
       <c r="B311" s="6"/>
       <c r="C311" s="7"/>
@@ -11664,7 +12292,7 @@
       <c r="N311" s="1"/>
       <c r="O311" s="1"/>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A312" s="6"/>
       <c r="B312" s="6"/>
       <c r="C312" s="7"/>
@@ -11681,7 +12309,7 @@
       <c r="N312" s="1"/>
       <c r="O312" s="1"/>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A313" s="6"/>
       <c r="B313" s="6"/>
       <c r="C313" s="7"/>
@@ -11698,7 +12326,7 @@
       <c r="N313" s="1"/>
       <c r="O313" s="1"/>
     </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A314" s="6"/>
       <c r="B314" s="6"/>
       <c r="C314" s="7"/>
@@ -11715,7 +12343,7 @@
       <c r="N314" s="1"/>
       <c r="O314" s="1"/>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A315" s="6"/>
       <c r="B315" s="6"/>
       <c r="C315" s="7"/>
@@ -11732,7 +12360,7 @@
       <c r="N315" s="1"/>
       <c r="O315" s="1"/>
     </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A316" s="6"/>
       <c r="B316" s="6"/>
       <c r="C316" s="7"/>
@@ -11749,7 +12377,7 @@
       <c r="N316" s="1"/>
       <c r="O316" s="1"/>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A317" s="6"/>
       <c r="B317" s="6"/>
       <c r="C317" s="7"/>
@@ -11766,7 +12394,7 @@
       <c r="N317" s="1"/>
       <c r="O317" s="1"/>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A318" s="6"/>
       <c r="B318" s="6"/>
       <c r="C318" s="7"/>
@@ -11783,7 +12411,7 @@
       <c r="N318" s="1"/>
       <c r="O318" s="1"/>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A319" s="6"/>
       <c r="B319" s="6"/>
       <c r="C319" s="7"/>
@@ -11800,7 +12428,7 @@
       <c r="N319" s="1"/>
       <c r="O319" s="1"/>
     </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A320" s="6"/>
       <c r="B320" s="6"/>
       <c r="C320" s="7"/>
@@ -11817,7 +12445,7 @@
       <c r="N320" s="1"/>
       <c r="O320" s="1"/>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A321" s="6"/>
       <c r="B321" s="6"/>
       <c r="C321" s="7"/>
@@ -11834,7 +12462,7 @@
       <c r="N321" s="1"/>
       <c r="O321" s="1"/>
     </row>
-    <row r="322" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A322" s="6"/>
       <c r="B322" s="6"/>
       <c r="C322" s="7"/>
@@ -11851,7 +12479,7 @@
       <c r="N322" s="1"/>
       <c r="O322" s="1"/>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A323" s="6"/>
       <c r="B323" s="6"/>
       <c r="C323" s="7"/>
@@ -11868,7 +12496,7 @@
       <c r="N323" s="1"/>
       <c r="O323" s="1"/>
     </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A324" s="6"/>
       <c r="B324" s="6"/>
       <c r="C324" s="7"/>
@@ -11885,7 +12513,7 @@
       <c r="N324" s="1"/>
       <c r="O324" s="1"/>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A325" s="6"/>
       <c r="B325" s="6"/>
       <c r="C325" s="7"/>
@@ -11902,7 +12530,7 @@
       <c r="N325" s="1"/>
       <c r="O325" s="1"/>
     </row>
-    <row r="326" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A326" s="6"/>
       <c r="B326" s="6"/>
       <c r="C326" s="7"/>
@@ -11919,7 +12547,7 @@
       <c r="N326" s="1"/>
       <c r="O326" s="1"/>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A327" s="6"/>
       <c r="B327" s="6"/>
       <c r="C327" s="7"/>
@@ -11936,7 +12564,7 @@
       <c r="N327" s="1"/>
       <c r="O327" s="1"/>
     </row>
-    <row r="328" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A328" s="6"/>
       <c r="B328" s="6"/>
       <c r="C328" s="7"/>
@@ -11953,7 +12581,7 @@
       <c r="N328" s="1"/>
       <c r="O328" s="1"/>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A329" s="6"/>
       <c r="B329" s="6"/>
       <c r="C329" s="7"/>
@@ -11970,7 +12598,7 @@
       <c r="N329" s="1"/>
       <c r="O329" s="1"/>
     </row>
-    <row r="330" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A330" s="6"/>
       <c r="B330" s="6"/>
       <c r="C330" s="7"/>
@@ -11987,7 +12615,7 @@
       <c r="N330" s="1"/>
       <c r="O330" s="1"/>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A331" s="6"/>
       <c r="B331" s="6"/>
       <c r="C331" s="7"/>
@@ -12004,7 +12632,7 @@
       <c r="N331" s="1"/>
       <c r="O331" s="1"/>
     </row>
-    <row r="332" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A332" s="6"/>
       <c r="B332" s="6"/>
       <c r="C332" s="7"/>
@@ -12021,7 +12649,7 @@
       <c r="N332" s="1"/>
       <c r="O332" s="1"/>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A333" s="6"/>
       <c r="B333" s="6"/>
       <c r="C333" s="7"/>
@@ -12038,7 +12666,7 @@
       <c r="N333" s="1"/>
       <c r="O333" s="1"/>
     </row>
-    <row r="334" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A334" s="6"/>
       <c r="B334" s="6"/>
       <c r="C334" s="7"/>
@@ -12055,7 +12683,7 @@
       <c r="N334" s="1"/>
       <c r="O334" s="1"/>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A335" s="6"/>
       <c r="B335" s="6"/>
       <c r="C335" s="7"/>
@@ -12072,7 +12700,7 @@
       <c r="N335" s="1"/>
       <c r="O335" s="1"/>
     </row>
-    <row r="336" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A336" s="6"/>
       <c r="B336" s="6"/>
       <c r="C336" s="7"/>
@@ -12089,7 +12717,7 @@
       <c r="N336" s="1"/>
       <c r="O336" s="1"/>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A337" s="6"/>
       <c r="B337" s="6"/>
       <c r="C337" s="7"/>
@@ -12106,7 +12734,7 @@
       <c r="N337" s="1"/>
       <c r="O337" s="1"/>
     </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A338" s="6"/>
       <c r="B338" s="6"/>
       <c r="C338" s="7"/>
@@ -12123,7 +12751,7 @@
       <c r="N338" s="1"/>
       <c r="O338" s="1"/>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A339" s="6"/>
       <c r="B339" s="6"/>
       <c r="C339" s="7"/>
@@ -12140,7 +12768,7 @@
       <c r="N339" s="1"/>
       <c r="O339" s="1"/>
     </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A340" s="6"/>
       <c r="B340" s="6"/>
       <c r="C340" s="7"/>
@@ -12157,7 +12785,7 @@
       <c r="N340" s="1"/>
       <c r="O340" s="1"/>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A341" s="6"/>
       <c r="B341" s="6"/>
       <c r="C341" s="7"/>
@@ -12174,7 +12802,7 @@
       <c r="N341" s="1"/>
       <c r="O341" s="1"/>
     </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A342" s="6"/>
       <c r="B342" s="6"/>
       <c r="C342" s="7"/>
@@ -12191,7 +12819,7 @@
       <c r="N342" s="1"/>
       <c r="O342" s="1"/>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A343" s="6"/>
       <c r="B343" s="6"/>
       <c r="C343" s="7"/>
@@ -12208,7 +12836,7 @@
       <c r="N343" s="1"/>
       <c r="O343" s="1"/>
     </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A344" s="6"/>
       <c r="B344" s="6"/>
       <c r="C344" s="7"/>
@@ -12225,7 +12853,7 @@
       <c r="N344" s="1"/>
       <c r="O344" s="1"/>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A345" s="6"/>
       <c r="B345" s="6"/>
       <c r="C345" s="7"/>
@@ -12242,7 +12870,7 @@
       <c r="N345" s="1"/>
       <c r="O345" s="1"/>
     </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A346" s="6"/>
       <c r="B346" s="6"/>
       <c r="C346" s="7"/>
@@ -12259,7 +12887,7 @@
       <c r="N346" s="1"/>
       <c r="O346" s="1"/>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A347" s="6"/>
       <c r="B347" s="6"/>
       <c r="C347" s="7"/>
@@ -12276,7 +12904,7 @@
       <c r="N347" s="1"/>
       <c r="O347" s="1"/>
     </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A348" s="6"/>
       <c r="B348" s="6"/>
       <c r="C348" s="7"/>
@@ -12293,7 +12921,7 @@
       <c r="N348" s="1"/>
       <c r="O348" s="1"/>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A349" s="6"/>
       <c r="B349" s="6"/>
       <c r="C349" s="7"/>
@@ -12310,7 +12938,7 @@
       <c r="N349" s="1"/>
       <c r="O349" s="1"/>
     </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A350" s="6"/>
       <c r="B350" s="6"/>
       <c r="C350" s="7"/>
@@ -12327,7 +12955,7 @@
       <c r="N350" s="1"/>
       <c r="O350" s="1"/>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A351" s="6"/>
       <c r="B351" s="6"/>
       <c r="C351" s="7"/>
@@ -12344,7 +12972,7 @@
       <c r="N351" s="1"/>
       <c r="O351" s="1"/>
     </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A352" s="6"/>
       <c r="B352" s="6"/>
       <c r="C352" s="7"/>
@@ -12361,7 +12989,7 @@
       <c r="N352" s="1"/>
       <c r="O352" s="1"/>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A353" s="6"/>
       <c r="B353" s="6"/>
       <c r="C353" s="7"/>
@@ -12378,7 +13006,7 @@
       <c r="N353" s="1"/>
       <c r="O353" s="1"/>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A354" s="6"/>
       <c r="B354" s="6"/>
       <c r="C354" s="7"/>
@@ -12395,7 +13023,7 @@
       <c r="N354" s="1"/>
       <c r="O354" s="1"/>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A355" s="6"/>
       <c r="B355" s="6"/>
       <c r="C355" s="7"/>
@@ -12412,7 +13040,7 @@
       <c r="N355" s="1"/>
       <c r="O355" s="1"/>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A356" s="6"/>
       <c r="B356" s="6"/>
       <c r="C356" s="7"/>
@@ -12429,7 +13057,7 @@
       <c r="N356" s="1"/>
       <c r="O356" s="1"/>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A357" s="6"/>
       <c r="B357" s="6"/>
       <c r="C357" s="7"/>
@@ -12446,7 +13074,7 @@
       <c r="N357" s="1"/>
       <c r="O357" s="1"/>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A358" s="6"/>
       <c r="B358" s="6"/>
       <c r="C358" s="7"/>
@@ -12463,7 +13091,7 @@
       <c r="N358" s="1"/>
       <c r="O358" s="1"/>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A359" s="6"/>
       <c r="B359" s="6"/>
       <c r="C359" s="7"/>
@@ -12480,7 +13108,7 @@
       <c r="N359" s="1"/>
       <c r="O359" s="1"/>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A360" s="6"/>
       <c r="B360" s="6"/>
       <c r="C360" s="7"/>
@@ -12497,7 +13125,7 @@
       <c r="N360" s="1"/>
       <c r="O360" s="1"/>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A361" s="6"/>
       <c r="B361" s="6"/>
       <c r="C361" s="7"/>
@@ -12514,7 +13142,7 @@
       <c r="N361" s="1"/>
       <c r="O361" s="1"/>
     </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A362" s="6"/>
       <c r="B362" s="6"/>
       <c r="C362" s="7"/>
@@ -12531,7 +13159,7 @@
       <c r="N362" s="1"/>
       <c r="O362" s="1"/>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A363" s="6"/>
       <c r="B363" s="6"/>
       <c r="C363" s="7"/>
@@ -12548,7 +13176,7 @@
       <c r="N363" s="1"/>
       <c r="O363" s="1"/>
     </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A364" s="6"/>
       <c r="B364" s="6"/>
       <c r="C364" s="7"/>
@@ -12565,7 +13193,7 @@
       <c r="N364" s="1"/>
       <c r="O364" s="1"/>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A365" s="6"/>
       <c r="B365" s="6"/>
       <c r="C365" s="7"/>
@@ -12582,7 +13210,7 @@
       <c r="N365" s="1"/>
       <c r="O365" s="1"/>
     </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A366" s="6"/>
       <c r="B366" s="6"/>
       <c r="C366" s="7"/>
@@ -12599,7 +13227,7 @@
       <c r="N366" s="1"/>
       <c r="O366" s="1"/>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A367" s="6"/>
       <c r="B367" s="6"/>
       <c r="C367" s="7"/>
@@ -12616,7 +13244,7 @@
       <c r="N367" s="1"/>
       <c r="O367" s="1"/>
     </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A368" s="6"/>
       <c r="B368" s="6"/>
       <c r="C368" s="7"/>
@@ -12633,7 +13261,7 @@
       <c r="N368" s="1"/>
       <c r="O368" s="1"/>
     </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A369" s="6"/>
       <c r="B369" s="6"/>
       <c r="C369" s="7"/>
@@ -12650,7 +13278,7 @@
       <c r="N369" s="1"/>
       <c r="O369" s="1"/>
     </row>
-    <row r="370" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A370" s="6"/>
       <c r="B370" s="6"/>
       <c r="C370" s="7"/>
@@ -12667,7 +13295,7 @@
       <c r="N370" s="1"/>
       <c r="O370" s="1"/>
     </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A371" s="6"/>
       <c r="B371" s="6"/>
       <c r="C371" s="7"/>
@@ -12684,7 +13312,7 @@
       <c r="N371" s="1"/>
       <c r="O371" s="1"/>
     </row>
-    <row r="372" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A372" s="6"/>
       <c r="B372" s="6"/>
       <c r="C372" s="7"/>
@@ -12701,7 +13329,7 @@
       <c r="N372" s="1"/>
       <c r="O372" s="1"/>
     </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A373" s="6"/>
       <c r="B373" s="6"/>
       <c r="C373" s="7"/>
@@ -12718,7 +13346,7 @@
       <c r="N373" s="1"/>
       <c r="O373" s="1"/>
     </row>
-    <row r="374" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A374" s="6"/>
       <c r="B374" s="6"/>
       <c r="C374" s="7"/>
@@ -12735,7 +13363,7 @@
       <c r="N374" s="1"/>
       <c r="O374" s="1"/>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A375" s="6"/>
       <c r="B375" s="6"/>
       <c r="C375" s="7"/>
@@ -12752,7 +13380,7 @@
       <c r="N375" s="1"/>
       <c r="O375" s="1"/>
     </row>
-    <row r="376" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A376" s="6"/>
       <c r="B376" s="6"/>
       <c r="C376" s="7"/>
@@ -12769,7 +13397,7 @@
       <c r="N376" s="1"/>
       <c r="O376" s="1"/>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A377" s="6"/>
       <c r="B377" s="6"/>
       <c r="C377" s="7"/>
@@ -12786,7 +13414,7 @@
       <c r="N377" s="1"/>
       <c r="O377" s="1"/>
     </row>
-    <row r="378" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A378" s="6"/>
       <c r="B378" s="6"/>
       <c r="C378" s="7"/>
@@ -12803,7 +13431,7 @@
       <c r="N378" s="1"/>
       <c r="O378" s="1"/>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A379" s="6"/>
       <c r="B379" s="6"/>
       <c r="C379" s="7"/>
@@ -12820,7 +13448,7 @@
       <c r="N379" s="1"/>
       <c r="O379" s="1"/>
     </row>
-    <row r="380" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A380" s="6"/>
       <c r="B380" s="6"/>
       <c r="C380" s="7"/>
@@ -12837,7 +13465,7 @@
       <c r="N380" s="1"/>
       <c r="O380" s="1"/>
     </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A381" s="6"/>
       <c r="B381" s="6"/>
       <c r="C381" s="7"/>
@@ -12854,7 +13482,7 @@
       <c r="N381" s="1"/>
       <c r="O381" s="1"/>
     </row>
-    <row r="382" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A382" s="6"/>
       <c r="B382" s="6"/>
       <c r="C382" s="7"/>
@@ -12871,7 +13499,7 @@
       <c r="N382" s="1"/>
       <c r="O382" s="1"/>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A383" s="6"/>
       <c r="B383" s="6"/>
       <c r="C383" s="7"/>
@@ -12888,7 +13516,7 @@
       <c r="N383" s="1"/>
       <c r="O383" s="1"/>
     </row>
-    <row r="384" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A384" s="6"/>
       <c r="B384" s="6"/>
       <c r="C384" s="7"/>
@@ -12905,7 +13533,7 @@
       <c r="N384" s="1"/>
       <c r="O384" s="1"/>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A385" s="6"/>
       <c r="B385" s="6"/>
       <c r="C385" s="7"/>
@@ -12922,7 +13550,7 @@
       <c r="N385" s="1"/>
       <c r="O385" s="1"/>
     </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A386" s="6"/>
       <c r="B386" s="6"/>
       <c r="C386" s="7"/>
@@ -12939,7 +13567,7 @@
       <c r="N386" s="1"/>
       <c r="O386" s="1"/>
     </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A387" s="6"/>
       <c r="B387" s="6"/>
       <c r="C387" s="7"/>
@@ -12956,7 +13584,7 @@
       <c r="N387" s="1"/>
       <c r="O387" s="1"/>
     </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A388" s="6"/>
       <c r="B388" s="6"/>
       <c r="C388" s="7"/>
@@ -12973,7 +13601,7 @@
       <c r="N388" s="1"/>
       <c r="O388" s="1"/>
     </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A389" s="6"/>
       <c r="B389" s="6"/>
       <c r="C389" s="7"/>
@@ -12990,7 +13618,7 @@
       <c r="N389" s="1"/>
       <c r="O389" s="1"/>
     </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A390" s="6"/>
       <c r="B390" s="6"/>
       <c r="C390" s="7"/>
@@ -13007,7 +13635,7 @@
       <c r="N390" s="1"/>
       <c r="O390" s="1"/>
     </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A391" s="6"/>
       <c r="B391" s="6"/>
       <c r="C391" s="7"/>
@@ -13024,7 +13652,7 @@
       <c r="N391" s="1"/>
       <c r="O391" s="1"/>
     </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A392" s="6"/>
       <c r="B392" s="6"/>
       <c r="C392" s="7"/>
@@ -13041,7 +13669,7 @@
       <c r="N392" s="1"/>
       <c r="O392" s="1"/>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A393" s="6"/>
       <c r="B393" s="6"/>
       <c r="C393" s="7"/>
@@ -13058,7 +13686,7 @@
       <c r="N393" s="1"/>
       <c r="O393" s="1"/>
     </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A394" s="6"/>
       <c r="B394" s="6"/>
       <c r="C394" s="7"/>
@@ -13075,7 +13703,7 @@
       <c r="N394" s="1"/>
       <c r="O394" s="1"/>
     </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A395" s="6"/>
       <c r="B395" s="6"/>
       <c r="C395" s="7"/>
@@ -13092,7 +13720,7 @@
       <c r="N395" s="1"/>
       <c r="O395" s="1"/>
     </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A396" s="6"/>
       <c r="B396" s="6"/>
       <c r="C396" s="7"/>
@@ -13109,7 +13737,7 @@
       <c r="N396" s="1"/>
       <c r="O396" s="1"/>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A397" s="6"/>
       <c r="B397" s="6"/>
       <c r="C397" s="7"/>
@@ -13126,7 +13754,7 @@
       <c r="N397" s="1"/>
       <c r="O397" s="1"/>
     </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A398" s="6"/>
       <c r="B398" s="6"/>
       <c r="C398" s="7"/>
@@ -13143,7 +13771,7 @@
       <c r="N398" s="1"/>
       <c r="O398" s="1"/>
     </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A399" s="6"/>
       <c r="B399" s="6"/>
       <c r="C399" s="7"/>
@@ -13160,7 +13788,7 @@
       <c r="N399" s="1"/>
       <c r="O399" s="1"/>
     </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A400" s="6"/>
       <c r="B400" s="6"/>
       <c r="C400" s="7"/>
@@ -13177,7 +13805,7 @@
       <c r="N400" s="1"/>
       <c r="O400" s="1"/>
     </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A401" s="6"/>
       <c r="B401" s="6"/>
       <c r="C401" s="7"/>
@@ -13194,7 +13822,7 @@
       <c r="N401" s="1"/>
       <c r="O401" s="1"/>
     </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A402" s="6"/>
       <c r="B402" s="6"/>
       <c r="C402" s="7"/>
@@ -13211,7 +13839,7 @@
       <c r="N402" s="1"/>
       <c r="O402" s="1"/>
     </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A403" s="6"/>
       <c r="B403" s="6"/>
       <c r="C403" s="7"/>
@@ -13228,7 +13856,7 @@
       <c r="N403" s="1"/>
       <c r="O403" s="1"/>
     </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A404" s="6"/>
       <c r="B404" s="6"/>
       <c r="C404" s="7"/>
@@ -13245,7 +13873,7 @@
       <c r="N404" s="1"/>
       <c r="O404" s="1"/>
     </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A405" s="6"/>
       <c r="B405" s="6"/>
       <c r="C405" s="7"/>
@@ -13262,7 +13890,7 @@
       <c r="N405" s="1"/>
       <c r="O405" s="1"/>
     </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A406" s="6"/>
       <c r="B406" s="6"/>
       <c r="C406" s="7"/>
@@ -13279,7 +13907,7 @@
       <c r="N406" s="1"/>
       <c r="O406" s="1"/>
     </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A407" s="6"/>
       <c r="B407" s="6"/>
       <c r="C407" s="7"/>
@@ -13296,7 +13924,7 @@
       <c r="N407" s="1"/>
       <c r="O407" s="1"/>
     </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A408" s="6"/>
       <c r="B408" s="6"/>
       <c r="C408" s="7"/>
@@ -13313,7 +13941,7 @@
       <c r="N408" s="1"/>
       <c r="O408" s="1"/>
     </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A409" s="6"/>
       <c r="B409" s="6"/>
       <c r="C409" s="7"/>
@@ -13330,7 +13958,7 @@
       <c r="N409" s="1"/>
       <c r="O409" s="1"/>
     </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A410" s="6"/>
       <c r="B410" s="6"/>
       <c r="C410" s="7"/>
@@ -13347,7 +13975,7 @@
       <c r="N410" s="1"/>
       <c r="O410" s="1"/>
     </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A411" s="6"/>
       <c r="B411" s="6"/>
       <c r="C411" s="7"/>
@@ -13364,7 +13992,7 @@
       <c r="N411" s="1"/>
       <c r="O411" s="1"/>
     </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A412" s="6"/>
       <c r="B412" s="6"/>
       <c r="C412" s="7"/>
@@ -13381,7 +14009,7 @@
       <c r="N412" s="1"/>
       <c r="O412" s="1"/>
     </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A413" s="6"/>
       <c r="B413" s="6"/>
       <c r="C413" s="7"/>
@@ -13398,7 +14026,7 @@
       <c r="N413" s="1"/>
       <c r="O413" s="1"/>
     </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A414" s="6"/>
       <c r="B414" s="6"/>
       <c r="C414" s="7"/>
@@ -13415,7 +14043,7 @@
       <c r="N414" s="1"/>
       <c r="O414" s="1"/>
     </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A415" s="6"/>
       <c r="B415" s="6"/>
       <c r="C415" s="7"/>
@@ -13432,7 +14060,7 @@
       <c r="N415" s="1"/>
       <c r="O415" s="1"/>
     </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A416" s="6"/>
       <c r="B416" s="6"/>
       <c r="C416" s="7"/>
@@ -13449,7 +14077,7 @@
       <c r="N416" s="1"/>
       <c r="O416" s="1"/>
     </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A417" s="6"/>
       <c r="B417" s="6"/>
       <c r="C417" s="7"/>
@@ -13466,7 +14094,7 @@
       <c r="N417" s="1"/>
       <c r="O417" s="1"/>
     </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A418" s="6"/>
       <c r="B418" s="6"/>
       <c r="C418" s="7"/>
@@ -13483,7 +14111,7 @@
       <c r="N418" s="1"/>
       <c r="O418" s="1"/>
     </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A419" s="6"/>
       <c r="B419" s="6"/>
       <c r="C419" s="7"/>
@@ -13500,7 +14128,7 @@
       <c r="N419" s="1"/>
       <c r="O419" s="1"/>
     </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A420" s="6"/>
       <c r="B420" s="6"/>
       <c r="C420" s="7"/>
@@ -13517,7 +14145,7 @@
       <c r="N420" s="1"/>
       <c r="O420" s="1"/>
     </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A421" s="6"/>
       <c r="B421" s="6"/>
       <c r="C421" s="7"/>
@@ -13534,7 +14162,7 @@
       <c r="N421" s="1"/>
       <c r="O421" s="1"/>
     </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A422" s="6"/>
       <c r="B422" s="6"/>
       <c r="C422" s="7"/>
@@ -13551,7 +14179,7 @@
       <c r="N422" s="1"/>
       <c r="O422" s="1"/>
     </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A423" s="6"/>
       <c r="B423" s="6"/>
       <c r="C423" s="7"/>
@@ -13568,7 +14196,7 @@
       <c r="N423" s="1"/>
       <c r="O423" s="1"/>
     </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A424" s="6"/>
       <c r="B424" s="6"/>
       <c r="C424" s="7"/>
@@ -13585,7 +14213,7 @@
       <c r="N424" s="1"/>
       <c r="O424" s="1"/>
     </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A425" s="6"/>
       <c r="B425" s="6"/>
       <c r="C425" s="7"/>
@@ -13602,7 +14230,7 @@
       <c r="N425" s="1"/>
       <c r="O425" s="1"/>
     </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A426" s="6"/>
       <c r="B426" s="6"/>
       <c r="C426" s="7"/>
@@ -13619,7 +14247,7 @@
       <c r="N426" s="1"/>
       <c r="O426" s="1"/>
     </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A427" s="6"/>
       <c r="B427" s="6"/>
       <c r="C427" s="7"/>
@@ -13636,7 +14264,7 @@
       <c r="N427" s="1"/>
       <c r="O427" s="1"/>
     </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A428" s="6"/>
       <c r="B428" s="6"/>
       <c r="C428" s="7"/>
@@ -13653,7 +14281,7 @@
       <c r="N428" s="1"/>
       <c r="O428" s="1"/>
     </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A429" s="6"/>
       <c r="B429" s="6"/>
       <c r="C429" s="7"/>
@@ -13670,7 +14298,7 @@
       <c r="N429" s="1"/>
       <c r="O429" s="1"/>
     </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A430" s="6"/>
       <c r="B430" s="6"/>
       <c r="C430" s="7"/>
@@ -13687,7 +14315,7 @@
       <c r="N430" s="1"/>
       <c r="O430" s="1"/>
     </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A431" s="6"/>
       <c r="B431" s="6"/>
       <c r="C431" s="7"/>
@@ -13704,7 +14332,7 @@
       <c r="N431" s="1"/>
       <c r="O431" s="1"/>
     </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A432" s="6"/>
       <c r="B432" s="6"/>
       <c r="C432" s="7"/>
@@ -13721,7 +14349,7 @@
       <c r="N432" s="1"/>
       <c r="O432" s="1"/>
     </row>
-    <row r="433" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A433" s="6"/>
       <c r="B433" s="6"/>
       <c r="C433" s="7"/>
@@ -13738,7 +14366,7 @@
       <c r="N433" s="1"/>
       <c r="O433" s="1"/>
     </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A434" s="6"/>
       <c r="B434" s="6"/>
       <c r="C434" s="7"/>
@@ -13755,7 +14383,7 @@
       <c r="N434" s="1"/>
       <c r="O434" s="1"/>
     </row>
-    <row r="435" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A435" s="6"/>
       <c r="B435" s="6"/>
       <c r="C435" s="7"/>
@@ -13772,7 +14400,7 @@
       <c r="N435" s="1"/>
       <c r="O435" s="1"/>
     </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A436" s="6"/>
       <c r="B436" s="6"/>
       <c r="C436" s="7"/>
@@ -13789,7 +14417,7 @@
       <c r="N436" s="1"/>
       <c r="O436" s="1"/>
     </row>
-    <row r="437" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A437" s="6"/>
       <c r="B437" s="6"/>
       <c r="C437" s="7"/>
@@ -13806,7 +14434,7 @@
       <c r="N437" s="1"/>
       <c r="O437" s="1"/>
     </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A438" s="6"/>
       <c r="B438" s="6"/>
       <c r="C438" s="7"/>
@@ -13823,7 +14451,7 @@
       <c r="N438" s="1"/>
       <c r="O438" s="1"/>
     </row>
-    <row r="439" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A439" s="6"/>
       <c r="B439" s="6"/>
       <c r="C439" s="7"/>
@@ -13840,7 +14468,7 @@
       <c r="N439" s="1"/>
       <c r="O439" s="1"/>
     </row>
-    <row r="440" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A440" s="6"/>
       <c r="B440" s="6"/>
       <c r="C440" s="7"/>
@@ -13857,7 +14485,7 @@
       <c r="N440" s="1"/>
       <c r="O440" s="1"/>
     </row>
-    <row r="441" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A441" s="6"/>
       <c r="B441" s="6"/>
       <c r="C441" s="7"/>
@@ -13874,7 +14502,7 @@
       <c r="N441" s="1"/>
       <c r="O441" s="1"/>
     </row>
-    <row r="442" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A442" s="6"/>
       <c r="B442" s="6"/>
       <c r="C442" s="7"/>
@@ -13891,7 +14519,7 @@
       <c r="N442" s="1"/>
       <c r="O442" s="1"/>
     </row>
-    <row r="443" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A443" s="6"/>
       <c r="B443" s="6"/>
       <c r="C443" s="7"/>
@@ -13908,7 +14536,7 @@
       <c r="N443" s="1"/>
       <c r="O443" s="1"/>
     </row>
-    <row r="444" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A444" s="6"/>
       <c r="B444" s="6"/>
       <c r="C444" s="7"/>
@@ -13925,7 +14553,7 @@
       <c r="N444" s="1"/>
       <c r="O444" s="1"/>
     </row>
-    <row r="445" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A445" s="6"/>
       <c r="B445" s="6"/>
       <c r="C445" s="7"/>
@@ -13942,7 +14570,7 @@
       <c r="N445" s="1"/>
       <c r="O445" s="1"/>
     </row>
-    <row r="446" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A446" s="6"/>
       <c r="B446" s="6"/>
       <c r="C446" s="7"/>
@@ -13959,7 +14587,7 @@
       <c r="N446" s="1"/>
       <c r="O446" s="1"/>
     </row>
-    <row r="447" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A447" s="6"/>
       <c r="B447" s="6"/>
       <c r="C447" s="7"/>
@@ -13976,7 +14604,7 @@
       <c r="N447" s="1"/>
       <c r="O447" s="1"/>
     </row>
-    <row r="448" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A448" s="6"/>
       <c r="B448" s="6"/>
       <c r="C448" s="7"/>
@@ -13993,7 +14621,7 @@
       <c r="N448" s="1"/>
       <c r="O448" s="1"/>
     </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A449" s="6"/>
       <c r="B449" s="6"/>
       <c r="C449" s="7"/>
@@ -14010,7 +14638,7 @@
       <c r="N449" s="1"/>
       <c r="O449" s="1"/>
     </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A450" s="6"/>
       <c r="B450" s="6"/>
       <c r="C450" s="7"/>
@@ -14027,7 +14655,7 @@
       <c r="N450" s="1"/>
       <c r="O450" s="1"/>
     </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A451" s="6"/>
       <c r="B451" s="6"/>
       <c r="C451" s="7"/>
@@ -14044,7 +14672,7 @@
       <c r="N451" s="1"/>
       <c r="O451" s="1"/>
     </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A452" s="6"/>
       <c r="B452" s="6"/>
       <c r="C452" s="7"/>
@@ -14061,7 +14689,7 @@
       <c r="N452" s="1"/>
       <c r="O452" s="1"/>
     </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A453" s="6"/>
       <c r="B453" s="6"/>
       <c r="C453" s="7"/>
@@ -14078,7 +14706,7 @@
       <c r="N453" s="1"/>
       <c r="O453" s="1"/>
     </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A454" s="6"/>
       <c r="B454" s="6"/>
       <c r="C454" s="7"/>
@@ -14095,7 +14723,7 @@
       <c r="N454" s="1"/>
       <c r="O454" s="1"/>
     </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A455" s="6"/>
       <c r="B455" s="6"/>
       <c r="C455" s="7"/>
@@ -14112,7 +14740,7 @@
       <c r="N455" s="1"/>
       <c r="O455" s="1"/>
     </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A456" s="6"/>
       <c r="B456" s="6"/>
       <c r="C456" s="7"/>
@@ -14129,7 +14757,7 @@
       <c r="N456" s="1"/>
       <c r="O456" s="1"/>
     </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A457" s="6"/>
       <c r="B457" s="6"/>
       <c r="C457" s="7"/>
@@ -14146,7 +14774,7 @@
       <c r="N457" s="1"/>
       <c r="O457" s="1"/>
     </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A458" s="6"/>
       <c r="B458" s="6"/>
       <c r="C458" s="7"/>
@@ -14163,7 +14791,7 @@
       <c r="N458" s="1"/>
       <c r="O458" s="1"/>
     </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A459" s="6"/>
       <c r="B459" s="6"/>
       <c r="C459" s="7"/>
@@ -14180,7 +14808,7 @@
       <c r="N459" s="1"/>
       <c r="O459" s="1"/>
     </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A460" s="6"/>
       <c r="B460" s="6"/>
       <c r="C460" s="7"/>
@@ -14197,7 +14825,7 @@
       <c r="N460" s="1"/>
       <c r="O460" s="1"/>
     </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A461" s="6"/>
       <c r="B461" s="6"/>
       <c r="C461" s="7"/>
@@ -14214,7 +14842,7 @@
       <c r="N461" s="1"/>
       <c r="O461" s="1"/>
     </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A462" s="6"/>
       <c r="B462" s="6"/>
       <c r="C462" s="7"/>
@@ -14231,7 +14859,7 @@
       <c r="N462" s="1"/>
       <c r="O462" s="1"/>
     </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A463" s="6"/>
       <c r="B463" s="6"/>
       <c r="C463" s="7"/>
@@ -14248,7 +14876,7 @@
       <c r="N463" s="1"/>
       <c r="O463" s="1"/>
     </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A464" s="6"/>
       <c r="B464" s="6"/>
       <c r="C464" s="7"/>
@@ -14265,7 +14893,7 @@
       <c r="N464" s="1"/>
       <c r="O464" s="1"/>
     </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A465" s="6"/>
       <c r="B465" s="6"/>
       <c r="C465" s="7"/>
@@ -14282,7 +14910,7 @@
       <c r="N465" s="1"/>
       <c r="O465" s="1"/>
     </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A466" s="6"/>
       <c r="B466" s="6"/>
       <c r="C466" s="7"/>
@@ -14299,7 +14927,7 @@
       <c r="N466" s="1"/>
       <c r="O466" s="1"/>
     </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A467" s="6"/>
       <c r="B467" s="6"/>
       <c r="C467" s="7"/>
@@ -14316,7 +14944,7 @@
       <c r="N467" s="1"/>
       <c r="O467" s="1"/>
     </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A468" s="6"/>
       <c r="B468" s="6"/>
       <c r="C468" s="7"/>
@@ -14333,7 +14961,7 @@
       <c r="N468" s="1"/>
       <c r="O468" s="1"/>
     </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A469" s="6"/>
       <c r="B469" s="6"/>
       <c r="C469" s="7"/>
@@ -14350,7 +14978,7 @@
       <c r="N469" s="1"/>
       <c r="O469" s="1"/>
     </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A470" s="6"/>
       <c r="B470" s="6"/>
       <c r="C470" s="7"/>
@@ -14367,7 +14995,7 @@
       <c r="N470" s="1"/>
       <c r="O470" s="1"/>
     </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A471" s="6"/>
       <c r="B471" s="6"/>
       <c r="C471" s="7"/>
@@ -14384,7 +15012,7 @@
       <c r="N471" s="1"/>
       <c r="O471" s="1"/>
     </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A472" s="6"/>
       <c r="B472" s="6"/>
       <c r="C472" s="7"/>
@@ -14401,7 +15029,7 @@
       <c r="N472" s="1"/>
       <c r="O472" s="1"/>
     </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A473" s="6"/>
       <c r="B473" s="6"/>
       <c r="C473" s="7"/>
@@ -14418,7 +15046,7 @@
       <c r="N473" s="1"/>
       <c r="O473" s="1"/>
     </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A474" s="6"/>
       <c r="B474" s="6"/>
       <c r="C474" s="7"/>
@@ -14435,7 +15063,7 @@
       <c r="N474" s="1"/>
       <c r="O474" s="1"/>
     </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A475" s="6"/>
       <c r="B475" s="6"/>
       <c r="C475" s="7"/>
@@ -14452,7 +15080,7 @@
       <c r="N475" s="1"/>
       <c r="O475" s="1"/>
     </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A476" s="6"/>
       <c r="B476" s="6"/>
       <c r="C476" s="7"/>
@@ -14469,7 +15097,7 @@
       <c r="N476" s="1"/>
       <c r="O476" s="1"/>
     </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A477" s="6"/>
       <c r="B477" s="6"/>
       <c r="C477" s="7"/>
@@ -14486,7 +15114,7 @@
       <c r="N477" s="1"/>
       <c r="O477" s="1"/>
     </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A478" s="6"/>
       <c r="B478" s="6"/>
       <c r="C478" s="7"/>
@@ -14503,7 +15131,7 @@
       <c r="N478" s="1"/>
       <c r="O478" s="1"/>
     </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A479" s="6"/>
       <c r="B479" s="6"/>
       <c r="C479" s="7"/>
@@ -14520,7 +15148,7 @@
       <c r="N479" s="1"/>
       <c r="O479" s="1"/>
     </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A480" s="6"/>
       <c r="B480" s="6"/>
       <c r="C480" s="7"/>
@@ -14537,7 +15165,7 @@
       <c r="N480" s="1"/>
       <c r="O480" s="1"/>
     </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A481" s="6"/>
       <c r="B481" s="6"/>
       <c r="C481" s="7"/>
@@ -14554,7 +15182,7 @@
       <c r="N481" s="1"/>
       <c r="O481" s="1"/>
     </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A482" s="6"/>
       <c r="B482" s="6"/>
       <c r="C482" s="7"/>
@@ -14571,7 +15199,7 @@
       <c r="N482" s="1"/>
       <c r="O482" s="1"/>
     </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A483" s="6"/>
       <c r="B483" s="6"/>
       <c r="C483" s="7"/>
@@ -14588,7 +15216,7 @@
       <c r="N483" s="1"/>
       <c r="O483" s="1"/>
     </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A484" s="6"/>
       <c r="B484" s="6"/>
       <c r="C484" s="7"/>
@@ -14605,7 +15233,7 @@
       <c r="N484" s="1"/>
       <c r="O484" s="1"/>
     </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A485" s="6"/>
       <c r="B485" s="6"/>
       <c r="C485" s="7"/>
@@ -14622,7 +15250,7 @@
       <c r="N485" s="1"/>
       <c r="O485" s="1"/>
     </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A486" s="6"/>
       <c r="B486" s="6"/>
       <c r="C486" s="7"/>
@@ -14639,7 +15267,7 @@
       <c r="N486" s="1"/>
       <c r="O486" s="1"/>
     </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A487" s="6"/>
       <c r="B487" s="6"/>
       <c r="C487" s="7"/>
@@ -14656,7 +15284,7 @@
       <c r="N487" s="1"/>
       <c r="O487" s="1"/>
     </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A488" s="6"/>
       <c r="B488" s="6"/>
       <c r="C488" s="7"/>
@@ -14673,7 +15301,7 @@
       <c r="N488" s="1"/>
       <c r="O488" s="1"/>
     </row>
-    <row r="489" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A489" s="6"/>
       <c r="B489" s="6"/>
       <c r="C489" s="7"/>
@@ -14690,7 +15318,7 @@
       <c r="N489" s="1"/>
       <c r="O489" s="1"/>
     </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A490" s="6"/>
       <c r="B490" s="6"/>
       <c r="C490" s="7"/>
@@ -14707,7 +15335,7 @@
       <c r="N490" s="1"/>
       <c r="O490" s="1"/>
     </row>
-    <row r="491" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A491" s="6"/>
       <c r="B491" s="6"/>
       <c r="C491" s="7"/>
@@ -14724,7 +15352,7 @@
       <c r="N491" s="1"/>
       <c r="O491" s="1"/>
     </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A492" s="6"/>
       <c r="B492" s="6"/>
       <c r="C492" s="7"/>
@@ -14741,7 +15369,7 @@
       <c r="N492" s="1"/>
       <c r="O492" s="1"/>
     </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A493" s="6"/>
       <c r="B493" s="6"/>
       <c r="C493" s="7"/>
@@ -14758,7 +15386,7 @@
       <c r="N493" s="1"/>
       <c r="O493" s="1"/>
     </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A494" s="6"/>
       <c r="B494" s="6"/>
       <c r="C494" s="7"/>
@@ -14775,7 +15403,7 @@
       <c r="N494" s="1"/>
       <c r="O494" s="1"/>
     </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A495" s="6"/>
       <c r="B495" s="6"/>
       <c r="C495" s="7"/>
@@ -14792,7 +15420,7 @@
       <c r="N495" s="1"/>
       <c r="O495" s="1"/>
     </row>
-    <row r="496" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A496" s="6"/>
       <c r="B496" s="6"/>
       <c r="C496" s="7"/>
@@ -14809,7 +15437,7 @@
       <c r="N496" s="1"/>
       <c r="O496" s="1"/>
     </row>
-    <row r="497" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A497" s="6"/>
       <c r="B497" s="6"/>
       <c r="C497" s="7"/>
@@ -14826,7 +15454,7 @@
       <c r="N497" s="1"/>
       <c r="O497" s="1"/>
     </row>
-    <row r="498" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A498" s="6"/>
       <c r="B498" s="6"/>
       <c r="C498" s="7"/>
@@ -14843,7 +15471,7 @@
       <c r="N498" s="1"/>
       <c r="O498" s="1"/>
     </row>
-    <row r="499" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A499" s="6"/>
       <c r="B499" s="6"/>
       <c r="C499" s="7"/>
@@ -14860,7 +15488,7 @@
       <c r="N499" s="1"/>
       <c r="O499" s="1"/>
     </row>
-    <row r="500" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A500" s="6"/>
       <c r="B500" s="6"/>
       <c r="C500" s="7"/>
@@ -14877,7 +15505,7 @@
       <c r="N500" s="1"/>
       <c r="O500" s="1"/>
     </row>
-    <row r="501" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A501" s="6"/>
       <c r="B501" s="6"/>
       <c r="C501" s="7"/>
@@ -14894,7 +15522,7 @@
       <c r="N501" s="1"/>
       <c r="O501" s="1"/>
     </row>
-    <row r="502" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A502" s="6"/>
       <c r="B502" s="6"/>
       <c r="C502" s="7"/>
@@ -14911,7 +15539,7 @@
       <c r="N502" s="1"/>
       <c r="O502" s="1"/>
     </row>
-    <row r="503" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A503" s="6"/>
       <c r="B503" s="6"/>
       <c r="C503" s="7"/>
@@ -14928,7 +15556,7 @@
       <c r="N503" s="1"/>
       <c r="O503" s="1"/>
     </row>
-    <row r="504" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A504" s="6"/>
       <c r="B504" s="6"/>
       <c r="C504" s="7"/>
@@ -14945,7 +15573,7 @@
       <c r="N504" s="1"/>
       <c r="O504" s="1"/>
     </row>
-    <row r="505" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A505" s="6"/>
       <c r="B505" s="6"/>
       <c r="C505" s="7"/>
@@ -14962,7 +15590,7 @@
       <c r="N505" s="1"/>
       <c r="O505" s="1"/>
     </row>
-    <row r="506" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A506" s="6"/>
       <c r="B506" s="6"/>
       <c r="C506" s="7"/>
@@ -14979,7 +15607,7 @@
       <c r="N506" s="1"/>
       <c r="O506" s="1"/>
     </row>
-    <row r="507" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A507" s="6"/>
       <c r="B507" s="6"/>
       <c r="C507" s="7"/>
@@ -14996,7 +15624,7 @@
       <c r="N507" s="1"/>
       <c r="O507" s="1"/>
     </row>
-    <row r="508" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A508" s="6"/>
       <c r="B508" s="6"/>
       <c r="C508" s="7"/>
@@ -15013,7 +15641,7 @@
       <c r="N508" s="1"/>
       <c r="O508" s="1"/>
     </row>
-    <row r="509" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A509" s="6"/>
       <c r="B509" s="6"/>
       <c r="C509" s="7"/>
@@ -15030,7 +15658,7 @@
       <c r="N509" s="1"/>
       <c r="O509" s="1"/>
     </row>
-    <row r="510" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A510" s="6"/>
       <c r="B510" s="6"/>
       <c r="C510" s="7"/>
@@ -15047,7 +15675,7 @@
       <c r="N510" s="1"/>
       <c r="O510" s="1"/>
     </row>
-    <row r="511" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A511" s="6"/>
       <c r="B511" s="6"/>
       <c r="C511" s="7"/>
@@ -15064,7 +15692,7 @@
       <c r="N511" s="1"/>
       <c r="O511" s="1"/>
     </row>
-    <row r="512" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A512" s="6"/>
       <c r="B512" s="6"/>
       <c r="C512" s="7"/>
@@ -15081,7 +15709,7 @@
       <c r="N512" s="1"/>
       <c r="O512" s="1"/>
     </row>
-    <row r="513" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A513" s="6"/>
       <c r="B513" s="6"/>
       <c r="C513" s="7"/>
@@ -15098,7 +15726,7 @@
       <c r="N513" s="1"/>
       <c r="O513" s="1"/>
     </row>
-    <row r="514" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A514" s="6"/>
       <c r="B514" s="6"/>
       <c r="C514" s="7"/>
@@ -15115,7 +15743,7 @@
       <c r="N514" s="1"/>
       <c r="O514" s="1"/>
     </row>
-    <row r="515" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A515" s="6"/>
       <c r="B515" s="6"/>
       <c r="C515" s="7"/>
@@ -15132,7 +15760,7 @@
       <c r="N515" s="1"/>
       <c r="O515" s="1"/>
     </row>
-    <row r="516" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A516" s="6"/>
       <c r="B516" s="6"/>
       <c r="C516" s="7"/>
@@ -15149,7 +15777,7 @@
       <c r="N516" s="1"/>
       <c r="O516" s="1"/>
     </row>
-    <row r="517" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A517" s="6"/>
       <c r="B517" s="6"/>
       <c r="C517" s="7"/>
@@ -15166,7 +15794,7 @@
       <c r="N517" s="1"/>
       <c r="O517" s="1"/>
     </row>
-    <row r="518" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A518" s="6"/>
       <c r="B518" s="6"/>
       <c r="C518" s="7"/>
@@ -15183,7 +15811,7 @@
       <c r="N518" s="1"/>
       <c r="O518" s="1"/>
     </row>
-    <row r="519" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A519" s="6"/>
       <c r="B519" s="6"/>
       <c r="C519" s="7"/>
@@ -15200,7 +15828,7 @@
       <c r="N519" s="1"/>
       <c r="O519" s="1"/>
     </row>
-    <row r="520" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A520" s="6"/>
       <c r="B520" s="6"/>
       <c r="C520" s="7"/>
@@ -15217,7 +15845,7 @@
       <c r="N520" s="1"/>
       <c r="O520" s="1"/>
     </row>
-    <row r="521" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A521" s="6"/>
       <c r="B521" s="6"/>
       <c r="C521" s="7"/>
@@ -15234,7 +15862,7 @@
       <c r="N521" s="1"/>
       <c r="O521" s="1"/>
     </row>
-    <row r="522" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A522" s="6"/>
       <c r="B522" s="6"/>
       <c r="C522" s="7"/>
@@ -15251,7 +15879,7 @@
       <c r="N522" s="1"/>
       <c r="O522" s="1"/>
     </row>
-    <row r="523" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A523" s="6"/>
       <c r="B523" s="6"/>
       <c r="C523" s="7"/>
@@ -15268,7 +15896,7 @@
       <c r="N523" s="1"/>
       <c r="O523" s="1"/>
     </row>
-    <row r="524" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A524" s="6"/>
       <c r="B524" s="6"/>
       <c r="C524" s="7"/>
@@ -15285,7 +15913,7 @@
       <c r="N524" s="1"/>
       <c r="O524" s="1"/>
     </row>
-    <row r="525" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A525" s="6"/>
       <c r="B525" s="6"/>
       <c r="C525" s="7"/>
@@ -15302,7 +15930,7 @@
       <c r="N525" s="1"/>
       <c r="O525" s="1"/>
     </row>
-    <row r="526" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A526" s="6"/>
       <c r="B526" s="6"/>
       <c r="C526" s="7"/>
@@ -15319,7 +15947,7 @@
       <c r="N526" s="1"/>
       <c r="O526" s="1"/>
     </row>
-    <row r="527" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A527" s="6"/>
       <c r="B527" s="6"/>
       <c r="C527" s="7"/>
@@ -15336,7 +15964,7 @@
       <c r="N527" s="1"/>
       <c r="O527" s="1"/>
     </row>
-    <row r="528" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A528" s="6"/>
       <c r="B528" s="6"/>
       <c r="C528" s="7"/>
@@ -15353,7 +15981,7 @@
       <c r="N528" s="1"/>
       <c r="O528" s="1"/>
     </row>
-    <row r="529" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A529" s="6"/>
       <c r="B529" s="6"/>
       <c r="C529" s="7"/>
@@ -15370,7 +15998,7 @@
       <c r="N529" s="1"/>
       <c r="O529" s="1"/>
     </row>
-    <row r="530" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A530" s="6"/>
       <c r="B530" s="6"/>
       <c r="C530" s="7"/>
@@ -15387,7 +16015,7 @@
       <c r="N530" s="1"/>
       <c r="O530" s="1"/>
     </row>
-    <row r="531" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A531" s="6"/>
       <c r="B531" s="6"/>
       <c r="C531" s="7"/>
@@ -15404,7 +16032,7 @@
       <c r="N531" s="1"/>
       <c r="O531" s="1"/>
     </row>
-    <row r="532" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A532" s="6"/>
       <c r="B532" s="6"/>
       <c r="C532" s="7"/>
@@ -15421,7 +16049,7 @@
       <c r="N532" s="1"/>
       <c r="O532" s="1"/>
     </row>
-    <row r="533" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A533" s="6"/>
       <c r="B533" s="6"/>
       <c r="C533" s="7"/>
@@ -15438,7 +16066,7 @@
       <c r="N533" s="1"/>
       <c r="O533" s="1"/>
     </row>
-    <row r="534" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A534" s="6"/>
       <c r="B534" s="6"/>
       <c r="C534" s="7"/>
@@ -15455,7 +16083,7 @@
       <c r="N534" s="1"/>
       <c r="O534" s="1"/>
     </row>
-    <row r="535" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A535" s="6"/>
       <c r="B535" s="6"/>
       <c r="C535" s="7"/>
@@ -15472,7 +16100,7 @@
       <c r="N535" s="1"/>
       <c r="O535" s="1"/>
     </row>
-    <row r="536" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A536" s="6"/>
       <c r="B536" s="6"/>
       <c r="C536" s="7"/>
@@ -15489,7 +16117,7 @@
       <c r="N536" s="1"/>
       <c r="O536" s="1"/>
     </row>
-    <row r="537" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A537" s="6"/>
       <c r="B537" s="6"/>
       <c r="C537" s="7"/>
@@ -15506,7 +16134,7 @@
       <c r="N537" s="1"/>
       <c r="O537" s="1"/>
     </row>
-    <row r="538" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A538" s="6"/>
       <c r="B538" s="6"/>
       <c r="C538" s="7"/>
@@ -15523,7 +16151,7 @@
       <c r="N538" s="1"/>
       <c r="O538" s="1"/>
     </row>
-    <row r="539" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A539" s="6"/>
       <c r="B539" s="6"/>
       <c r="C539" s="7"/>
@@ -15540,7 +16168,7 @@
       <c r="N539" s="1"/>
       <c r="O539" s="1"/>
     </row>
-    <row r="540" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A540" s="6"/>
       <c r="B540" s="6"/>
       <c r="C540" s="7"/>
@@ -15557,7 +16185,7 @@
       <c r="N540" s="1"/>
       <c r="O540" s="1"/>
     </row>
-    <row r="541" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A541" s="6"/>
       <c r="B541" s="6"/>
       <c r="C541" s="7"/>
@@ -15574,7 +16202,7 @@
       <c r="N541" s="1"/>
       <c r="O541" s="1"/>
     </row>
-    <row r="542" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A542" s="6"/>
       <c r="B542" s="6"/>
       <c r="C542" s="7"/>
@@ -15591,7 +16219,7 @@
       <c r="N542" s="1"/>
       <c r="O542" s="1"/>
     </row>
-    <row r="543" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A543" s="6"/>
       <c r="B543" s="6"/>
       <c r="C543" s="7"/>
@@ -15608,7 +16236,7 @@
       <c r="N543" s="1"/>
       <c r="O543" s="1"/>
     </row>
-    <row r="544" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A544" s="6"/>
       <c r="B544" s="6"/>
       <c r="C544" s="7"/>
@@ -15625,7 +16253,7 @@
       <c r="N544" s="1"/>
       <c r="O544" s="1"/>
     </row>
-    <row r="545" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A545" s="6"/>
       <c r="B545" s="6"/>
       <c r="C545" s="7"/>
@@ -15642,7 +16270,7 @@
       <c r="N545" s="1"/>
       <c r="O545" s="1"/>
     </row>
-    <row r="546" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A546" s="6"/>
       <c r="B546" s="6"/>
       <c r="C546" s="7"/>
@@ -15659,7 +16287,7 @@
       <c r="N546" s="1"/>
       <c r="O546" s="1"/>
     </row>
-    <row r="547" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A547" s="6"/>
       <c r="B547" s="6"/>
       <c r="C547" s="7"/>
@@ -15676,7 +16304,7 @@
       <c r="N547" s="1"/>
       <c r="O547" s="1"/>
     </row>
-    <row r="548" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A548" s="6"/>
       <c r="B548" s="6"/>
       <c r="C548" s="7"/>
@@ -15693,7 +16321,7 @@
       <c r="N548" s="1"/>
       <c r="O548" s="1"/>
     </row>
-    <row r="549" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A549" s="6"/>
       <c r="B549" s="6"/>
       <c r="C549" s="7"/>
@@ -15710,7 +16338,7 @@
       <c r="N549" s="1"/>
       <c r="O549" s="1"/>
     </row>
-    <row r="550" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A550" s="6"/>
       <c r="B550" s="6"/>
       <c r="C550" s="7"/>
@@ -15727,7 +16355,7 @@
       <c r="N550" s="1"/>
       <c r="O550" s="1"/>
     </row>
-    <row r="551" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A551" s="6"/>
       <c r="B551" s="6"/>
       <c r="C551" s="7"/>
@@ -15744,7 +16372,7 @@
       <c r="N551" s="1"/>
       <c r="O551" s="1"/>
     </row>
-    <row r="552" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A552" s="6"/>
       <c r="B552" s="6"/>
       <c r="C552" s="7"/>
@@ -15761,7 +16389,7 @@
       <c r="N552" s="1"/>
       <c r="O552" s="1"/>
     </row>
-    <row r="553" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A553" s="6"/>
       <c r="B553" s="6"/>
       <c r="C553" s="7"/>
@@ -15778,7 +16406,7 @@
       <c r="N553" s="1"/>
       <c r="O553" s="1"/>
     </row>
-    <row r="554" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A554" s="6"/>
       <c r="B554" s="6"/>
       <c r="C554" s="7"/>
@@ -15795,7 +16423,7 @@
       <c r="N554" s="1"/>
       <c r="O554" s="1"/>
     </row>
-    <row r="555" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A555" s="6"/>
       <c r="B555" s="6"/>
       <c r="C555" s="7"/>
@@ -15812,7 +16440,7 @@
       <c r="N555" s="1"/>
       <c r="O555" s="1"/>
     </row>
-    <row r="556" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A556" s="6"/>
       <c r="B556" s="6"/>
       <c r="C556" s="7"/>
@@ -15829,7 +16457,7 @@
       <c r="N556" s="1"/>
       <c r="O556" s="1"/>
     </row>
-    <row r="557" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A557" s="6"/>
       <c r="B557" s="6"/>
       <c r="C557" s="7"/>
@@ -15846,7 +16474,7 @@
       <c r="N557" s="1"/>
       <c r="O557" s="1"/>
     </row>
-    <row r="558" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A558" s="6"/>
       <c r="B558" s="6"/>
       <c r="C558" s="7"/>
@@ -15863,7 +16491,7 @@
       <c r="N558" s="1"/>
       <c r="O558" s="1"/>
     </row>
-    <row r="559" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A559" s="6"/>
       <c r="B559" s="6"/>
       <c r="C559" s="7"/>
@@ -15880,7 +16508,7 @@
       <c r="N559" s="1"/>
       <c r="O559" s="1"/>
     </row>
-    <row r="560" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A560" s="6"/>
       <c r="B560" s="6"/>
       <c r="C560" s="7"/>
@@ -15897,7 +16525,7 @@
       <c r="N560" s="1"/>
       <c r="O560" s="1"/>
     </row>
-    <row r="561" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A561" s="6"/>
       <c r="B561" s="6"/>
       <c r="C561" s="7"/>
@@ -15914,7 +16542,7 @@
       <c r="N561" s="1"/>
       <c r="O561" s="1"/>
     </row>
-    <row r="562" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A562" s="6"/>
       <c r="B562" s="6"/>
       <c r="C562" s="7"/>
@@ -15931,7 +16559,7 @@
       <c r="N562" s="1"/>
       <c r="O562" s="1"/>
     </row>
-    <row r="563" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A563" s="6"/>
       <c r="B563" s="6"/>
       <c r="C563" s="7"/>
@@ -15948,7 +16576,7 @@
       <c r="N563" s="1"/>
       <c r="O563" s="1"/>
     </row>
-    <row r="564" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A564" s="6"/>
       <c r="B564" s="6"/>
       <c r="C564" s="7"/>
@@ -15965,7 +16593,7 @@
       <c r="N564" s="1"/>
       <c r="O564" s="1"/>
     </row>
-    <row r="565" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A565" s="6"/>
       <c r="B565" s="6"/>
       <c r="C565" s="7"/>
@@ -15982,7 +16610,7 @@
       <c r="N565" s="1"/>
       <c r="O565" s="1"/>
     </row>
-    <row r="566" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A566" s="6"/>
       <c r="B566" s="6"/>
       <c r="C566" s="7"/>
@@ -15999,7 +16627,7 @@
       <c r="N566" s="1"/>
       <c r="O566" s="1"/>
     </row>
-    <row r="567" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A567" s="6"/>
       <c r="B567" s="6"/>
       <c r="C567" s="7"/>
@@ -16016,7 +16644,7 @@
       <c r="N567" s="1"/>
       <c r="O567" s="1"/>
     </row>
-    <row r="568" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A568" s="6"/>
       <c r="B568" s="6"/>
       <c r="C568" s="7"/>
@@ -16033,7 +16661,7 @@
       <c r="N568" s="1"/>
       <c r="O568" s="1"/>
     </row>
-    <row r="569" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A569" s="6"/>
       <c r="B569" s="6"/>
       <c r="C569" s="7"/>
@@ -16050,7 +16678,7 @@
       <c r="N569" s="1"/>
       <c r="O569" s="1"/>
     </row>
-    <row r="570" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A570" s="6"/>
       <c r="B570" s="6"/>
       <c r="C570" s="7"/>
@@ -16067,7 +16695,7 @@
       <c r="N570" s="1"/>
       <c r="O570" s="1"/>
     </row>
-    <row r="571" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A571" s="6"/>
       <c r="B571" s="6"/>
       <c r="C571" s="7"/>
@@ -16084,7 +16712,7 @@
       <c r="N571" s="1"/>
       <c r="O571" s="1"/>
     </row>
-    <row r="572" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A572" s="6"/>
       <c r="B572" s="6"/>
       <c r="C572" s="7"/>
@@ -16101,7 +16729,7 @@
       <c r="N572" s="1"/>
       <c r="O572" s="1"/>
     </row>
-    <row r="573" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A573" s="6"/>
       <c r="B573" s="6"/>
       <c r="C573" s="7"/>
@@ -16118,7 +16746,7 @@
       <c r="N573" s="1"/>
       <c r="O573" s="1"/>
     </row>
-    <row r="574" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A574" s="6"/>
       <c r="B574" s="6"/>
       <c r="C574" s="7"/>
@@ -16135,7 +16763,7 @@
       <c r="N574" s="1"/>
       <c r="O574" s="1"/>
     </row>
-    <row r="575" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A575" s="6"/>
       <c r="B575" s="6"/>
       <c r="C575" s="7"/>
@@ -16152,7 +16780,7 @@
       <c r="N575" s="1"/>
       <c r="O575" s="1"/>
     </row>
-    <row r="576" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A576" s="6"/>
       <c r="B576" s="6"/>
       <c r="C576" s="7"/>
@@ -16169,7 +16797,7 @@
       <c r="N576" s="1"/>
       <c r="O576" s="1"/>
     </row>
-    <row r="577" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A577" s="6"/>
       <c r="B577" s="6"/>
       <c r="C577" s="7"/>
@@ -16186,7 +16814,7 @@
       <c r="N577" s="1"/>
       <c r="O577" s="1"/>
     </row>
-    <row r="578" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A578" s="6"/>
       <c r="B578" s="6"/>
       <c r="C578" s="7"/>
@@ -16203,7 +16831,7 @@
       <c r="N578" s="1"/>
       <c r="O578" s="1"/>
     </row>
-    <row r="579" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A579" s="6"/>
       <c r="B579" s="6"/>
       <c r="C579" s="7"/>
@@ -16220,7 +16848,7 @@
       <c r="N579" s="1"/>
       <c r="O579" s="1"/>
     </row>
-    <row r="580" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A580" s="6"/>
       <c r="B580" s="6"/>
       <c r="C580" s="7"/>
@@ -16237,7 +16865,7 @@
       <c r="N580" s="1"/>
       <c r="O580" s="1"/>
     </row>
-    <row r="581" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A581" s="6"/>
       <c r="B581" s="6"/>
       <c r="C581" s="7"/>
@@ -16254,7 +16882,7 @@
       <c r="N581" s="1"/>
       <c r="O581" s="1"/>
     </row>
-    <row r="582" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A582" s="6"/>
       <c r="B582" s="6"/>
       <c r="C582" s="7"/>
@@ -16271,7 +16899,7 @@
       <c r="N582" s="1"/>
       <c r="O582" s="1"/>
     </row>
-    <row r="583" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A583" s="6"/>
       <c r="B583" s="6"/>
       <c r="C583" s="7"/>
@@ -16288,7 +16916,7 @@
       <c r="N583" s="1"/>
       <c r="O583" s="1"/>
     </row>
-    <row r="584" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A584" s="6"/>
       <c r="B584" s="6"/>
       <c r="C584" s="7"/>
@@ -16305,7 +16933,7 @@
       <c r="N584" s="1"/>
       <c r="O584" s="1"/>
     </row>
-    <row r="585" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A585" s="6"/>
       <c r="B585" s="6"/>
       <c r="C585" s="7"/>
@@ -16322,7 +16950,7 @@
       <c r="N585" s="1"/>
       <c r="O585" s="1"/>
     </row>
-    <row r="586" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A586" s="6"/>
       <c r="B586" s="6"/>
       <c r="C586" s="7"/>
@@ -16339,7 +16967,7 @@
       <c r="N586" s="1"/>
       <c r="O586" s="1"/>
     </row>
-    <row r="587" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A587" s="6"/>
       <c r="B587" s="6"/>
       <c r="C587" s="7"/>
@@ -16356,7 +16984,7 @@
       <c r="N587" s="1"/>
       <c r="O587" s="1"/>
     </row>
-    <row r="588" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A588" s="6"/>
       <c r="B588" s="6"/>
       <c r="C588" s="7"/>
@@ -16373,7 +17001,7 @@
       <c r="N588" s="1"/>
       <c r="O588" s="1"/>
     </row>
-    <row r="589" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A589" s="6"/>
       <c r="B589" s="6"/>
       <c r="C589" s="7"/>
@@ -16390,7 +17018,7 @@
       <c r="N589" s="1"/>
       <c r="O589" s="1"/>
     </row>
-    <row r="590" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A590" s="6"/>
       <c r="B590" s="6"/>
       <c r="C590" s="7"/>
@@ -16407,7 +17035,7 @@
       <c r="N590" s="1"/>
       <c r="O590" s="1"/>
     </row>
-    <row r="591" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A591" s="6"/>
       <c r="B591" s="6"/>
       <c r="C591" s="7"/>
@@ -16424,7 +17052,7 @@
       <c r="N591" s="1"/>
       <c r="O591" s="1"/>
     </row>
-    <row r="592" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A592" s="6"/>
       <c r="B592" s="6"/>
       <c r="C592" s="7"/>
@@ -16441,7 +17069,7 @@
       <c r="N592" s="1"/>
       <c r="O592" s="1"/>
     </row>
-    <row r="593" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A593" s="6"/>
       <c r="B593" s="6"/>
       <c r="C593" s="7"/>
@@ -16458,7 +17086,7 @@
       <c r="N593" s="1"/>
       <c r="O593" s="1"/>
     </row>
-    <row r="594" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A594" s="6"/>
       <c r="B594" s="6"/>
       <c r="C594" s="7"/>
@@ -16475,7 +17103,7 @@
       <c r="N594" s="1"/>
       <c r="O594" s="1"/>
     </row>
-    <row r="595" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A595" s="6"/>
       <c r="B595" s="6"/>
       <c r="C595" s="7"/>
@@ -16485,14 +17113,9 @@
       <c r="G595" s="5"/>
       <c r="H595" s="1"/>
       <c r="I595" s="1"/>
-      <c r="J595" s="1"/>
       <c r="K595" s="9"/>
-      <c r="L595" s="1"/>
-      <c r="M595" s="1"/>
-      <c r="N595" s="1"/>
-      <c r="O595" s="1"/>
-    </row>
-    <row r="596" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="596" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A596" s="6"/>
       <c r="B596" s="6"/>
       <c r="C596" s="7"/>
@@ -16502,14 +17125,9 @@
       <c r="G596" s="5"/>
       <c r="H596" s="1"/>
       <c r="I596" s="1"/>
-      <c r="J596" s="1"/>
       <c r="K596" s="9"/>
-      <c r="L596" s="1"/>
-      <c r="M596" s="1"/>
-      <c r="N596" s="1"/>
-      <c r="O596" s="1"/>
-    </row>
-    <row r="597" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="597" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A597" s="6"/>
       <c r="B597" s="6"/>
       <c r="C597" s="7"/>
@@ -16519,14 +17137,9 @@
       <c r="G597" s="5"/>
       <c r="H597" s="1"/>
       <c r="I597" s="1"/>
-      <c r="J597" s="1"/>
       <c r="K597" s="9"/>
-      <c r="L597" s="1"/>
-      <c r="M597" s="1"/>
-      <c r="N597" s="1"/>
-      <c r="O597" s="1"/>
-    </row>
-    <row r="598" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="598" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A598" s="6"/>
       <c r="B598" s="6"/>
       <c r="C598" s="7"/>
@@ -16536,14 +17149,9 @@
       <c r="G598" s="5"/>
       <c r="H598" s="1"/>
       <c r="I598" s="1"/>
-      <c r="J598" s="1"/>
       <c r="K598" s="9"/>
-      <c r="L598" s="1"/>
-      <c r="M598" s="1"/>
-      <c r="N598" s="1"/>
-      <c r="O598" s="1"/>
-    </row>
-    <row r="599" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="599" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A599" s="6"/>
       <c r="B599" s="6"/>
       <c r="C599" s="7"/>
@@ -16553,14 +17161,9 @@
       <c r="G599" s="5"/>
       <c r="H599" s="1"/>
       <c r="I599" s="1"/>
-      <c r="J599" s="1"/>
       <c r="K599" s="9"/>
-      <c r="L599" s="1"/>
-      <c r="M599" s="1"/>
-      <c r="N599" s="1"/>
-      <c r="O599" s="1"/>
-    </row>
-    <row r="600" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="600" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A600" s="6"/>
       <c r="B600" s="6"/>
       <c r="C600" s="7"/>
@@ -16570,14 +17173,9 @@
       <c r="G600" s="5"/>
       <c r="H600" s="1"/>
       <c r="I600" s="1"/>
-      <c r="J600" s="1"/>
       <c r="K600" s="9"/>
-      <c r="L600" s="1"/>
-      <c r="M600" s="1"/>
-      <c r="N600" s="1"/>
-      <c r="O600" s="1"/>
-    </row>
-    <row r="601" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="601" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A601" s="6"/>
       <c r="B601" s="6"/>
       <c r="C601" s="7"/>
@@ -16587,14 +17185,9 @@
       <c r="G601" s="5"/>
       <c r="H601" s="1"/>
       <c r="I601" s="1"/>
-      <c r="J601" s="1"/>
       <c r="K601" s="9"/>
-      <c r="L601" s="1"/>
-      <c r="M601" s="1"/>
-      <c r="N601" s="1"/>
-      <c r="O601" s="1"/>
-    </row>
-    <row r="602" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="602" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A602" s="6"/>
       <c r="B602" s="6"/>
       <c r="C602" s="7"/>
@@ -16606,7 +17199,7 @@
       <c r="I602" s="1"/>
       <c r="K602" s="9"/>
     </row>
-    <row r="603" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A603" s="6"/>
       <c r="B603" s="6"/>
       <c r="C603" s="7"/>
@@ -16618,7 +17211,7 @@
       <c r="I603" s="1"/>
       <c r="K603" s="9"/>
     </row>
-    <row r="604" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A604" s="6"/>
       <c r="B604" s="6"/>
       <c r="C604" s="7"/>
@@ -16630,7 +17223,7 @@
       <c r="I604" s="1"/>
       <c r="K604" s="9"/>
     </row>
-    <row r="605" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A605" s="6"/>
       <c r="B605" s="6"/>
       <c r="C605" s="7"/>
@@ -16642,7 +17235,7 @@
       <c r="I605" s="1"/>
       <c r="K605" s="9"/>
     </row>
-    <row r="606" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A606" s="6"/>
       <c r="B606" s="6"/>
       <c r="C606" s="7"/>
@@ -16654,7 +17247,7 @@
       <c r="I606" s="1"/>
       <c r="K606" s="9"/>
     </row>
-    <row r="607" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A607" s="6"/>
       <c r="B607" s="6"/>
       <c r="C607" s="7"/>
@@ -16666,7 +17259,7 @@
       <c r="I607" s="1"/>
       <c r="K607" s="9"/>
     </row>
-    <row r="608" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A608" s="6"/>
       <c r="B608" s="6"/>
       <c r="C608" s="7"/>
@@ -16678,7 +17271,7 @@
       <c r="I608" s="1"/>
       <c r="K608" s="9"/>
     </row>
-    <row r="609" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A609" s="6"/>
       <c r="B609" s="6"/>
       <c r="C609" s="7"/>
@@ -16690,7 +17283,7 @@
       <c r="I609" s="1"/>
       <c r="K609" s="9"/>
     </row>
-    <row r="610" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A610" s="6"/>
       <c r="B610" s="6"/>
       <c r="C610" s="7"/>
@@ -16702,7 +17295,7 @@
       <c r="I610" s="1"/>
       <c r="K610" s="9"/>
     </row>
-    <row r="611" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A611" s="6"/>
       <c r="B611" s="6"/>
       <c r="C611" s="7"/>
@@ -16714,7 +17307,7 @@
       <c r="I611" s="1"/>
       <c r="K611" s="9"/>
     </row>
-    <row r="612" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A612" s="6"/>
       <c r="B612" s="6"/>
       <c r="C612" s="7"/>
@@ -16726,7 +17319,7 @@
       <c r="I612" s="1"/>
       <c r="K612" s="9"/>
     </row>
-    <row r="613" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A613" s="6"/>
       <c r="B613" s="6"/>
       <c r="C613" s="7"/>
@@ -16738,7 +17331,7 @@
       <c r="I613" s="1"/>
       <c r="K613" s="9"/>
     </row>
-    <row r="614" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A614" s="6"/>
       <c r="B614" s="6"/>
       <c r="C614" s="7"/>
@@ -16750,7 +17343,7 @@
       <c r="I614" s="1"/>
       <c r="K614" s="9"/>
     </row>
-    <row r="615" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A615" s="6"/>
       <c r="B615" s="6"/>
       <c r="C615" s="7"/>
@@ -16762,7 +17355,7 @@
       <c r="I615" s="1"/>
       <c r="K615" s="9"/>
     </row>
-    <row r="616" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A616" s="6"/>
       <c r="B616" s="6"/>
       <c r="C616" s="7"/>
@@ -16774,7 +17367,7 @@
       <c r="I616" s="1"/>
       <c r="K616" s="9"/>
     </row>
-    <row r="617" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A617" s="6"/>
       <c r="B617" s="6"/>
       <c r="C617" s="7"/>
@@ -16786,7 +17379,7 @@
       <c r="I617" s="1"/>
       <c r="K617" s="9"/>
     </row>
-    <row r="618" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A618" s="6"/>
       <c r="B618" s="6"/>
       <c r="C618" s="7"/>
@@ -16798,7 +17391,7 @@
       <c r="I618" s="1"/>
       <c r="K618" s="9"/>
     </row>
-    <row r="619" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A619" s="6"/>
       <c r="B619" s="6"/>
       <c r="C619" s="7"/>
@@ -16810,7 +17403,7 @@
       <c r="I619" s="1"/>
       <c r="K619" s="9"/>
     </row>
-    <row r="620" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A620" s="6"/>
       <c r="B620" s="6"/>
       <c r="C620" s="7"/>
@@ -16822,7 +17415,7 @@
       <c r="I620" s="1"/>
       <c r="K620" s="9"/>
     </row>
-    <row r="621" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A621" s="6"/>
       <c r="B621" s="6"/>
       <c r="C621" s="7"/>
@@ -16834,7 +17427,7 @@
       <c r="I621" s="1"/>
       <c r="K621" s="9"/>
     </row>
-    <row r="622" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A622" s="6"/>
       <c r="B622" s="6"/>
       <c r="C622" s="7"/>
@@ -16846,7 +17439,7 @@
       <c r="I622" s="1"/>
       <c r="K622" s="9"/>
     </row>
-    <row r="623" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A623" s="6"/>
       <c r="B623" s="6"/>
       <c r="C623" s="7"/>
@@ -16858,7 +17451,7 @@
       <c r="I623" s="1"/>
       <c r="K623" s="9"/>
     </row>
-    <row r="624" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A624" s="6"/>
       <c r="B624" s="6"/>
       <c r="C624" s="7"/>
@@ -16870,7 +17463,7 @@
       <c r="I624" s="1"/>
       <c r="K624" s="9"/>
     </row>
-    <row r="625" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A625" s="6"/>
       <c r="B625" s="6"/>
       <c r="C625" s="7"/>
@@ -16882,7 +17475,7 @@
       <c r="I625" s="1"/>
       <c r="K625" s="9"/>
     </row>
-    <row r="626" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A626" s="6"/>
       <c r="B626" s="6"/>
       <c r="C626" s="7"/>
@@ -16894,7 +17487,7 @@
       <c r="I626" s="1"/>
       <c r="K626" s="9"/>
     </row>
-    <row r="627" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A627" s="6"/>
       <c r="B627" s="6"/>
       <c r="C627" s="7"/>
@@ -16906,7 +17499,7 @@
       <c r="I627" s="1"/>
       <c r="K627" s="9"/>
     </row>
-    <row r="628" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A628" s="6"/>
       <c r="B628" s="6"/>
       <c r="C628" s="7"/>
@@ -16918,7 +17511,7 @@
       <c r="I628" s="1"/>
       <c r="K628" s="9"/>
     </row>
-    <row r="629" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A629" s="6"/>
       <c r="B629" s="6"/>
       <c r="C629" s="7"/>
@@ -16930,7 +17523,7 @@
       <c r="I629" s="1"/>
       <c r="K629" s="9"/>
     </row>
-    <row r="630" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A630" s="6"/>
       <c r="B630" s="6"/>
       <c r="C630" s="7"/>
@@ -16942,7 +17535,7 @@
       <c r="I630" s="1"/>
       <c r="K630" s="9"/>
     </row>
-    <row r="631" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A631" s="6"/>
       <c r="B631" s="6"/>
       <c r="C631" s="7"/>
@@ -16954,7 +17547,7 @@
       <c r="I631" s="1"/>
       <c r="K631" s="9"/>
     </row>
-    <row r="632" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A632" s="6"/>
       <c r="B632" s="6"/>
       <c r="C632" s="7"/>
@@ -16966,7 +17559,7 @@
       <c r="I632" s="1"/>
       <c r="K632" s="9"/>
     </row>
-    <row r="633" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A633" s="6"/>
       <c r="B633" s="6"/>
       <c r="C633" s="7"/>
@@ -16978,7 +17571,7 @@
       <c r="I633" s="1"/>
       <c r="K633" s="9"/>
     </row>
-    <row r="634" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A634" s="6"/>
       <c r="B634" s="6"/>
       <c r="C634" s="7"/>
@@ -16990,7 +17583,7 @@
       <c r="I634" s="1"/>
       <c r="K634" s="9"/>
     </row>
-    <row r="635" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A635" s="6"/>
       <c r="B635" s="6"/>
       <c r="C635" s="7"/>
@@ -17002,7 +17595,7 @@
       <c r="I635" s="1"/>
       <c r="K635" s="9"/>
     </row>
-    <row r="636" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A636" s="6"/>
       <c r="B636" s="6"/>
       <c r="C636" s="7"/>
@@ -17014,7 +17607,7 @@
       <c r="I636" s="1"/>
       <c r="K636" s="9"/>
     </row>
-    <row r="637" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A637" s="6"/>
       <c r="B637" s="6"/>
       <c r="C637" s="7"/>
@@ -17026,7 +17619,7 @@
       <c r="I637" s="1"/>
       <c r="K637" s="9"/>
     </row>
-    <row r="638" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A638" s="6"/>
       <c r="B638" s="6"/>
       <c r="C638" s="7"/>
@@ -17038,7 +17631,7 @@
       <c r="I638" s="1"/>
       <c r="K638" s="9"/>
     </row>
-    <row r="639" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A639" s="6"/>
       <c r="B639" s="6"/>
       <c r="C639" s="7"/>
@@ -17050,7 +17643,7 @@
       <c r="I639" s="1"/>
       <c r="K639" s="9"/>
     </row>
-    <row r="640" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A640" s="6"/>
       <c r="B640" s="6"/>
       <c r="C640" s="7"/>
@@ -17062,7 +17655,7 @@
       <c r="I640" s="1"/>
       <c r="K640" s="9"/>
     </row>
-    <row r="641" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A641" s="6"/>
       <c r="B641" s="6"/>
       <c r="C641" s="7"/>
@@ -17074,7 +17667,7 @@
       <c r="I641" s="1"/>
       <c r="K641" s="9"/>
     </row>
-    <row r="642" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A642" s="6"/>
       <c r="B642" s="6"/>
       <c r="C642" s="7"/>
@@ -17086,7 +17679,7 @@
       <c r="I642" s="1"/>
       <c r="K642" s="9"/>
     </row>
-    <row r="643" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A643" s="6"/>
       <c r="B643" s="6"/>
       <c r="C643" s="7"/>
@@ -17098,7 +17691,7 @@
       <c r="I643" s="1"/>
       <c r="K643" s="9"/>
     </row>
-    <row r="644" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A644" s="6"/>
       <c r="B644" s="6"/>
       <c r="C644" s="7"/>
@@ -17110,7 +17703,7 @@
       <c r="I644" s="1"/>
       <c r="K644" s="9"/>
     </row>
-    <row r="645" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A645" s="6"/>
       <c r="B645" s="6"/>
       <c r="C645" s="7"/>
@@ -17122,7 +17715,7 @@
       <c r="I645" s="1"/>
       <c r="K645" s="9"/>
     </row>
-    <row r="646" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A646" s="6"/>
       <c r="B646" s="6"/>
       <c r="C646" s="7"/>
@@ -17134,7 +17727,7 @@
       <c r="I646" s="1"/>
       <c r="K646" s="9"/>
     </row>
-    <row r="647" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A647" s="6"/>
       <c r="B647" s="6"/>
       <c r="C647" s="7"/>
@@ -17146,7 +17739,7 @@
       <c r="I647" s="1"/>
       <c r="K647" s="9"/>
     </row>
-    <row r="648" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A648" s="6"/>
       <c r="B648" s="6"/>
       <c r="C648" s="7"/>
@@ -17158,7 +17751,7 @@
       <c r="I648" s="1"/>
       <c r="K648" s="9"/>
     </row>
-    <row r="649" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A649" s="6"/>
       <c r="B649" s="6"/>
       <c r="C649" s="7"/>
@@ -17170,7 +17763,7 @@
       <c r="I649" s="1"/>
       <c r="K649" s="9"/>
     </row>
-    <row r="650" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A650" s="6"/>
       <c r="B650" s="6"/>
       <c r="C650" s="7"/>
@@ -17182,7 +17775,7 @@
       <c r="I650" s="1"/>
       <c r="K650" s="9"/>
     </row>
-    <row r="651" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A651" s="6"/>
       <c r="B651" s="6"/>
       <c r="C651" s="7"/>
@@ -17194,7 +17787,7 @@
       <c r="I651" s="1"/>
       <c r="K651" s="9"/>
     </row>
-    <row r="652" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A652" s="6"/>
       <c r="B652" s="6"/>
       <c r="C652" s="7"/>
@@ -17206,7 +17799,7 @@
       <c r="I652" s="1"/>
       <c r="K652" s="9"/>
     </row>
-    <row r="653" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A653" s="6"/>
       <c r="B653" s="6"/>
       <c r="C653" s="7"/>
@@ -17218,7 +17811,7 @@
       <c r="I653" s="1"/>
       <c r="K653" s="9"/>
     </row>
-    <row r="654" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A654" s="6"/>
       <c r="B654" s="6"/>
       <c r="C654" s="7"/>
@@ -17230,7 +17823,7 @@
       <c r="I654" s="1"/>
       <c r="K654" s="9"/>
     </row>
-    <row r="655" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A655" s="6"/>
       <c r="B655" s="6"/>
       <c r="C655" s="7"/>
@@ -17242,7 +17835,7 @@
       <c r="I655" s="1"/>
       <c r="K655" s="9"/>
     </row>
-    <row r="656" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A656" s="6"/>
       <c r="B656" s="6"/>
       <c r="C656" s="7"/>
@@ -17254,7 +17847,7 @@
       <c r="I656" s="1"/>
       <c r="K656" s="9"/>
     </row>
-    <row r="657" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A657" s="6"/>
       <c r="B657" s="6"/>
       <c r="C657" s="7"/>
@@ -17266,7 +17859,7 @@
       <c r="I657" s="1"/>
       <c r="K657" s="9"/>
     </row>
-    <row r="658" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A658" s="6"/>
       <c r="B658" s="6"/>
       <c r="C658" s="7"/>
@@ -17278,7 +17871,7 @@
       <c r="I658" s="1"/>
       <c r="K658" s="9"/>
     </row>
-    <row r="659" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A659" s="6"/>
       <c r="B659" s="6"/>
       <c r="C659" s="7"/>
@@ -17290,7 +17883,7 @@
       <c r="I659" s="1"/>
       <c r="K659" s="9"/>
     </row>
-    <row r="660" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A660" s="6"/>
       <c r="B660" s="6"/>
       <c r="C660" s="7"/>
@@ -17302,7 +17895,7 @@
       <c r="I660" s="1"/>
       <c r="K660" s="9"/>
     </row>
-    <row r="661" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A661" s="6"/>
       <c r="B661" s="6"/>
       <c r="C661" s="7"/>
@@ -17314,7 +17907,7 @@
       <c r="I661" s="1"/>
       <c r="K661" s="9"/>
     </row>
-    <row r="662" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A662" s="6"/>
       <c r="B662" s="6"/>
       <c r="C662" s="7"/>
@@ -17326,7 +17919,7 @@
       <c r="I662" s="1"/>
       <c r="K662" s="9"/>
     </row>
-    <row r="663" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A663" s="6"/>
       <c r="B663" s="6"/>
       <c r="C663" s="7"/>
@@ -17338,7 +17931,7 @@
       <c r="I663" s="1"/>
       <c r="K663" s="9"/>
     </row>
-    <row r="664" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A664" s="6"/>
       <c r="B664" s="6"/>
       <c r="C664" s="7"/>
@@ -17350,7 +17943,7 @@
       <c r="I664" s="1"/>
       <c r="K664" s="9"/>
     </row>
-    <row r="665" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A665" s="6"/>
       <c r="B665" s="6"/>
       <c r="C665" s="7"/>
@@ -17362,7 +17955,7 @@
       <c r="I665" s="1"/>
       <c r="K665" s="9"/>
     </row>
-    <row r="666" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A666" s="6"/>
       <c r="B666" s="6"/>
       <c r="C666" s="7"/>
@@ -17374,7 +17967,7 @@
       <c r="I666" s="1"/>
       <c r="K666" s="9"/>
     </row>
-    <row r="667" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A667" s="6"/>
       <c r="B667" s="6"/>
       <c r="C667" s="7"/>
@@ -17386,7 +17979,7 @@
       <c r="I667" s="1"/>
       <c r="K667" s="9"/>
     </row>
-    <row r="668" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A668" s="6"/>
       <c r="B668" s="6"/>
       <c r="C668" s="7"/>
@@ -17398,7 +17991,7 @@
       <c r="I668" s="1"/>
       <c r="K668" s="9"/>
     </row>
-    <row r="669" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A669" s="6"/>
       <c r="B669" s="6"/>
       <c r="C669" s="7"/>
@@ -17410,7 +18003,7 @@
       <c r="I669" s="1"/>
       <c r="K669" s="9"/>
     </row>
-    <row r="670" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A670" s="6"/>
       <c r="B670" s="6"/>
       <c r="C670" s="7"/>
@@ -17422,7 +18015,7 @@
       <c r="I670" s="1"/>
       <c r="K670" s="9"/>
     </row>
-    <row r="671" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A671" s="6"/>
       <c r="B671" s="6"/>
       <c r="C671" s="7"/>
@@ -17434,7 +18027,7 @@
       <c r="I671" s="1"/>
       <c r="K671" s="9"/>
     </row>
-    <row r="672" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A672" s="6"/>
       <c r="B672" s="6"/>
       <c r="C672" s="7"/>
@@ -17446,7 +18039,7 @@
       <c r="I672" s="1"/>
       <c r="K672" s="9"/>
     </row>
-    <row r="673" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A673" s="6"/>
       <c r="B673" s="6"/>
       <c r="C673" s="7"/>
@@ -17458,7 +18051,7 @@
       <c r="I673" s="1"/>
       <c r="K673" s="9"/>
     </row>
-    <row r="674" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A674" s="6"/>
       <c r="B674" s="6"/>
       <c r="C674" s="7"/>
@@ -17470,7 +18063,7 @@
       <c r="I674" s="1"/>
       <c r="K674" s="9"/>
     </row>
-    <row r="675" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A675" s="6"/>
       <c r="B675" s="6"/>
       <c r="C675" s="7"/>
@@ -17482,7 +18075,7 @@
       <c r="I675" s="1"/>
       <c r="K675" s="9"/>
     </row>
-    <row r="676" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A676" s="6"/>
       <c r="B676" s="6"/>
       <c r="C676" s="7"/>
@@ -17494,7 +18087,7 @@
       <c r="I676" s="1"/>
       <c r="K676" s="9"/>
     </row>
-    <row r="677" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A677" s="6"/>
       <c r="B677" s="6"/>
       <c r="C677" s="7"/>
@@ -17506,7 +18099,7 @@
       <c r="I677" s="1"/>
       <c r="K677" s="9"/>
     </row>
-    <row r="678" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A678" s="6"/>
       <c r="B678" s="6"/>
       <c r="C678" s="7"/>
@@ -17518,7 +18111,7 @@
       <c r="I678" s="1"/>
       <c r="K678" s="9"/>
     </row>
-    <row r="679" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A679" s="6"/>
       <c r="B679" s="6"/>
       <c r="C679" s="7"/>
@@ -17530,7 +18123,7 @@
       <c r="I679" s="1"/>
       <c r="K679" s="9"/>
     </row>
-    <row r="680" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A680" s="6"/>
       <c r="B680" s="6"/>
       <c r="C680" s="7"/>
@@ -17542,7 +18135,7 @@
       <c r="I680" s="1"/>
       <c r="K680" s="9"/>
     </row>
-    <row r="681" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A681" s="6"/>
       <c r="B681" s="6"/>
       <c r="C681" s="7"/>
@@ -17554,7 +18147,7 @@
       <c r="I681" s="1"/>
       <c r="K681" s="9"/>
     </row>
-    <row r="682" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A682" s="6"/>
       <c r="B682" s="6"/>
       <c r="C682" s="7"/>
@@ -17566,7 +18159,7 @@
       <c r="I682" s="1"/>
       <c r="K682" s="9"/>
     </row>
-    <row r="683" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A683" s="6"/>
       <c r="B683" s="6"/>
       <c r="C683" s="7"/>
@@ -17578,7 +18171,7 @@
       <c r="I683" s="1"/>
       <c r="K683" s="9"/>
     </row>
-    <row r="684" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A684" s="6"/>
       <c r="B684" s="6"/>
       <c r="C684" s="7"/>
@@ -17590,7 +18183,7 @@
       <c r="I684" s="1"/>
       <c r="K684" s="9"/>
     </row>
-    <row r="685" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A685" s="6"/>
       <c r="B685" s="6"/>
       <c r="C685" s="7"/>
@@ -17602,7 +18195,7 @@
       <c r="I685" s="1"/>
       <c r="K685" s="9"/>
     </row>
-    <row r="686" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A686" s="6"/>
       <c r="B686" s="6"/>
       <c r="C686" s="7"/>
@@ -17614,7 +18207,7 @@
       <c r="I686" s="1"/>
       <c r="K686" s="9"/>
     </row>
-    <row r="687" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A687" s="6"/>
       <c r="B687" s="6"/>
       <c r="C687" s="7"/>
@@ -17626,7 +18219,7 @@
       <c r="I687" s="1"/>
       <c r="K687" s="9"/>
     </row>
-    <row r="688" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A688" s="6"/>
       <c r="B688" s="6"/>
       <c r="C688" s="7"/>
@@ -17638,7 +18231,7 @@
       <c r="I688" s="1"/>
       <c r="K688" s="9"/>
     </row>
-    <row r="689" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A689" s="6"/>
       <c r="B689" s="6"/>
       <c r="C689" s="7"/>
@@ -17650,7 +18243,7 @@
       <c r="I689" s="1"/>
       <c r="K689" s="9"/>
     </row>
-    <row r="690" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A690" s="6"/>
       <c r="B690" s="6"/>
       <c r="C690" s="7"/>
@@ -17662,7 +18255,7 @@
       <c r="I690" s="1"/>
       <c r="K690" s="9"/>
     </row>
-    <row r="691" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A691" s="6"/>
       <c r="B691" s="6"/>
       <c r="C691" s="7"/>
@@ -17674,7 +18267,7 @@
       <c r="I691" s="1"/>
       <c r="K691" s="9"/>
     </row>
-    <row r="692" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A692" s="6"/>
       <c r="B692" s="6"/>
       <c r="C692" s="7"/>
@@ -17686,7 +18279,7 @@
       <c r="I692" s="1"/>
       <c r="K692" s="9"/>
     </row>
-    <row r="693" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A693" s="6"/>
       <c r="B693" s="6"/>
       <c r="C693" s="7"/>
@@ -17698,7 +18291,7 @@
       <c r="I693" s="1"/>
       <c r="K693" s="9"/>
     </row>
-    <row r="694" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A694" s="6"/>
       <c r="B694" s="6"/>
       <c r="C694" s="7"/>
@@ -17710,7 +18303,7 @@
       <c r="I694" s="1"/>
       <c r="K694" s="9"/>
     </row>
-    <row r="695" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A695" s="6"/>
       <c r="B695" s="6"/>
       <c r="C695" s="7"/>
@@ -17722,7 +18315,7 @@
       <c r="I695" s="1"/>
       <c r="K695" s="9"/>
     </row>
-    <row r="696" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A696" s="6"/>
       <c r="B696" s="6"/>
       <c r="C696" s="7"/>
@@ -17734,7 +18327,7 @@
       <c r="I696" s="1"/>
       <c r="K696" s="9"/>
     </row>
-    <row r="697" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A697" s="6"/>
       <c r="B697" s="6"/>
       <c r="C697" s="7"/>
@@ -17746,7 +18339,7 @@
       <c r="I697" s="1"/>
       <c r="K697" s="9"/>
     </row>
-    <row r="698" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A698" s="6"/>
       <c r="B698" s="6"/>
       <c r="C698" s="7"/>
@@ -17758,7 +18351,7 @@
       <c r="I698" s="1"/>
       <c r="K698" s="9"/>
     </row>
-    <row r="699" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A699" s="6"/>
       <c r="B699" s="6"/>
       <c r="C699" s="7"/>
@@ -17770,7 +18363,7 @@
       <c r="I699" s="1"/>
       <c r="K699" s="9"/>
     </row>
-    <row r="700" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A700" s="6"/>
       <c r="B700" s="6"/>
       <c r="C700" s="7"/>
@@ -17782,7 +18375,7 @@
       <c r="I700" s="1"/>
       <c r="K700" s="9"/>
     </row>
-    <row r="701" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A701" s="6"/>
       <c r="B701" s="6"/>
       <c r="C701" s="7"/>
@@ -17794,7 +18387,7 @@
       <c r="I701" s="1"/>
       <c r="K701" s="9"/>
     </row>
-    <row r="702" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A702" s="6"/>
       <c r="B702" s="6"/>
       <c r="C702" s="7"/>
@@ -17806,7 +18399,7 @@
       <c r="I702" s="1"/>
       <c r="K702" s="9"/>
     </row>
-    <row r="703" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A703" s="6"/>
       <c r="B703" s="6"/>
       <c r="C703" s="7"/>
@@ -17818,7 +18411,7 @@
       <c r="I703" s="1"/>
       <c r="K703" s="9"/>
     </row>
-    <row r="704" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A704" s="6"/>
       <c r="B704" s="6"/>
       <c r="C704" s="7"/>
@@ -17830,7 +18423,7 @@
       <c r="I704" s="1"/>
       <c r="K704" s="9"/>
     </row>
-    <row r="705" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A705" s="6"/>
       <c r="B705" s="6"/>
       <c r="C705" s="7"/>
@@ -17842,7 +18435,7 @@
       <c r="I705" s="1"/>
       <c r="K705" s="9"/>
     </row>
-    <row r="706" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A706" s="6"/>
       <c r="B706" s="6"/>
       <c r="C706" s="7"/>
@@ -17854,7 +18447,7 @@
       <c r="I706" s="1"/>
       <c r="K706" s="9"/>
     </row>
-    <row r="707" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A707" s="6"/>
       <c r="B707" s="6"/>
       <c r="C707" s="7"/>
@@ -17866,7 +18459,7 @@
       <c r="I707" s="1"/>
       <c r="K707" s="9"/>
     </row>
-    <row r="708" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A708" s="6"/>
       <c r="B708" s="6"/>
       <c r="C708" s="7"/>
@@ -17878,7 +18471,7 @@
       <c r="I708" s="1"/>
       <c r="K708" s="9"/>
     </row>
-    <row r="709" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A709" s="6"/>
       <c r="B709" s="6"/>
       <c r="C709" s="7"/>
@@ -17890,7 +18483,7 @@
       <c r="I709" s="1"/>
       <c r="K709" s="9"/>
     </row>
-    <row r="710" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A710" s="6"/>
       <c r="B710" s="6"/>
       <c r="C710" s="7"/>
@@ -17902,7 +18495,7 @@
       <c r="I710" s="1"/>
       <c r="K710" s="9"/>
     </row>
-    <row r="711" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A711" s="6"/>
       <c r="B711" s="6"/>
       <c r="C711" s="7"/>
@@ -17914,7 +18507,7 @@
       <c r="I711" s="1"/>
       <c r="K711" s="9"/>
     </row>
-    <row r="712" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A712" s="6"/>
       <c r="B712" s="6"/>
       <c r="C712" s="7"/>
@@ -17926,7 +18519,7 @@
       <c r="I712" s="1"/>
       <c r="K712" s="9"/>
     </row>
-    <row r="713" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A713" s="6"/>
       <c r="B713" s="6"/>
       <c r="C713" s="7"/>
@@ -17938,7 +18531,7 @@
       <c r="I713" s="1"/>
       <c r="K713" s="9"/>
     </row>
-    <row r="714" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A714" s="6"/>
       <c r="B714" s="6"/>
       <c r="C714" s="7"/>
@@ -17950,7 +18543,7 @@
       <c r="I714" s="1"/>
       <c r="K714" s="9"/>
     </row>
-    <row r="715" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A715" s="6"/>
       <c r="B715" s="6"/>
       <c r="C715" s="7"/>
@@ -17962,7 +18555,7 @@
       <c r="I715" s="1"/>
       <c r="K715" s="9"/>
     </row>
-    <row r="716" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A716" s="6"/>
       <c r="B716" s="6"/>
       <c r="C716" s="7"/>
@@ -17974,7 +18567,7 @@
       <c r="I716" s="1"/>
       <c r="K716" s="9"/>
     </row>
-    <row r="717" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A717" s="6"/>
       <c r="B717" s="6"/>
       <c r="C717" s="7"/>
@@ -17986,7 +18579,7 @@
       <c r="I717" s="1"/>
       <c r="K717" s="9"/>
     </row>
-    <row r="718" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A718" s="6"/>
       <c r="B718" s="6"/>
       <c r="C718" s="7"/>
@@ -17998,7 +18591,7 @@
       <c r="I718" s="1"/>
       <c r="K718" s="9"/>
     </row>
-    <row r="719" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A719" s="6"/>
       <c r="B719" s="6"/>
       <c r="C719" s="7"/>
@@ -18010,7 +18603,7 @@
       <c r="I719" s="1"/>
       <c r="K719" s="9"/>
     </row>
-    <row r="720" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A720" s="6"/>
       <c r="B720" s="6"/>
       <c r="C720" s="7"/>
@@ -18022,7 +18615,7 @@
       <c r="I720" s="1"/>
       <c r="K720" s="9"/>
     </row>
-    <row r="721" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A721" s="6"/>
       <c r="B721" s="6"/>
       <c r="C721" s="7"/>
@@ -18034,7 +18627,7 @@
       <c r="I721" s="1"/>
       <c r="K721" s="9"/>
     </row>
-    <row r="722" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A722" s="6"/>
       <c r="B722" s="6"/>
       <c r="C722" s="7"/>
@@ -18046,7 +18639,7 @@
       <c r="I722" s="1"/>
       <c r="K722" s="9"/>
     </row>
-    <row r="723" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A723" s="6"/>
       <c r="B723" s="6"/>
       <c r="C723" s="7"/>
@@ -18058,7 +18651,7 @@
       <c r="I723" s="1"/>
       <c r="K723" s="9"/>
     </row>
-    <row r="724" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A724" s="6"/>
       <c r="B724" s="6"/>
       <c r="C724" s="7"/>
@@ -18070,7 +18663,7 @@
       <c r="I724" s="1"/>
       <c r="K724" s="9"/>
     </row>
-    <row r="725" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A725" s="6"/>
       <c r="B725" s="6"/>
       <c r="C725" s="7"/>
@@ -18082,7 +18675,7 @@
       <c r="I725" s="1"/>
       <c r="K725" s="9"/>
     </row>
-    <row r="726" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A726" s="6"/>
       <c r="B726" s="6"/>
       <c r="C726" s="7"/>
@@ -18094,7 +18687,7 @@
       <c r="I726" s="1"/>
       <c r="K726" s="9"/>
     </row>
-    <row r="727" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A727" s="6"/>
       <c r="B727" s="6"/>
       <c r="C727" s="7"/>
@@ -18106,7 +18699,7 @@
       <c r="I727" s="1"/>
       <c r="K727" s="9"/>
     </row>
-    <row r="728" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A728" s="6"/>
       <c r="B728" s="6"/>
       <c r="C728" s="7"/>
@@ -18118,7 +18711,7 @@
       <c r="I728" s="1"/>
       <c r="K728" s="9"/>
     </row>
-    <row r="729" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A729" s="6"/>
       <c r="B729" s="6"/>
       <c r="C729" s="7"/>
@@ -18130,7 +18723,7 @@
       <c r="I729" s="1"/>
       <c r="K729" s="9"/>
     </row>
-    <row r="730" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A730" s="6"/>
       <c r="B730" s="6"/>
       <c r="C730" s="7"/>
@@ -18142,7 +18735,7 @@
       <c r="I730" s="1"/>
       <c r="K730" s="9"/>
     </row>
-    <row r="731" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A731" s="6"/>
       <c r="B731" s="6"/>
       <c r="C731" s="7"/>
@@ -18154,7 +18747,7 @@
       <c r="I731" s="1"/>
       <c r="K731" s="9"/>
     </row>
-    <row r="732" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A732" s="6"/>
       <c r="B732" s="6"/>
       <c r="C732" s="7"/>
@@ -18166,7 +18759,7 @@
       <c r="I732" s="1"/>
       <c r="K732" s="9"/>
     </row>
-    <row r="733" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A733" s="6"/>
       <c r="B733" s="6"/>
       <c r="C733" s="7"/>
@@ -18178,7 +18771,7 @@
       <c r="I733" s="1"/>
       <c r="K733" s="9"/>
     </row>
-    <row r="734" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A734" s="6"/>
       <c r="B734" s="6"/>
       <c r="C734" s="7"/>
@@ -18190,7 +18783,7 @@
       <c r="I734" s="1"/>
       <c r="K734" s="9"/>
     </row>
-    <row r="735" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A735" s="6"/>
       <c r="B735" s="6"/>
       <c r="C735" s="7"/>
@@ -18202,7 +18795,7 @@
       <c r="I735" s="1"/>
       <c r="K735" s="9"/>
     </row>
-    <row r="736" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A736" s="6"/>
       <c r="B736" s="6"/>
       <c r="C736" s="7"/>
@@ -18214,7 +18807,7 @@
       <c r="I736" s="1"/>
       <c r="K736" s="9"/>
     </row>
-    <row r="737" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A737" s="6"/>
       <c r="B737" s="6"/>
       <c r="C737" s="7"/>
@@ -18226,7 +18819,7 @@
       <c r="I737" s="1"/>
       <c r="K737" s="9"/>
     </row>
-    <row r="738" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A738" s="6"/>
       <c r="B738" s="6"/>
       <c r="C738" s="7"/>
@@ -18238,7 +18831,7 @@
       <c r="I738" s="1"/>
       <c r="K738" s="9"/>
     </row>
-    <row r="739" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A739" s="6"/>
       <c r="B739" s="6"/>
       <c r="C739" s="7"/>
@@ -18250,7 +18843,7 @@
       <c r="I739" s="1"/>
       <c r="K739" s="9"/>
     </row>
-    <row r="740" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A740" s="6"/>
       <c r="B740" s="6"/>
       <c r="C740" s="7"/>
@@ -18262,7 +18855,7 @@
       <c r="I740" s="1"/>
       <c r="K740" s="9"/>
     </row>
-    <row r="741" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A741" s="6"/>
       <c r="B741" s="6"/>
       <c r="C741" s="7"/>
@@ -18274,7 +18867,7 @@
       <c r="I741" s="1"/>
       <c r="K741" s="9"/>
     </row>
-    <row r="742" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A742" s="6"/>
       <c r="B742" s="6"/>
       <c r="C742" s="7"/>
@@ -18286,7 +18879,7 @@
       <c r="I742" s="1"/>
       <c r="K742" s="9"/>
     </row>
-    <row r="743" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A743" s="6"/>
       <c r="B743" s="6"/>
       <c r="C743" s="7"/>
@@ -18298,7 +18891,7 @@
       <c r="I743" s="1"/>
       <c r="K743" s="9"/>
     </row>
-    <row r="744" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A744" s="6"/>
       <c r="B744" s="6"/>
       <c r="C744" s="7"/>
@@ -18310,7 +18903,7 @@
       <c r="I744" s="1"/>
       <c r="K744" s="9"/>
     </row>
-    <row r="745" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A745" s="6"/>
       <c r="B745" s="6"/>
       <c r="C745" s="7"/>
@@ -18322,7 +18915,7 @@
       <c r="I745" s="1"/>
       <c r="K745" s="9"/>
     </row>
-    <row r="746" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A746" s="6"/>
       <c r="B746" s="6"/>
       <c r="C746" s="7"/>
@@ -18334,7 +18927,7 @@
       <c r="I746" s="1"/>
       <c r="K746" s="9"/>
     </row>
-    <row r="747" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A747" s="6"/>
       <c r="B747" s="6"/>
       <c r="C747" s="7"/>
@@ -18346,7 +18939,7 @@
       <c r="I747" s="1"/>
       <c r="K747" s="9"/>
     </row>
-    <row r="748" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A748" s="6"/>
       <c r="B748" s="6"/>
       <c r="C748" s="7"/>
@@ -18358,7 +18951,7 @@
       <c r="I748" s="1"/>
       <c r="K748" s="9"/>
     </row>
-    <row r="749" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A749" s="6"/>
       <c r="B749" s="6"/>
       <c r="C749" s="7"/>
@@ -18370,7 +18963,7 @@
       <c r="I749" s="1"/>
       <c r="K749" s="9"/>
     </row>
-    <row r="750" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A750" s="6"/>
       <c r="B750" s="6"/>
       <c r="C750" s="7"/>
@@ -18380,9 +18973,8 @@
       <c r="G750" s="5"/>
       <c r="H750" s="1"/>
       <c r="I750" s="1"/>
-      <c r="K750" s="9"/>
-    </row>
-    <row r="751" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="751" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A751" s="6"/>
       <c r="B751" s="6"/>
       <c r="C751" s="7"/>
@@ -18392,9 +18984,8 @@
       <c r="G751" s="5"/>
       <c r="H751" s="1"/>
       <c r="I751" s="1"/>
-      <c r="K751" s="9"/>
-    </row>
-    <row r="752" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="752" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A752" s="6"/>
       <c r="B752" s="6"/>
       <c r="C752" s="7"/>
@@ -18404,9 +18995,8 @@
       <c r="G752" s="5"/>
       <c r="H752" s="1"/>
       <c r="I752" s="1"/>
-      <c r="K752" s="9"/>
-    </row>
-    <row r="753" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="753" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A753" s="6"/>
       <c r="B753" s="6"/>
       <c r="C753" s="7"/>
@@ -18416,9 +19006,8 @@
       <c r="G753" s="5"/>
       <c r="H753" s="1"/>
       <c r="I753" s="1"/>
-      <c r="K753" s="9"/>
-    </row>
-    <row r="754" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="754" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A754" s="6"/>
       <c r="B754" s="6"/>
       <c r="C754" s="7"/>
@@ -18428,9 +19017,8 @@
       <c r="G754" s="5"/>
       <c r="H754" s="1"/>
       <c r="I754" s="1"/>
-      <c r="K754" s="9"/>
-    </row>
-    <row r="755" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="755" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A755" s="6"/>
       <c r="B755" s="6"/>
       <c r="C755" s="7"/>
@@ -18440,9 +19028,8 @@
       <c r="G755" s="5"/>
       <c r="H755" s="1"/>
       <c r="I755" s="1"/>
-      <c r="K755" s="9"/>
-    </row>
-    <row r="756" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="756" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A756" s="6"/>
       <c r="B756" s="6"/>
       <c r="C756" s="7"/>
@@ -18452,9 +19039,8 @@
       <c r="G756" s="5"/>
       <c r="H756" s="1"/>
       <c r="I756" s="1"/>
-      <c r="K756" s="9"/>
-    </row>
-    <row r="757" spans="1:11" x14ac:dyDescent="0.25">
+    </row>
+    <row r="757" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A757" s="6"/>
       <c r="B757" s="6"/>
       <c r="C757" s="7"/>
@@ -18465,7 +19051,7 @@
       <c r="H757" s="1"/>
       <c r="I757" s="1"/>
     </row>
-    <row r="758" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A758" s="6"/>
       <c r="B758" s="6"/>
       <c r="C758" s="7"/>
@@ -18476,7 +19062,7 @@
       <c r="H758" s="1"/>
       <c r="I758" s="1"/>
     </row>
-    <row r="759" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A759" s="6"/>
       <c r="B759" s="6"/>
       <c r="C759" s="7"/>
@@ -18487,7 +19073,7 @@
       <c r="H759" s="1"/>
       <c r="I759" s="1"/>
     </row>
-    <row r="760" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A760" s="6"/>
       <c r="B760" s="6"/>
       <c r="C760" s="7"/>
@@ -18498,7 +19084,7 @@
       <c r="H760" s="1"/>
       <c r="I760" s="1"/>
     </row>
-    <row r="761" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A761" s="6"/>
       <c r="B761" s="6"/>
       <c r="C761" s="7"/>
@@ -18509,7 +19095,7 @@
       <c r="H761" s="1"/>
       <c r="I761" s="1"/>
     </row>
-    <row r="762" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A762" s="6"/>
       <c r="B762" s="6"/>
       <c r="C762" s="7"/>
@@ -18520,7 +19106,7 @@
       <c r="H762" s="1"/>
       <c r="I762" s="1"/>
     </row>
-    <row r="763" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A763" s="6"/>
       <c r="B763" s="6"/>
       <c r="C763" s="7"/>
@@ -18531,7 +19117,7 @@
       <c r="H763" s="1"/>
       <c r="I763" s="1"/>
     </row>
-    <row r="764" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A764" s="6"/>
       <c r="B764" s="6"/>
       <c r="C764" s="7"/>
@@ -18542,7 +19128,7 @@
       <c r="H764" s="1"/>
       <c r="I764" s="1"/>
     </row>
-    <row r="765" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A765" s="6"/>
       <c r="B765" s="6"/>
       <c r="C765" s="7"/>
@@ -18553,7 +19139,7 @@
       <c r="H765" s="1"/>
       <c r="I765" s="1"/>
     </row>
-    <row r="766" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A766" s="6"/>
       <c r="B766" s="6"/>
       <c r="C766" s="7"/>
@@ -18564,7 +19150,7 @@
       <c r="H766" s="1"/>
       <c r="I766" s="1"/>
     </row>
-    <row r="767" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A767" s="6"/>
       <c r="B767" s="6"/>
       <c r="C767" s="7"/>
@@ -18575,7 +19161,7 @@
       <c r="H767" s="1"/>
       <c r="I767" s="1"/>
     </row>
-    <row r="768" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A768" s="6"/>
       <c r="B768" s="6"/>
       <c r="C768" s="7"/>
@@ -18586,7 +19172,7 @@
       <c r="H768" s="1"/>
       <c r="I768" s="1"/>
     </row>
-    <row r="769" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A769" s="6"/>
       <c r="B769" s="6"/>
       <c r="C769" s="7"/>
@@ -18597,7 +19183,7 @@
       <c r="H769" s="1"/>
       <c r="I769" s="1"/>
     </row>
-    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A770" s="6"/>
       <c r="B770" s="6"/>
       <c r="C770" s="7"/>
@@ -18608,7 +19194,7 @@
       <c r="H770" s="1"/>
       <c r="I770" s="1"/>
     </row>
-    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A771" s="6"/>
       <c r="B771" s="6"/>
       <c r="C771" s="7"/>
@@ -18619,7 +19205,7 @@
       <c r="H771" s="1"/>
       <c r="I771" s="1"/>
     </row>
-    <row r="772" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A772" s="6"/>
       <c r="B772" s="6"/>
       <c r="C772" s="7"/>
@@ -18630,7 +19216,7 @@
       <c r="H772" s="1"/>
       <c r="I772" s="1"/>
     </row>
-    <row r="773" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A773" s="6"/>
       <c r="B773" s="6"/>
       <c r="C773" s="7"/>
@@ -18641,7 +19227,7 @@
       <c r="H773" s="1"/>
       <c r="I773" s="1"/>
     </row>
-    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A774" s="6"/>
       <c r="B774" s="6"/>
       <c r="C774" s="7"/>
@@ -18652,7 +19238,7 @@
       <c r="H774" s="1"/>
       <c r="I774" s="1"/>
     </row>
-    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A775" s="6"/>
       <c r="B775" s="6"/>
       <c r="C775" s="7"/>
@@ -18663,7 +19249,7 @@
       <c r="H775" s="1"/>
       <c r="I775" s="1"/>
     </row>
-    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A776" s="6"/>
       <c r="B776" s="6"/>
       <c r="C776" s="7"/>
@@ -18674,7 +19260,7 @@
       <c r="H776" s="1"/>
       <c r="I776" s="1"/>
     </row>
-    <row r="777" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A777" s="6"/>
       <c r="B777" s="6"/>
       <c r="C777" s="7"/>
@@ -18685,7 +19271,7 @@
       <c r="H777" s="1"/>
       <c r="I777" s="1"/>
     </row>
-    <row r="778" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A778" s="6"/>
       <c r="B778" s="6"/>
       <c r="C778" s="7"/>
@@ -18696,7 +19282,7 @@
       <c r="H778" s="1"/>
       <c r="I778" s="1"/>
     </row>
-    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A779" s="6"/>
       <c r="B779" s="6"/>
       <c r="C779" s="7"/>
@@ -18707,7 +19293,7 @@
       <c r="H779" s="1"/>
       <c r="I779" s="1"/>
     </row>
-    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A780" s="6"/>
       <c r="B780" s="6"/>
       <c r="C780" s="7"/>
@@ -18718,7 +19304,7 @@
       <c r="H780" s="1"/>
       <c r="I780" s="1"/>
     </row>
-    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A781" s="6"/>
       <c r="B781" s="6"/>
       <c r="C781" s="7"/>
@@ -18729,7 +19315,7 @@
       <c r="H781" s="1"/>
       <c r="I781" s="1"/>
     </row>
-    <row r="782" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A782" s="6"/>
       <c r="B782" s="6"/>
       <c r="C782" s="7"/>
@@ -18740,7 +19326,7 @@
       <c r="H782" s="1"/>
       <c r="I782" s="1"/>
     </row>
-    <row r="783" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A783" s="6"/>
       <c r="B783" s="6"/>
       <c r="C783" s="7"/>
@@ -18751,7 +19337,7 @@
       <c r="H783" s="1"/>
       <c r="I783" s="1"/>
     </row>
-    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A784" s="6"/>
       <c r="B784" s="6"/>
       <c r="C784" s="7"/>
@@ -18762,7 +19348,7 @@
       <c r="H784" s="1"/>
       <c r="I784" s="1"/>
     </row>
-    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A785" s="6"/>
       <c r="B785" s="6"/>
       <c r="C785" s="7"/>
@@ -18773,7 +19359,7 @@
       <c r="H785" s="1"/>
       <c r="I785" s="1"/>
     </row>
-    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A786" s="6"/>
       <c r="B786" s="6"/>
       <c r="C786" s="7"/>
@@ -18784,7 +19370,7 @@
       <c r="H786" s="1"/>
       <c r="I786" s="1"/>
     </row>
-    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A787" s="6"/>
       <c r="B787" s="6"/>
       <c r="C787" s="7"/>
@@ -18795,7 +19381,7 @@
       <c r="H787" s="1"/>
       <c r="I787" s="1"/>
     </row>
-    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A788" s="6"/>
       <c r="B788" s="6"/>
       <c r="C788" s="7"/>
@@ -18806,7 +19392,7 @@
       <c r="H788" s="1"/>
       <c r="I788" s="1"/>
     </row>
-    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A789" s="6"/>
       <c r="B789" s="6"/>
       <c r="C789" s="7"/>
@@ -18817,7 +19403,7 @@
       <c r="H789" s="1"/>
       <c r="I789" s="1"/>
     </row>
-    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A790" s="6"/>
       <c r="B790" s="6"/>
       <c r="C790" s="7"/>
@@ -18828,7 +19414,7 @@
       <c r="H790" s="1"/>
       <c r="I790" s="1"/>
     </row>
-    <row r="791" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A791" s="6"/>
       <c r="B791" s="6"/>
       <c r="C791" s="7"/>
@@ -18839,7 +19425,7 @@
       <c r="H791" s="1"/>
       <c r="I791" s="1"/>
     </row>
-    <row r="792" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A792" s="6"/>
       <c r="B792" s="6"/>
       <c r="C792" s="7"/>
@@ -18850,7 +19436,7 @@
       <c r="H792" s="1"/>
       <c r="I792" s="1"/>
     </row>
-    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A793" s="6"/>
       <c r="B793" s="6"/>
       <c r="C793" s="7"/>
@@ -18861,7 +19447,7 @@
       <c r="H793" s="1"/>
       <c r="I793" s="1"/>
     </row>
-    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A794" s="6"/>
       <c r="B794" s="6"/>
       <c r="C794" s="7"/>
@@ -18872,7 +19458,7 @@
       <c r="H794" s="1"/>
       <c r="I794" s="1"/>
     </row>
-    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A795" s="6"/>
       <c r="B795" s="6"/>
       <c r="C795" s="7"/>
@@ -18883,7 +19469,7 @@
       <c r="H795" s="1"/>
       <c r="I795" s="1"/>
     </row>
-    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A796" s="6"/>
       <c r="B796" s="6"/>
       <c r="C796" s="7"/>
@@ -18894,7 +19480,7 @@
       <c r="H796" s="1"/>
       <c r="I796" s="1"/>
     </row>
-    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A797" s="6"/>
       <c r="B797" s="6"/>
       <c r="C797" s="7"/>
@@ -18905,7 +19491,7 @@
       <c r="H797" s="1"/>
       <c r="I797" s="1"/>
     </row>
-    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A798" s="6"/>
       <c r="B798" s="6"/>
       <c r="C798" s="7"/>
@@ -18916,7 +19502,7 @@
       <c r="H798" s="1"/>
       <c r="I798" s="1"/>
     </row>
-    <row r="799" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A799" s="6"/>
       <c r="B799" s="6"/>
       <c r="C799" s="7"/>
@@ -18927,7 +19513,7 @@
       <c r="H799" s="1"/>
       <c r="I799" s="1"/>
     </row>
-    <row r="800" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A800" s="6"/>
       <c r="B800" s="6"/>
       <c r="C800" s="7"/>
@@ -18938,7 +19524,7 @@
       <c r="H800" s="1"/>
       <c r="I800" s="1"/>
     </row>
-    <row r="801" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A801" s="6"/>
       <c r="B801" s="6"/>
       <c r="C801" s="7"/>
@@ -18949,7 +19535,7 @@
       <c r="H801" s="1"/>
       <c r="I801" s="1"/>
     </row>
-    <row r="802" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A802" s="6"/>
       <c r="B802" s="6"/>
       <c r="C802" s="7"/>
@@ -18960,7 +19546,7 @@
       <c r="H802" s="1"/>
       <c r="I802" s="1"/>
     </row>
-    <row r="803" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A803" s="6"/>
       <c r="B803" s="6"/>
       <c r="C803" s="7"/>
@@ -18971,7 +19557,7 @@
       <c r="H803" s="1"/>
       <c r="I803" s="1"/>
     </row>
-    <row r="804" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A804" s="6"/>
       <c r="B804" s="6"/>
       <c r="C804" s="7"/>
@@ -18982,7 +19568,7 @@
       <c r="H804" s="1"/>
       <c r="I804" s="1"/>
     </row>
-    <row r="805" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A805" s="6"/>
       <c r="B805" s="6"/>
       <c r="C805" s="7"/>
@@ -18993,7 +19579,7 @@
       <c r="H805" s="1"/>
       <c r="I805" s="1"/>
     </row>
-    <row r="806" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A806" s="6"/>
       <c r="B806" s="6"/>
       <c r="C806" s="7"/>
@@ -19004,7 +19590,7 @@
       <c r="H806" s="1"/>
       <c r="I806" s="1"/>
     </row>
-    <row r="807" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A807" s="6"/>
       <c r="B807" s="6"/>
       <c r="C807" s="7"/>
@@ -19015,7 +19601,7 @@
       <c r="H807" s="1"/>
       <c r="I807" s="1"/>
     </row>
-    <row r="808" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A808" s="6"/>
       <c r="B808" s="6"/>
       <c r="C808" s="7"/>
@@ -19026,7 +19612,7 @@
       <c r="H808" s="1"/>
       <c r="I808" s="1"/>
     </row>
-    <row r="809" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A809" s="6"/>
       <c r="B809" s="6"/>
       <c r="C809" s="7"/>
@@ -19037,7 +19623,7 @@
       <c r="H809" s="1"/>
       <c r="I809" s="1"/>
     </row>
-    <row r="810" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A810" s="6"/>
       <c r="B810" s="6"/>
       <c r="C810" s="7"/>
@@ -19048,7 +19634,7 @@
       <c r="H810" s="1"/>
       <c r="I810" s="1"/>
     </row>
-    <row r="811" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A811" s="6"/>
       <c r="B811" s="6"/>
       <c r="C811" s="7"/>
@@ -19059,7 +19645,7 @@
       <c r="H811" s="1"/>
       <c r="I811" s="1"/>
     </row>
-    <row r="812" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A812" s="6"/>
       <c r="B812" s="6"/>
       <c r="C812" s="7"/>
@@ -19070,7 +19656,7 @@
       <c r="H812" s="1"/>
       <c r="I812" s="1"/>
     </row>
-    <row r="813" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A813" s="6"/>
       <c r="B813" s="6"/>
       <c r="C813" s="7"/>
@@ -19081,7 +19667,7 @@
       <c r="H813" s="1"/>
       <c r="I813" s="1"/>
     </row>
-    <row r="814" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A814" s="6"/>
       <c r="B814" s="6"/>
       <c r="C814" s="7"/>
@@ -19092,7 +19678,7 @@
       <c r="H814" s="1"/>
       <c r="I814" s="1"/>
     </row>
-    <row r="815" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A815" s="6"/>
       <c r="B815" s="6"/>
       <c r="C815" s="7"/>
@@ -19103,7 +19689,7 @@
       <c r="H815" s="1"/>
       <c r="I815" s="1"/>
     </row>
-    <row r="816" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A816" s="6"/>
       <c r="B816" s="6"/>
       <c r="C816" s="7"/>
@@ -19114,7 +19700,7 @@
       <c r="H816" s="1"/>
       <c r="I816" s="1"/>
     </row>
-    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A817" s="6"/>
       <c r="B817" s="6"/>
       <c r="C817" s="7"/>
@@ -19125,7 +19711,7 @@
       <c r="H817" s="1"/>
       <c r="I817" s="1"/>
     </row>
-    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A818" s="6"/>
       <c r="B818" s="6"/>
       <c r="C818" s="7"/>
@@ -19136,7 +19722,7 @@
       <c r="H818" s="1"/>
       <c r="I818" s="1"/>
     </row>
-    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A819" s="6"/>
       <c r="B819" s="6"/>
       <c r="C819" s="7"/>
@@ -19147,7 +19733,7 @@
       <c r="H819" s="1"/>
       <c r="I819" s="1"/>
     </row>
-    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A820" s="6"/>
       <c r="B820" s="6"/>
       <c r="C820" s="7"/>
@@ -19158,7 +19744,7 @@
       <c r="H820" s="1"/>
       <c r="I820" s="1"/>
     </row>
-    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A821" s="6"/>
       <c r="B821" s="6"/>
       <c r="C821" s="7"/>
@@ -19169,7 +19755,7 @@
       <c r="H821" s="1"/>
       <c r="I821" s="1"/>
     </row>
-    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A822" s="6"/>
       <c r="B822" s="6"/>
       <c r="C822" s="7"/>
@@ -19180,7 +19766,7 @@
       <c r="H822" s="1"/>
       <c r="I822" s="1"/>
     </row>
-    <row r="823" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A823" s="6"/>
       <c r="B823" s="6"/>
       <c r="C823" s="7"/>
@@ -19191,7 +19777,7 @@
       <c r="H823" s="1"/>
       <c r="I823" s="1"/>
     </row>
-    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A824" s="6"/>
       <c r="B824" s="6"/>
       <c r="C824" s="7"/>
@@ -19202,7 +19788,7 @@
       <c r="H824" s="1"/>
       <c r="I824" s="1"/>
     </row>
-    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A825" s="6"/>
       <c r="B825" s="6"/>
       <c r="C825" s="7"/>
@@ -19213,7 +19799,7 @@
       <c r="H825" s="1"/>
       <c r="I825" s="1"/>
     </row>
-    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A826" s="6"/>
       <c r="B826" s="6"/>
       <c r="C826" s="7"/>
@@ -19224,7 +19810,7 @@
       <c r="H826" s="1"/>
       <c r="I826" s="1"/>
     </row>
-    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A827" s="6"/>
       <c r="B827" s="6"/>
       <c r="C827" s="7"/>
@@ -19235,7 +19821,7 @@
       <c r="H827" s="1"/>
       <c r="I827" s="1"/>
     </row>
-    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A828" s="6"/>
       <c r="B828" s="6"/>
       <c r="C828" s="7"/>
@@ -19246,7 +19832,7 @@
       <c r="H828" s="1"/>
       <c r="I828" s="1"/>
     </row>
-    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A829" s="6"/>
       <c r="B829" s="6"/>
       <c r="C829" s="7"/>
@@ -19257,7 +19843,7 @@
       <c r="H829" s="1"/>
       <c r="I829" s="1"/>
     </row>
-    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A830" s="6"/>
       <c r="B830" s="6"/>
       <c r="C830" s="7"/>
@@ -19268,7 +19854,7 @@
       <c r="H830" s="1"/>
       <c r="I830" s="1"/>
     </row>
-    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A831" s="6"/>
       <c r="B831" s="6"/>
       <c r="C831" s="7"/>
@@ -19279,7 +19865,7 @@
       <c r="H831" s="1"/>
       <c r="I831" s="1"/>
     </row>
-    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A832" s="6"/>
       <c r="B832" s="6"/>
       <c r="C832" s="7"/>
@@ -19290,7 +19876,7 @@
       <c r="H832" s="1"/>
       <c r="I832" s="1"/>
     </row>
-    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A833" s="6"/>
       <c r="B833" s="6"/>
       <c r="C833" s="7"/>
@@ -19301,84 +19887,70 @@
       <c r="H833" s="1"/>
       <c r="I833" s="1"/>
     </row>
-    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A834" s="6"/>
+    <row r="834" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B834" s="6"/>
       <c r="C834" s="7"/>
-      <c r="D834" s="7"/>
       <c r="E834" s="1"/>
       <c r="F834" s="5"/>
       <c r="G834" s="5"/>
       <c r="H834" s="1"/>
       <c r="I834" s="1"/>
     </row>
-    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A835" s="6"/>
+    <row r="835" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B835" s="6"/>
       <c r="C835" s="7"/>
-      <c r="D835" s="7"/>
       <c r="E835" s="1"/>
       <c r="F835" s="5"/>
       <c r="G835" s="5"/>
       <c r="H835" s="1"/>
       <c r="I835" s="1"/>
     </row>
-    <row r="836" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A836" s="6"/>
+    <row r="836" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B836" s="6"/>
       <c r="C836" s="7"/>
-      <c r="D836" s="7"/>
       <c r="E836" s="1"/>
       <c r="F836" s="5"/>
       <c r="G836" s="5"/>
       <c r="H836" s="1"/>
       <c r="I836" s="1"/>
     </row>
-    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A837" s="6"/>
+    <row r="837" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B837" s="6"/>
       <c r="C837" s="7"/>
-      <c r="D837" s="7"/>
       <c r="E837" s="1"/>
       <c r="F837" s="5"/>
       <c r="G837" s="5"/>
       <c r="H837" s="1"/>
       <c r="I837" s="1"/>
     </row>
-    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A838" s="6"/>
+    <row r="838" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B838" s="6"/>
       <c r="C838" s="7"/>
-      <c r="D838" s="7"/>
       <c r="E838" s="1"/>
       <c r="F838" s="5"/>
       <c r="G838" s="5"/>
       <c r="H838" s="1"/>
       <c r="I838" s="1"/>
     </row>
-    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A839" s="6"/>
+    <row r="839" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B839" s="6"/>
       <c r="C839" s="7"/>
-      <c r="D839" s="7"/>
       <c r="E839" s="1"/>
       <c r="F839" s="5"/>
       <c r="G839" s="5"/>
       <c r="H839" s="1"/>
       <c r="I839" s="1"/>
     </row>
-    <row r="840" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A840" s="6"/>
+    <row r="840" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B840" s="6"/>
       <c r="C840" s="7"/>
-      <c r="D840" s="7"/>
       <c r="E840" s="1"/>
       <c r="F840" s="5"/>
       <c r="G840" s="5"/>
       <c r="H840" s="1"/>
       <c r="I840" s="1"/>
     </row>
-    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B841" s="6"/>
       <c r="C841" s="7"/>
       <c r="E841" s="1"/>
@@ -19387,7 +19959,7 @@
       <c r="H841" s="1"/>
       <c r="I841" s="1"/>
     </row>
-    <row r="842" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B842" s="6"/>
       <c r="C842" s="7"/>
       <c r="E842" s="1"/>
@@ -19396,7 +19968,7 @@
       <c r="H842" s="1"/>
       <c r="I842" s="1"/>
     </row>
-    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B843" s="6"/>
       <c r="C843" s="7"/>
       <c r="E843" s="1"/>
@@ -19405,7 +19977,7 @@
       <c r="H843" s="1"/>
       <c r="I843" s="1"/>
     </row>
-    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B844" s="6"/>
       <c r="C844" s="7"/>
       <c r="E844" s="1"/>
@@ -19414,7 +19986,7 @@
       <c r="H844" s="1"/>
       <c r="I844" s="1"/>
     </row>
-    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B845" s="6"/>
       <c r="C845" s="7"/>
       <c r="E845" s="1"/>
@@ -19423,7 +19995,7 @@
       <c r="H845" s="1"/>
       <c r="I845" s="1"/>
     </row>
-    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B846" s="6"/>
       <c r="C846" s="7"/>
       <c r="E846" s="1"/>
@@ -19432,7 +20004,7 @@
       <c r="H846" s="1"/>
       <c r="I846" s="1"/>
     </row>
-    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B847" s="6"/>
       <c r="C847" s="7"/>
       <c r="E847" s="1"/>
@@ -19441,7 +20013,7 @@
       <c r="H847" s="1"/>
       <c r="I847" s="1"/>
     </row>
-    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:9" x14ac:dyDescent="0.35">
       <c r="B848" s="6"/>
       <c r="C848" s="7"/>
       <c r="E848" s="1"/>
@@ -19450,7 +20022,7 @@
       <c r="H848" s="1"/>
       <c r="I848" s="1"/>
     </row>
-    <row r="849" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="849" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B849" s="6"/>
       <c r="C849" s="7"/>
       <c r="E849" s="1"/>
@@ -19459,7 +20031,7 @@
       <c r="H849" s="1"/>
       <c r="I849" s="1"/>
     </row>
-    <row r="850" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="850" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B850" s="6"/>
       <c r="C850" s="7"/>
       <c r="E850" s="1"/>
@@ -19468,7 +20040,7 @@
       <c r="H850" s="1"/>
       <c r="I850" s="1"/>
     </row>
-    <row r="851" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="851" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B851" s="6"/>
       <c r="C851" s="7"/>
       <c r="E851" s="1"/>
@@ -19477,7 +20049,7 @@
       <c r="H851" s="1"/>
       <c r="I851" s="1"/>
     </row>
-    <row r="852" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="852" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B852" s="6"/>
       <c r="C852" s="7"/>
       <c r="E852" s="1"/>
@@ -19486,7 +20058,7 @@
       <c r="H852" s="1"/>
       <c r="I852" s="1"/>
     </row>
-    <row r="853" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="853" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B853" s="6"/>
       <c r="C853" s="7"/>
       <c r="E853" s="1"/>
@@ -19495,7 +20067,7 @@
       <c r="H853" s="1"/>
       <c r="I853" s="1"/>
     </row>
-    <row r="854" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="854" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B854" s="6"/>
       <c r="C854" s="7"/>
       <c r="E854" s="1"/>
@@ -19504,7 +20076,7 @@
       <c r="H854" s="1"/>
       <c r="I854" s="1"/>
     </row>
-    <row r="855" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="855" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B855" s="6"/>
       <c r="C855" s="7"/>
       <c r="E855" s="1"/>
@@ -19513,7 +20085,7 @@
       <c r="H855" s="1"/>
       <c r="I855" s="1"/>
     </row>
-    <row r="856" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="856" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B856" s="6"/>
       <c r="C856" s="7"/>
       <c r="E856" s="1"/>
@@ -19522,7 +20094,7 @@
       <c r="H856" s="1"/>
       <c r="I856" s="1"/>
     </row>
-    <row r="857" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="857" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B857" s="6"/>
       <c r="C857" s="7"/>
       <c r="E857" s="1"/>
@@ -19531,7 +20103,7 @@
       <c r="H857" s="1"/>
       <c r="I857" s="1"/>
     </row>
-    <row r="858" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="858" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B858" s="6"/>
       <c r="C858" s="7"/>
       <c r="E858" s="1"/>
@@ -19540,7 +20112,7 @@
       <c r="H858" s="1"/>
       <c r="I858" s="1"/>
     </row>
-    <row r="859" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="859" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B859" s="6"/>
       <c r="C859" s="7"/>
       <c r="E859" s="1"/>
@@ -19549,7 +20121,7 @@
       <c r="H859" s="1"/>
       <c r="I859" s="1"/>
     </row>
-    <row r="860" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="860" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B860" s="6"/>
       <c r="C860" s="7"/>
       <c r="E860" s="1"/>
@@ -19558,7 +20130,7 @@
       <c r="H860" s="1"/>
       <c r="I860" s="1"/>
     </row>
-    <row r="861" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="861" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B861" s="6"/>
       <c r="C861" s="7"/>
       <c r="E861" s="1"/>
@@ -19567,7 +20139,7 @@
       <c r="H861" s="1"/>
       <c r="I861" s="1"/>
     </row>
-    <row r="862" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="862" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B862" s="6"/>
       <c r="C862" s="7"/>
       <c r="E862" s="1"/>
@@ -19576,7 +20148,7 @@
       <c r="H862" s="1"/>
       <c r="I862" s="1"/>
     </row>
-    <row r="863" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="863" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B863" s="6"/>
       <c r="C863" s="7"/>
       <c r="E863" s="1"/>
@@ -19585,7 +20157,7 @@
       <c r="H863" s="1"/>
       <c r="I863" s="1"/>
     </row>
-    <row r="864" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="864" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B864" s="6"/>
       <c r="C864" s="7"/>
       <c r="E864" s="1"/>
@@ -19594,7 +20166,7 @@
       <c r="H864" s="1"/>
       <c r="I864" s="1"/>
     </row>
-    <row r="865" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="865" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B865" s="6"/>
       <c r="C865" s="7"/>
       <c r="E865" s="1"/>
@@ -19603,7 +20175,7 @@
       <c r="H865" s="1"/>
       <c r="I865" s="1"/>
     </row>
-    <row r="866" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="866" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B866" s="6"/>
       <c r="C866" s="7"/>
       <c r="E866" s="1"/>
@@ -19612,7 +20184,7 @@
       <c r="H866" s="1"/>
       <c r="I866" s="1"/>
     </row>
-    <row r="867" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="867" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B867" s="6"/>
       <c r="C867" s="7"/>
       <c r="E867" s="1"/>
@@ -19621,7 +20193,7 @@
       <c r="H867" s="1"/>
       <c r="I867" s="1"/>
     </row>
-    <row r="868" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="868" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B868" s="6"/>
       <c r="C868" s="7"/>
       <c r="E868" s="1"/>
@@ -19630,7 +20202,7 @@
       <c r="H868" s="1"/>
       <c r="I868" s="1"/>
     </row>
-    <row r="869" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="869" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B869" s="6"/>
       <c r="C869" s="7"/>
       <c r="E869" s="1"/>
@@ -19639,7 +20211,7 @@
       <c r="H869" s="1"/>
       <c r="I869" s="1"/>
     </row>
-    <row r="870" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="870" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B870" s="6"/>
       <c r="C870" s="7"/>
       <c r="E870" s="1"/>
@@ -19648,7 +20220,7 @@
       <c r="H870" s="1"/>
       <c r="I870" s="1"/>
     </row>
-    <row r="871" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="871" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B871" s="6"/>
       <c r="C871" s="7"/>
       <c r="E871" s="1"/>
@@ -19657,7 +20229,7 @@
       <c r="H871" s="1"/>
       <c r="I871" s="1"/>
     </row>
-    <row r="872" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="872" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B872" s="6"/>
       <c r="C872" s="7"/>
       <c r="E872" s="1"/>
@@ -19666,7 +20238,7 @@
       <c r="H872" s="1"/>
       <c r="I872" s="1"/>
     </row>
-    <row r="873" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="873" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B873" s="6"/>
       <c r="C873" s="7"/>
       <c r="E873" s="1"/>
@@ -19675,7 +20247,7 @@
       <c r="H873" s="1"/>
       <c r="I873" s="1"/>
     </row>
-    <row r="874" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="874" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B874" s="6"/>
       <c r="C874" s="7"/>
       <c r="E874" s="1"/>
@@ -19684,7 +20256,7 @@
       <c r="H874" s="1"/>
       <c r="I874" s="1"/>
     </row>
-    <row r="875" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="875" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B875" s="6"/>
       <c r="C875" s="7"/>
       <c r="E875" s="1"/>
@@ -19693,7 +20265,7 @@
       <c r="H875" s="1"/>
       <c r="I875" s="1"/>
     </row>
-    <row r="876" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="876" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B876" s="6"/>
       <c r="C876" s="7"/>
       <c r="E876" s="1"/>
@@ -19702,7 +20274,7 @@
       <c r="H876" s="1"/>
       <c r="I876" s="1"/>
     </row>
-    <row r="877" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="877" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B877" s="6"/>
       <c r="C877" s="7"/>
       <c r="E877" s="1"/>
@@ -19711,7 +20283,7 @@
       <c r="H877" s="1"/>
       <c r="I877" s="1"/>
     </row>
-    <row r="878" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="878" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B878" s="6"/>
       <c r="C878" s="7"/>
       <c r="E878" s="1"/>
@@ -19720,7 +20292,7 @@
       <c r="H878" s="1"/>
       <c r="I878" s="1"/>
     </row>
-    <row r="879" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="879" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B879" s="6"/>
       <c r="C879" s="7"/>
       <c r="E879" s="1"/>
@@ -19729,7 +20301,7 @@
       <c r="H879" s="1"/>
       <c r="I879" s="1"/>
     </row>
-    <row r="880" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="880" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B880" s="6"/>
       <c r="C880" s="7"/>
       <c r="E880" s="1"/>
@@ -19738,7 +20310,7 @@
       <c r="H880" s="1"/>
       <c r="I880" s="1"/>
     </row>
-    <row r="881" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="881" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B881" s="6"/>
       <c r="C881" s="7"/>
       <c r="E881" s="1"/>
@@ -19747,7 +20319,7 @@
       <c r="H881" s="1"/>
       <c r="I881" s="1"/>
     </row>
-    <row r="882" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="882" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B882" s="6"/>
       <c r="C882" s="7"/>
       <c r="E882" s="1"/>
@@ -19756,7 +20328,7 @@
       <c r="H882" s="1"/>
       <c r="I882" s="1"/>
     </row>
-    <row r="883" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="883" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B883" s="6"/>
       <c r="C883" s="7"/>
       <c r="E883" s="1"/>
@@ -19765,7 +20337,7 @@
       <c r="H883" s="1"/>
       <c r="I883" s="1"/>
     </row>
-    <row r="884" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="884" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B884" s="6"/>
       <c r="C884" s="7"/>
       <c r="E884" s="1"/>
@@ -19774,7 +20346,7 @@
       <c r="H884" s="1"/>
       <c r="I884" s="1"/>
     </row>
-    <row r="885" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="885" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B885" s="6"/>
       <c r="C885" s="7"/>
       <c r="E885" s="1"/>
@@ -19783,7 +20355,7 @@
       <c r="H885" s="1"/>
       <c r="I885" s="1"/>
     </row>
-    <row r="886" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="886" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B886" s="6"/>
       <c r="C886" s="7"/>
       <c r="E886" s="1"/>
@@ -19792,7 +20364,7 @@
       <c r="H886" s="1"/>
       <c r="I886" s="1"/>
     </row>
-    <row r="887" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="887" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B887" s="6"/>
       <c r="C887" s="7"/>
       <c r="E887" s="1"/>
@@ -19801,7 +20373,7 @@
       <c r="H887" s="1"/>
       <c r="I887" s="1"/>
     </row>
-    <row r="888" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="888" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B888" s="6"/>
       <c r="C888" s="7"/>
       <c r="E888" s="1"/>
@@ -19810,7 +20382,7 @@
       <c r="H888" s="1"/>
       <c r="I888" s="1"/>
     </row>
-    <row r="889" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="889" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B889" s="6"/>
       <c r="C889" s="7"/>
       <c r="E889" s="1"/>
@@ -19819,7 +20391,7 @@
       <c r="H889" s="1"/>
       <c r="I889" s="1"/>
     </row>
-    <row r="890" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="890" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B890" s="6"/>
       <c r="C890" s="7"/>
       <c r="E890" s="1"/>
@@ -19828,7 +20400,7 @@
       <c r="H890" s="1"/>
       <c r="I890" s="1"/>
     </row>
-    <row r="891" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="891" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B891" s="6"/>
       <c r="C891" s="7"/>
       <c r="E891" s="1"/>
@@ -19837,7 +20409,7 @@
       <c r="H891" s="1"/>
       <c r="I891" s="1"/>
     </row>
-    <row r="892" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="892" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B892" s="6"/>
       <c r="C892" s="7"/>
       <c r="E892" s="1"/>
@@ -19846,7 +20418,7 @@
       <c r="H892" s="1"/>
       <c r="I892" s="1"/>
     </row>
-    <row r="893" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="893" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B893" s="6"/>
       <c r="C893" s="7"/>
       <c r="E893" s="1"/>
@@ -19855,7 +20427,7 @@
       <c r="H893" s="1"/>
       <c r="I893" s="1"/>
     </row>
-    <row r="894" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="894" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B894" s="6"/>
       <c r="C894" s="7"/>
       <c r="E894" s="1"/>
@@ -19864,7 +20436,7 @@
       <c r="H894" s="1"/>
       <c r="I894" s="1"/>
     </row>
-    <row r="895" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="895" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B895" s="6"/>
       <c r="C895" s="7"/>
       <c r="E895" s="1"/>
@@ -19873,7 +20445,7 @@
       <c r="H895" s="1"/>
       <c r="I895" s="1"/>
     </row>
-    <row r="896" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="896" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B896" s="6"/>
       <c r="C896" s="7"/>
       <c r="E896" s="1"/>
@@ -19882,7 +20454,7 @@
       <c r="H896" s="1"/>
       <c r="I896" s="1"/>
     </row>
-    <row r="897" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="897" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B897" s="6"/>
       <c r="C897" s="7"/>
       <c r="E897" s="1"/>
@@ -19891,7 +20463,7 @@
       <c r="H897" s="1"/>
       <c r="I897" s="1"/>
     </row>
-    <row r="898" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="898" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B898" s="6"/>
       <c r="C898" s="7"/>
       <c r="E898" s="1"/>
@@ -19900,7 +20472,7 @@
       <c r="H898" s="1"/>
       <c r="I898" s="1"/>
     </row>
-    <row r="899" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="899" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B899" s="6"/>
       <c r="C899" s="7"/>
       <c r="E899" s="1"/>
@@ -19909,7 +20481,7 @@
       <c r="H899" s="1"/>
       <c r="I899" s="1"/>
     </row>
-    <row r="900" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="900" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B900" s="6"/>
       <c r="C900" s="7"/>
       <c r="E900" s="1"/>
@@ -19918,7 +20490,7 @@
       <c r="H900" s="1"/>
       <c r="I900" s="1"/>
     </row>
-    <row r="901" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="901" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B901" s="6"/>
       <c r="C901" s="7"/>
       <c r="E901" s="1"/>
@@ -19927,7 +20499,7 @@
       <c r="H901" s="1"/>
       <c r="I901" s="1"/>
     </row>
-    <row r="902" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="902" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B902" s="6"/>
       <c r="C902" s="7"/>
       <c r="E902" s="1"/>
@@ -19936,7 +20508,7 @@
       <c r="H902" s="1"/>
       <c r="I902" s="1"/>
     </row>
-    <row r="903" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="903" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B903" s="6"/>
       <c r="C903" s="7"/>
       <c r="E903" s="1"/>
@@ -19945,7 +20517,7 @@
       <c r="H903" s="1"/>
       <c r="I903" s="1"/>
     </row>
-    <row r="904" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="904" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B904" s="6"/>
       <c r="C904" s="7"/>
       <c r="E904" s="1"/>
@@ -19954,7 +20526,7 @@
       <c r="H904" s="1"/>
       <c r="I904" s="1"/>
     </row>
-    <row r="905" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="905" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B905" s="6"/>
       <c r="C905" s="7"/>
       <c r="E905" s="1"/>
@@ -19963,7 +20535,7 @@
       <c r="H905" s="1"/>
       <c r="I905" s="1"/>
     </row>
-    <row r="906" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="906" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B906" s="6"/>
       <c r="C906" s="7"/>
       <c r="E906" s="1"/>
@@ -19972,7 +20544,7 @@
       <c r="H906" s="1"/>
       <c r="I906" s="1"/>
     </row>
-    <row r="907" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="907" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B907" s="6"/>
       <c r="C907" s="7"/>
       <c r="E907" s="1"/>
@@ -19981,7 +20553,7 @@
       <c r="H907" s="1"/>
       <c r="I907" s="1"/>
     </row>
-    <row r="908" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="908" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B908" s="6"/>
       <c r="C908" s="7"/>
       <c r="E908" s="1"/>
@@ -19990,7 +20562,7 @@
       <c r="H908" s="1"/>
       <c r="I908" s="1"/>
     </row>
-    <row r="909" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="909" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B909" s="6"/>
       <c r="C909" s="7"/>
       <c r="E909" s="1"/>
@@ -19999,7 +20571,7 @@
       <c r="H909" s="1"/>
       <c r="I909" s="1"/>
     </row>
-    <row r="910" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="910" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B910" s="6"/>
       <c r="C910" s="7"/>
       <c r="E910" s="1"/>
@@ -20008,7 +20580,7 @@
       <c r="H910" s="1"/>
       <c r="I910" s="1"/>
     </row>
-    <row r="911" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="911" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B911" s="6"/>
       <c r="C911" s="7"/>
       <c r="E911" s="1"/>
@@ -20017,7 +20589,7 @@
       <c r="H911" s="1"/>
       <c r="I911" s="1"/>
     </row>
-    <row r="912" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="912" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B912" s="6"/>
       <c r="C912" s="7"/>
       <c r="E912" s="1"/>
@@ -20026,7 +20598,7 @@
       <c r="H912" s="1"/>
       <c r="I912" s="1"/>
     </row>
-    <row r="913" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="913" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B913" s="6"/>
       <c r="C913" s="7"/>
       <c r="E913" s="1"/>
@@ -20035,7 +20607,7 @@
       <c r="H913" s="1"/>
       <c r="I913" s="1"/>
     </row>
-    <row r="914" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="914" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B914" s="6"/>
       <c r="C914" s="7"/>
       <c r="E914" s="1"/>
@@ -20044,7 +20616,7 @@
       <c r="H914" s="1"/>
       <c r="I914" s="1"/>
     </row>
-    <row r="915" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="915" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B915" s="6"/>
       <c r="C915" s="7"/>
       <c r="E915" s="1"/>
@@ -20053,7 +20625,7 @@
       <c r="H915" s="1"/>
       <c r="I915" s="1"/>
     </row>
-    <row r="916" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="916" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B916" s="6"/>
       <c r="C916" s="7"/>
       <c r="E916" s="1"/>
@@ -20062,7 +20634,7 @@
       <c r="H916" s="1"/>
       <c r="I916" s="1"/>
     </row>
-    <row r="917" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="917" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B917" s="6"/>
       <c r="C917" s="7"/>
       <c r="E917" s="1"/>
@@ -20071,7 +20643,7 @@
       <c r="H917" s="1"/>
       <c r="I917" s="1"/>
     </row>
-    <row r="918" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="918" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B918" s="6"/>
       <c r="C918" s="7"/>
       <c r="E918" s="1"/>
@@ -20080,7 +20652,7 @@
       <c r="H918" s="1"/>
       <c r="I918" s="1"/>
     </row>
-    <row r="919" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="919" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B919" s="6"/>
       <c r="C919" s="7"/>
       <c r="E919" s="1"/>
@@ -20089,7 +20661,7 @@
       <c r="H919" s="1"/>
       <c r="I919" s="1"/>
     </row>
-    <row r="920" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="920" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B920" s="6"/>
       <c r="C920" s="7"/>
       <c r="E920" s="1"/>
@@ -20098,7 +20670,7 @@
       <c r="H920" s="1"/>
       <c r="I920" s="1"/>
     </row>
-    <row r="921" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="921" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B921" s="6"/>
       <c r="C921" s="7"/>
       <c r="E921" s="1"/>
@@ -20107,7 +20679,7 @@
       <c r="H921" s="1"/>
       <c r="I921" s="1"/>
     </row>
-    <row r="922" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="922" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B922" s="6"/>
       <c r="C922" s="7"/>
       <c r="E922" s="1"/>
@@ -20116,7 +20688,7 @@
       <c r="H922" s="1"/>
       <c r="I922" s="1"/>
     </row>
-    <row r="923" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="923" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B923" s="6"/>
       <c r="C923" s="7"/>
       <c r="E923" s="1"/>
@@ -20125,7 +20697,7 @@
       <c r="H923" s="1"/>
       <c r="I923" s="1"/>
     </row>
-    <row r="924" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="924" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B924" s="6"/>
       <c r="C924" s="7"/>
       <c r="E924" s="1"/>
@@ -20134,7 +20706,7 @@
       <c r="H924" s="1"/>
       <c r="I924" s="1"/>
     </row>
-    <row r="925" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="925" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B925" s="6"/>
       <c r="C925" s="7"/>
       <c r="E925" s="1"/>
@@ -20143,7 +20715,7 @@
       <c r="H925" s="1"/>
       <c r="I925" s="1"/>
     </row>
-    <row r="926" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="926" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B926" s="6"/>
       <c r="C926" s="7"/>
       <c r="E926" s="1"/>
@@ -20152,7 +20724,7 @@
       <c r="H926" s="1"/>
       <c r="I926" s="1"/>
     </row>
-    <row r="927" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="927" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B927" s="6"/>
       <c r="C927" s="7"/>
       <c r="E927" s="1"/>
@@ -20161,7 +20733,7 @@
       <c r="H927" s="1"/>
       <c r="I927" s="1"/>
     </row>
-    <row r="928" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="928" spans="2:9" x14ac:dyDescent="0.35">
       <c r="B928" s="6"/>
       <c r="C928" s="7"/>
       <c r="E928" s="1"/>
@@ -20170,69 +20742,6 @@
       <c r="H928" s="1"/>
       <c r="I928" s="1"/>
     </row>
-    <row r="929" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B929" s="6"/>
-      <c r="C929" s="7"/>
-      <c r="E929" s="1"/>
-      <c r="F929" s="5"/>
-      <c r="G929" s="5"/>
-      <c r="H929" s="1"/>
-      <c r="I929" s="1"/>
-    </row>
-    <row r="930" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B930" s="6"/>
-      <c r="C930" s="7"/>
-      <c r="E930" s="1"/>
-      <c r="F930" s="5"/>
-      <c r="G930" s="5"/>
-      <c r="H930" s="1"/>
-      <c r="I930" s="1"/>
-    </row>
-    <row r="931" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B931" s="6"/>
-      <c r="C931" s="7"/>
-      <c r="E931" s="1"/>
-      <c r="F931" s="5"/>
-      <c r="G931" s="5"/>
-      <c r="H931" s="1"/>
-      <c r="I931" s="1"/>
-    </row>
-    <row r="932" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B932" s="6"/>
-      <c r="C932" s="7"/>
-      <c r="E932" s="1"/>
-      <c r="F932" s="5"/>
-      <c r="G932" s="5"/>
-      <c r="H932" s="1"/>
-      <c r="I932" s="1"/>
-    </row>
-    <row r="933" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B933" s="6"/>
-      <c r="C933" s="7"/>
-      <c r="E933" s="1"/>
-      <c r="F933" s="5"/>
-      <c r="G933" s="5"/>
-      <c r="H933" s="1"/>
-      <c r="I933" s="1"/>
-    </row>
-    <row r="934" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B934" s="6"/>
-      <c r="C934" s="7"/>
-      <c r="E934" s="1"/>
-      <c r="F934" s="5"/>
-      <c r="G934" s="5"/>
-      <c r="H934" s="1"/>
-      <c r="I934" s="1"/>
-    </row>
-    <row r="935" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B935" s="6"/>
-      <c r="C935" s="7"/>
-      <c r="E935" s="1"/>
-      <c r="F935" s="5"/>
-      <c r="G935" s="5"/>
-      <c r="H935" s="1"/>
-      <c r="I935" s="1"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
